--- a/files/港岛-黄竹坑-滶晨.xlsx
+++ b/files/港岛-黄竹坑-滶晨.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1A座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1B座 销控表" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -112,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -177,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -193,45 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -21305,4407 +21171,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:H39"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>滶晨 - 1A座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>207 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>200 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>7 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>41&amp;42/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 1020呎 (3房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 1034呎 (3房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>C | 1083呎 (3房)
-$3,890万
-$35,921/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E6" s="18" t="inlineStr"/>
-      <c r="F6" s="18" t="inlineStr"/>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>P2 | 3120呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H6" s="18" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>41/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr"/>
-      <c r="C7" s="18" t="inlineStr"/>
-      <c r="D7" s="18" t="inlineStr"/>
-      <c r="E7" s="18" t="inlineStr"/>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>P1 | 1536呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="G7" s="18" t="inlineStr"/>
-      <c r="H7" s="18" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>40/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,593万
-$32,776/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-$1,142万
-$23,109/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>C | 517呎 (2房)
-$1,235万
-$23,892/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr"/>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>P1 | 1536呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>P2 | 1706呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H8" s="18" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>39/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,566万
-$32,222/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-$1,130万
-$22,881/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>C | 517呎 (2房)
-$1,276万
-$24,689/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr"/>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>P1 | 1536呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="G9" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 1706呎 (4+房)
-$10,775万
-$63,158/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="H9" s="18" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,429万
-$29,401/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-$1,227万
-$24,844/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>C | 517呎 (2房)
-$1,245万
-$24,087/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr"/>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 1536呎 (4+房)
-$7,296万
-$47,500/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="G10" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 1706呎 (4+房)
-$8,530万
-$50,000/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H10" s="18" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,117万
-$22,990/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-$1,131万
-$22,903/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>C | 517呎 (2房)
-$1,154万
-$22,317/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr"/>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 1536呎 (4+房)
-$6,543万
-$42,600/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G11" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 1706呎 (4+房)
-$8,189万
-$48,000/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H11" s="18" t="inlineStr"/>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,086万
-$22,346/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-$1,100万
-$22,265/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>C | 517呎 (2房)
-$1,217万
-$23,536/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr"/>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 1536呎 (4+房)
-$6,420万
-$41,800/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G12" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 1706呎 (4+房)
-$7,558万
-$44,300/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H12" s="18" t="inlineStr"/>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,083万
-$22,292/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-$1,097万
-$22,211/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>C | 517呎 (2房)
-$1,137万
-$21,986/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr"/>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 1536呎 (4+房)
-$6,298万
-$41,000/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G13" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 1706呎 (4+房)
-$7,421万
-$43,500/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H13" s="18" t="inlineStr"/>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,067万
-$21,963/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-$1,081万
-$21,881/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>C | 517呎 (2房)
-$1,128万
-$21,822/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr"/>
-      <c r="F14" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 1536呎 (4+房)
-$6,089万
-$39,641/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G14" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 1706呎 (4+房)
-$7,319万
-$42,900/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H14" s="18" t="inlineStr"/>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,048万
-$21,562/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-$1,061万
-$21,482/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>C | 517呎 (2房)
-$1,123万
-$21,714/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr"/>
-      <c r="F15" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 1536呎 (4+房)
-$5,990万
-$39,000/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G15" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 1706呎 (4+房)
-$6,726万
-$39,425/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H15" s="18" t="inlineStr"/>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,107万
-$22,772/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-$1,055万
-$21,354/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>C | 517呎 (2房)
-$1,187万
-$22,956/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr"/>
-      <c r="F16" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 1536呎 (4+房)
-$5,574万
-$36,290/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G16" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 1706呎 (4+房)
-$6,596万
-$38,665/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H16" s="18" t="inlineStr"/>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,100万
-$22,638/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-$1,114万
-$22,553/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>C | 517呎 (2房)
-$1,112万
-$21,499/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr"/>
-      <c r="F17" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 1536呎 (4+房)
-$5,076万
-$33,047/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G17" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 1706呎 (4+房)
-$6,467万
-$37,906/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H17" s="18" t="inlineStr"/>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,094万
-$22,502/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-$1,108万
-$22,419/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>C | 517呎 (2房)
-$1,175万
-$22,729/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr"/>
-      <c r="F18" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 1469呎 (4+房)
-$5,739万
-$39,066/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G18" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 1706呎 (4+房)
-$6,739万
-$39,501/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H18" s="18" t="inlineStr"/>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,025万
-$21,095/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-$1,036万
-$20,972/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>C | 517呎 (2房)
-$1,084万
-$20,973/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-$1,011万
-$21,201/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F19" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 1258呎 (4+房)
-$4,422万
-$35,149/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G19" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 870呎 (3房)
-$2,694万
-$30,970/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H19" s="17" t="inlineStr">
-        <is>
-          <t>P3 | 952呎 (3房)
-$3,313万
-$34,800/呎
-(25年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,021万
-$21,010/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-$1,032万
-$20,889/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>C | 517呎 (2房)
-$1,066万
-$20,629/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-$1,005万
-$21,073/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F20" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 1261呎 (4+房)
-$4,351万
-$34,508/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G20" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 870呎 (3房)
-$2,653万
-$30,495/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H20" s="17" t="inlineStr">
-        <is>
-          <t>P3 | 952呎 (3房)
-$3,447万
-$36,211/呎
-(25年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,017万
-$20,926/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-$1,028万
-$20,806/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>C | 517呎 (2房)
-$1,076万
-$20,805/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-$999万
-$20,948/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F21" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 1261呎 (4+房)
-$4,540万
-$36,000/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G21" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 870呎 (3房)
-$2,612万
-$30,020/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H21" s="17" t="inlineStr">
-        <is>
-          <t>P3 | 952呎 (3房)
-$3,256万
-$34,200/呎
-(25年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,013万
-$20,844/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-$1,024万
-$20,723/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>C | 517呎 (2房)
-$1,138万
-$22,017/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-$993万
-$20,824/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F22" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 1261呎 (4+房)
-$4,265万
-$33,820/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G22" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 870呎 (3房)
-$2,579万
-$29,640/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H22" s="17" t="inlineStr">
-        <is>
-          <t>P3 | 952呎 (3房)
-$3,220万
-$33,820/呎
-(25年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,009万
-$20,759/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-$1,020万
-$20,640/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>C | 517呎 (2房)
-$1,067万
-$20,640/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-$987万
-$20,700/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 1261呎 (4+房)
-$4,229万
-$33,535/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G23" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 870呎 (3房)
-$2,688万
-$30,900/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H23" s="17" t="inlineStr">
-        <is>
-          <t>P3 | 952呎 (3房)
-$3,056万
-$32,100/呎
-(25年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,005万
-$20,677/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-$1,079万
-$21,842/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr">
-        <is>
-          <t>C | 517呎 (2房)
-$1,063万
-$20,557/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-$984万
-$20,618/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F24" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 1261呎 (4+房)
-$4,193万
-$33,250/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G24" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 870呎 (3房)
-$2,529万
-$29,070/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H24" s="17" t="inlineStr">
-        <is>
-          <t>P3 | 952呎 (3房)
-$2,876万
-$30,210/呎
-(25年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,001万
-$20,595/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-$1,008万
-$20,397/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>C | 517呎 (2房)
-$1,059万
-$20,476/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-$980万
-$20,537/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 1261呎 (4+房)
-$4,184万
-$33,180/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G25" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 870呎 (3房)
-$2,504万
-$28,785/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H25" s="17" t="inlineStr">
-        <is>
-          <t>P3 | 952呎 (3房)
-$3,299万
-$34,651/呎
-(25年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$997万
-$20,512/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-$1,004万
-$20,316/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D26" s="17" t="inlineStr">
-        <is>
-          <t>C | 517呎 (2房)
-$1,113万
-$21,522/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E26" s="17" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-$1,037万
-$21,732/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F26" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 1261呎 (4+房)
-$4,374万
-$34,688/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G26" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 870呎 (3房)
-$2,480万
-$28,500/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H26" s="17" t="inlineStr">
-        <is>
-          <t>P3 | 952呎 (3房)
-$3,122万
-$32,791/呎
-(25年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$993万
-$20,430/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-$1,000万
-$20,235/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D27" s="17" t="inlineStr">
-        <is>
-          <t>C | 517呎 (2房)
-$1,043万
-$20,176/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E27" s="17" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-$972万
-$20,371/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F27" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 1261呎 (4+房)
-$3,725万
-$29,538/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G27" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 870呎 (3房)
-$2,406万
-$27,653/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H27" s="17" t="inlineStr">
-        <is>
-          <t>P3 | 952呎 (3房)
-$2,893万
-$30,386/呎
-(25年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$989万
-$20,350/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-$996万
-$20,154/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D28" s="17" t="inlineStr">
-        <is>
-          <t>C | 517呎 (2房)
-$1,039万
-$20,095/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E28" s="17" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-$968万
-$20,291/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F28" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 1261呎 (4+房)
-$3,680万
-$29,187/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G28" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 870呎 (3房)
-$2,526万
-$29,032/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H28" s="17" t="inlineStr">
-        <is>
-          <t>P3 | 952呎 (3房)
-$2,850万
-$29,936/呎
-(25年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$985万
-$20,270/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C29" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-$992万
-$20,073/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D29" s="17" t="inlineStr">
-        <is>
-          <t>C | 517呎 (2房)
-$1,022万
-$19,764/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-$1,024万
-$21,474/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F29" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 1261呎 (4+房)
-$3,955万
-$31,363/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G29" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 870呎 (3房)
-$2,349万
-$27,001/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H29" s="17" t="inlineStr">
-        <is>
-          <t>P3 | 952呎 (3房)
-$2,652万
-$27,852/呎
-(25年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B30" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$981万
-$20,189/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C30" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-$1,049万
-$21,243/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="inlineStr">
-        <is>
-          <t>C | 517呎 (2房)
-$1,095万
-$21,182/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-$948万
-$19,878/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F30" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 1261呎 (4+房)
-$3,818万
-$30,281/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G30" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 870呎 (3房)
-$2,319万
-$26,654/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H30" s="17" t="inlineStr">
-        <is>
-          <t>P3 | 952呎 (3房)
-$2,784万
-$29,242/呎
-(25年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,038万
-$21,364/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C31" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-$1,045万
-$21,158/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="inlineStr">
-        <is>
-          <t>C | 517呎 (2房)
-$1,091万
-$21,097/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E31" s="17" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-$956万
-$20,050/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F31" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 1261呎 (4+房)
-$3,862万
-$30,626/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G31" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 870呎 (3房)
-$2,396万
-$27,545/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="H31" s="17" t="inlineStr">
-        <is>
-          <t>P3 | 952呎 (3房)
-$2,708万
-$28,441/呎
-(25年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B32" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,034万
-$21,278/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C32" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-$1,041万
-$21,073/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D32" s="17" t="inlineStr">
-        <is>
-          <t>C | 517呎 (2房)
-$1,086万
-$21,012/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E32" s="17" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-$952万
-$19,969/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F32" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 1261呎 (4+房)
-$3,819万
-$30,289/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G32" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 870呎 (3房)
-$2,361万
-$27,138/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H32" s="17" t="inlineStr">
-        <is>
-          <t>P3 | 952呎 (3房)
-$2,668万
-$28,021/呎
-(25年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,030万
-$21,195/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C33" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-$976万
-$19,755/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D33" s="17" t="inlineStr">
-        <is>
-          <t>C | 517呎 (2房)
-$1,006万
-$19,451/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E33" s="17" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-$949万
-$19,891/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F33" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 1261呎 (4+房)
-$3,785万
-$30,014/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G33" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 870呎 (3房)
-$2,338万
-$26,869/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="H33" s="17" t="inlineStr">
-        <is>
-          <t>P3 | 952呎 (3房)
-$2,641万
-$27,744/呎
-(25年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B34" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,026万
-$21,109/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C34" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-$1,033万
-$20,907/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D34" s="17" t="inlineStr">
-        <is>
-          <t>C | 517呎 (2房)
-$1,014万
-$19,619/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E34" s="17" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-$945万
-$19,811/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F34" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 1261呎 (4+房)
-$3,474万
-$27,550/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G34" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 870呎 (3房)
-$2,306万
-$26,506/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H34" s="17" t="inlineStr">
-        <is>
-          <t>P3 | 952呎 (3房)
-$2,578万
-$27,075/呎
-(25年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B35" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$962万
-$19,788/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C35" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-$968万
-$19,597/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D35" s="17" t="inlineStr">
-        <is>
-          <t>C | 517呎 (2房)
-$1,010万
-$19,542/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E35" s="17" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-$938万
-$19,654/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F35" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 1261呎 (4+房)
-$3,632万
-$28,800/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G35" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 870呎 (3房)
-$2,392万
-$27,500/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H35" s="17" t="inlineStr">
-        <is>
-          <t>P3 | 952呎 (3房)
-$2,586万
-$27,168/呎
-(25年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B36" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,018万
-$20,940/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C36" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-$964万
-$19,520/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D36" s="17" t="inlineStr">
-        <is>
-          <t>C | 517呎 (2房)
-$1,069万
-$20,681/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E36" s="17" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-$928万
-$19,459/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F36" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 1261呎 (4+房)
-$3,426万
-$27,170/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G36" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 870呎 (3房)
-$2,399万
-$27,579/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="H36" s="17" t="inlineStr">
-        <is>
-          <t>P3 | 952呎 (3房)
-$2,675万
-$28,100/呎
-(25年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="65" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B37" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,014万
-$20,858/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C37" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-$960万
-$19,441/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D37" s="17" t="inlineStr">
-        <is>
-          <t>C | 517呎 (2房)
-$1,002万
-$19,387/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E37" s="17" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-$976万
-$20,470/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F37" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 1261呎 (4+房)
-$3,881万
-$30,779/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G37" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 870呎 (3房)
-$2,314万
-$26,600/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="H37" s="17" t="inlineStr">
-        <is>
-          <t>P3 | 952呎 (3房)
-$2,570万
-$27,000/呎
-(25年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="65" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B38" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,010万
-$20,776/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C38" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-$957万
-$19,364/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D38" s="17" t="inlineStr">
-        <is>
-          <t>C | 517呎 (2房)
-$998万
-$19,309/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E38" s="17" t="inlineStr">
-        <is>
-          <t>D | 477呎 (2房)
-$910万
-$19,075/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F38" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 1261呎 (4+房)
-$3,577万
-$28,368/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="G38" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 870呎 (3房)
-$2,490万
-$28,620/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="H38" s="17" t="inlineStr">
-        <is>
-          <t>P3 | 952呎 (3房)
-$2,686万
-$28,211/呎
-(25年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="65" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B39" s="17" t="inlineStr">
-        <is>
-          <t>A | 440呎 (2房)
-$1,088万
-$24,716/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C39" s="17" t="inlineStr">
-        <is>
-          <t>B | 448呎 (2房)
-$1,120万
-$25,000/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D39" s="17" t="inlineStr">
-        <is>
-          <t>C | 467呎 (2房)
-$1,238万
-$26,501/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E39" s="17" t="inlineStr">
-        <is>
-          <t>D | 430呎 (2房)
-$999万
-$23,233/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F39" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 1162呎 (4+房)
-$3,650万
-$31,411/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G39" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 870呎 (3房)
-$2,436万
-$28,000/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="H39" s="17" t="inlineStr">
-        <is>
-          <t>P3 | 952呎 (3房)
-$2,758万
-$28,971/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:I39"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>滶晨 - 1B座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>240 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>230 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>10 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>41&amp;42/F</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>A | 1020呎 (3房)
-$3,652万
-$35,800/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 1016呎 (3房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>C | 1029呎 (3房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>D | 1083呎 (3房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F6" s="18" t="inlineStr"/>
-      <c r="G6" s="18" t="inlineStr"/>
-      <c r="H6" s="16" t="inlineStr">
-        <is>
-          <t>P2 | 2871呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="I6" s="18" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>41/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr"/>
-      <c r="C7" s="18" t="inlineStr"/>
-      <c r="D7" s="18" t="inlineStr"/>
-      <c r="E7" s="18" t="inlineStr"/>
-      <c r="F7" s="18" t="inlineStr"/>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>P1 | 1417呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H7" s="18" t="inlineStr"/>
-      <c r="I7" s="18" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>40/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,245万
-$25,619/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>B | 485呎 (2房)
-$1,138万
-$23,474/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>C | 491呎 (2房)
-$1,137万
-$23,161/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>D | 476呎 (2房)
-$1,804万
-$37,903/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr"/>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>P1 | 1422呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>P2 | 1559呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="I8" s="18" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>39/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,180万
-$24,274/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>B | 485呎 (2房)
-$1,556万
-$32,089/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>C | 491呎 (2房)
-$1,196万
-$24,365/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>D | 476呎 (2房)
-$1,532万
-$32,191/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F9" s="18" t="inlineStr"/>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>P1 | 1422呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
-        <is>
-          <t>P2 | 1559呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="I9" s="18" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,543万
-$31,745/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>B | 485呎 (2房)
-$1,169万
-$24,095/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>C | 491呎 (2房)
-$1,174万
-$23,906/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E10" s="17" t="inlineStr">
-        <is>
-          <t>D | 476呎 (2房)
-$1,137万
-$23,895/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F10" s="18" t="inlineStr"/>
-      <c r="G10" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 1422呎 (4+房)
-$6,754万
-$47,500/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="H10" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 1559呎 (4+房)
-$8,574万
-$55,000/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="I10" s="18" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,170万
-$24,078/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>B | 485呎 (2房)
-$1,112万
-$22,926/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>C | 491呎 (2房)
-$1,116万
-$22,723/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>D | 476呎 (2房)
-$1,081万
-$22,714/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F11" s="18" t="inlineStr"/>
-      <c r="G11" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 1422呎 (4+房)
-$6,086万
-$42,800/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="H11" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 1559呎 (4+房)
-$7,592万
-$48,700/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="I11" s="18" t="inlineStr"/>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,084万
-$22,307/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>B | 485呎 (2房)
-$1,081万
-$22,287/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>C | 491呎 (2房)
-$1,276万
-$25,982/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="inlineStr">
-        <is>
-          <t>D | 476呎 (2房)
-$1,064万
-$22,357/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="F12" s="18" t="inlineStr"/>
-      <c r="G12" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 1422呎 (4+房)
-$5,644万
-$39,690/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H12" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 1559呎 (4+房)
-$6,715万
-$43,071/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="I12" s="18" t="inlineStr"/>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,081万
-$22,251/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>B | 485呎 (2房)
-$1,078万
-$22,231/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>C | 491呎 (2房)
-$1,082万
-$22,035/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>D | 476呎 (2房)
-$1,048万
-$22,027/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="inlineStr"/>
-      <c r="G13" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 1422呎 (4+房)
-$5,431万
-$38,190/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H13" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 1559呎 (4+房)
-$6,324万
-$40,565/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="I13" s="18" t="inlineStr"/>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,065万
-$21,922/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>B | 485呎 (2房)
-$1,128万
-$23,256/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>C | 491呎 (2房)
-$1,132万
-$23,051/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>D | 476呎 (2房)
-$998万
-$20,958/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F14" s="18" t="inlineStr"/>
-      <c r="G14" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 1422呎 (4+房)
-$5,404万
-$38,000/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H14" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 1559呎 (4+房)
-$6,018万
-$38,602/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="I14" s="18" t="inlineStr"/>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,046万
-$21,523/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>B | 485呎 (2房)
-$1,108万
-$22,847/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>C | 491呎 (2房)
-$1,046万
-$21,314/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>D | 476呎 (2房)
-$993万
-$20,855/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F15" s="18" t="inlineStr"/>
-      <c r="G15" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 1422呎 (4+房)
-$5,494万
-$38,634/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H15" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 1559呎 (4+房)
-$6,220万
-$39,900/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="I15" s="18" t="inlineStr"/>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,040万
-$21,395/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>B | 485呎 (2房)
-$1,102万
-$22,713/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>C | 491呎 (2房)
-$1,040万
-$21,187/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>D | 476呎 (2房)
-$988万
-$20,750/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F16" s="18" t="inlineStr"/>
-      <c r="G16" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 1422呎 (4+房)
-$5,052万
-$35,530/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H16" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 1559呎 (4+房)
-$5,850万
-$37,525/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="I16" s="18" t="inlineStr"/>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,034万
-$21,267/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>B | 485呎 (2房)
-$1,030万
-$21,247/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>C | 491呎 (2房)
-$1,099万
-$22,377/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>D | 476呎 (2房)
-$983万
-$20,647/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F17" s="18" t="inlineStr"/>
-      <c r="G17" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 1422呎 (4+房)
-$4,996万
-$35,136/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H17" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 1559呎 (4+房)
-$5,791万
-$37,145/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="I17" s="18" t="inlineStr"/>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,027万
-$21,140/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>B | 485呎 (2房)
-$1,024万
-$21,122/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>C | 491呎 (2房)
-$1,028万
-$20,937/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>D | 476呎 (2房)
-$978万
-$20,546/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F18" s="18" t="inlineStr"/>
-      <c r="G18" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 1422呎 (4+房)
-$4,839万
-$34,028/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H18" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 1559呎 (4+房)
-$5,609万
-$35,977/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="I18" s="18" t="inlineStr"/>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,083万
-$22,282/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>B | 485呎 (2房)
-$1,063万
-$21,915/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>C | 490呎 (2房)
-$1,005万
-$20,506/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>D | 476呎 (2房)
-$964万
-$20,261/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F19" s="17" t="inlineStr">
-        <is>
-          <t>E | 455呎 (2房)
-$917万
-$20,160/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G19" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 926呎 (3房)
-$3,273万
-$35,350/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H19" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 860呎 (3房)
-$2,726万
-$31,700/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="I19" s="17" t="inlineStr">
-        <is>
-          <t>P3 | 826呎 (3房)
-$2,494万
-$30,200/呎
-(25年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,015万
-$20,889/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>B | 485呎 (2房)
-$1,059万
-$21,829/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>C | 490呎 (2房)
-$1,063万
-$21,700/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>D | 476呎 (2房)
-$961万
-$20,181/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F20" s="17" t="inlineStr">
-        <is>
-          <t>E | 455呎 (2房)
-$971万
-$21,334/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G20" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 926呎 (3房)
-$3,084万
-$33,300/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H20" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 860呎 (3房)
-$2,582万
-$30,020/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="I20" s="17" t="inlineStr">
-        <is>
-          <t>P3 | 826呎 (3房)
-$2,591万
-$31,368/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,011万
-$20,807/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>B | 485呎 (2房)
-$1,054万
-$21,742/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>C | 490呎 (2房)
-$1,059万
-$21,614/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>D | 476呎 (2房)
-$957万
-$20,101/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F21" s="17" t="inlineStr">
-        <is>
-          <t>E | 455呎 (2房)
-$910万
-$20,000/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G21" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 926呎 (3房)
-$3,337万
-$36,040/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H21" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 860呎 (3房)
-$2,541万
-$29,545/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="I21" s="17" t="inlineStr">
-        <is>
-          <t>P3 | 826呎 (3房)
-$2,548万
-$30,850/呎
-(25年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,070万
-$22,016/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>B | 485呎 (2房)
-$1,050万
-$21,656/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>C | 490呎 (2房)
-$993万
-$20,261/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>D | 476呎 (2房)
-$1,012万
-$21,271/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F22" s="17" t="inlineStr">
-        <is>
-          <t>E | 455呎 (2房)
-$906万
-$19,921/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G22" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 926呎 (3房)
-$3,300万
-$35,639/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H22" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 860呎 (3房)
-$2,500万
-$29,070/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="I22" s="17" t="inlineStr">
-        <is>
-          <t>P3 | 826呎 (3房)
-$2,519万
-$30,500/呎
-(25年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,003万
-$20,640/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>B | 485呎 (2房)
-$984万
-$20,299/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>C | 490呎 (2房)
-$989万
-$20,180/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>D | 476呎 (2房)
-$949万
-$19,941/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr">
-        <is>
-          <t>E | 455呎 (2房)
-$903万
-$19,842/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G23" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 926呎 (3房)
-$2,824万
-$30,495/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H23" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 860呎 (3房)
-$2,623万
-$30,500/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="I23" s="17" t="inlineStr">
-        <is>
-          <t>P3 | 826呎 (3房)
-$2,490万
-$30,150/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,062万
-$21,842/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>B | 485呎 (2房)
-$981万
-$20,219/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr">
-        <is>
-          <t>C | 490呎 (2房)
-$985万
-$20,100/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>D | 476呎 (2房)
-$945万
-$19,861/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F24" s="17" t="inlineStr">
-        <is>
-          <t>E | 455呎 (2房)
-$955万
-$20,998/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G24" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 926呎 (3房)
-$2,784万
-$30,068/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H24" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 860呎 (3房)
-$2,487万
-$28,916/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="I24" s="17" t="inlineStr">
-        <is>
-          <t>P3 | 826呎 (3房)
-$2,437万
-$29,500/呎
-(25年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$983万
-$20,220/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>B | 485呎 (2房)
-$977万
-$20,140/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>C | 490呎 (2房)
-$1,042万
-$21,269/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="inlineStr">
-        <is>
-          <t>D | 476呎 (2房)
-$942万
-$19,782/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="inlineStr">
-        <is>
-          <t>E | 455呎 (2房)
-$896万
-$19,684/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G25" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 926呎 (3房)
-$3,217万
-$34,740/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H25" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 860呎 (3房)
-$2,482万
-$28,856/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="I25" s="17" t="inlineStr">
-        <is>
-          <t>P3 | 826呎 (3房)
-$2,342万
-$28,350/呎
-(25年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,053万
-$21,669/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>B | 485呎 (2房)
-$973万
-$20,058/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D26" s="17" t="inlineStr">
-        <is>
-          <t>C | 490呎 (2房)
-$977万
-$19,941/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E26" s="17" t="inlineStr">
-        <is>
-          <t>D | 476呎 (2房)
-$996万
-$20,935/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F26" s="17" t="inlineStr">
-        <is>
-          <t>E | 455呎 (2房)
-$892万
-$19,604/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G26" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 926呎 (3房)
-$3,045万
-$32,880/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H26" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 860呎 (3房)
-$2,451万
-$28,500/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="I26" s="17" t="inlineStr">
-        <is>
-          <t>P3 | 826呎 (3房)
-$2,321万
-$28,100/呎
-(25年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$987万
-$20,313/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>B | 485呎 (2房)
-$969万
-$19,977/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D27" s="17" t="inlineStr">
-        <is>
-          <t>C | 490呎 (2房)
-$1,034万
-$21,102/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E27" s="17" t="inlineStr">
-        <is>
-          <t>D | 476呎 (2房)
-$934万
-$19,624/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="F27" s="17" t="inlineStr">
-        <is>
-          <t>E | 455呎 (2房)
-$888万
-$19,525/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G27" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 926呎 (3房)
-$2,727万
-$29,450/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H27" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 860呎 (3房)
-$2,426万
-$28,215/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="I27" s="17" t="inlineStr">
-        <is>
-          <t>P3 | 826呎 (3房)
-$2,310万
-$27,970/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$983万
-$20,233/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="inlineStr">
-        <is>
-          <t>B | 485呎 (2房)
-$965万
-$19,899/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D28" s="17" t="inlineStr">
-        <is>
-          <t>C | 490呎 (2房)
-$969万
-$19,780/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E28" s="17" t="inlineStr">
-        <is>
-          <t>D | 476呎 (2房)
-$988万
-$20,767/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F28" s="17" t="inlineStr">
-        <is>
-          <t>E | 455呎 (2房)
-$885万
-$19,448/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G28" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 926呎 (3房)
-$2,701万
-$29,165/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H28" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 860呎 (3房)
-$2,402万
-$27,930/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="I28" s="17" t="inlineStr">
-        <is>
-          <t>P3 | 826呎 (3房)
-$2,294万
-$27,770/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$979万
-$20,152/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C29" s="17" t="inlineStr">
-        <is>
-          <t>B | 485呎 (2房)
-$949万
-$19,571/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D29" s="17" t="inlineStr">
-        <is>
-          <t>C | 490呎 (2房)
-$965万
-$19,702/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>D | 476呎 (2房)
-$927万
-$19,468/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F29" s="17" t="inlineStr">
-        <is>
-          <t>E | 455呎 (2房)
-$926万
-$20,341/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G29" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 926呎 (3房)
-$2,674万
-$28,880/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H29" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 860呎 (3房)
-$2,498万
-$29,041/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="I29" s="17" t="inlineStr">
-        <is>
-          <t>P3 | 826呎 (3房)
-$2,277万
-$27,570/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B30" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$976万
-$20,072/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C30" s="17" t="inlineStr">
-        <is>
-          <t>B | 485呎 (2房)
-$957万
-$19,740/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="inlineStr">
-        <is>
-          <t>C | 490呎 (2房)
-$962万
-$19,624/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>D | 476呎 (2房)
-$981万
-$20,603/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F30" s="17" t="inlineStr">
-        <is>
-          <t>E | 455呎 (2房)
-$878万
-$19,295/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G30" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 926呎 (3房)
-$2,787万
-$30,100/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H30" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 860呎 (3房)
-$2,555万
-$29,713/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="I30" s="17" t="inlineStr">
-        <is>
-          <t>P3 | 826呎 (3房)
-$2,355万
-$28,511/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,032万
-$21,241/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C31" s="17" t="inlineStr">
-        <is>
-          <t>B | 485呎 (2房)
-$1,013万
-$20,891/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="inlineStr">
-        <is>
-          <t>C | 490呎 (2房)
-$1,018万
-$20,767/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E31" s="17" t="inlineStr">
-        <is>
-          <t>D | 476呎 (2房)
-$919万
-$19,313/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F31" s="17" t="inlineStr">
-        <is>
-          <t>E | 455呎 (2房)
-$874万
-$19,218/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G31" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 926呎 (3房)
-$2,622万
-$28,310/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H31" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 860呎 (3房)
-$2,378万
-$27,650/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="I31" s="17" t="inlineStr">
-        <is>
-          <t>P3 | 826呎 (3房)
-$2,244万
-$27,169/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B32" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,028万
-$21,156/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C32" s="17" t="inlineStr">
-        <is>
-          <t>B | 485呎 (2房)
-$1,009万
-$20,808/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D32" s="17" t="inlineStr">
-        <is>
-          <t>C | 490呎 (2房)
-$1,014万
-$20,686/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E32" s="17" t="inlineStr">
-        <is>
-          <t>D | 476呎 (2房)
-$916万
-$19,235/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F32" s="17" t="inlineStr">
-        <is>
-          <t>E | 455呎 (2房)
-$871万
-$19,141/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G32" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 926呎 (3房)
-$2,734万
-$29,526/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="H32" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 860呎 (3房)
-$2,382万
-$27,700/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="I32" s="17" t="inlineStr">
-        <is>
-          <t>P3 | 826呎 (3房)
-$2,304万
-$27,900/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,024万
-$21,072/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C33" s="17" t="inlineStr">
-        <is>
-          <t>B | 485呎 (2房)
-$934万
-$19,262/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D33" s="17" t="inlineStr">
-        <is>
-          <t>C | 490呎 (2房)
-$950万
-$19,390/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E33" s="17" t="inlineStr">
-        <is>
-          <t>D | 476呎 (2房)
-$969万
-$20,357/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F33" s="17" t="inlineStr">
-        <is>
-          <t>E | 455呎 (2房)
-$867万
-$19,064/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G33" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 926呎 (3房)
-$2,715万
-$29,316/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H33" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 860呎 (3房)
-$2,365万
-$27,500/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="I33" s="17" t="inlineStr">
-        <is>
-          <t>P3 | 826呎 (3房)
-$2,211万
-$26,770/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B34" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,020万
-$20,988/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C34" s="17" t="inlineStr">
-        <is>
-          <t>B | 485呎 (2房)
-$1,001万
-$20,643/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D34" s="17" t="inlineStr">
-        <is>
-          <t>C | 490呎 (2房)
-$946万
-$19,314/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E34" s="17" t="inlineStr">
-        <is>
-          <t>D | 476呎 (2房)
-$908万
-$19,084/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F34" s="17" t="inlineStr">
-        <is>
-          <t>E | 455呎 (2房)
-$864万
-$18,989/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G34" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 926呎 (3房)
-$2,584万
-$27,900/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="H34" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 860呎 (3房)
-$2,348万
-$27,300/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="I34" s="17" t="inlineStr">
-        <is>
-          <t>P3 | 826呎 (3房)
-$2,272万
-$27,500/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B35" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1,016万
-$20,905/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C35" s="17" t="inlineStr">
-        <is>
-          <t>B | 485呎 (2房)
-$938万
-$19,351/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D35" s="17" t="inlineStr">
-        <is>
-          <t>C | 490呎 (2房)
-$943万
-$19,237/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E35" s="17" t="inlineStr">
-        <is>
-          <t>D | 476呎 (2房)
-$905万
-$19,008/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F35" s="17" t="inlineStr">
-        <is>
-          <t>E | 455呎 (2房)
-$914万
-$20,095/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G35" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 926呎 (3房)
-$2,565万
-$27,700/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="H35" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 860呎 (3房)
-$2,331万
-$27,100/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="I35" s="17" t="inlineStr">
-        <is>
-          <t>P3 | 826呎 (3房)
-$2,296万
-$27,800/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B36" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$952万
-$19,597/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C36" s="17" t="inlineStr">
-        <is>
-          <t>B | 485呎 (2房)
-$993万
-$20,478/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D36" s="17" t="inlineStr">
-        <is>
-          <t>C | 490呎 (2房)
-$939万
-$19,159/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E36" s="17" t="inlineStr">
-        <is>
-          <t>D | 476呎 (2房)
-$901万
-$18,933/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F36" s="17" t="inlineStr">
-        <is>
-          <t>E | 455呎 (2房)
-$911万
-$20,013/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G36" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 926呎 (3房)
-$2,680万
-$28,947/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="H36" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 860呎 (3房)
-$2,313万
-$26,895/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="I36" s="17" t="inlineStr">
-        <is>
-          <t>P3 | 826呎 (3房)
-$2,280万
-$27,599/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="65" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B37" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$949万
-$19,519/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C37" s="17" t="inlineStr">
-        <is>
-          <t>B | 485呎 (2房)
-$931万
-$19,196/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D37" s="17" t="inlineStr">
-        <is>
-          <t>C | 490呎 (2房)
-$935万
-$19,084/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E37" s="17" t="inlineStr">
-        <is>
-          <t>D | 476呎 (2房)
-$954万
-$20,036/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F37" s="17" t="inlineStr">
-        <is>
-          <t>E | 455呎 (2房)
-$854万
-$18,763/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G37" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 926呎 (3房)
-$2,556万
-$27,600/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="H37" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 860呎 (3房)
-$2,339万
-$27,200/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="I37" s="17" t="inlineStr">
-        <is>
-          <t>P3 | 826呎 (3房)
-$2,263万
-$27,400/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="65" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B38" s="17" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$945万
-$19,440/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C38" s="17" t="inlineStr">
-        <is>
-          <t>B | 485呎 (2房)
-$927万
-$19,120/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D38" s="17" t="inlineStr">
-        <is>
-          <t>C | 490呎 (2房)
-$931万
-$19,006/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E38" s="17" t="inlineStr">
-        <is>
-          <t>D | 476呎 (2房)
-$894万
-$18,782/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F38" s="17" t="inlineStr">
-        <is>
-          <t>E | 455呎 (2房)
-$850万
-$18,688/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G38" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 926呎 (3房)
-$2,574万
-$27,800/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H38" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 860呎 (3房)
-$2,365万
-$27,500/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="I38" s="17" t="inlineStr">
-        <is>
-          <t>P3 | 826呎 (3房)
-$2,247万
-$27,200/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="65" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B39" s="17" t="inlineStr">
-        <is>
-          <t>A | 440呎 (2房)
-$1,158万
-$26,316/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C39" s="17" t="inlineStr">
-        <is>
-          <t>B | 439呎 (2房)
-$1,089万
-$24,800/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D39" s="17" t="inlineStr">
-        <is>
-          <t>C | 444呎 (2房)
-$1,092万
-$24,599/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E39" s="17" t="inlineStr">
-        <is>
-          <t>D | 430呎 (2房)
-$1,182万
-$27,500/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F39" s="17" t="inlineStr">
-        <is>
-          <t>E | 408呎 (2房)
-$1,040万
-$25,500/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G39" s="17" t="inlineStr">
-        <is>
-          <t>P1 | 926呎 (3房)
-$2,546万
-$27,499/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H39" s="17" t="inlineStr">
-        <is>
-          <t>P2 | 860呎 (3房)
-$2,471万
-$28,737/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="I39" s="17" t="inlineStr">
-        <is>
-          <t>P3 | 826呎 (3房)
-$2,354万
-$28,500/呎
-(26年-01月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/港岛-黄竹坑-滶晨.xlsx
+++ b/files/港岛-黄竹坑-滶晨.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1A座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1B座" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +43,91 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +138,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +219,57 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +646,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -21171,4 +21343,4407 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1A座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr"/>
+      <c r="E5" s="20" t="inlineStr"/>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>P1 | 1536呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr"/>
+      <c r="H5" s="20" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>41&amp;42</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 1020呎 (3房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1034呎 (3房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 1083呎 (3房)
+$3890万
+$35,921/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>P2 | 3120呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1593万
+$32,776/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+$1142万
+$23,109/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 517呎 (2房)
+$1235万
+$23,892/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>P1 | 1536呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>P2 | 1706呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1566万
+$32,222/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+$1130万
+$22,881/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 517呎 (2房)
+$1276万
+$24,689/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr"/>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>P1 | 1536呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 1706呎 (4+房)
+$10775万
+$63,158/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1429万
+$29,401/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+$1227万
+$24,844/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 517呎 (2房)
+$1245万
+$24,087/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr"/>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1536呎 (4+房)
+$7296万
+$47,500/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 1706呎 (4+房)
+$8530万
+$50,000/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1117万
+$22,990/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+$1131万
+$22,903/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 517呎 (2房)
+$1154万
+$22,317/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr"/>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1536呎 (4+房)
+$6543万
+$42,600/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 1706呎 (4+房)
+$8189万
+$48,000/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1086万
+$22,346/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+$1100万
+$22,265/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 517呎 (2房)
+$1217万
+$23,536/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr"/>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1536呎 (4+房)
+$6420万
+$41,800/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 1706呎 (4+房)
+$7558万
+$44,300/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1083万
+$22,292/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+$1097万
+$22,211/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 517呎 (2房)
+$1137万
+$21,986/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr"/>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1536呎 (4+房)
+$6298万
+$41,000/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 1706呎 (4+房)
+$7421万
+$43,500/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1067万
+$21,963/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+$1081万
+$21,881/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 517呎 (2房)
+$1128万
+$21,822/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr"/>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1536呎 (4+房)
+$6089万
+$39,641/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 1706呎 (4+房)
+$7319万
+$42,900/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr"/>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1048万
+$21,562/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+$1061万
+$21,482/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 517呎 (2房)
+$1123万
+$21,714/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr"/>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1536呎 (4+房)
+$5990万
+$39,000/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 1706呎 (4+房)
+$6726万
+$39,425/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1107万
+$22,772/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+$1055万
+$21,354/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 517呎 (2房)
+$1187万
+$22,956/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr"/>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1536呎 (4+房)
+$5574万
+$36,290/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 1706呎 (4+房)
+$6596万
+$38,665/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1100万
+$22,638/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+$1114万
+$22,553/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 517呎 (2房)
+$1112万
+$21,499/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr"/>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1536呎 (4+房)
+$5076万
+$33,047/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 1706呎 (4+房)
+$6467万
+$37,906/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr"/>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1094万
+$22,502/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+$1108万
+$22,419/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 517呎 (2房)
+$1175万
+$22,729/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr"/>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1469呎 (4+房)
+$5739万
+$39,066/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 1706呎 (4+房)
+$6739万
+$39,501/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr"/>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1025万
+$21,095/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+$1036万
+$20,972/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 517呎 (2房)
+$1084万
+$20,973/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+$1011万
+$21,201/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1258呎 (4+房)
+$4422万
+$35,149/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 870呎 (3房)
+$2694万
+$30,970/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr">
+        <is>
+          <t>P3 | 952呎 (3房)
+$3313万
+$34,800/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1021万
+$21,010/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+$1032万
+$20,889/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 517呎 (2房)
+$1066万
+$20,629/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+$1005万
+$21,073/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1261呎 (4+房)
+$4351万
+$34,508/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 870呎 (3房)
+$2653万
+$30,495/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H19" s="22" t="inlineStr">
+        <is>
+          <t>P3 | 952呎 (3房)
+$3447万
+$36,211/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1017万
+$20,926/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+$1028万
+$20,806/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 517呎 (2房)
+$1076万
+$20,805/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+$999万
+$20,948/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1261呎 (4+房)
+$4540万
+$36,000/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 870呎 (3房)
+$2612万
+$30,020/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="inlineStr">
+        <is>
+          <t>P3 | 952呎 (3房)
+$3256万
+$34,200/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1013万
+$20,844/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+$1024万
+$20,723/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 517呎 (2房)
+$1138万
+$22,017/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+$993万
+$20,824/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1261呎 (4+房)
+$4265万
+$33,820/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 870呎 (3房)
+$2579万
+$29,640/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H21" s="22" t="inlineStr">
+        <is>
+          <t>P3 | 952呎 (3房)
+$3220万
+$33,820/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1009万
+$20,759/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+$1020万
+$20,640/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 517呎 (2房)
+$1067万
+$20,640/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+$987万
+$20,700/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1261呎 (4+房)
+$4229万
+$33,535/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G22" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 870呎 (3房)
+$2688万
+$30,900/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
+        <is>
+          <t>P3 | 952呎 (3房)
+$3056万
+$32,100/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1005万
+$20,677/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+$1079万
+$21,842/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 517呎 (2房)
+$1063万
+$20,557/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+$984万
+$20,618/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1261呎 (4+房)
+$4193万
+$33,250/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 870呎 (3房)
+$2529万
+$29,070/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H23" s="22" t="inlineStr">
+        <is>
+          <t>P3 | 952呎 (3房)
+$2876万
+$30,210/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1001万
+$20,595/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+$1008万
+$20,397/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 517呎 (2房)
+$1059万
+$20,476/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+$980万
+$20,537/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1261呎 (4+房)
+$4184万
+$33,180/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 870呎 (3房)
+$2504万
+$28,785/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H24" s="22" t="inlineStr">
+        <is>
+          <t>P3 | 952呎 (3房)
+$3299万
+$34,651/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$997万
+$20,512/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+$1004万
+$20,316/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C | 517呎 (2房)
+$1113万
+$21,522/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+$1037万
+$21,732/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1261呎 (4+房)
+$4374万
+$34,688/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 870呎 (3房)
+$2480万
+$28,500/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H25" s="22" t="inlineStr">
+        <is>
+          <t>P3 | 952呎 (3房)
+$3122万
+$32,791/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$993万
+$20,430/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+$1000万
+$20,235/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>C | 517呎 (2房)
+$1043万
+$20,176/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+$972万
+$20,371/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1261呎 (4+房)
+$3725万
+$29,538/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 870呎 (3房)
+$2406万
+$27,653/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H26" s="22" t="inlineStr">
+        <is>
+          <t>P3 | 952呎 (3房)
+$2893万
+$30,386/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$989万
+$20,350/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+$996万
+$20,154/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>C | 517呎 (2房)
+$1039万
+$20,095/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+$968万
+$20,291/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1261呎 (4+房)
+$3680万
+$29,187/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G27" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 870呎 (3房)
+$2526万
+$29,032/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H27" s="22" t="inlineStr">
+        <is>
+          <t>P3 | 952呎 (3房)
+$2850万
+$29,936/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$985万
+$20,270/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+$992万
+$20,073/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>C | 517呎 (2房)
+$1022万
+$19,764/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+$1024万
+$21,474/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1261呎 (4+房)
+$3955万
+$31,363/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G28" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 870呎 (3房)
+$2349万
+$27,001/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H28" s="22" t="inlineStr">
+        <is>
+          <t>P3 | 952呎 (3房)
+$2652万
+$27,852/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$981万
+$20,189/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+$1049万
+$21,243/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>C | 517呎 (2房)
+$1095万
+$21,182/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+$948万
+$19,878/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F29" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1261呎 (4+房)
+$3818万
+$30,281/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G29" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 870呎 (3房)
+$2319万
+$26,654/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H29" s="22" t="inlineStr">
+        <is>
+          <t>P3 | 952呎 (3房)
+$2784万
+$29,242/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1038万
+$21,364/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+$1045万
+$21,158/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
+        <is>
+          <t>C | 517呎 (2房)
+$1091万
+$21,097/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+$956万
+$20,050/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F30" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1261呎 (4+房)
+$3862万
+$30,626/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G30" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 870呎 (3房)
+$2396万
+$27,545/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="H30" s="22" t="inlineStr">
+        <is>
+          <t>P3 | 952呎 (3房)
+$2708万
+$28,441/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1034万
+$21,278/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+$1041万
+$21,073/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>C | 517呎 (2房)
+$1086万
+$21,012/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+$952万
+$19,969/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F31" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1261呎 (4+房)
+$3819万
+$30,289/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G31" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 870呎 (3房)
+$2361万
+$27,138/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H31" s="22" t="inlineStr">
+        <is>
+          <t>P3 | 952呎 (3房)
+$2668万
+$28,021/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1030万
+$21,195/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+$976万
+$19,755/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="inlineStr">
+        <is>
+          <t>C | 517呎 (2房)
+$1006万
+$19,451/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E32" s="22" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+$949万
+$19,891/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F32" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1261呎 (4+房)
+$3785万
+$30,014/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G32" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 870呎 (3房)
+$2338万
+$26,869/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H32" s="22" t="inlineStr">
+        <is>
+          <t>P3 | 952呎 (3房)
+$2641万
+$27,744/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1026万
+$21,109/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C33" s="22" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+$1033万
+$20,907/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D33" s="22" t="inlineStr">
+        <is>
+          <t>C | 517呎 (2房)
+$1014万
+$19,619/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E33" s="22" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+$945万
+$19,811/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F33" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1261呎 (4+房)
+$3474万
+$27,550/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G33" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 870呎 (3房)
+$2306万
+$26,506/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H33" s="22" t="inlineStr">
+        <is>
+          <t>P3 | 952呎 (3房)
+$2578万
+$27,075/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$962万
+$19,788/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+$968万
+$19,597/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D34" s="22" t="inlineStr">
+        <is>
+          <t>C | 517呎 (2房)
+$1010万
+$19,542/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E34" s="22" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+$938万
+$19,654/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F34" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1261呎 (4+房)
+$3632万
+$28,800/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G34" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 870呎 (3房)
+$2392万
+$27,500/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H34" s="22" t="inlineStr">
+        <is>
+          <t>P3 | 952呎 (3房)
+$2586万
+$27,168/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1018万
+$20,940/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C35" s="22" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+$964万
+$19,520/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="inlineStr">
+        <is>
+          <t>C | 517呎 (2房)
+$1069万
+$20,681/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E35" s="22" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+$928万
+$19,459/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F35" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1261呎 (4+房)
+$3426万
+$27,170/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G35" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 870呎 (3房)
+$2399万
+$27,579/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="H35" s="22" t="inlineStr">
+        <is>
+          <t>P3 | 952呎 (3房)
+$2675万
+$28,100/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1014万
+$20,858/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C36" s="22" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+$960万
+$19,441/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D36" s="22" t="inlineStr">
+        <is>
+          <t>C | 517呎 (2房)
+$1002万
+$19,387/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E36" s="22" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+$976万
+$20,470/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F36" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1261呎 (4+房)
+$3881万
+$30,779/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G36" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 870呎 (3房)
+$2314万
+$26,600/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H36" s="22" t="inlineStr">
+        <is>
+          <t>P3 | 952呎 (3房)
+$2570万
+$27,000/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B37" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1010万
+$20,776/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C37" s="22" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+$957万
+$19,364/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D37" s="22" t="inlineStr">
+        <is>
+          <t>C | 517呎 (2房)
+$998万
+$19,309/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E37" s="22" t="inlineStr">
+        <is>
+          <t>D | 477呎 (2房)
+$910万
+$19,075/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F37" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1261呎 (4+房)
+$3577万
+$28,368/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="G37" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 870呎 (3房)
+$2490万
+$28,620/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H37" s="22" t="inlineStr">
+        <is>
+          <t>P3 | 952呎 (3房)
+$2686万
+$28,211/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B38" s="22" t="inlineStr">
+        <is>
+          <t>A | 440呎 (2房)
+$1088万
+$24,716/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C38" s="22" t="inlineStr">
+        <is>
+          <t>B | 448呎 (2房)
+$1120万
+$25,000/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D38" s="22" t="inlineStr">
+        <is>
+          <t>C | 467呎 (2房)
+$1238万
+$26,501/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E38" s="22" t="inlineStr">
+        <is>
+          <t>D | 430呎 (2房)
+$999万
+$23,233/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F38" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1162呎 (4+房)
+$3650万
+$31,411/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G38" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 870呎 (3房)
+$2436万
+$28,000/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H38" s="22" t="inlineStr">
+        <is>
+          <t>P3 | 952呎 (3房)
+$2758万
+$28,971/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1B座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr"/>
+      <c r="E5" s="20" t="inlineStr"/>
+      <c r="F5" s="20" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr">
+        <is>
+          <t>P1 | 1417呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr"/>
+      <c r="I5" s="20" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>41&amp;42</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 1020呎 (3房)
+$3652万
+$35,800/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1016呎 (3房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 1029呎 (3房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 1083呎 (3房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>P2 | 2871呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1245万
+$25,619/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 485呎 (2房)
+$1138万
+$23,474/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 491呎 (2房)
+$1137万
+$23,161/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+$1804万
+$37,903/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>P1 | 1422呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t>P2 | 1559呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1180万
+$24,274/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 485呎 (2房)
+$1556万
+$32,089/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 491呎 (2房)
+$1196万
+$24,365/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+$1532万
+$32,191/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr"/>
+      <c r="G8" s="21" t="inlineStr">
+        <is>
+          <t>P1 | 1422呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t>P2 | 1559呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1543万
+$31,745/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 485呎 (2房)
+$1169万
+$24,095/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 491呎 (2房)
+$1174万
+$23,906/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+$1137万
+$23,895/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr"/>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1422呎 (4+房)
+$6754万
+$47,500/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H9" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 1559呎 (4+房)
+$8574万
+$55,000/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1170万
+$24,078/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 485呎 (2房)
+$1112万
+$22,926/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 491呎 (2房)
+$1116万
+$22,723/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+$1081万
+$22,714/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr"/>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1422呎 (4+房)
+$6086万
+$42,800/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 1559呎 (4+房)
+$7592万
+$48,700/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1084万
+$22,307/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 485呎 (2房)
+$1081万
+$22,287/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 491呎 (2房)
+$1276万
+$25,982/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+$1064万
+$22,357/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr"/>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1422呎 (4+房)
+$5644万
+$39,690/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H11" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 1559呎 (4+房)
+$6715万
+$43,071/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="I11" s="20" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1081万
+$22,251/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 485呎 (2房)
+$1078万
+$22,231/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 491呎 (2房)
+$1082万
+$22,035/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+$1048万
+$22,027/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr"/>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1422呎 (4+房)
+$5431万
+$38,190/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H12" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 1559呎 (4+房)
+$6324万
+$40,565/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="I12" s="20" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1065万
+$21,922/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 485呎 (2房)
+$1128万
+$23,256/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 491呎 (2房)
+$1132万
+$23,051/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+$998万
+$20,958/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr"/>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1422呎 (4+房)
+$5404万
+$38,000/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H13" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 1559呎 (4+房)
+$6018万
+$38,602/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="I13" s="20" t="inlineStr"/>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1046万
+$21,523/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 485呎 (2房)
+$1108万
+$22,847/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 491呎 (2房)
+$1046万
+$21,314/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+$993万
+$20,855/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr"/>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1422呎 (4+房)
+$5494万
+$38,634/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 1559呎 (4+房)
+$6220万
+$39,900/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="I14" s="20" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1040万
+$21,395/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 485呎 (2房)
+$1102万
+$22,713/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 491呎 (2房)
+$1040万
+$21,187/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+$988万
+$20,750/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr"/>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1422呎 (4+房)
+$5052万
+$35,530/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H15" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 1559呎 (4+房)
+$5850万
+$37,525/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="I15" s="20" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1034万
+$21,267/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 485呎 (2房)
+$1030万
+$21,247/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 491呎 (2房)
+$1099万
+$22,377/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+$983万
+$20,647/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr"/>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1422呎 (4+房)
+$4996万
+$35,136/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H16" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 1559呎 (4+房)
+$5791万
+$37,145/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="I16" s="20" t="inlineStr"/>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1027万
+$21,140/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 485呎 (2房)
+$1024万
+$21,122/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 491呎 (2房)
+$1028万
+$20,937/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+$978万
+$20,546/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr"/>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1422呎 (4+房)
+$4839万
+$34,028/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H17" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 1559呎 (4+房)
+$5609万
+$35,977/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr"/>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1083万
+$22,282/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 485呎 (2房)
+$1063万
+$21,915/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 490呎 (2房)
+$1005万
+$20,506/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+$964万
+$20,261/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>E | 455呎 (2房)
+$917万
+$20,160/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 926呎 (3房)
+$3273万
+$35,350/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 860呎 (3房)
+$2726万
+$31,700/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="I18" s="22" t="inlineStr">
+        <is>
+          <t>P3 | 826呎 (3房)
+$2494万
+$30,200/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1015万
+$20,889/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 485呎 (2房)
+$1059万
+$21,829/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 490呎 (2房)
+$1063万
+$21,700/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+$961万
+$20,181/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>E | 455呎 (2房)
+$971万
+$21,334/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 926呎 (3房)
+$3084万
+$33,300/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H19" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 860呎 (3房)
+$2582万
+$30,020/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="I19" s="22" t="inlineStr">
+        <is>
+          <t>P3 | 826呎 (3房)
+$2591万
+$31,368/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1011万
+$20,807/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 485呎 (2房)
+$1054万
+$21,742/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 490呎 (2房)
+$1059万
+$21,614/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+$957万
+$20,101/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>E | 455呎 (2房)
+$910万
+$20,000/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 926呎 (3房)
+$3337万
+$36,040/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 860呎 (3房)
+$2541万
+$29,545/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="I20" s="22" t="inlineStr">
+        <is>
+          <t>P3 | 826呎 (3房)
+$2548万
+$30,850/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1070万
+$22,016/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 485呎 (2房)
+$1050万
+$21,656/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 490呎 (2房)
+$993万
+$20,261/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+$1012万
+$21,271/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>E | 455呎 (2房)
+$906万
+$19,921/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 926呎 (3房)
+$3300万
+$35,639/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H21" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 860呎 (3房)
+$2500万
+$29,070/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="I21" s="22" t="inlineStr">
+        <is>
+          <t>P3 | 826呎 (3房)
+$2519万
+$30,500/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1003万
+$20,640/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 485呎 (2房)
+$984万
+$20,299/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 490呎 (2房)
+$989万
+$20,180/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+$949万
+$19,941/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>E | 455呎 (2房)
+$903万
+$19,842/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G22" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 926呎 (3房)
+$2824万
+$30,495/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 860呎 (3房)
+$2623万
+$30,500/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="I22" s="22" t="inlineStr">
+        <is>
+          <t>P3 | 826呎 (3房)
+$2490万
+$30,150/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1062万
+$21,842/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 485呎 (2房)
+$981万
+$20,219/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 490呎 (2房)
+$985万
+$20,100/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+$945万
+$19,861/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>E | 455呎 (2房)
+$955万
+$20,998/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 926呎 (3房)
+$2784万
+$30,068/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H23" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 860呎 (3房)
+$2487万
+$28,916/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="I23" s="22" t="inlineStr">
+        <is>
+          <t>P3 | 826呎 (3房)
+$2437万
+$29,500/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$983万
+$20,220/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 485呎 (2房)
+$977万
+$20,140/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 490呎 (2房)
+$1042万
+$21,269/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+$942万
+$19,782/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>E | 455呎 (2房)
+$896万
+$19,684/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 926呎 (3房)
+$3217万
+$34,740/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H24" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 860呎 (3房)
+$2482万
+$28,856/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="I24" s="22" t="inlineStr">
+        <is>
+          <t>P3 | 826呎 (3房)
+$2342万
+$28,350/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1053万
+$21,669/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 485呎 (2房)
+$973万
+$20,058/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C | 490呎 (2房)
+$977万
+$19,941/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+$996万
+$20,935/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>E | 455呎 (2房)
+$892万
+$19,604/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 926呎 (3房)
+$3045万
+$32,880/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H25" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 860呎 (3房)
+$2451万
+$28,500/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="I25" s="22" t="inlineStr">
+        <is>
+          <t>P3 | 826呎 (3房)
+$2321万
+$28,100/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$987万
+$20,313/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B | 485呎 (2房)
+$969万
+$19,977/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>C | 490呎 (2房)
+$1034万
+$21,102/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+$934万
+$19,624/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>E | 455呎 (2房)
+$888万
+$19,525/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 926呎 (3房)
+$2727万
+$29,450/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H26" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 860呎 (3房)
+$2426万
+$28,215/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="I26" s="22" t="inlineStr">
+        <is>
+          <t>P3 | 826呎 (3房)
+$2310万
+$27,970/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$983万
+$20,233/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>B | 485呎 (2房)
+$965万
+$19,899/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>C | 490呎 (2房)
+$969万
+$19,780/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+$988万
+$20,767/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
+        <is>
+          <t>E | 455呎 (2房)
+$885万
+$19,448/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G27" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 926呎 (3房)
+$2701万
+$29,165/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H27" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 860呎 (3房)
+$2402万
+$27,930/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="I27" s="22" t="inlineStr">
+        <is>
+          <t>P3 | 826呎 (3房)
+$2294万
+$27,770/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$979万
+$20,152/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>B | 485呎 (2房)
+$949万
+$19,571/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>C | 490呎 (2房)
+$965万
+$19,702/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+$927万
+$19,468/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>E | 455呎 (2房)
+$926万
+$20,341/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G28" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 926呎 (3房)
+$2674万
+$28,880/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H28" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 860呎 (3房)
+$2498万
+$29,041/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="I28" s="22" t="inlineStr">
+        <is>
+          <t>P3 | 826呎 (3房)
+$2277万
+$27,570/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$976万
+$20,072/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>B | 485呎 (2房)
+$957万
+$19,740/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>C | 490呎 (2房)
+$962万
+$19,624/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+$981万
+$20,603/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F29" s="22" t="inlineStr">
+        <is>
+          <t>E | 455呎 (2房)
+$878万
+$19,295/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G29" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 926呎 (3房)
+$2787万
+$30,100/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H29" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 860呎 (3房)
+$2555万
+$29,713/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="I29" s="22" t="inlineStr">
+        <is>
+          <t>P3 | 826呎 (3房)
+$2355万
+$28,511/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1032万
+$21,241/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>B | 485呎 (2房)
+$1013万
+$20,891/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
+        <is>
+          <t>C | 490呎 (2房)
+$1018万
+$20,767/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+$919万
+$19,313/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F30" s="22" t="inlineStr">
+        <is>
+          <t>E | 455呎 (2房)
+$874万
+$19,218/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G30" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 926呎 (3房)
+$2622万
+$28,310/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H30" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 860呎 (3房)
+$2378万
+$27,650/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="I30" s="22" t="inlineStr">
+        <is>
+          <t>P3 | 826呎 (3房)
+$2244万
+$27,169/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1028万
+$21,156/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>B | 485呎 (2房)
+$1009万
+$20,808/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>C | 490呎 (2房)
+$1014万
+$20,686/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+$916万
+$19,235/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F31" s="22" t="inlineStr">
+        <is>
+          <t>E | 455呎 (2房)
+$871万
+$19,141/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G31" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 926呎 (3房)
+$2734万
+$29,526/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="H31" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 860呎 (3房)
+$2382万
+$27,700/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="I31" s="22" t="inlineStr">
+        <is>
+          <t>P3 | 826呎 (3房)
+$2304万
+$27,900/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1024万
+$21,072/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>B | 485呎 (2房)
+$934万
+$19,262/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="inlineStr">
+        <is>
+          <t>C | 490呎 (2房)
+$950万
+$19,390/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E32" s="22" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+$969万
+$20,357/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F32" s="22" t="inlineStr">
+        <is>
+          <t>E | 455呎 (2房)
+$867万
+$19,064/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G32" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 926呎 (3房)
+$2715万
+$29,316/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H32" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 860呎 (3房)
+$2365万
+$27,500/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="I32" s="22" t="inlineStr">
+        <is>
+          <t>P3 | 826呎 (3房)
+$2211万
+$26,770/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1020万
+$20,988/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C33" s="22" t="inlineStr">
+        <is>
+          <t>B | 485呎 (2房)
+$1001万
+$20,643/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D33" s="22" t="inlineStr">
+        <is>
+          <t>C | 490呎 (2房)
+$946万
+$19,314/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E33" s="22" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+$908万
+$19,084/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F33" s="22" t="inlineStr">
+        <is>
+          <t>E | 455呎 (2房)
+$864万
+$18,989/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G33" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 926呎 (3房)
+$2584万
+$27,900/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="H33" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 860呎 (3房)
+$2348万
+$27,300/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="I33" s="22" t="inlineStr">
+        <is>
+          <t>P3 | 826呎 (3房)
+$2272万
+$27,500/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1016万
+$20,905/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>B | 485呎 (2房)
+$938万
+$19,351/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D34" s="22" t="inlineStr">
+        <is>
+          <t>C | 490呎 (2房)
+$943万
+$19,237/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E34" s="22" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+$905万
+$19,008/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F34" s="22" t="inlineStr">
+        <is>
+          <t>E | 455呎 (2房)
+$914万
+$20,095/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G34" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 926呎 (3房)
+$2565万
+$27,700/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H34" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 860呎 (3房)
+$2331万
+$27,100/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="I34" s="22" t="inlineStr">
+        <is>
+          <t>P3 | 826呎 (3房)
+$2296万
+$27,800/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$952万
+$19,597/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C35" s="22" t="inlineStr">
+        <is>
+          <t>B | 485呎 (2房)
+$993万
+$20,478/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="inlineStr">
+        <is>
+          <t>C | 490呎 (2房)
+$939万
+$19,159/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E35" s="22" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+$901万
+$18,933/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F35" s="22" t="inlineStr">
+        <is>
+          <t>E | 455呎 (2房)
+$911万
+$20,013/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G35" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 926呎 (3房)
+$2680万
+$28,947/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H35" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 860呎 (3房)
+$2313万
+$26,895/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="I35" s="22" t="inlineStr">
+        <is>
+          <t>P3 | 826呎 (3房)
+$2280万
+$27,599/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$949万
+$19,519/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C36" s="22" t="inlineStr">
+        <is>
+          <t>B | 485呎 (2房)
+$931万
+$19,196/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D36" s="22" t="inlineStr">
+        <is>
+          <t>C | 490呎 (2房)
+$935万
+$19,084/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E36" s="22" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+$954万
+$20,036/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F36" s="22" t="inlineStr">
+        <is>
+          <t>E | 455呎 (2房)
+$854万
+$18,763/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G36" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 926呎 (3房)
+$2556万
+$27,600/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H36" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 860呎 (3房)
+$2339万
+$27,200/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I36" s="22" t="inlineStr">
+        <is>
+          <t>P3 | 826呎 (3房)
+$2263万
+$27,400/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B37" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$945万
+$19,440/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C37" s="22" t="inlineStr">
+        <is>
+          <t>B | 485呎 (2房)
+$927万
+$19,120/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D37" s="22" t="inlineStr">
+        <is>
+          <t>C | 490呎 (2房)
+$931万
+$19,006/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E37" s="22" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+$894万
+$18,782/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F37" s="22" t="inlineStr">
+        <is>
+          <t>E | 455呎 (2房)
+$850万
+$18,688/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G37" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 926呎 (3房)
+$2574万
+$27,800/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H37" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 860呎 (3房)
+$2365万
+$27,500/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I37" s="22" t="inlineStr">
+        <is>
+          <t>P3 | 826呎 (3房)
+$2247万
+$27,200/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B38" s="22" t="inlineStr">
+        <is>
+          <t>A | 440呎 (2房)
+$1158万
+$26,316/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C38" s="22" t="inlineStr">
+        <is>
+          <t>B | 439呎 (2房)
+$1089万
+$24,800/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D38" s="22" t="inlineStr">
+        <is>
+          <t>C | 444呎 (2房)
+$1092万
+$24,599/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E38" s="22" t="inlineStr">
+        <is>
+          <t>D | 430呎 (2房)
+$1182万
+$27,500/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F38" s="22" t="inlineStr">
+        <is>
+          <t>E | 408呎 (2房)
+$1040万
+$25,500/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G38" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 926呎 (3房)
+$2546万
+$27,499/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H38" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 860呎 (3房)
+$2471万
+$28,737/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I38" s="22" t="inlineStr">
+        <is>
+          <t>P3 | 826呎 (3房)
+$2354万
+$28,500/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/港岛-黄竹坑-滶晨.xlsx
+++ b/files/港岛-黄竹坑-滶晨.xlsx
@@ -262,13 +262,13 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -646,7 +646,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -21480,14 +21480,56 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
+          <t>41&amp;42</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 1020呎 (3房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 1034呎 (3房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 1083呎 (3房)
+$3890万
+$35,921/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr"/>
+      <c r="F5" s="22" t="inlineStr"/>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>P2 | 3120呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H5" s="22" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr"/>
-      <c r="C5" s="20" t="inlineStr"/>
-      <c r="D5" s="20" t="inlineStr"/>
-      <c r="E5" s="20" t="inlineStr"/>
-      <c r="F5" s="21" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr"/>
+      <c r="C6" s="22" t="inlineStr"/>
+      <c r="D6" s="22" t="inlineStr"/>
+      <c r="E6" s="22" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 招标单位
@@ -21495,50 +21537,8 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="G5" s="20" t="inlineStr"/>
-      <c r="H5" s="20" t="inlineStr"/>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>41&amp;42</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>A | 1020呎 (3房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr">
-        <is>
-          <t>B | 1034呎 (3房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D6" s="22" t="inlineStr">
-        <is>
-          <t>C | 1083呎 (3房)
-$3890万
-$35,921/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E6" s="20" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr">
-        <is>
-          <t>P2 | 3120呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H6" s="20" t="inlineStr"/>
+      <c r="G6" s="22" t="inlineStr"/>
+      <c r="H6" s="22" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
@@ -21546,7 +21546,7 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1593万
@@ -21554,7 +21554,7 @@
 (26年-04月)</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1142万
@@ -21562,7 +21562,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1235万
@@ -21570,8 +21570,8 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr"/>
-      <c r="F7" s="21" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 招标单位
@@ -21579,7 +21579,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="G7" s="21" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 招标单位
@@ -21587,7 +21587,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="H7" s="20" t="inlineStr"/>
+      <c r="H7" s="22" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -21595,7 +21595,7 @@
           <t>39</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1566万
@@ -21603,7 +21603,7 @@
 (26年-04月)</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1130万
@@ -21611,7 +21611,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1276万
@@ -21619,8 +21619,8 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr"/>
-      <c r="F8" s="21" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr"/>
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 招标单位
@@ -21628,7 +21628,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="G8" s="22" t="inlineStr">
+      <c r="G8" s="21" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $10775万
@@ -21636,7 +21636,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="H8" s="20" t="inlineStr"/>
+      <c r="H8" s="22" t="inlineStr"/>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -21644,7 +21644,7 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1429万
@@ -21652,7 +21652,7 @@
 (26年-03月)</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1227万
@@ -21660,7 +21660,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1245万
@@ -21668,8 +21668,8 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr"/>
-      <c r="F9" s="22" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr"/>
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $7296万
@@ -21677,7 +21677,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $8530万
@@ -21685,7 +21685,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="H9" s="20" t="inlineStr"/>
+      <c r="H9" s="22" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
@@ -21693,7 +21693,7 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1117万
@@ -21701,7 +21701,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1131万
@@ -21709,7 +21709,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1154万
@@ -21717,8 +21717,8 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr"/>
-      <c r="F10" s="22" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr"/>
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $6543万
@@ -21726,7 +21726,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="G10" s="22" t="inlineStr">
+      <c r="G10" s="21" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $8189万
@@ -21734,7 +21734,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="H10" s="20" t="inlineStr"/>
+      <c r="H10" s="22" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -21742,7 +21742,7 @@
           <t>36</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1086万
@@ -21750,7 +21750,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1100万
@@ -21758,7 +21758,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D11" s="22" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1217万
@@ -21766,8 +21766,8 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr"/>
-      <c r="F11" s="22" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr"/>
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $6420万
@@ -21775,7 +21775,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="G11" s="22" t="inlineStr">
+      <c r="G11" s="21" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $7558万
@@ -21783,7 +21783,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="H11" s="20" t="inlineStr"/>
+      <c r="H11" s="22" t="inlineStr"/>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
@@ -21791,7 +21791,7 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1083万
@@ -21799,7 +21799,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1097万
@@ -21807,7 +21807,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D12" s="22" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1137万
@@ -21815,8 +21815,8 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E12" s="20" t="inlineStr"/>
-      <c r="F12" s="22" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr"/>
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $6298万
@@ -21824,7 +21824,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="G12" s="22" t="inlineStr">
+      <c r="G12" s="21" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $7421万
@@ -21832,7 +21832,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="H12" s="20" t="inlineStr"/>
+      <c r="H12" s="22" t="inlineStr"/>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -21840,7 +21840,7 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1067万
@@ -21848,7 +21848,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1081万
@@ -21856,7 +21856,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D13" s="22" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1128万
@@ -21864,8 +21864,8 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E13" s="20" t="inlineStr"/>
-      <c r="F13" s="22" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr"/>
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $6089万
@@ -21873,7 +21873,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="G13" s="22" t="inlineStr">
+      <c r="G13" s="21" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $7319万
@@ -21881,7 +21881,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="H13" s="20" t="inlineStr"/>
+      <c r="H13" s="22" t="inlineStr"/>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -21889,7 +21889,7 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1048万
@@ -21897,7 +21897,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1061万
@@ -21905,7 +21905,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1123万
@@ -21913,8 +21913,8 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E14" s="20" t="inlineStr"/>
-      <c r="F14" s="22" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr"/>
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $5990万
@@ -21922,7 +21922,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="G14" s="22" t="inlineStr">
+      <c r="G14" s="21" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $6726万
@@ -21930,7 +21930,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="H14" s="20" t="inlineStr"/>
+      <c r="H14" s="22" t="inlineStr"/>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
@@ -21938,7 +21938,7 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1107万
@@ -21946,7 +21946,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1055万
@@ -21954,7 +21954,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D15" s="22" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1187万
@@ -21962,8 +21962,8 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr"/>
-      <c r="F15" s="22" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr"/>
+      <c r="F15" s="21" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $5574万
@@ -21971,7 +21971,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="G15" s="22" t="inlineStr">
+      <c r="G15" s="21" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $6596万
@@ -21979,7 +21979,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="H15" s="20" t="inlineStr"/>
+      <c r="H15" s="22" t="inlineStr"/>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
@@ -21987,7 +21987,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1100万
@@ -21995,7 +21995,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C16" s="22" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1114万
@@ -22003,7 +22003,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1112万
@@ -22011,8 +22011,8 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E16" s="20" t="inlineStr"/>
-      <c r="F16" s="22" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr"/>
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $5076万
@@ -22020,7 +22020,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="G16" s="22" t="inlineStr">
+      <c r="G16" s="21" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $6467万
@@ -22028,7 +22028,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="H16" s="20" t="inlineStr"/>
+      <c r="H16" s="22" t="inlineStr"/>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
@@ -22036,7 +22036,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1094万
@@ -22044,7 +22044,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1108万
@@ -22052,7 +22052,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D17" s="22" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1175万
@@ -22060,8 +22060,8 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E17" s="20" t="inlineStr"/>
-      <c r="F17" s="22" t="inlineStr">
+      <c r="E17" s="22" t="inlineStr"/>
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t>P1 | 1469呎 (4+房)
 $5739万
@@ -22069,7 +22069,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="G17" s="22" t="inlineStr">
+      <c r="G17" s="21" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $6739万
@@ -22077,7 +22077,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="H17" s="20" t="inlineStr"/>
+      <c r="H17" s="22" t="inlineStr"/>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
@@ -22085,7 +22085,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1025万
@@ -22093,7 +22093,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1036万
@@ -22101,7 +22101,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D18" s="22" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1084万
@@ -22109,7 +22109,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E18" s="22" t="inlineStr">
+      <c r="E18" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $1011万
@@ -22117,7 +22117,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F18" s="22" t="inlineStr">
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t>P1 | 1258呎 (4+房)
 $4422万
@@ -22125,7 +22125,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="G18" s="22" t="inlineStr">
+      <c r="G18" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2694万
@@ -22133,7 +22133,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="H18" s="22" t="inlineStr">
+      <c r="H18" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3313万
@@ -22148,7 +22148,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B19" s="22" t="inlineStr">
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1021万
@@ -22156,7 +22156,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1032万
@@ -22164,7 +22164,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D19" s="22" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1066万
@@ -22172,7 +22172,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E19" s="22" t="inlineStr">
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $1005万
@@ -22180,7 +22180,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F19" s="22" t="inlineStr">
+      <c r="F19" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4351万
@@ -22188,7 +22188,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="G19" s="22" t="inlineStr">
+      <c r="G19" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2653万
@@ -22196,7 +22196,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="H19" s="22" t="inlineStr">
+      <c r="H19" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3447万
@@ -22211,7 +22211,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B20" s="22" t="inlineStr">
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1017万
@@ -22219,7 +22219,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C20" s="22" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1028万
@@ -22227,7 +22227,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D20" s="22" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1076万
@@ -22235,7 +22235,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E20" s="22" t="inlineStr">
+      <c r="E20" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $999万
@@ -22243,7 +22243,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F20" s="22" t="inlineStr">
+      <c r="F20" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4540万
@@ -22251,7 +22251,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="G20" s="22" t="inlineStr">
+      <c r="G20" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2612万
@@ -22259,7 +22259,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="H20" s="22" t="inlineStr">
+      <c r="H20" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3256万
@@ -22274,7 +22274,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B21" s="22" t="inlineStr">
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1013万
@@ -22282,7 +22282,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C21" s="22" t="inlineStr">
+      <c r="C21" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1024万
@@ -22290,7 +22290,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D21" s="22" t="inlineStr">
+      <c r="D21" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1138万
@@ -22298,7 +22298,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E21" s="22" t="inlineStr">
+      <c r="E21" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $993万
@@ -22306,7 +22306,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F21" s="22" t="inlineStr">
+      <c r="F21" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4265万
@@ -22314,7 +22314,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="G21" s="22" t="inlineStr">
+      <c r="G21" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2579万
@@ -22322,7 +22322,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="H21" s="22" t="inlineStr">
+      <c r="H21" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3220万
@@ -22337,7 +22337,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1009万
@@ -22345,7 +22345,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C22" s="22" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1020万
@@ -22353,7 +22353,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D22" s="22" t="inlineStr">
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1067万
@@ -22361,7 +22361,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E22" s="22" t="inlineStr">
+      <c r="E22" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $987万
@@ -22369,7 +22369,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F22" s="22" t="inlineStr">
+      <c r="F22" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4229万
@@ -22377,7 +22377,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="G22" s="22" t="inlineStr">
+      <c r="G22" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2688万
@@ -22385,7 +22385,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="H22" s="22" t="inlineStr">
+      <c r="H22" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3056万
@@ -22400,7 +22400,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1005万
@@ -22408,7 +22408,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C23" s="22" t="inlineStr">
+      <c r="C23" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1079万
@@ -22416,7 +22416,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D23" s="22" t="inlineStr">
+      <c r="D23" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1063万
@@ -22424,7 +22424,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E23" s="22" t="inlineStr">
+      <c r="E23" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $984万
@@ -22432,7 +22432,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F23" s="22" t="inlineStr">
+      <c r="F23" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4193万
@@ -22440,7 +22440,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="G23" s="22" t="inlineStr">
+      <c r="G23" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2529万
@@ -22448,7 +22448,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="H23" s="22" t="inlineStr">
+      <c r="H23" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2876万
@@ -22463,7 +22463,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1001万
@@ -22471,7 +22471,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C24" s="22" t="inlineStr">
+      <c r="C24" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1008万
@@ -22479,7 +22479,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D24" s="22" t="inlineStr">
+      <c r="D24" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1059万
@@ -22487,7 +22487,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E24" s="22" t="inlineStr">
+      <c r="E24" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $980万
@@ -22495,7 +22495,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F24" s="22" t="inlineStr">
+      <c r="F24" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4184万
@@ -22503,7 +22503,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="G24" s="22" t="inlineStr">
+      <c r="G24" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2504万
@@ -22511,7 +22511,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="H24" s="22" t="inlineStr">
+      <c r="H24" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3299万
@@ -22526,7 +22526,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $997万
@@ -22534,7 +22534,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C25" s="22" t="inlineStr">
+      <c r="C25" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1004万
@@ -22542,7 +22542,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D25" s="22" t="inlineStr">
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1113万
@@ -22550,7 +22550,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E25" s="22" t="inlineStr">
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $1037万
@@ -22558,7 +22558,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F25" s="22" t="inlineStr">
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4374万
@@ -22566,7 +22566,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="G25" s="22" t="inlineStr">
+      <c r="G25" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2480万
@@ -22574,7 +22574,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="H25" s="22" t="inlineStr">
+      <c r="H25" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3122万
@@ -22589,7 +22589,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B26" s="22" t="inlineStr">
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $993万
@@ -22597,7 +22597,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C26" s="22" t="inlineStr">
+      <c r="C26" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1000万
@@ -22605,7 +22605,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D26" s="22" t="inlineStr">
+      <c r="D26" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1043万
@@ -22613,7 +22613,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E26" s="22" t="inlineStr">
+      <c r="E26" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $972万
@@ -22621,7 +22621,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F26" s="22" t="inlineStr">
+      <c r="F26" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3725万
@@ -22629,7 +22629,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="G26" s="22" t="inlineStr">
+      <c r="G26" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2406万
@@ -22637,7 +22637,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="H26" s="22" t="inlineStr">
+      <c r="H26" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2893万
@@ -22652,7 +22652,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B27" s="22" t="inlineStr">
+      <c r="B27" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $989万
@@ -22660,7 +22660,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C27" s="22" t="inlineStr">
+      <c r="C27" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $996万
@@ -22668,7 +22668,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D27" s="22" t="inlineStr">
+      <c r="D27" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1039万
@@ -22676,7 +22676,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E27" s="22" t="inlineStr">
+      <c r="E27" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $968万
@@ -22684,7 +22684,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F27" s="22" t="inlineStr">
+      <c r="F27" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3680万
@@ -22692,7 +22692,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="G27" s="22" t="inlineStr">
+      <c r="G27" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2526万
@@ -22700,7 +22700,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="H27" s="22" t="inlineStr">
+      <c r="H27" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2850万
@@ -22715,7 +22715,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B28" s="22" t="inlineStr">
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $985万
@@ -22723,7 +22723,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C28" s="22" t="inlineStr">
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $992万
@@ -22731,7 +22731,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D28" s="22" t="inlineStr">
+      <c r="D28" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1022万
@@ -22739,7 +22739,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E28" s="22" t="inlineStr">
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $1024万
@@ -22747,7 +22747,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F28" s="22" t="inlineStr">
+      <c r="F28" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3955万
@@ -22755,7 +22755,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="G28" s="22" t="inlineStr">
+      <c r="G28" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2349万
@@ -22763,7 +22763,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="H28" s="22" t="inlineStr">
+      <c r="H28" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2652万
@@ -22778,7 +22778,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B29" s="22" t="inlineStr">
+      <c r="B29" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $981万
@@ -22786,7 +22786,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C29" s="22" t="inlineStr">
+      <c r="C29" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1049万
@@ -22794,7 +22794,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D29" s="22" t="inlineStr">
+      <c r="D29" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1095万
@@ -22802,7 +22802,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E29" s="22" t="inlineStr">
+      <c r="E29" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $948万
@@ -22810,7 +22810,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F29" s="22" t="inlineStr">
+      <c r="F29" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3818万
@@ -22818,7 +22818,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="G29" s="22" t="inlineStr">
+      <c r="G29" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2319万
@@ -22826,7 +22826,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="H29" s="22" t="inlineStr">
+      <c r="H29" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2784万
@@ -22841,7 +22841,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B30" s="22" t="inlineStr">
+      <c r="B30" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1038万
@@ -22849,7 +22849,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C30" s="22" t="inlineStr">
+      <c r="C30" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1045万
@@ -22857,7 +22857,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D30" s="22" t="inlineStr">
+      <c r="D30" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1091万
@@ -22865,7 +22865,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E30" s="22" t="inlineStr">
+      <c r="E30" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $956万
@@ -22873,7 +22873,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F30" s="22" t="inlineStr">
+      <c r="F30" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3862万
@@ -22881,7 +22881,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="G30" s="22" t="inlineStr">
+      <c r="G30" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2396万
@@ -22889,7 +22889,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="H30" s="22" t="inlineStr">
+      <c r="H30" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2708万
@@ -22904,7 +22904,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B31" s="22" t="inlineStr">
+      <c r="B31" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1034万
@@ -22912,7 +22912,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C31" s="22" t="inlineStr">
+      <c r="C31" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1041万
@@ -22920,7 +22920,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D31" s="22" t="inlineStr">
+      <c r="D31" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1086万
@@ -22928,7 +22928,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E31" s="22" t="inlineStr">
+      <c r="E31" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $952万
@@ -22936,7 +22936,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F31" s="22" t="inlineStr">
+      <c r="F31" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3819万
@@ -22944,7 +22944,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="G31" s="22" t="inlineStr">
+      <c r="G31" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2361万
@@ -22952,7 +22952,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="H31" s="22" t="inlineStr">
+      <c r="H31" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2668万
@@ -22967,7 +22967,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B32" s="22" t="inlineStr">
+      <c r="B32" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1030万
@@ -22975,7 +22975,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C32" s="22" t="inlineStr">
+      <c r="C32" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $976万
@@ -22983,7 +22983,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D32" s="22" t="inlineStr">
+      <c r="D32" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1006万
@@ -22991,7 +22991,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E32" s="22" t="inlineStr">
+      <c r="E32" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $949万
@@ -22999,7 +22999,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F32" s="22" t="inlineStr">
+      <c r="F32" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3785万
@@ -23007,7 +23007,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="G32" s="22" t="inlineStr">
+      <c r="G32" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2338万
@@ -23015,7 +23015,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="H32" s="22" t="inlineStr">
+      <c r="H32" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2641万
@@ -23030,7 +23030,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B33" s="22" t="inlineStr">
+      <c r="B33" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1026万
@@ -23038,7 +23038,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C33" s="22" t="inlineStr">
+      <c r="C33" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1033万
@@ -23046,7 +23046,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D33" s="22" t="inlineStr">
+      <c r="D33" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1014万
@@ -23054,7 +23054,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E33" s="22" t="inlineStr">
+      <c r="E33" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $945万
@@ -23062,7 +23062,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F33" s="22" t="inlineStr">
+      <c r="F33" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3474万
@@ -23070,7 +23070,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="G33" s="22" t="inlineStr">
+      <c r="G33" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2306万
@@ -23078,7 +23078,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="H33" s="22" t="inlineStr">
+      <c r="H33" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2578万
@@ -23093,7 +23093,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B34" s="22" t="inlineStr">
+      <c r="B34" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $962万
@@ -23101,7 +23101,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C34" s="22" t="inlineStr">
+      <c r="C34" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $968万
@@ -23109,7 +23109,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D34" s="22" t="inlineStr">
+      <c r="D34" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1010万
@@ -23117,7 +23117,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E34" s="22" t="inlineStr">
+      <c r="E34" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $938万
@@ -23125,7 +23125,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F34" s="22" t="inlineStr">
+      <c r="F34" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3632万
@@ -23133,7 +23133,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="G34" s="22" t="inlineStr">
+      <c r="G34" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2392万
@@ -23141,7 +23141,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="H34" s="22" t="inlineStr">
+      <c r="H34" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2586万
@@ -23156,7 +23156,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B35" s="22" t="inlineStr">
+      <c r="B35" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1018万
@@ -23164,7 +23164,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C35" s="22" t="inlineStr">
+      <c r="C35" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $964万
@@ -23172,7 +23172,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D35" s="22" t="inlineStr">
+      <c r="D35" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1069万
@@ -23180,7 +23180,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E35" s="22" t="inlineStr">
+      <c r="E35" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $928万
@@ -23188,7 +23188,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F35" s="22" t="inlineStr">
+      <c r="F35" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3426万
@@ -23196,7 +23196,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="G35" s="22" t="inlineStr">
+      <c r="G35" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2399万
@@ -23204,7 +23204,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="H35" s="22" t="inlineStr">
+      <c r="H35" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2675万
@@ -23219,7 +23219,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B36" s="22" t="inlineStr">
+      <c r="B36" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1014万
@@ -23227,7 +23227,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C36" s="22" t="inlineStr">
+      <c r="C36" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $960万
@@ -23235,7 +23235,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D36" s="22" t="inlineStr">
+      <c r="D36" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1002万
@@ -23243,7 +23243,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E36" s="22" t="inlineStr">
+      <c r="E36" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $976万
@@ -23251,7 +23251,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F36" s="22" t="inlineStr">
+      <c r="F36" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3881万
@@ -23259,7 +23259,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="G36" s="22" t="inlineStr">
+      <c r="G36" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2314万
@@ -23267,7 +23267,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="H36" s="22" t="inlineStr">
+      <c r="H36" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2570万
@@ -23282,7 +23282,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B37" s="22" t="inlineStr">
+      <c r="B37" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1010万
@@ -23290,7 +23290,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C37" s="22" t="inlineStr">
+      <c r="C37" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $957万
@@ -23298,7 +23298,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D37" s="22" t="inlineStr">
+      <c r="D37" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $998万
@@ -23306,7 +23306,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E37" s="22" t="inlineStr">
+      <c r="E37" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $910万
@@ -23314,7 +23314,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F37" s="22" t="inlineStr">
+      <c r="F37" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3577万
@@ -23322,7 +23322,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="G37" s="22" t="inlineStr">
+      <c r="G37" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2490万
@@ -23330,7 +23330,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="H37" s="22" t="inlineStr">
+      <c r="H37" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2686万
@@ -23345,7 +23345,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B38" s="22" t="inlineStr">
+      <c r="B38" s="21" t="inlineStr">
         <is>
           <t>A | 440呎 (2房)
 $1088万
@@ -23353,7 +23353,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C38" s="22" t="inlineStr">
+      <c r="C38" s="21" t="inlineStr">
         <is>
           <t>B | 448呎 (2房)
 $1120万
@@ -23361,7 +23361,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D38" s="22" t="inlineStr">
+      <c r="D38" s="21" t="inlineStr">
         <is>
           <t>C | 467呎 (2房)
 $1238万
@@ -23369,7 +23369,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E38" s="22" t="inlineStr">
+      <c r="E38" s="21" t="inlineStr">
         <is>
           <t>D | 430呎 (2房)
 $999万
@@ -23377,7 +23377,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F38" s="22" t="inlineStr">
+      <c r="F38" s="21" t="inlineStr">
         <is>
           <t>P1 | 1162呎 (4+房)
 $3650万
@@ -23385,7 +23385,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="G38" s="22" t="inlineStr">
+      <c r="G38" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2436万
@@ -23393,7 +23393,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="H38" s="22" t="inlineStr">
+      <c r="H38" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2758万
@@ -23552,15 +23552,65 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
+          <t>41&amp;42</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>A | 1020呎 (3房)
+$3652万
+$35,800/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 1016呎 (3房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 1029呎 (3房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 1083呎 (3房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr"/>
+      <c r="G5" s="22" t="inlineStr"/>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>P2 | 2871呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="I5" s="22" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr"/>
-      <c r="C5" s="20" t="inlineStr"/>
-      <c r="D5" s="20" t="inlineStr"/>
-      <c r="E5" s="20" t="inlineStr"/>
-      <c r="F5" s="20" t="inlineStr"/>
-      <c r="G5" s="21" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr"/>
+      <c r="C6" s="22" t="inlineStr"/>
+      <c r="D6" s="22" t="inlineStr"/>
+      <c r="E6" s="22" t="inlineStr"/>
+      <c r="F6" s="22" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>P1 | 1417呎 (4+房)
 招标单位
@@ -23568,58 +23618,8 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="H5" s="20" t="inlineStr"/>
-      <c r="I5" s="20" t="inlineStr"/>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>41&amp;42</t>
-        </is>
-      </c>
-      <c r="B6" s="22" t="inlineStr">
-        <is>
-          <t>A | 1020呎 (3房)
-$3652万
-$35,800/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr">
-        <is>
-          <t>B | 1016呎 (3房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t>C | 1029呎 (3房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E6" s="21" t="inlineStr">
-        <is>
-          <t>D | 1083呎 (3房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t>P2 | 2871呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="I6" s="20" t="inlineStr"/>
+      <c r="H6" s="22" t="inlineStr"/>
+      <c r="I6" s="22" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
@@ -23627,7 +23627,7 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1245万
@@ -23635,7 +23635,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1138万
@@ -23643,7 +23643,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1137万
@@ -23651,7 +23651,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E7" s="21" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1804万
@@ -23659,8 +23659,8 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="F7" s="20" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr">
+      <c r="F7" s="22" t="inlineStr"/>
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 招标单位
@@ -23668,7 +23668,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="H7" s="21" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 招标单位
@@ -23676,7 +23676,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="I7" s="20" t="inlineStr"/>
+      <c r="I7" s="22" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -23684,7 +23684,7 @@
           <t>39</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1180万
@@ -23692,7 +23692,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1556万
@@ -23700,7 +23700,7 @@
 (26年-04月)</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1196万
@@ -23708,7 +23708,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr">
+      <c r="E8" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1532万
@@ -23716,8 +23716,8 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="F8" s="20" t="inlineStr"/>
-      <c r="G8" s="21" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr"/>
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 招标单位
@@ -23725,7 +23725,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="H8" s="21" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 招标单位
@@ -23733,7 +23733,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="I8" s="20" t="inlineStr"/>
+      <c r="I8" s="22" t="inlineStr"/>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -23741,7 +23741,7 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1543万
@@ -23749,7 +23749,7 @@
 (26年-04月)</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1169万
@@ -23757,7 +23757,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1174万
@@ -23765,7 +23765,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1137万
@@ -23773,8 +23773,8 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F9" s="20" t="inlineStr"/>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="F9" s="22" t="inlineStr"/>
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $6754万
@@ -23782,7 +23782,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="H9" s="22" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $8574万
@@ -23790,7 +23790,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="I9" s="20" t="inlineStr"/>
+      <c r="I9" s="22" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
@@ -23798,7 +23798,7 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1170万
@@ -23806,7 +23806,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1112万
@@ -23814,7 +23814,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1116万
@@ -23822,7 +23822,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E10" s="22" t="inlineStr">
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1081万
@@ -23830,8 +23830,8 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F10" s="20" t="inlineStr"/>
-      <c r="G10" s="22" t="inlineStr">
+      <c r="F10" s="22" t="inlineStr"/>
+      <c r="G10" s="21" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $6086万
@@ -23839,7 +23839,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="H10" s="22" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $7592万
@@ -23847,7 +23847,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="I10" s="20" t="inlineStr"/>
+      <c r="I10" s="22" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -23855,7 +23855,7 @@
           <t>36</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1084万
@@ -23863,7 +23863,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1081万
@@ -23871,7 +23871,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D11" s="22" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1276万
@@ -23879,7 +23879,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1064万
@@ -23887,8 +23887,8 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="F11" s="20" t="inlineStr"/>
-      <c r="G11" s="22" t="inlineStr">
+      <c r="F11" s="22" t="inlineStr"/>
+      <c r="G11" s="21" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $5644万
@@ -23896,7 +23896,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="H11" s="22" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $6715万
@@ -23904,7 +23904,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="I11" s="20" t="inlineStr"/>
+      <c r="I11" s="22" t="inlineStr"/>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
@@ -23912,7 +23912,7 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1081万
@@ -23920,7 +23920,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1078万
@@ -23928,7 +23928,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D12" s="22" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1082万
@@ -23936,7 +23936,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1048万
@@ -23944,8 +23944,8 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F12" s="20" t="inlineStr"/>
-      <c r="G12" s="22" t="inlineStr">
+      <c r="F12" s="22" t="inlineStr"/>
+      <c r="G12" s="21" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $5431万
@@ -23953,7 +23953,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="H12" s="22" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $6324万
@@ -23961,7 +23961,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="I12" s="20" t="inlineStr"/>
+      <c r="I12" s="22" t="inlineStr"/>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -23969,7 +23969,7 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1065万
@@ -23977,7 +23977,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1128万
@@ -23985,7 +23985,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D13" s="22" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1132万
@@ -23993,7 +23993,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E13" s="22" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $998万
@@ -24001,8 +24001,8 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F13" s="20" t="inlineStr"/>
-      <c r="G13" s="22" t="inlineStr">
+      <c r="F13" s="22" t="inlineStr"/>
+      <c r="G13" s="21" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $5404万
@@ -24010,7 +24010,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="H13" s="22" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $6018万
@@ -24018,7 +24018,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="I13" s="20" t="inlineStr"/>
+      <c r="I13" s="22" t="inlineStr"/>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -24026,7 +24026,7 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1046万
@@ -24034,7 +24034,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1108万
@@ -24042,7 +24042,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1046万
@@ -24050,7 +24050,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E14" s="22" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $993万
@@ -24058,8 +24058,8 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F14" s="20" t="inlineStr"/>
-      <c r="G14" s="22" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr"/>
+      <c r="G14" s="21" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $5494万
@@ -24067,7 +24067,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="H14" s="22" t="inlineStr">
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $6220万
@@ -24075,7 +24075,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="I14" s="20" t="inlineStr"/>
+      <c r="I14" s="22" t="inlineStr"/>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
@@ -24083,7 +24083,7 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1040万
@@ -24091,7 +24091,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1102万
@@ -24099,7 +24099,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D15" s="22" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1040万
@@ -24107,7 +24107,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E15" s="22" t="inlineStr">
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $988万
@@ -24115,8 +24115,8 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F15" s="20" t="inlineStr"/>
-      <c r="G15" s="22" t="inlineStr">
+      <c r="F15" s="22" t="inlineStr"/>
+      <c r="G15" s="21" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $5052万
@@ -24124,7 +24124,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="H15" s="22" t="inlineStr">
+      <c r="H15" s="21" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $5850万
@@ -24132,7 +24132,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="I15" s="20" t="inlineStr"/>
+      <c r="I15" s="22" t="inlineStr"/>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
@@ -24140,7 +24140,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1034万
@@ -24148,7 +24148,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C16" s="22" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1030万
@@ -24156,7 +24156,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1099万
@@ -24164,7 +24164,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E16" s="22" t="inlineStr">
+      <c r="E16" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $983万
@@ -24172,8 +24172,8 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F16" s="20" t="inlineStr"/>
-      <c r="G16" s="22" t="inlineStr">
+      <c r="F16" s="22" t="inlineStr"/>
+      <c r="G16" s="21" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $4996万
@@ -24181,7 +24181,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="H16" s="22" t="inlineStr">
+      <c r="H16" s="21" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $5791万
@@ -24189,7 +24189,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="I16" s="20" t="inlineStr"/>
+      <c r="I16" s="22" t="inlineStr"/>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
@@ -24197,7 +24197,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1027万
@@ -24205,7 +24205,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1024万
@@ -24213,7 +24213,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D17" s="22" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1028万
@@ -24221,7 +24221,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E17" s="22" t="inlineStr">
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $978万
@@ -24229,8 +24229,8 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F17" s="20" t="inlineStr"/>
-      <c r="G17" s="22" t="inlineStr">
+      <c r="F17" s="22" t="inlineStr"/>
+      <c r="G17" s="21" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $4839万
@@ -24238,7 +24238,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="H17" s="22" t="inlineStr">
+      <c r="H17" s="21" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $5609万
@@ -24246,7 +24246,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="I17" s="20" t="inlineStr"/>
+      <c r="I17" s="22" t="inlineStr"/>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
@@ -24254,7 +24254,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1083万
@@ -24262,7 +24262,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1063万
@@ -24270,7 +24270,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D18" s="22" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1005万
@@ -24278,7 +24278,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E18" s="22" t="inlineStr">
+      <c r="E18" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $964万
@@ -24286,7 +24286,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F18" s="22" t="inlineStr">
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $917万
@@ -24294,7 +24294,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="G18" s="22" t="inlineStr">
+      <c r="G18" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $3273万
@@ -24302,7 +24302,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="H18" s="22" t="inlineStr">
+      <c r="H18" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2726万
@@ -24310,7 +24310,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="I18" s="22" t="inlineStr">
+      <c r="I18" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2494万
@@ -24325,7 +24325,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B19" s="22" t="inlineStr">
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1015万
@@ -24333,7 +24333,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1059万
@@ -24341,7 +24341,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D19" s="22" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1063万
@@ -24349,7 +24349,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E19" s="22" t="inlineStr">
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $961万
@@ -24357,7 +24357,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F19" s="22" t="inlineStr">
+      <c r="F19" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $971万
@@ -24365,7 +24365,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="G19" s="22" t="inlineStr">
+      <c r="G19" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $3084万
@@ -24373,7 +24373,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="H19" s="22" t="inlineStr">
+      <c r="H19" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2582万
@@ -24381,7 +24381,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="I19" s="22" t="inlineStr">
+      <c r="I19" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2591万
@@ -24396,7 +24396,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B20" s="22" t="inlineStr">
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1011万
@@ -24404,7 +24404,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C20" s="22" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1054万
@@ -24412,7 +24412,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D20" s="22" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1059万
@@ -24420,7 +24420,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E20" s="22" t="inlineStr">
+      <c r="E20" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $957万
@@ -24428,7 +24428,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F20" s="22" t="inlineStr">
+      <c r="F20" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $910万
@@ -24436,7 +24436,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="G20" s="22" t="inlineStr">
+      <c r="G20" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $3337万
@@ -24444,7 +24444,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="H20" s="22" t="inlineStr">
+      <c r="H20" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2541万
@@ -24452,7 +24452,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="I20" s="22" t="inlineStr">
+      <c r="I20" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2548万
@@ -24467,7 +24467,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B21" s="22" t="inlineStr">
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1070万
@@ -24475,7 +24475,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C21" s="22" t="inlineStr">
+      <c r="C21" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1050万
@@ -24483,7 +24483,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D21" s="22" t="inlineStr">
+      <c r="D21" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $993万
@@ -24491,7 +24491,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="E21" s="22" t="inlineStr">
+      <c r="E21" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1012万
@@ -24499,7 +24499,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F21" s="22" t="inlineStr">
+      <c r="F21" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $906万
@@ -24507,7 +24507,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="G21" s="22" t="inlineStr">
+      <c r="G21" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $3300万
@@ -24515,7 +24515,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="H21" s="22" t="inlineStr">
+      <c r="H21" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2500万
@@ -24523,7 +24523,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="I21" s="22" t="inlineStr">
+      <c r="I21" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2519万
@@ -24538,7 +24538,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1003万
@@ -24546,7 +24546,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C22" s="22" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $984万
@@ -24554,7 +24554,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D22" s="22" t="inlineStr">
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $989万
@@ -24562,7 +24562,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E22" s="22" t="inlineStr">
+      <c r="E22" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $949万
@@ -24570,7 +24570,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F22" s="22" t="inlineStr">
+      <c r="F22" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $903万
@@ -24578,7 +24578,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="G22" s="22" t="inlineStr">
+      <c r="G22" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2824万
@@ -24586,7 +24586,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="H22" s="22" t="inlineStr">
+      <c r="H22" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2623万
@@ -24594,7 +24594,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="I22" s="22" t="inlineStr">
+      <c r="I22" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2490万
@@ -24609,7 +24609,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1062万
@@ -24617,7 +24617,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C23" s="22" t="inlineStr">
+      <c r="C23" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $981万
@@ -24625,7 +24625,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D23" s="22" t="inlineStr">
+      <c r="D23" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $985万
@@ -24633,7 +24633,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E23" s="22" t="inlineStr">
+      <c r="E23" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $945万
@@ -24641,7 +24641,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F23" s="22" t="inlineStr">
+      <c r="F23" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $955万
@@ -24649,7 +24649,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="G23" s="22" t="inlineStr">
+      <c r="G23" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2784万
@@ -24657,7 +24657,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="H23" s="22" t="inlineStr">
+      <c r="H23" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2487万
@@ -24665,7 +24665,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="I23" s="22" t="inlineStr">
+      <c r="I23" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2437万
@@ -24680,7 +24680,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $983万
@@ -24688,7 +24688,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C24" s="22" t="inlineStr">
+      <c r="C24" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $977万
@@ -24696,7 +24696,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D24" s="22" t="inlineStr">
+      <c r="D24" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1042万
@@ -24704,7 +24704,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E24" s="22" t="inlineStr">
+      <c r="E24" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $942万
@@ -24712,7 +24712,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F24" s="22" t="inlineStr">
+      <c r="F24" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $896万
@@ -24720,7 +24720,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="G24" s="22" t="inlineStr">
+      <c r="G24" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $3217万
@@ -24728,7 +24728,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="H24" s="22" t="inlineStr">
+      <c r="H24" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2482万
@@ -24736,7 +24736,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="I24" s="22" t="inlineStr">
+      <c r="I24" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2342万
@@ -24751,7 +24751,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1053万
@@ -24759,7 +24759,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C25" s="22" t="inlineStr">
+      <c r="C25" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $973万
@@ -24767,7 +24767,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D25" s="22" t="inlineStr">
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $977万
@@ -24775,7 +24775,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E25" s="22" t="inlineStr">
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $996万
@@ -24783,7 +24783,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F25" s="22" t="inlineStr">
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $892万
@@ -24791,7 +24791,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="G25" s="22" t="inlineStr">
+      <c r="G25" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $3045万
@@ -24799,7 +24799,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="H25" s="22" t="inlineStr">
+      <c r="H25" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2451万
@@ -24807,7 +24807,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="I25" s="22" t="inlineStr">
+      <c r="I25" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2321万
@@ -24822,7 +24822,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B26" s="22" t="inlineStr">
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $987万
@@ -24830,7 +24830,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="C26" s="22" t="inlineStr">
+      <c r="C26" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $969万
@@ -24838,7 +24838,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D26" s="22" t="inlineStr">
+      <c r="D26" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1034万
@@ -24846,7 +24846,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E26" s="22" t="inlineStr">
+      <c r="E26" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $934万
@@ -24854,7 +24854,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="F26" s="22" t="inlineStr">
+      <c r="F26" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $888万
@@ -24862,7 +24862,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="G26" s="22" t="inlineStr">
+      <c r="G26" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2727万
@@ -24870,7 +24870,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="H26" s="22" t="inlineStr">
+      <c r="H26" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2426万
@@ -24878,7 +24878,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="I26" s="22" t="inlineStr">
+      <c r="I26" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2310万
@@ -24893,7 +24893,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B27" s="22" t="inlineStr">
+      <c r="B27" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $983万
@@ -24901,7 +24901,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C27" s="22" t="inlineStr">
+      <c r="C27" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $965万
@@ -24909,7 +24909,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D27" s="22" t="inlineStr">
+      <c r="D27" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $969万
@@ -24917,7 +24917,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E27" s="22" t="inlineStr">
+      <c r="E27" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $988万
@@ -24925,7 +24925,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F27" s="22" t="inlineStr">
+      <c r="F27" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $885万
@@ -24933,7 +24933,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="G27" s="22" t="inlineStr">
+      <c r="G27" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2701万
@@ -24941,7 +24941,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="H27" s="22" t="inlineStr">
+      <c r="H27" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2402万
@@ -24949,7 +24949,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="I27" s="22" t="inlineStr">
+      <c r="I27" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2294万
@@ -24964,7 +24964,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B28" s="22" t="inlineStr">
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $979万
@@ -24972,7 +24972,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C28" s="22" t="inlineStr">
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $949万
@@ -24980,7 +24980,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D28" s="22" t="inlineStr">
+      <c r="D28" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $965万
@@ -24988,7 +24988,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E28" s="22" t="inlineStr">
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $927万
@@ -24996,7 +24996,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F28" s="22" t="inlineStr">
+      <c r="F28" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $926万
@@ -25004,7 +25004,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="G28" s="22" t="inlineStr">
+      <c r="G28" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2674万
@@ -25012,7 +25012,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="H28" s="22" t="inlineStr">
+      <c r="H28" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2498万
@@ -25020,7 +25020,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="I28" s="22" t="inlineStr">
+      <c r="I28" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2277万
@@ -25035,7 +25035,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B29" s="22" t="inlineStr">
+      <c r="B29" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $976万
@@ -25043,7 +25043,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C29" s="22" t="inlineStr">
+      <c r="C29" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $957万
@@ -25051,7 +25051,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D29" s="22" t="inlineStr">
+      <c r="D29" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $962万
@@ -25059,7 +25059,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E29" s="22" t="inlineStr">
+      <c r="E29" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $981万
@@ -25067,7 +25067,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F29" s="22" t="inlineStr">
+      <c r="F29" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $878万
@@ -25075,7 +25075,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="G29" s="22" t="inlineStr">
+      <c r="G29" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2787万
@@ -25083,7 +25083,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="H29" s="22" t="inlineStr">
+      <c r="H29" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2555万
@@ -25091,7 +25091,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="I29" s="22" t="inlineStr">
+      <c r="I29" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2355万
@@ -25106,7 +25106,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B30" s="22" t="inlineStr">
+      <c r="B30" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1032万
@@ -25114,7 +25114,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C30" s="22" t="inlineStr">
+      <c r="C30" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1013万
@@ -25122,7 +25122,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D30" s="22" t="inlineStr">
+      <c r="D30" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1018万
@@ -25130,7 +25130,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E30" s="22" t="inlineStr">
+      <c r="E30" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $919万
@@ -25138,7 +25138,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F30" s="22" t="inlineStr">
+      <c r="F30" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $874万
@@ -25146,7 +25146,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="G30" s="22" t="inlineStr">
+      <c r="G30" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2622万
@@ -25154,7 +25154,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="H30" s="22" t="inlineStr">
+      <c r="H30" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2378万
@@ -25162,7 +25162,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="I30" s="22" t="inlineStr">
+      <c r="I30" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2244万
@@ -25177,7 +25177,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B31" s="22" t="inlineStr">
+      <c r="B31" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1028万
@@ -25185,7 +25185,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C31" s="22" t="inlineStr">
+      <c r="C31" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1009万
@@ -25193,7 +25193,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D31" s="22" t="inlineStr">
+      <c r="D31" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1014万
@@ -25201,7 +25201,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E31" s="22" t="inlineStr">
+      <c r="E31" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $916万
@@ -25209,7 +25209,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F31" s="22" t="inlineStr">
+      <c r="F31" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $871万
@@ -25217,7 +25217,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="G31" s="22" t="inlineStr">
+      <c r="G31" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2734万
@@ -25225,7 +25225,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="H31" s="22" t="inlineStr">
+      <c r="H31" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2382万
@@ -25233,7 +25233,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="I31" s="22" t="inlineStr">
+      <c r="I31" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2304万
@@ -25248,7 +25248,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B32" s="22" t="inlineStr">
+      <c r="B32" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1024万
@@ -25256,7 +25256,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C32" s="22" t="inlineStr">
+      <c r="C32" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $934万
@@ -25264,7 +25264,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D32" s="22" t="inlineStr">
+      <c r="D32" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $950万
@@ -25272,7 +25272,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E32" s="22" t="inlineStr">
+      <c r="E32" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $969万
@@ -25280,7 +25280,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F32" s="22" t="inlineStr">
+      <c r="F32" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $867万
@@ -25288,7 +25288,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="G32" s="22" t="inlineStr">
+      <c r="G32" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2715万
@@ -25296,7 +25296,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="H32" s="22" t="inlineStr">
+      <c r="H32" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2365万
@@ -25304,7 +25304,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="I32" s="22" t="inlineStr">
+      <c r="I32" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2211万
@@ -25319,7 +25319,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B33" s="22" t="inlineStr">
+      <c r="B33" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1020万
@@ -25327,7 +25327,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C33" s="22" t="inlineStr">
+      <c r="C33" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1001万
@@ -25335,7 +25335,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D33" s="22" t="inlineStr">
+      <c r="D33" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $946万
@@ -25343,7 +25343,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E33" s="22" t="inlineStr">
+      <c r="E33" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $908万
@@ -25351,7 +25351,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F33" s="22" t="inlineStr">
+      <c r="F33" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $864万
@@ -25359,7 +25359,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="G33" s="22" t="inlineStr">
+      <c r="G33" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2584万
@@ -25367,7 +25367,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="H33" s="22" t="inlineStr">
+      <c r="H33" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2348万
@@ -25375,7 +25375,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="I33" s="22" t="inlineStr">
+      <c r="I33" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2272万
@@ -25390,7 +25390,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B34" s="22" t="inlineStr">
+      <c r="B34" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1016万
@@ -25398,7 +25398,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C34" s="22" t="inlineStr">
+      <c r="C34" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $938万
@@ -25406,7 +25406,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D34" s="22" t="inlineStr">
+      <c r="D34" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $943万
@@ -25414,7 +25414,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E34" s="22" t="inlineStr">
+      <c r="E34" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $905万
@@ -25422,7 +25422,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F34" s="22" t="inlineStr">
+      <c r="F34" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $914万
@@ -25430,7 +25430,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="G34" s="22" t="inlineStr">
+      <c r="G34" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2565万
@@ -25438,7 +25438,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="H34" s="22" t="inlineStr">
+      <c r="H34" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2331万
@@ -25446,7 +25446,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="I34" s="22" t="inlineStr">
+      <c r="I34" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2296万
@@ -25461,7 +25461,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B35" s="22" t="inlineStr">
+      <c r="B35" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $952万
@@ -25469,7 +25469,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C35" s="22" t="inlineStr">
+      <c r="C35" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $993万
@@ -25477,7 +25477,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D35" s="22" t="inlineStr">
+      <c r="D35" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $939万
@@ -25485,7 +25485,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E35" s="22" t="inlineStr">
+      <c r="E35" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $901万
@@ -25493,7 +25493,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F35" s="22" t="inlineStr">
+      <c r="F35" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $911万
@@ -25501,7 +25501,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="G35" s="22" t="inlineStr">
+      <c r="G35" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2680万
@@ -25509,7 +25509,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="H35" s="22" t="inlineStr">
+      <c r="H35" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2313万
@@ -25517,7 +25517,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="I35" s="22" t="inlineStr">
+      <c r="I35" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2280万
@@ -25532,7 +25532,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B36" s="22" t="inlineStr">
+      <c r="B36" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $949万
@@ -25540,7 +25540,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C36" s="22" t="inlineStr">
+      <c r="C36" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $931万
@@ -25548,7 +25548,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D36" s="22" t="inlineStr">
+      <c r="D36" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $935万
@@ -25556,7 +25556,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E36" s="22" t="inlineStr">
+      <c r="E36" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $954万
@@ -25564,7 +25564,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F36" s="22" t="inlineStr">
+      <c r="F36" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $854万
@@ -25572,7 +25572,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="G36" s="22" t="inlineStr">
+      <c r="G36" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2556万
@@ -25580,7 +25580,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="H36" s="22" t="inlineStr">
+      <c r="H36" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2339万
@@ -25588,7 +25588,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="I36" s="22" t="inlineStr">
+      <c r="I36" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2263万
@@ -25603,7 +25603,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B37" s="22" t="inlineStr">
+      <c r="B37" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $945万
@@ -25611,7 +25611,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C37" s="22" t="inlineStr">
+      <c r="C37" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $927万
@@ -25619,7 +25619,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D37" s="22" t="inlineStr">
+      <c r="D37" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $931万
@@ -25627,7 +25627,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E37" s="22" t="inlineStr">
+      <c r="E37" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $894万
@@ -25635,7 +25635,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F37" s="22" t="inlineStr">
+      <c r="F37" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $850万
@@ -25643,7 +25643,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="G37" s="22" t="inlineStr">
+      <c r="G37" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2574万
@@ -25651,7 +25651,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="H37" s="22" t="inlineStr">
+      <c r="H37" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2365万
@@ -25659,7 +25659,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="I37" s="22" t="inlineStr">
+      <c r="I37" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2247万
@@ -25674,7 +25674,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B38" s="22" t="inlineStr">
+      <c r="B38" s="21" t="inlineStr">
         <is>
           <t>A | 440呎 (2房)
 $1158万
@@ -25682,7 +25682,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C38" s="22" t="inlineStr">
+      <c r="C38" s="21" t="inlineStr">
         <is>
           <t>B | 439呎 (2房)
 $1089万
@@ -25690,7 +25690,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D38" s="22" t="inlineStr">
+      <c r="D38" s="21" t="inlineStr">
         <is>
           <t>C | 444呎 (2房)
 $1092万
@@ -25698,7 +25698,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="E38" s="22" t="inlineStr">
+      <c r="E38" s="21" t="inlineStr">
         <is>
           <t>D | 430呎 (2房)
 $1182万
@@ -25706,7 +25706,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="F38" s="22" t="inlineStr">
+      <c r="F38" s="21" t="inlineStr">
         <is>
           <t>E | 408呎 (2房)
 $1040万
@@ -25714,7 +25714,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="G38" s="22" t="inlineStr">
+      <c r="G38" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2546万
@@ -25722,7 +25722,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="H38" s="22" t="inlineStr">
+      <c r="H38" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2471万
@@ -25730,7 +25730,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="I38" s="22" t="inlineStr">
+      <c r="I38" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2354万

--- a/files/港岛-黄竹坑-滶晨.xlsx
+++ b/files/港岛-黄竹坑-滶晨.xlsx
@@ -14218,14 +14218,14 @@
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K218" s="5" t="n">
-        <v>14433600</v>
+        <v>15516120</v>
       </c>
       <c r="L218" s="5" t="n">
-        <v>30323</v>
+        <v>32597</v>
       </c>
       <c r="M218" s="3" t="inlineStr">
         <is>

--- a/files/港岛-黄竹坑-滶晨.xlsx
+++ b/files/港岛-黄竹坑-滶晨.xlsx
@@ -262,13 +262,13 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -28720,10 +28720,31 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr"/>
+      <c r="E5" s="20" t="inlineStr"/>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>P1 | 1536呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr"/>
+      <c r="H5" s="20" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
           <t>41&amp;42</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>A | 1020呎 (3房)
 招标单位
@@ -28731,7 +28752,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>B | 1034呎 (3房)
 招标单位
@@ -28739,7 +28760,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D6" s="22" t="inlineStr">
         <is>
           <t>C | 1083呎 (3房)
 $3890万
@@ -28747,9 +28768,9 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="E5" s="22" t="inlineStr"/>
-      <c r="F5" s="22" t="inlineStr"/>
-      <c r="G5" s="20" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr">
         <is>
           <t>P2 | 3120呎 (4+房)
 招标单位
@@ -28757,19 +28778,40 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="H5" s="22" t="inlineStr"/>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B6" s="22" t="inlineStr"/>
-      <c r="C6" s="22" t="inlineStr"/>
-      <c r="D6" s="22" t="inlineStr"/>
-      <c r="E6" s="22" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1593万
+$32,776/呎
+(26年-04月-29日)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+$1142万
+$23,109/呎
+(25年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 517呎 (2房)
+$1235万
+$23,892/呎
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 招标单位
@@ -28777,41 +28819,48 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="G6" s="22" t="inlineStr"/>
-      <c r="H6" s="22" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>P2 | 1706呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
-$1593万
-$32,776/呎
-(26年-04月-29日)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr">
+$1566万
+$32,222/呎
+(26年-04月-23日)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
-$1142万
-$23,109/呎
-(25年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
+$1130万
+$22,881/呎
+(25年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
-$1235万
-$23,892/呎
-(25年-07月-10日)</t>
-        </is>
-      </c>
-      <c r="E7" s="22" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr">
+$1276万
+$24,689/呎
+(25年-07月-16日)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr"/>
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 招标单位
@@ -28819,56 +28868,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr">
-        <is>
-          <t>P2 | 1706呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H7" s="22" t="inlineStr"/>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1566万
-$32,222/呎
-(26年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="C8" s="21" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-$1130万
-$22,881/呎
-(25年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t>C | 517呎 (2房)
-$1276万
-$24,689/呎
-(25年-07月-16日)</t>
-        </is>
-      </c>
-      <c r="E8" s="22" t="inlineStr"/>
-      <c r="F8" s="20" t="inlineStr">
-        <is>
-          <t>P1 | 1536呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="G8" s="21" t="inlineStr">
+      <c r="G8" s="22" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $10775万
@@ -28876,7 +28876,7 @@
 (26年-01月-26日)</t>
         </is>
       </c>
-      <c r="H8" s="22" t="inlineStr"/>
+      <c r="H8" s="20" t="inlineStr"/>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -28884,7 +28884,7 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1429万
@@ -28892,7 +28892,7 @@
 (26年-03月-05日)</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1227万
@@ -28900,7 +28900,7 @@
 (25年-08月-10日)</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1245万
@@ -28908,8 +28908,8 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr"/>
-      <c r="F9" s="21" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr"/>
+      <c r="F9" s="22" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $7296万
@@ -28917,7 +28917,7 @@
 (25年-11月-05日)</t>
         </is>
       </c>
-      <c r="G9" s="21" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $8530万
@@ -28925,7 +28925,7 @@
 (25年-06月-25日)</t>
         </is>
       </c>
-      <c r="H9" s="22" t="inlineStr"/>
+      <c r="H9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
@@ -28933,7 +28933,7 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1117万
@@ -28941,7 +28941,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1131万
@@ -28949,7 +28949,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1154万
@@ -28957,8 +28957,8 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E10" s="22" t="inlineStr"/>
-      <c r="F10" s="21" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr"/>
+      <c r="F10" s="22" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $6543万
@@ -28966,7 +28966,7 @@
 (25年-06月-22日)</t>
         </is>
       </c>
-      <c r="G10" s="21" t="inlineStr">
+      <c r="G10" s="22" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $8189万
@@ -28974,7 +28974,7 @@
 (25年-06月-22日)</t>
         </is>
       </c>
-      <c r="H10" s="22" t="inlineStr"/>
+      <c r="H10" s="20" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -28982,7 +28982,7 @@
           <t>36</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1086万
@@ -28990,7 +28990,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1100万
@@ -28998,7 +28998,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1217万
@@ -29006,8 +29006,8 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="E11" s="22" t="inlineStr"/>
-      <c r="F11" s="21" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr"/>
+      <c r="F11" s="22" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $6420万
@@ -29015,7 +29015,7 @@
 (25年-06月-23日)</t>
         </is>
       </c>
-      <c r="G11" s="21" t="inlineStr">
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $7558万
@@ -29023,7 +29023,7 @@
 (25年-06月-23日)</t>
         </is>
       </c>
-      <c r="H11" s="22" t="inlineStr"/>
+      <c r="H11" s="20" t="inlineStr"/>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
@@ -29031,7 +29031,7 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1083万
@@ -29039,7 +29039,7 @@
 (25年-07月-22日)</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1097万
@@ -29047,7 +29047,7 @@
 (25年-07月-22日)</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1137万
@@ -29055,8 +29055,8 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr"/>
-      <c r="F12" s="21" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr"/>
+      <c r="F12" s="22" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $6298万
@@ -29064,7 +29064,7 @@
 (25年-06月-23日)</t>
         </is>
       </c>
-      <c r="G12" s="21" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $7421万
@@ -29072,7 +29072,7 @@
 (25年-06月-23日)</t>
         </is>
       </c>
-      <c r="H12" s="22" t="inlineStr"/>
+      <c r="H12" s="20" t="inlineStr"/>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -29080,7 +29080,7 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1067万
@@ -29088,7 +29088,7 @@
 (25年-06月-24日)</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1081万
@@ -29096,7 +29096,7 @@
 (25年-07月-22日)</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1128万
@@ -29104,8 +29104,8 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="E13" s="22" t="inlineStr"/>
-      <c r="F13" s="21" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr"/>
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $6089万
@@ -29113,7 +29113,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="G13" s="21" t="inlineStr">
+      <c r="G13" s="22" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $7319万
@@ -29121,7 +29121,7 @@
 (25年-06月-23日)</t>
         </is>
       </c>
-      <c r="H13" s="22" t="inlineStr"/>
+      <c r="H13" s="20" t="inlineStr"/>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -29129,7 +29129,7 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1048万
@@ -29137,7 +29137,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1061万
@@ -29145,7 +29145,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1123万
@@ -29153,8 +29153,8 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="E14" s="22" t="inlineStr"/>
-      <c r="F14" s="21" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr"/>
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $5990万
@@ -29162,7 +29162,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="G14" s="21" t="inlineStr">
+      <c r="G14" s="22" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $6726万
@@ -29170,7 +29170,7 @@
 (25年-06月-24日)</t>
         </is>
       </c>
-      <c r="H14" s="22" t="inlineStr"/>
+      <c r="H14" s="20" t="inlineStr"/>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
@@ -29178,7 +29178,7 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1107万
@@ -29186,7 +29186,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1055万
@@ -29194,7 +29194,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1187万
@@ -29202,8 +29202,8 @@
 (25年-06月-19日)</t>
         </is>
       </c>
-      <c r="E15" s="22" t="inlineStr"/>
-      <c r="F15" s="21" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr"/>
+      <c r="F15" s="22" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $5574万
@@ -29211,7 +29211,7 @@
 (25年-06月-11日)</t>
         </is>
       </c>
-      <c r="G15" s="21" t="inlineStr">
+      <c r="G15" s="22" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $6596万
@@ -29219,7 +29219,7 @@
 (25年-06月-11日)</t>
         </is>
       </c>
-      <c r="H15" s="22" t="inlineStr"/>
+      <c r="H15" s="20" t="inlineStr"/>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
@@ -29227,7 +29227,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B16" s="21" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1100万
@@ -29235,7 +29235,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1114万
@@ -29243,7 +29243,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="D16" s="21" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1112万
@@ -29251,8 +29251,8 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E16" s="22" t="inlineStr"/>
-      <c r="F16" s="21" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr"/>
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $5076万
@@ -29260,7 +29260,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="G16" s="21" t="inlineStr">
+      <c r="G16" s="22" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $6467万
@@ -29268,7 +29268,7 @@
 (25年-06月-11日)</t>
         </is>
       </c>
-      <c r="H16" s="22" t="inlineStr"/>
+      <c r="H16" s="20" t="inlineStr"/>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
@@ -29276,7 +29276,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B17" s="21" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1094万
@@ -29284,7 +29284,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="C17" s="21" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1108万
@@ -29292,7 +29292,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="D17" s="21" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1175万
@@ -29300,8 +29300,8 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="E17" s="22" t="inlineStr"/>
-      <c r="F17" s="21" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr"/>
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>P1 | 1469呎 (4+房)
 $5739万
@@ -29309,7 +29309,7 @@
 (25年-06月-18日)</t>
         </is>
       </c>
-      <c r="G17" s="21" t="inlineStr">
+      <c r="G17" s="22" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $6739万
@@ -29317,7 +29317,7 @@
 (25年-06月-18日)</t>
         </is>
       </c>
-      <c r="H17" s="22" t="inlineStr"/>
+      <c r="H17" s="20" t="inlineStr"/>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
@@ -29325,7 +29325,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1025万
@@ -29333,7 +29333,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="C18" s="21" t="inlineStr">
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1036万
@@ -29341,7 +29341,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1084万
@@ -29349,7 +29349,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="E18" s="21" t="inlineStr">
+      <c r="E18" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $1011万
@@ -29357,7 +29357,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="F18" s="21" t="inlineStr">
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>P1 | 1258呎 (4+房)
 $4422万
@@ -29365,7 +29365,7 @@
 (25年-06月-10日)</t>
         </is>
       </c>
-      <c r="G18" s="21" t="inlineStr">
+      <c r="G18" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2694万
@@ -29373,7 +29373,7 @@
 (25年-07月-01日)</t>
         </is>
       </c>
-      <c r="H18" s="21" t="inlineStr">
+      <c r="H18" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3313万
@@ -29388,7 +29388,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B19" s="21" t="inlineStr">
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1021万
@@ -29396,7 +29396,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="C19" s="21" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1032万
@@ -29404,7 +29404,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr">
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1066万
@@ -29412,7 +29412,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E19" s="21" t="inlineStr">
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $1005万
@@ -29420,7 +29420,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="F19" s="21" t="inlineStr">
+      <c r="F19" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4351万
@@ -29428,7 +29428,7 @@
 (25年-06月-24日)</t>
         </is>
       </c>
-      <c r="G19" s="21" t="inlineStr">
+      <c r="G19" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2653万
@@ -29436,7 +29436,7 @@
 (25年-06月-29日)</t>
         </is>
       </c>
-      <c r="H19" s="21" t="inlineStr">
+      <c r="H19" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3447万
@@ -29451,7 +29451,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B20" s="21" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1017万
@@ -29459,7 +29459,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="C20" s="21" t="inlineStr">
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1028万
@@ -29467,7 +29467,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="D20" s="21" t="inlineStr">
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1076万
@@ -29475,7 +29475,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="E20" s="21" t="inlineStr">
+      <c r="E20" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $999万
@@ -29483,7 +29483,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="F20" s="21" t="inlineStr">
+      <c r="F20" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4540万
@@ -29491,7 +29491,7 @@
 (25年-06月-25日)</t>
         </is>
       </c>
-      <c r="G20" s="21" t="inlineStr">
+      <c r="G20" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2612万
@@ -29499,7 +29499,7 @@
 (25年-06月-22日)</t>
         </is>
       </c>
-      <c r="H20" s="21" t="inlineStr">
+      <c r="H20" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3256万
@@ -29514,7 +29514,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B21" s="21" t="inlineStr">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1013万
@@ -29522,7 +29522,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="C21" s="21" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1024万
@@ -29530,7 +29530,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1138万
@@ -29538,7 +29538,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="E21" s="21" t="inlineStr">
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $993万
@@ -29546,7 +29546,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="F21" s="21" t="inlineStr">
+      <c r="F21" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4265万
@@ -29554,7 +29554,7 @@
 (25年-06月-11日)</t>
         </is>
       </c>
-      <c r="G21" s="21" t="inlineStr">
+      <c r="G21" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2579万
@@ -29562,7 +29562,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="H21" s="21" t="inlineStr">
+      <c r="H21" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3220万
@@ -29577,7 +29577,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B22" s="21" t="inlineStr">
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1009万
@@ -29585,7 +29585,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="C22" s="21" t="inlineStr">
+      <c r="C22" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1020万
@@ -29593,7 +29593,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="D22" s="21" t="inlineStr">
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1067万
@@ -29601,7 +29601,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="E22" s="21" t="inlineStr">
+      <c r="E22" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $987万
@@ -29609,7 +29609,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="F22" s="21" t="inlineStr">
+      <c r="F22" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4229万
@@ -29617,7 +29617,7 @@
 (25年-06月-19日)</t>
         </is>
       </c>
-      <c r="G22" s="21" t="inlineStr">
+      <c r="G22" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2688万
@@ -29625,7 +29625,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="H22" s="21" t="inlineStr">
+      <c r="H22" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3056万
@@ -29640,7 +29640,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B23" s="21" t="inlineStr">
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1005万
@@ -29648,7 +29648,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="C23" s="21" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1079万
@@ -29656,7 +29656,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="D23" s="21" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1063万
@@ -29664,7 +29664,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="E23" s="21" t="inlineStr">
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $984万
@@ -29672,7 +29672,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="F23" s="21" t="inlineStr">
+      <c r="F23" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4193万
@@ -29680,7 +29680,7 @@
 (25年-06月-23日)</t>
         </is>
       </c>
-      <c r="G23" s="21" t="inlineStr">
+      <c r="G23" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2529万
@@ -29688,7 +29688,7 @@
 (25年-06月-23日)</t>
         </is>
       </c>
-      <c r="H23" s="21" t="inlineStr">
+      <c r="H23" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2876万
@@ -29703,7 +29703,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B24" s="21" t="inlineStr">
+      <c r="B24" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1001万
@@ -29711,7 +29711,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="C24" s="21" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1008万
@@ -29719,7 +29719,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="D24" s="21" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1059万
@@ -29727,7 +29727,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E24" s="21" t="inlineStr">
+      <c r="E24" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $980万
@@ -29735,7 +29735,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="F24" s="21" t="inlineStr">
+      <c r="F24" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4184万
@@ -29743,7 +29743,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="G24" s="21" t="inlineStr">
+      <c r="G24" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2504万
@@ -29751,7 +29751,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="H24" s="21" t="inlineStr">
+      <c r="H24" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3299万
@@ -29766,7 +29766,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $997万
@@ -29774,7 +29774,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="C25" s="21" t="inlineStr">
+      <c r="C25" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1004万
@@ -29782,7 +29782,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="D25" s="21" t="inlineStr">
+      <c r="D25" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1113万
@@ -29790,7 +29790,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="E25" s="21" t="inlineStr">
+      <c r="E25" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $1037万
@@ -29798,7 +29798,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="F25" s="21" t="inlineStr">
+      <c r="F25" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4374万
@@ -29806,7 +29806,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="G25" s="21" t="inlineStr">
+      <c r="G25" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2480万
@@ -29814,7 +29814,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="H25" s="21" t="inlineStr">
+      <c r="H25" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3122万
@@ -29829,7 +29829,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B26" s="21" t="inlineStr">
+      <c r="B26" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $993万
@@ -29837,7 +29837,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="C26" s="21" t="inlineStr">
+      <c r="C26" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1000万
@@ -29845,7 +29845,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="D26" s="21" t="inlineStr">
+      <c r="D26" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1043万
@@ -29853,7 +29853,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="E26" s="21" t="inlineStr">
+      <c r="E26" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $972万
@@ -29861,7 +29861,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="F26" s="21" t="inlineStr">
+      <c r="F26" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3725万
@@ -29869,7 +29869,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="G26" s="21" t="inlineStr">
+      <c r="G26" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2406万
@@ -29877,7 +29877,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="H26" s="21" t="inlineStr">
+      <c r="H26" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2893万
@@ -29892,7 +29892,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B27" s="21" t="inlineStr">
+      <c r="B27" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $989万
@@ -29900,7 +29900,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="C27" s="21" t="inlineStr">
+      <c r="C27" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $996万
@@ -29908,7 +29908,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="D27" s="21" t="inlineStr">
+      <c r="D27" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1039万
@@ -29916,7 +29916,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="E27" s="21" t="inlineStr">
+      <c r="E27" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $968万
@@ -29924,7 +29924,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="F27" s="21" t="inlineStr">
+      <c r="F27" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3680万
@@ -29932,7 +29932,7 @@
 (25年-06月-13日)</t>
         </is>
       </c>
-      <c r="G27" s="21" t="inlineStr">
+      <c r="G27" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2526万
@@ -29940,7 +29940,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="H27" s="21" t="inlineStr">
+      <c r="H27" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2850万
@@ -29955,7 +29955,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B28" s="21" t="inlineStr">
+      <c r="B28" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $985万
@@ -29963,7 +29963,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="C28" s="21" t="inlineStr">
+      <c r="C28" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $992万
@@ -29971,7 +29971,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="D28" s="21" t="inlineStr">
+      <c r="D28" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1022万
@@ -29979,7 +29979,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="E28" s="21" t="inlineStr">
+      <c r="E28" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $1024万
@@ -29987,7 +29987,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="F28" s="21" t="inlineStr">
+      <c r="F28" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3955万
@@ -29995,7 +29995,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="G28" s="21" t="inlineStr">
+      <c r="G28" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2349万
@@ -30003,7 +30003,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="H28" s="21" t="inlineStr">
+      <c r="H28" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2652万
@@ -30018,7 +30018,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B29" s="21" t="inlineStr">
+      <c r="B29" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $981万
@@ -30026,7 +30026,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="C29" s="21" t="inlineStr">
+      <c r="C29" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1049万
@@ -30034,7 +30034,7 @@
 (25年-07月-01日)</t>
         </is>
       </c>
-      <c r="D29" s="21" t="inlineStr">
+      <c r="D29" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1095万
@@ -30042,7 +30042,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E29" s="21" t="inlineStr">
+      <c r="E29" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $948万
@@ -30050,7 +30050,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="F29" s="21" t="inlineStr">
+      <c r="F29" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3818万
@@ -30058,7 +30058,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="G29" s="21" t="inlineStr">
+      <c r="G29" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2319万
@@ -30066,7 +30066,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="H29" s="21" t="inlineStr">
+      <c r="H29" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2784万
@@ -30081,7 +30081,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B30" s="21" t="inlineStr">
+      <c r="B30" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1038万
@@ -30089,7 +30089,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="C30" s="21" t="inlineStr">
+      <c r="C30" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1045万
@@ -30097,7 +30097,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="D30" s="21" t="inlineStr">
+      <c r="D30" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1091万
@@ -30105,7 +30105,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E30" s="21" t="inlineStr">
+      <c r="E30" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $956万
@@ -30113,7 +30113,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="F30" s="21" t="inlineStr">
+      <c r="F30" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3862万
@@ -30121,7 +30121,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="G30" s="21" t="inlineStr">
+      <c r="G30" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2396万
@@ -30129,7 +30129,7 @@
 (25年-08月-05日)</t>
         </is>
       </c>
-      <c r="H30" s="21" t="inlineStr">
+      <c r="H30" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2708万
@@ -30144,7 +30144,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B31" s="21" t="inlineStr">
+      <c r="B31" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1034万
@@ -30152,7 +30152,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="C31" s="21" t="inlineStr">
+      <c r="C31" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1041万
@@ -30160,7 +30160,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="D31" s="21" t="inlineStr">
+      <c r="D31" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1086万
@@ -30168,7 +30168,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="E31" s="21" t="inlineStr">
+      <c r="E31" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $952万
@@ -30176,7 +30176,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="F31" s="21" t="inlineStr">
+      <c r="F31" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3819万
@@ -30184,7 +30184,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="G31" s="21" t="inlineStr">
+      <c r="G31" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2361万
@@ -30192,7 +30192,7 @@
 (25年-07月-29日)</t>
         </is>
       </c>
-      <c r="H31" s="21" t="inlineStr">
+      <c r="H31" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2668万
@@ -30207,7 +30207,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B32" s="21" t="inlineStr">
+      <c r="B32" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1030万
@@ -30215,7 +30215,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="C32" s="21" t="inlineStr">
+      <c r="C32" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $976万
@@ -30223,7 +30223,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="D32" s="21" t="inlineStr">
+      <c r="D32" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1006万
@@ -30231,7 +30231,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="E32" s="21" t="inlineStr">
+      <c r="E32" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $949万
@@ -30239,7 +30239,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="F32" s="21" t="inlineStr">
+      <c r="F32" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3785万
@@ -30247,7 +30247,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="G32" s="21" t="inlineStr">
+      <c r="G32" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2338万
@@ -30255,7 +30255,7 @@
 (25年-09月-17日)</t>
         </is>
       </c>
-      <c r="H32" s="21" t="inlineStr">
+      <c r="H32" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2641万
@@ -30270,7 +30270,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B33" s="21" t="inlineStr">
+      <c r="B33" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1026万
@@ -30278,7 +30278,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="C33" s="21" t="inlineStr">
+      <c r="C33" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1033万
@@ -30286,7 +30286,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="D33" s="21" t="inlineStr">
+      <c r="D33" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1014万
@@ -30294,7 +30294,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E33" s="21" t="inlineStr">
+      <c r="E33" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $945万
@@ -30302,7 +30302,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="F33" s="21" t="inlineStr">
+      <c r="F33" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3474万
@@ -30310,7 +30310,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="G33" s="21" t="inlineStr">
+      <c r="G33" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2306万
@@ -30318,7 +30318,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="H33" s="21" t="inlineStr">
+      <c r="H33" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2578万
@@ -30333,7 +30333,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B34" s="21" t="inlineStr">
+      <c r="B34" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $962万
@@ -30341,7 +30341,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="C34" s="21" t="inlineStr">
+      <c r="C34" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $968万
@@ -30349,7 +30349,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="D34" s="21" t="inlineStr">
+      <c r="D34" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1010万
@@ -30357,7 +30357,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E34" s="21" t="inlineStr">
+      <c r="E34" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $938万
@@ -30365,7 +30365,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="F34" s="21" t="inlineStr">
+      <c r="F34" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3632万
@@ -30373,7 +30373,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="G34" s="21" t="inlineStr">
+      <c r="G34" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2392万
@@ -30381,7 +30381,7 @@
 (25年-07月-30日)</t>
         </is>
       </c>
-      <c r="H34" s="21" t="inlineStr">
+      <c r="H34" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2586万
@@ -30396,7 +30396,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B35" s="21" t="inlineStr">
+      <c r="B35" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1018万
@@ -30404,7 +30404,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="C35" s="21" t="inlineStr">
+      <c r="C35" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $964万
@@ -30412,7 +30412,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="D35" s="21" t="inlineStr">
+      <c r="D35" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1069万
@@ -30420,7 +30420,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="E35" s="21" t="inlineStr">
+      <c r="E35" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $928万
@@ -30428,7 +30428,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="F35" s="21" t="inlineStr">
+      <c r="F35" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3426万
@@ -30436,7 +30436,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="G35" s="21" t="inlineStr">
+      <c r="G35" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2399万
@@ -30444,7 +30444,7 @@
 (25年-08月-25日)</t>
         </is>
       </c>
-      <c r="H35" s="21" t="inlineStr">
+      <c r="H35" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2675万
@@ -30459,7 +30459,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B36" s="21" t="inlineStr">
+      <c r="B36" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1014万
@@ -30467,7 +30467,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="C36" s="21" t="inlineStr">
+      <c r="C36" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $960万
@@ -30475,7 +30475,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="D36" s="21" t="inlineStr">
+      <c r="D36" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1002万
@@ -30483,7 +30483,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="E36" s="21" t="inlineStr">
+      <c r="E36" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $976万
@@ -30491,7 +30491,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="F36" s="21" t="inlineStr">
+      <c r="F36" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3881万
@@ -30499,7 +30499,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="G36" s="21" t="inlineStr">
+      <c r="G36" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2314万
@@ -30507,7 +30507,7 @@
 (25年-09月-08日)</t>
         </is>
       </c>
-      <c r="H36" s="21" t="inlineStr">
+      <c r="H36" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2570万
@@ -30522,7 +30522,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B37" s="21" t="inlineStr">
+      <c r="B37" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1010万
@@ -30530,7 +30530,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="C37" s="21" t="inlineStr">
+      <c r="C37" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $957万
@@ -30538,7 +30538,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="D37" s="21" t="inlineStr">
+      <c r="D37" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $998万
@@ -30546,7 +30546,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="E37" s="21" t="inlineStr">
+      <c r="E37" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $910万
@@ -30554,7 +30554,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="F37" s="21" t="inlineStr">
+      <c r="F37" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3577万
@@ -30562,7 +30562,7 @@
 (25年-08月-05日)</t>
         </is>
       </c>
-      <c r="G37" s="21" t="inlineStr">
+      <c r="G37" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2490万
@@ -30570,7 +30570,7 @@
 (25年-12月-30日)</t>
         </is>
       </c>
-      <c r="H37" s="21" t="inlineStr">
+      <c r="H37" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2686万
@@ -30585,7 +30585,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B38" s="21" t="inlineStr">
+      <c r="B38" s="22" t="inlineStr">
         <is>
           <t>A | 440呎 (2房)
 $1088万
@@ -30593,7 +30593,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="C38" s="21" t="inlineStr">
+      <c r="C38" s="22" t="inlineStr">
         <is>
           <t>B | 448呎 (2房)
 $1120万
@@ -30601,7 +30601,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="D38" s="21" t="inlineStr">
+      <c r="D38" s="22" t="inlineStr">
         <is>
           <t>C | 467呎 (2房)
 $1238万
@@ -30609,7 +30609,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="E38" s="21" t="inlineStr">
+      <c r="E38" s="22" t="inlineStr">
         <is>
           <t>D | 430呎 (2房)
 $999万
@@ -30617,7 +30617,7 @@
 (25年-07月-20日)</t>
         </is>
       </c>
-      <c r="F38" s="21" t="inlineStr">
+      <c r="F38" s="22" t="inlineStr">
         <is>
           <t>P1 | 1162呎 (4+房)
 $3650万
@@ -30625,7 +30625,7 @@
 (25年-07月-28日)</t>
         </is>
       </c>
-      <c r="G38" s="21" t="inlineStr">
+      <c r="G38" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2436万
@@ -30633,7 +30633,7 @@
 (25年-12月-18日)</t>
         </is>
       </c>
-      <c r="H38" s="21" t="inlineStr">
+      <c r="H38" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2758万
@@ -30792,10 +30792,32 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr"/>
+      <c r="E5" s="20" t="inlineStr"/>
+      <c r="F5" s="20" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr">
+        <is>
+          <t>P1 | 1417呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr"/>
+      <c r="I5" s="20" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
           <t>41&amp;42</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>A | 1020呎 (3房)
 $3652万
@@ -30803,7 +30825,7 @@
 (26年-03月-11日)</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>B | 1016呎 (3房)
 招标单位
@@ -30811,7 +30833,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t>C | 1029呎 (3房)
 招标单位
@@ -30819,7 +30841,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="E6" s="21" t="inlineStr">
         <is>
           <t>D | 1083呎 (3房)
 招标单位
@@ -30827,9 +30849,9 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="F5" s="22" t="inlineStr"/>
-      <c r="G5" s="22" t="inlineStr"/>
-      <c r="H5" s="20" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t>P2 | 2871呎 (4+房)
 招标单位
@@ -30837,29 +30859,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="I5" s="22" t="inlineStr"/>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B6" s="22" t="inlineStr"/>
-      <c r="C6" s="22" t="inlineStr"/>
-      <c r="D6" s="22" t="inlineStr"/>
-      <c r="E6" s="22" t="inlineStr"/>
-      <c r="F6" s="22" t="inlineStr"/>
-      <c r="G6" s="20" t="inlineStr">
-        <is>
-          <t>P1 | 1417呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H6" s="22" t="inlineStr"/>
-      <c r="I6" s="22" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
@@ -30867,7 +30867,7 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1245万
@@ -30875,7 +30875,7 @@
 (25年-09月-10日)</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1138万
@@ -30883,7 +30883,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1137万
@@ -30891,7 +30891,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1804万
@@ -30899,8 +30899,8 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="F7" s="22" t="inlineStr"/>
-      <c r="G7" s="20" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 招标单位
@@ -30908,7 +30908,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="H7" s="20" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 招标单位
@@ -30916,7 +30916,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="I7" s="22" t="inlineStr"/>
+      <c r="I7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -30924,7 +30924,7 @@
           <t>39</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1180万
@@ -30932,7 +30932,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1556万
@@ -30940,7 +30940,7 @@
 (26年-04月-21日)</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1196万
@@ -30948,7 +30948,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1532万
@@ -30956,8 +30956,8 @@
 (26年-06月-17日)</t>
         </is>
       </c>
-      <c r="F8" s="22" t="inlineStr"/>
-      <c r="G8" s="20" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr"/>
+      <c r="G8" s="21" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 招标单位
@@ -30965,7 +30965,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="H8" s="20" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 招标单位
@@ -30973,7 +30973,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="I8" s="22" t="inlineStr"/>
+      <c r="I8" s="20" t="inlineStr"/>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -30981,7 +30981,7 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1543万
@@ -30989,7 +30989,7 @@
 (26年-04月-27日)</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1169万
@@ -30997,7 +30997,7 @@
 (25年-07月-30日)</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1174万
@@ -31005,7 +31005,7 @@
 (25年-07月-24日)</t>
         </is>
       </c>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1137万
@@ -31013,8 +31013,8 @@
 (25年-07月-23日)</t>
         </is>
       </c>
-      <c r="F9" s="22" t="inlineStr"/>
-      <c r="G9" s="21" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr"/>
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $6754万
@@ -31022,7 +31022,7 @@
 (25年-11月-30日)</t>
         </is>
       </c>
-      <c r="H9" s="21" t="inlineStr">
+      <c r="H9" s="22" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $8574万
@@ -31030,7 +31030,7 @@
 (26年-02月-11日)</t>
         </is>
       </c>
-      <c r="I9" s="22" t="inlineStr"/>
+      <c r="I9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
@@ -31038,7 +31038,7 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1170万
@@ -31046,7 +31046,7 @@
 (25年-07月-21日)</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1112万
@@ -31054,7 +31054,7 @@
 (25年-07月-22日)</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1116万
@@ -31062,7 +31062,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="E10" s="21" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1081万
@@ -31070,8 +31070,8 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="F10" s="22" t="inlineStr"/>
-      <c r="G10" s="21" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr"/>
+      <c r="G10" s="22" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $6086万
@@ -31079,7 +31079,7 @@
 (25年-09月-08日)</t>
         </is>
       </c>
-      <c r="H10" s="21" t="inlineStr">
+      <c r="H10" s="22" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $7592万
@@ -31087,7 +31087,7 @@
 (25年-08月-11日)</t>
         </is>
       </c>
-      <c r="I10" s="22" t="inlineStr"/>
+      <c r="I10" s="20" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -31095,7 +31095,7 @@
           <t>36</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1084万
@@ -31103,7 +31103,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1081万
@@ -31111,7 +31111,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1276万
@@ -31119,7 +31119,7 @@
 (26年-02月-26日)</t>
         </is>
       </c>
-      <c r="E11" s="21" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1064万
@@ -31127,8 +31127,8 @@
 (25年-08月-03日)</t>
         </is>
       </c>
-      <c r="F11" s="22" t="inlineStr"/>
-      <c r="G11" s="21" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr"/>
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $5644万
@@ -31136,7 +31136,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="H11" s="21" t="inlineStr">
+      <c r="H11" s="22" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $6715万
@@ -31144,7 +31144,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="I11" s="22" t="inlineStr"/>
+      <c r="I11" s="20" t="inlineStr"/>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
@@ -31152,7 +31152,7 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1081万
@@ -31160,7 +31160,7 @@
 (25年-07月-22日)</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1078万
@@ -31168,7 +31168,7 @@
 (25年-07月-22日)</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1082万
@@ -31176,7 +31176,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1048万
@@ -31184,8 +31184,8 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="F12" s="22" t="inlineStr"/>
-      <c r="G12" s="21" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr"/>
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $5431万
@@ -31193,7 +31193,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="H12" s="21" t="inlineStr">
+      <c r="H12" s="22" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $6324万
@@ -31201,7 +31201,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr"/>
+      <c r="I12" s="20" t="inlineStr"/>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -31209,7 +31209,7 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1065万
@@ -31217,7 +31217,7 @@
 (25年-07月-22日)</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1128万
@@ -31225,7 +31225,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1132万
@@ -31233,7 +31233,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="E13" s="21" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $998万
@@ -31241,8 +31241,8 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="F13" s="22" t="inlineStr"/>
-      <c r="G13" s="21" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr"/>
+      <c r="G13" s="22" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $5404万
@@ -31250,7 +31250,7 @@
 (25年-07月-24日)</t>
         </is>
       </c>
-      <c r="H13" s="21" t="inlineStr">
+      <c r="H13" s="22" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $6018万
@@ -31258,7 +31258,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="I13" s="22" t="inlineStr"/>
+      <c r="I13" s="20" t="inlineStr"/>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -31266,7 +31266,7 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1046万
@@ -31274,7 +31274,7 @@
 (25年-06月-19日)</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1108万
@@ -31282,7 +31282,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1046万
@@ -31290,7 +31290,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="E14" s="21" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $993万
@@ -31298,8 +31298,8 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="F14" s="22" t="inlineStr"/>
-      <c r="G14" s="21" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr"/>
+      <c r="G14" s="22" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $5494万
@@ -31307,7 +31307,7 @@
 (25年-07月-22日)</t>
         </is>
       </c>
-      <c r="H14" s="21" t="inlineStr">
+      <c r="H14" s="22" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $6220万
@@ -31315,7 +31315,7 @@
 (25年-06月-23日)</t>
         </is>
       </c>
-      <c r="I14" s="22" t="inlineStr"/>
+      <c r="I14" s="20" t="inlineStr"/>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
@@ -31323,7 +31323,7 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1040万
@@ -31331,7 +31331,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1102万
@@ -31339,7 +31339,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1040万
@@ -31347,7 +31347,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="E15" s="21" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $988万
@@ -31355,8 +31355,8 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="F15" s="22" t="inlineStr"/>
-      <c r="G15" s="21" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr"/>
+      <c r="G15" s="22" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $5052万
@@ -31364,7 +31364,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="H15" s="21" t="inlineStr">
+      <c r="H15" s="22" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $5850万
@@ -31372,7 +31372,7 @@
 (25年-06月-22日)</t>
         </is>
       </c>
-      <c r="I15" s="22" t="inlineStr"/>
+      <c r="I15" s="20" t="inlineStr"/>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
@@ -31380,7 +31380,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B16" s="21" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1034万
@@ -31388,7 +31388,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1030万
@@ -31396,7 +31396,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="D16" s="21" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1099万
@@ -31404,7 +31404,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="E16" s="21" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $983万
@@ -31412,8 +31412,8 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="F16" s="22" t="inlineStr"/>
-      <c r="G16" s="21" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr"/>
+      <c r="G16" s="22" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $4996万
@@ -31421,7 +31421,7 @@
 (25年-06月-08日)</t>
         </is>
       </c>
-      <c r="H16" s="21" t="inlineStr">
+      <c r="H16" s="22" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $5791万
@@ -31429,7 +31429,7 @@
 (25年-06月-24日)</t>
         </is>
       </c>
-      <c r="I16" s="22" t="inlineStr"/>
+      <c r="I16" s="20" t="inlineStr"/>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
@@ -31437,7 +31437,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B17" s="21" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1027万
@@ -31445,7 +31445,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="C17" s="21" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1024万
@@ -31453,7 +31453,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="D17" s="21" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1028万
@@ -31461,7 +31461,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="E17" s="21" t="inlineStr">
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $978万
@@ -31469,8 +31469,8 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="F17" s="22" t="inlineStr"/>
-      <c r="G17" s="21" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr"/>
+      <c r="G17" s="22" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $4839万
@@ -31478,7 +31478,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="H17" s="21" t="inlineStr">
+      <c r="H17" s="22" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $5609万
@@ -31486,7 +31486,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="I17" s="22" t="inlineStr"/>
+      <c r="I17" s="20" t="inlineStr"/>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
@@ -31494,7 +31494,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1083万
@@ -31502,7 +31502,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="C18" s="21" t="inlineStr">
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1063万
@@ -31510,7 +31510,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1005万
@@ -31518,7 +31518,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E18" s="21" t="inlineStr">
+      <c r="E18" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $964万
@@ -31526,7 +31526,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="F18" s="21" t="inlineStr">
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $917万
@@ -31534,7 +31534,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="G18" s="21" t="inlineStr">
+      <c r="G18" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $3273万
@@ -31542,7 +31542,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="H18" s="21" t="inlineStr">
+      <c r="H18" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2726万
@@ -31550,7 +31550,7 @@
 (25年-07月-30日)</t>
         </is>
       </c>
-      <c r="I18" s="21" t="inlineStr">
+      <c r="I18" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2494万
@@ -31565,7 +31565,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B19" s="21" t="inlineStr">
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1015万
@@ -31573,7 +31573,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="C19" s="21" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1059万
@@ -31581,7 +31581,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr">
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1063万
@@ -31589,7 +31589,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="E19" s="21" t="inlineStr">
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $961万
@@ -31597,7 +31597,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="F19" s="21" t="inlineStr">
+      <c r="F19" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $971万
@@ -31605,7 +31605,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="G19" s="21" t="inlineStr">
+      <c r="G19" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $3084万
@@ -31613,7 +31613,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="H19" s="21" t="inlineStr">
+      <c r="H19" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2582万
@@ -31621,7 +31621,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="I19" s="21" t="inlineStr">
+      <c r="I19" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2591万
@@ -31636,7 +31636,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B20" s="21" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1011万
@@ -31644,7 +31644,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="C20" s="21" t="inlineStr">
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1054万
@@ -31652,7 +31652,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="D20" s="21" t="inlineStr">
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1059万
@@ -31660,7 +31660,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="E20" s="21" t="inlineStr">
+      <c r="E20" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $957万
@@ -31668,7 +31668,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="F20" s="21" t="inlineStr">
+      <c r="F20" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $910万
@@ -31676,7 +31676,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="G20" s="21" t="inlineStr">
+      <c r="G20" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $3337万
@@ -31684,7 +31684,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="H20" s="21" t="inlineStr">
+      <c r="H20" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2541万
@@ -31692,7 +31692,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="I20" s="21" t="inlineStr">
+      <c r="I20" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2548万
@@ -31707,7 +31707,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B21" s="21" t="inlineStr">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1070万
@@ -31715,7 +31715,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="C21" s="21" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1050万
@@ -31723,7 +31723,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $993万
@@ -31731,7 +31731,7 @@
 (25年-06月-13日)</t>
         </is>
       </c>
-      <c r="E21" s="21" t="inlineStr">
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1012万
@@ -31739,7 +31739,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="F21" s="21" t="inlineStr">
+      <c r="F21" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $906万
@@ -31747,7 +31747,7 @@
 (25年-06月-13日)</t>
         </is>
       </c>
-      <c r="G21" s="21" t="inlineStr">
+      <c r="G21" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $3300万
@@ -31755,7 +31755,7 @@
 (25年-06月-26日)</t>
         </is>
       </c>
-      <c r="H21" s="21" t="inlineStr">
+      <c r="H21" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2500万
@@ -31763,7 +31763,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="I21" s="21" t="inlineStr">
+      <c r="I21" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2519万
@@ -31778,7 +31778,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B22" s="21" t="inlineStr">
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1003万
@@ -31786,7 +31786,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="C22" s="21" t="inlineStr">
+      <c r="C22" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $984万
@@ -31794,7 +31794,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="D22" s="21" t="inlineStr">
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $989万
@@ -31802,7 +31802,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="E22" s="21" t="inlineStr">
+      <c r="E22" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $949万
@@ -31810,7 +31810,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="F22" s="21" t="inlineStr">
+      <c r="F22" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $903万
@@ -31818,7 +31818,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="G22" s="21" t="inlineStr">
+      <c r="G22" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2824万
@@ -31826,7 +31826,7 @@
 (25年-06月-18日)</t>
         </is>
       </c>
-      <c r="H22" s="21" t="inlineStr">
+      <c r="H22" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2623万
@@ -31834,7 +31834,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="I22" s="21" t="inlineStr">
+      <c r="I22" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2490万
@@ -31849,7 +31849,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B23" s="21" t="inlineStr">
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1062万
@@ -31857,7 +31857,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="C23" s="21" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $981万
@@ -31865,7 +31865,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="D23" s="21" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $985万
@@ -31873,7 +31873,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="E23" s="21" t="inlineStr">
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $945万
@@ -31881,7 +31881,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="F23" s="21" t="inlineStr">
+      <c r="F23" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $955万
@@ -31889,7 +31889,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="G23" s="21" t="inlineStr">
+      <c r="G23" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2784万
@@ -31897,7 +31897,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="H23" s="21" t="inlineStr">
+      <c r="H23" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2487万
@@ -31905,7 +31905,7 @@
 (25年-07月-22日)</t>
         </is>
       </c>
-      <c r="I23" s="21" t="inlineStr">
+      <c r="I23" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2437万
@@ -31920,7 +31920,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B24" s="21" t="inlineStr">
+      <c r="B24" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $983万
@@ -31928,7 +31928,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="C24" s="21" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $977万
@@ -31936,7 +31936,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="D24" s="21" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1042万
@@ -31944,7 +31944,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="E24" s="21" t="inlineStr">
+      <c r="E24" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $942万
@@ -31952,7 +31952,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="F24" s="21" t="inlineStr">
+      <c r="F24" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $896万
@@ -31960,7 +31960,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="G24" s="21" t="inlineStr">
+      <c r="G24" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $3217万
@@ -31968,7 +31968,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="H24" s="21" t="inlineStr">
+      <c r="H24" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2482万
@@ -31976,7 +31976,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="I24" s="21" t="inlineStr">
+      <c r="I24" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2342万
@@ -31991,7 +31991,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1053万
@@ -31999,7 +31999,7 @@
 (25年-07月-01日)</t>
         </is>
       </c>
-      <c r="C25" s="21" t="inlineStr">
+      <c r="C25" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $973万
@@ -32007,7 +32007,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="D25" s="21" t="inlineStr">
+      <c r="D25" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $977万
@@ -32015,7 +32015,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="E25" s="21" t="inlineStr">
+      <c r="E25" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $996万
@@ -32023,7 +32023,7 @@
 (25年-07月-01日)</t>
         </is>
       </c>
-      <c r="F25" s="21" t="inlineStr">
+      <c r="F25" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $892万
@@ -32031,7 +32031,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="G25" s="21" t="inlineStr">
+      <c r="G25" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $3045万
@@ -32039,7 +32039,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="H25" s="21" t="inlineStr">
+      <c r="H25" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2451万
@@ -32047,7 +32047,7 @@
 (25年-07月-22日)</t>
         </is>
       </c>
-      <c r="I25" s="21" t="inlineStr">
+      <c r="I25" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2321万
@@ -32062,7 +32062,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B26" s="21" t="inlineStr">
+      <c r="B26" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $987万
@@ -32070,7 +32070,7 @@
 (25年-06月-29日)</t>
         </is>
       </c>
-      <c r="C26" s="21" t="inlineStr">
+      <c r="C26" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $969万
@@ -32078,7 +32078,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="D26" s="21" t="inlineStr">
+      <c r="D26" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1034万
@@ -32086,7 +32086,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="E26" s="21" t="inlineStr">
+      <c r="E26" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $934万
@@ -32094,7 +32094,7 @@
 (25年-06月-13日)</t>
         </is>
       </c>
-      <c r="F26" s="21" t="inlineStr">
+      <c r="F26" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $888万
@@ -32102,7 +32102,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="G26" s="21" t="inlineStr">
+      <c r="G26" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2727万
@@ -32110,7 +32110,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="H26" s="21" t="inlineStr">
+      <c r="H26" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2426万
@@ -32118,7 +32118,7 @@
 (25年-07月-29日)</t>
         </is>
       </c>
-      <c r="I26" s="21" t="inlineStr">
+      <c r="I26" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2310万
@@ -32133,7 +32133,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B27" s="21" t="inlineStr">
+      <c r="B27" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $983万
@@ -32141,7 +32141,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="C27" s="21" t="inlineStr">
+      <c r="C27" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $965万
@@ -32149,7 +32149,7 @@
 (25年-07月-01日)</t>
         </is>
       </c>
-      <c r="D27" s="21" t="inlineStr">
+      <c r="D27" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $969万
@@ -32157,7 +32157,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="E27" s="21" t="inlineStr">
+      <c r="E27" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $988万
@@ -32165,7 +32165,7 @@
 (25年-07月-01日)</t>
         </is>
       </c>
-      <c r="F27" s="21" t="inlineStr">
+      <c r="F27" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $885万
@@ -32173,7 +32173,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="G27" s="21" t="inlineStr">
+      <c r="G27" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2701万
@@ -32181,7 +32181,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="H27" s="21" t="inlineStr">
+      <c r="H27" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2402万
@@ -32189,7 +32189,7 @@
 (25年-07月-22日)</t>
         </is>
       </c>
-      <c r="I27" s="21" t="inlineStr">
+      <c r="I27" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2294万
@@ -32204,7 +32204,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B28" s="21" t="inlineStr">
+      <c r="B28" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $979万
@@ -32212,7 +32212,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="C28" s="21" t="inlineStr">
+      <c r="C28" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $949万
@@ -32220,7 +32220,7 @@
 (25年-07月-01日)</t>
         </is>
       </c>
-      <c r="D28" s="21" t="inlineStr">
+      <c r="D28" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $965万
@@ -32228,7 +32228,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="E28" s="21" t="inlineStr">
+      <c r="E28" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $927万
@@ -32236,7 +32236,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="F28" s="21" t="inlineStr">
+      <c r="F28" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $926万
@@ -32244,7 +32244,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="G28" s="21" t="inlineStr">
+      <c r="G28" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2674万
@@ -32252,7 +32252,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="H28" s="21" t="inlineStr">
+      <c r="H28" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2498万
@@ -32260,7 +32260,7 @@
 (25年-07月-24日)</t>
         </is>
       </c>
-      <c r="I28" s="21" t="inlineStr">
+      <c r="I28" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2277万
@@ -32275,7 +32275,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B29" s="21" t="inlineStr">
+      <c r="B29" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $976万
@@ -32283,7 +32283,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="C29" s="21" t="inlineStr">
+      <c r="C29" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $957万
@@ -32291,7 +32291,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="D29" s="21" t="inlineStr">
+      <c r="D29" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $962万
@@ -32299,7 +32299,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="E29" s="21" t="inlineStr">
+      <c r="E29" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $981万
@@ -32307,7 +32307,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="F29" s="21" t="inlineStr">
+      <c r="F29" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $878万
@@ -32315,7 +32315,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="G29" s="21" t="inlineStr">
+      <c r="G29" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2787万
@@ -32323,7 +32323,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="H29" s="21" t="inlineStr">
+      <c r="H29" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2555万
@@ -32331,7 +32331,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="I29" s="21" t="inlineStr">
+      <c r="I29" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2355万
@@ -32346,7 +32346,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B30" s="21" t="inlineStr">
+      <c r="B30" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1032万
@@ -32354,7 +32354,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="C30" s="21" t="inlineStr">
+      <c r="C30" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1013万
@@ -32362,7 +32362,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="D30" s="21" t="inlineStr">
+      <c r="D30" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1018万
@@ -32370,7 +32370,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="E30" s="21" t="inlineStr">
+      <c r="E30" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $919万
@@ -32378,7 +32378,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="F30" s="21" t="inlineStr">
+      <c r="F30" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $874万
@@ -32386,7 +32386,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="G30" s="21" t="inlineStr">
+      <c r="G30" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2622万
@@ -32394,7 +32394,7 @@
 (25年-07月-22日)</t>
         </is>
       </c>
-      <c r="H30" s="21" t="inlineStr">
+      <c r="H30" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2378万
@@ -32402,7 +32402,7 @@
 (25年-08月-03日)</t>
         </is>
       </c>
-      <c r="I30" s="21" t="inlineStr">
+      <c r="I30" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2244万
@@ -32417,7 +32417,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B31" s="21" t="inlineStr">
+      <c r="B31" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1028万
@@ -32425,7 +32425,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="C31" s="21" t="inlineStr">
+      <c r="C31" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1009万
@@ -32433,7 +32433,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="D31" s="21" t="inlineStr">
+      <c r="D31" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1014万
@@ -32441,7 +32441,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="E31" s="21" t="inlineStr">
+      <c r="E31" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $916万
@@ -32449,7 +32449,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="F31" s="21" t="inlineStr">
+      <c r="F31" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $871万
@@ -32457,7 +32457,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="G31" s="21" t="inlineStr">
+      <c r="G31" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2734万
@@ -32465,7 +32465,7 @@
 (25年-08月-10日)</t>
         </is>
       </c>
-      <c r="H31" s="21" t="inlineStr">
+      <c r="H31" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2382万
@@ -32473,7 +32473,7 @@
 (25年-08月-20日)</t>
         </is>
       </c>
-      <c r="I31" s="21" t="inlineStr">
+      <c r="I31" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2304万
@@ -32488,7 +32488,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B32" s="21" t="inlineStr">
+      <c r="B32" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1024万
@@ -32496,7 +32496,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="C32" s="21" t="inlineStr">
+      <c r="C32" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $934万
@@ -32504,7 +32504,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="D32" s="21" t="inlineStr">
+      <c r="D32" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $950万
@@ -32512,7 +32512,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="E32" s="21" t="inlineStr">
+      <c r="E32" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $969万
@@ -32520,7 +32520,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="F32" s="21" t="inlineStr">
+      <c r="F32" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $867万
@@ -32528,7 +32528,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="G32" s="21" t="inlineStr">
+      <c r="G32" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2715万
@@ -32536,7 +32536,7 @@
 (25年-07月-31日)</t>
         </is>
       </c>
-      <c r="H32" s="21" t="inlineStr">
+      <c r="H32" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2365万
@@ -32544,7 +32544,7 @@
 (25年-08月-18日)</t>
         </is>
       </c>
-      <c r="I32" s="21" t="inlineStr">
+      <c r="I32" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2211万
@@ -32559,7 +32559,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B33" s="21" t="inlineStr">
+      <c r="B33" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1020万
@@ -32567,7 +32567,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="C33" s="21" t="inlineStr">
+      <c r="C33" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1001万
@@ -32575,7 +32575,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="D33" s="21" t="inlineStr">
+      <c r="D33" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $946万
@@ -32583,7 +32583,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="E33" s="21" t="inlineStr">
+      <c r="E33" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $908万
@@ -32591,7 +32591,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="F33" s="21" t="inlineStr">
+      <c r="F33" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $864万
@@ -32599,7 +32599,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="G33" s="21" t="inlineStr">
+      <c r="G33" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2584万
@@ -32607,7 +32607,7 @@
 (25年-08月-10日)</t>
         </is>
       </c>
-      <c r="H33" s="21" t="inlineStr">
+      <c r="H33" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2348万
@@ -32615,7 +32615,7 @@
 (25年-08月-18日)</t>
         </is>
       </c>
-      <c r="I33" s="21" t="inlineStr">
+      <c r="I33" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2272万
@@ -32630,7 +32630,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B34" s="21" t="inlineStr">
+      <c r="B34" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1016万
@@ -32638,7 +32638,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="C34" s="21" t="inlineStr">
+      <c r="C34" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $938万
@@ -32646,7 +32646,7 @@
 (25年-07月-01日)</t>
         </is>
       </c>
-      <c r="D34" s="21" t="inlineStr">
+      <c r="D34" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $943万
@@ -32654,7 +32654,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="E34" s="21" t="inlineStr">
+      <c r="E34" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $905万
@@ -32662,7 +32662,7 @@
 (25年-07月-01日)</t>
         </is>
       </c>
-      <c r="F34" s="21" t="inlineStr">
+      <c r="F34" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $914万
@@ -32670,7 +32670,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="G34" s="21" t="inlineStr">
+      <c r="G34" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2565万
@@ -32678,7 +32678,7 @@
 (25年-09月-16日)</t>
         </is>
       </c>
-      <c r="H34" s="21" t="inlineStr">
+      <c r="H34" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2331万
@@ -32686,7 +32686,7 @@
 (25年-09月-16日)</t>
         </is>
       </c>
-      <c r="I34" s="21" t="inlineStr">
+      <c r="I34" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2296万
@@ -32701,7 +32701,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B35" s="21" t="inlineStr">
+      <c r="B35" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $952万
@@ -32709,7 +32709,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="C35" s="21" t="inlineStr">
+      <c r="C35" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $993万
@@ -32717,7 +32717,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="D35" s="21" t="inlineStr">
+      <c r="D35" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $939万
@@ -32725,7 +32725,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E35" s="21" t="inlineStr">
+      <c r="E35" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $901万
@@ -32733,7 +32733,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="F35" s="21" t="inlineStr">
+      <c r="F35" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $911万
@@ -32741,7 +32741,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="G35" s="21" t="inlineStr">
+      <c r="G35" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2680万
@@ -32749,7 +32749,7 @@
 (25年-09月-02日)</t>
         </is>
       </c>
-      <c r="H35" s="21" t="inlineStr">
+      <c r="H35" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2313万
@@ -32757,7 +32757,7 @@
 (25年-09月-25日)</t>
         </is>
       </c>
-      <c r="I35" s="21" t="inlineStr">
+      <c r="I35" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2280万
@@ -32772,7 +32772,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B36" s="21" t="inlineStr">
+      <c r="B36" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $949万
@@ -32780,7 +32780,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="C36" s="21" t="inlineStr">
+      <c r="C36" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $931万
@@ -32788,7 +32788,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="D36" s="21" t="inlineStr">
+      <c r="D36" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $935万
@@ -32796,7 +32796,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E36" s="21" t="inlineStr">
+      <c r="E36" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $954万
@@ -32804,7 +32804,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="F36" s="21" t="inlineStr">
+      <c r="F36" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $854万
@@ -32812,7 +32812,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="G36" s="21" t="inlineStr">
+      <c r="G36" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2556万
@@ -32820,7 +32820,7 @@
 (25年-09月-11日)</t>
         </is>
       </c>
-      <c r="H36" s="21" t="inlineStr">
+      <c r="H36" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2339万
@@ -32828,7 +32828,7 @@
 (25年-10月-14日)</t>
         </is>
       </c>
-      <c r="I36" s="21" t="inlineStr">
+      <c r="I36" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2263万
@@ -32843,7 +32843,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B37" s="21" t="inlineStr">
+      <c r="B37" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $945万
@@ -32851,7 +32851,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="C37" s="21" t="inlineStr">
+      <c r="C37" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $927万
@@ -32859,7 +32859,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="D37" s="21" t="inlineStr">
+      <c r="D37" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $931万
@@ -32867,7 +32867,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="E37" s="21" t="inlineStr">
+      <c r="E37" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $894万
@@ -32875,7 +32875,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="F37" s="21" t="inlineStr">
+      <c r="F37" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $850万
@@ -32883,7 +32883,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="G37" s="21" t="inlineStr">
+      <c r="G37" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2574万
@@ -32891,7 +32891,7 @@
 (25年-10月-08日)</t>
         </is>
       </c>
-      <c r="H37" s="21" t="inlineStr">
+      <c r="H37" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2365万
@@ -32899,7 +32899,7 @@
 (25年-10月-20日)</t>
         </is>
       </c>
-      <c r="I37" s="21" t="inlineStr">
+      <c r="I37" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2247万
@@ -32914,7 +32914,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B38" s="21" t="inlineStr">
+      <c r="B38" s="22" t="inlineStr">
         <is>
           <t>A | 440呎 (2房)
 $1158万
@@ -32922,7 +32922,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="C38" s="21" t="inlineStr">
+      <c r="C38" s="22" t="inlineStr">
         <is>
           <t>B | 439呎 (2房)
 $1089万
@@ -32930,7 +32930,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="D38" s="21" t="inlineStr">
+      <c r="D38" s="22" t="inlineStr">
         <is>
           <t>C | 444呎 (2房)
 $1092万
@@ -32938,7 +32938,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="E38" s="21" t="inlineStr">
+      <c r="E38" s="22" t="inlineStr">
         <is>
           <t>D | 430呎 (2房)
 $1182万
@@ -32946,7 +32946,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="F38" s="21" t="inlineStr">
+      <c r="F38" s="22" t="inlineStr">
         <is>
           <t>E | 408呎 (2房)
 $1040万
@@ -32954,7 +32954,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="G38" s="21" t="inlineStr">
+      <c r="G38" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2546万
@@ -32962,7 +32962,7 @@
 (25年-10月-09日)</t>
         </is>
       </c>
-      <c r="H38" s="21" t="inlineStr">
+      <c r="H38" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2471万
@@ -32970,7 +32970,7 @@
 (25年-10月-21日)</t>
         </is>
       </c>
-      <c r="I38" s="21" t="inlineStr">
+      <c r="I38" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2354万

--- a/files/港岛-黄竹坑-滶晨.xlsx
+++ b/files/港岛-黄竹坑-滶晨.xlsx
@@ -262,13 +262,13 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -770,12 +770,12 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -785,12 +785,12 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -840,12 +840,12 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -855,12 +855,12 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -987,12 +987,12 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1057,12 +1057,12 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1127,12 +1127,12 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -1500,12 +1500,12 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -13660,12 +13660,12 @@
       </c>
       <c r="H210" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I210" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J210" s="3" t="inlineStr">
@@ -13675,12 +13675,12 @@
       </c>
       <c r="K210" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L210" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M210" s="3" t="inlineStr">
@@ -13690,7 +13690,7 @@
       </c>
       <c r="N210" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -13730,12 +13730,12 @@
       </c>
       <c r="H211" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I211" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J211" s="3" t="inlineStr">
@@ -13745,12 +13745,12 @@
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L211" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M211" s="3" t="inlineStr">
@@ -13760,7 +13760,7 @@
       </c>
       <c r="N211" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -13800,12 +13800,12 @@
       </c>
       <c r="H212" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I212" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J212" s="3" t="inlineStr">
@@ -13815,12 +13815,12 @@
       </c>
       <c r="K212" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L212" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M212" s="3" t="inlineStr">
@@ -13830,7 +13830,7 @@
       </c>
       <c r="N212" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -13870,12 +13870,12 @@
       </c>
       <c r="H213" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I213" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J213" s="3" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L213" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M213" s="3" t="inlineStr">
@@ -13900,7 +13900,7 @@
       </c>
       <c r="N213" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -13940,12 +13940,12 @@
       </c>
       <c r="H214" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I214" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J214" s="3" t="inlineStr">
@@ -13955,12 +13955,12 @@
       </c>
       <c r="K214" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L214" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M214" s="3" t="inlineStr">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="N214" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -14072,12 +14072,12 @@
       </c>
       <c r="H216" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I216" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J216" s="3" t="inlineStr">
@@ -14087,12 +14087,12 @@
       </c>
       <c r="K216" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L216" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M216" s="3" t="inlineStr">
@@ -14102,7 +14102,7 @@
       </c>
       <c r="N216" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -14142,12 +14142,12 @@
       </c>
       <c r="H217" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I217" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J217" s="3" t="inlineStr">
@@ -14157,12 +14157,12 @@
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L217" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M217" s="3" t="inlineStr">
@@ -14172,7 +14172,7 @@
       </c>
       <c r="N217" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -14218,7 +14218,7 @@
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="K218" s="5" t="n">
@@ -14460,12 +14460,12 @@
       </c>
       <c r="H222" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I222" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J222" s="3" t="inlineStr">
@@ -14475,12 +14475,12 @@
       </c>
       <c r="K222" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L222" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M222" s="3" t="inlineStr">
@@ -14490,7 +14490,7 @@
       </c>
       <c r="N222" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -14530,12 +14530,12 @@
       </c>
       <c r="H223" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I223" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J223" s="3" t="inlineStr">
@@ -14545,12 +14545,12 @@
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L223" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M223" s="3" t="inlineStr">
@@ -14560,7 +14560,7 @@
       </c>
       <c r="N223" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -28720,47 +28720,26 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr"/>
-      <c r="C5" s="20" t="inlineStr"/>
-      <c r="D5" s="20" t="inlineStr"/>
-      <c r="E5" s="20" t="inlineStr"/>
-      <c r="F5" s="21" t="inlineStr">
-        <is>
-          <t>P1 | 1536呎 (4+房)
-招标单位
+          <t>41&amp;42</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 1020呎 (3房)
+-
 -
 (暂停销售)</t>
         </is>
       </c>
-      <c r="G5" s="20" t="inlineStr"/>
-      <c r="H5" s="20" t="inlineStr"/>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>41&amp;42</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>A | 1020呎 (3房)
-招标单位
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 1034呎 (3房)
+-
 -
 (暂停销售)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr">
-        <is>
-          <t>B | 1034呎 (3房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t>C | 1083呎 (3房)
 $3890万
@@ -28768,17 +28747,38 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr">
+      <c r="E5" s="22" t="inlineStr"/>
+      <c r="F5" s="22" t="inlineStr"/>
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>P2 | 3120呎 (4+房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
       </c>
-      <c r="H6" s="20" t="inlineStr"/>
+      <c r="H5" s="22" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr"/>
+      <c r="C6" s="22" t="inlineStr"/>
+      <c r="D6" s="22" t="inlineStr"/>
+      <c r="E6" s="22" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>P1 | 1536呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr"/>
+      <c r="H6" s="22" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
@@ -28786,7 +28786,7 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1593万
@@ -28794,7 +28794,7 @@
 (26年-04月-29日)</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1142万
@@ -28802,7 +28802,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1235万
@@ -28810,24 +28810,24 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr"/>
-      <c r="F7" s="21" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
       </c>
-      <c r="G7" s="21" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
       </c>
-      <c r="H7" s="20" t="inlineStr"/>
+      <c r="H7" s="22" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -28835,7 +28835,7 @@
           <t>39</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1566万
@@ -28843,7 +28843,7 @@
 (26年-04月-23日)</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1130万
@@ -28851,7 +28851,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1276万
@@ -28859,16 +28859,16 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr"/>
-      <c r="F8" s="21" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr"/>
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
       </c>
-      <c r="G8" s="22" t="inlineStr">
+      <c r="G8" s="21" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $10775万
@@ -28876,7 +28876,7 @@
 (26年-01月-26日)</t>
         </is>
       </c>
-      <c r="H8" s="20" t="inlineStr"/>
+      <c r="H8" s="22" t="inlineStr"/>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -28884,7 +28884,7 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1429万
@@ -28892,7 +28892,7 @@
 (26年-03月-05日)</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1227万
@@ -28900,7 +28900,7 @@
 (25年-08月-10日)</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1245万
@@ -28908,8 +28908,8 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr"/>
-      <c r="F9" s="22" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr"/>
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $7296万
@@ -28917,7 +28917,7 @@
 (25年-11月-05日)</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $8530万
@@ -28925,7 +28925,7 @@
 (25年-06月-25日)</t>
         </is>
       </c>
-      <c r="H9" s="20" t="inlineStr"/>
+      <c r="H9" s="22" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
@@ -28933,7 +28933,7 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1117万
@@ -28941,7 +28941,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1131万
@@ -28949,7 +28949,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1154万
@@ -28957,8 +28957,8 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr"/>
-      <c r="F10" s="22" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr"/>
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $6543万
@@ -28966,7 +28966,7 @@
 (25年-06月-22日)</t>
         </is>
       </c>
-      <c r="G10" s="22" t="inlineStr">
+      <c r="G10" s="21" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $8189万
@@ -28974,7 +28974,7 @@
 (25年-06月-22日)</t>
         </is>
       </c>
-      <c r="H10" s="20" t="inlineStr"/>
+      <c r="H10" s="22" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -28982,7 +28982,7 @@
           <t>36</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1086万
@@ -28990,7 +28990,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1100万
@@ -28998,7 +28998,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="D11" s="22" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1217万
@@ -29006,8 +29006,8 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr"/>
-      <c r="F11" s="22" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr"/>
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $6420万
@@ -29015,7 +29015,7 @@
 (25年-06月-23日)</t>
         </is>
       </c>
-      <c r="G11" s="22" t="inlineStr">
+      <c r="G11" s="21" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $7558万
@@ -29023,7 +29023,7 @@
 (25年-06月-23日)</t>
         </is>
       </c>
-      <c r="H11" s="20" t="inlineStr"/>
+      <c r="H11" s="22" t="inlineStr"/>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
@@ -29031,7 +29031,7 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1083万
@@ -29039,7 +29039,7 @@
 (25年-07月-22日)</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1097万
@@ -29047,7 +29047,7 @@
 (25年-07月-22日)</t>
         </is>
       </c>
-      <c r="D12" s="22" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1137万
@@ -29055,8 +29055,8 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="E12" s="20" t="inlineStr"/>
-      <c r="F12" s="22" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr"/>
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $6298万
@@ -29064,7 +29064,7 @@
 (25年-06月-23日)</t>
         </is>
       </c>
-      <c r="G12" s="22" t="inlineStr">
+      <c r="G12" s="21" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $7421万
@@ -29072,7 +29072,7 @@
 (25年-06月-23日)</t>
         </is>
       </c>
-      <c r="H12" s="20" t="inlineStr"/>
+      <c r="H12" s="22" t="inlineStr"/>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -29080,7 +29080,7 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1067万
@@ -29088,7 +29088,7 @@
 (25年-06月-24日)</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1081万
@@ -29096,7 +29096,7 @@
 (25年-07月-22日)</t>
         </is>
       </c>
-      <c r="D13" s="22" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1128万
@@ -29104,8 +29104,8 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="E13" s="20" t="inlineStr"/>
-      <c r="F13" s="22" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr"/>
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $6089万
@@ -29113,7 +29113,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="G13" s="22" t="inlineStr">
+      <c r="G13" s="21" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $7319万
@@ -29121,7 +29121,7 @@
 (25年-06月-23日)</t>
         </is>
       </c>
-      <c r="H13" s="20" t="inlineStr"/>
+      <c r="H13" s="22" t="inlineStr"/>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -29129,7 +29129,7 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1048万
@@ -29137,7 +29137,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1061万
@@ -29145,7 +29145,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1123万
@@ -29153,8 +29153,8 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="E14" s="20" t="inlineStr"/>
-      <c r="F14" s="22" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr"/>
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $5990万
@@ -29162,7 +29162,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="G14" s="22" t="inlineStr">
+      <c r="G14" s="21" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $6726万
@@ -29170,7 +29170,7 @@
 (25年-06月-24日)</t>
         </is>
       </c>
-      <c r="H14" s="20" t="inlineStr"/>
+      <c r="H14" s="22" t="inlineStr"/>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
@@ -29178,7 +29178,7 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1107万
@@ -29186,7 +29186,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1055万
@@ -29194,7 +29194,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="D15" s="22" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1187万
@@ -29202,8 +29202,8 @@
 (25年-06月-19日)</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr"/>
-      <c r="F15" s="22" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr"/>
+      <c r="F15" s="21" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $5574万
@@ -29211,7 +29211,7 @@
 (25年-06月-11日)</t>
         </is>
       </c>
-      <c r="G15" s="22" t="inlineStr">
+      <c r="G15" s="21" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $6596万
@@ -29219,7 +29219,7 @@
 (25年-06月-11日)</t>
         </is>
       </c>
-      <c r="H15" s="20" t="inlineStr"/>
+      <c r="H15" s="22" t="inlineStr"/>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
@@ -29227,7 +29227,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1100万
@@ -29235,7 +29235,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="C16" s="22" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1114万
@@ -29243,7 +29243,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1112万
@@ -29251,8 +29251,8 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E16" s="20" t="inlineStr"/>
-      <c r="F16" s="22" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr"/>
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $5076万
@@ -29260,7 +29260,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="G16" s="22" t="inlineStr">
+      <c r="G16" s="21" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $6467万
@@ -29268,7 +29268,7 @@
 (25年-06月-11日)</t>
         </is>
       </c>
-      <c r="H16" s="20" t="inlineStr"/>
+      <c r="H16" s="22" t="inlineStr"/>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
@@ -29276,7 +29276,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1094万
@@ -29284,7 +29284,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1108万
@@ -29292,7 +29292,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="D17" s="22" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1175万
@@ -29300,8 +29300,8 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="E17" s="20" t="inlineStr"/>
-      <c r="F17" s="22" t="inlineStr">
+      <c r="E17" s="22" t="inlineStr"/>
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t>P1 | 1469呎 (4+房)
 $5739万
@@ -29309,7 +29309,7 @@
 (25年-06月-18日)</t>
         </is>
       </c>
-      <c r="G17" s="22" t="inlineStr">
+      <c r="G17" s="21" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $6739万
@@ -29317,7 +29317,7 @@
 (25年-06月-18日)</t>
         </is>
       </c>
-      <c r="H17" s="20" t="inlineStr"/>
+      <c r="H17" s="22" t="inlineStr"/>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
@@ -29325,7 +29325,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1025万
@@ -29333,7 +29333,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1036万
@@ -29341,7 +29341,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="D18" s="22" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1084万
@@ -29349,7 +29349,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="E18" s="22" t="inlineStr">
+      <c r="E18" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $1011万
@@ -29357,7 +29357,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="F18" s="22" t="inlineStr">
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t>P1 | 1258呎 (4+房)
 $4422万
@@ -29365,7 +29365,7 @@
 (25年-06月-10日)</t>
         </is>
       </c>
-      <c r="G18" s="22" t="inlineStr">
+      <c r="G18" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2694万
@@ -29373,7 +29373,7 @@
 (25年-07月-01日)</t>
         </is>
       </c>
-      <c r="H18" s="22" t="inlineStr">
+      <c r="H18" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3313万
@@ -29388,7 +29388,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B19" s="22" t="inlineStr">
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1021万
@@ -29396,7 +29396,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1032万
@@ -29404,7 +29404,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="D19" s="22" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1066万
@@ -29412,7 +29412,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E19" s="22" t="inlineStr">
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $1005万
@@ -29420,7 +29420,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="F19" s="22" t="inlineStr">
+      <c r="F19" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4351万
@@ -29428,7 +29428,7 @@
 (25年-06月-24日)</t>
         </is>
       </c>
-      <c r="G19" s="22" t="inlineStr">
+      <c r="G19" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2653万
@@ -29436,7 +29436,7 @@
 (25年-06月-29日)</t>
         </is>
       </c>
-      <c r="H19" s="22" t="inlineStr">
+      <c r="H19" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3447万
@@ -29451,7 +29451,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B20" s="22" t="inlineStr">
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1017万
@@ -29459,7 +29459,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="C20" s="22" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1028万
@@ -29467,7 +29467,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="D20" s="22" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1076万
@@ -29475,7 +29475,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="E20" s="22" t="inlineStr">
+      <c r="E20" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $999万
@@ -29483,7 +29483,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="F20" s="22" t="inlineStr">
+      <c r="F20" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4540万
@@ -29491,7 +29491,7 @@
 (25年-06月-25日)</t>
         </is>
       </c>
-      <c r="G20" s="22" t="inlineStr">
+      <c r="G20" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2612万
@@ -29499,7 +29499,7 @@
 (25年-06月-22日)</t>
         </is>
       </c>
-      <c r="H20" s="22" t="inlineStr">
+      <c r="H20" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3256万
@@ -29514,7 +29514,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B21" s="22" t="inlineStr">
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1013万
@@ -29522,7 +29522,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="C21" s="22" t="inlineStr">
+      <c r="C21" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1024万
@@ -29530,7 +29530,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="D21" s="22" t="inlineStr">
+      <c r="D21" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1138万
@@ -29538,7 +29538,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="E21" s="22" t="inlineStr">
+      <c r="E21" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $993万
@@ -29546,7 +29546,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="F21" s="22" t="inlineStr">
+      <c r="F21" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4265万
@@ -29554,7 +29554,7 @@
 (25年-06月-11日)</t>
         </is>
       </c>
-      <c r="G21" s="22" t="inlineStr">
+      <c r="G21" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2579万
@@ -29562,7 +29562,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="H21" s="22" t="inlineStr">
+      <c r="H21" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3220万
@@ -29577,7 +29577,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1009万
@@ -29585,7 +29585,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="C22" s="22" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1020万
@@ -29593,7 +29593,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="D22" s="22" t="inlineStr">
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1067万
@@ -29601,7 +29601,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="E22" s="22" t="inlineStr">
+      <c r="E22" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $987万
@@ -29609,7 +29609,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="F22" s="22" t="inlineStr">
+      <c r="F22" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4229万
@@ -29617,7 +29617,7 @@
 (25年-06月-19日)</t>
         </is>
       </c>
-      <c r="G22" s="22" t="inlineStr">
+      <c r="G22" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2688万
@@ -29625,7 +29625,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="H22" s="22" t="inlineStr">
+      <c r="H22" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3056万
@@ -29640,7 +29640,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1005万
@@ -29648,7 +29648,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="C23" s="22" t="inlineStr">
+      <c r="C23" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1079万
@@ -29656,7 +29656,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="D23" s="22" t="inlineStr">
+      <c r="D23" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1063万
@@ -29664,7 +29664,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="E23" s="22" t="inlineStr">
+      <c r="E23" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $984万
@@ -29672,7 +29672,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="F23" s="22" t="inlineStr">
+      <c r="F23" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4193万
@@ -29680,7 +29680,7 @@
 (25年-06月-23日)</t>
         </is>
       </c>
-      <c r="G23" s="22" t="inlineStr">
+      <c r="G23" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2529万
@@ -29688,7 +29688,7 @@
 (25年-06月-23日)</t>
         </is>
       </c>
-      <c r="H23" s="22" t="inlineStr">
+      <c r="H23" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2876万
@@ -29703,7 +29703,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1001万
@@ -29711,7 +29711,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="C24" s="22" t="inlineStr">
+      <c r="C24" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1008万
@@ -29719,7 +29719,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="D24" s="22" t="inlineStr">
+      <c r="D24" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1059万
@@ -29727,7 +29727,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E24" s="22" t="inlineStr">
+      <c r="E24" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $980万
@@ -29735,7 +29735,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="F24" s="22" t="inlineStr">
+      <c r="F24" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4184万
@@ -29743,7 +29743,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="G24" s="22" t="inlineStr">
+      <c r="G24" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2504万
@@ -29751,7 +29751,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="H24" s="22" t="inlineStr">
+      <c r="H24" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3299万
@@ -29766,7 +29766,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $997万
@@ -29774,7 +29774,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="C25" s="22" t="inlineStr">
+      <c r="C25" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1004万
@@ -29782,7 +29782,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="D25" s="22" t="inlineStr">
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1113万
@@ -29790,7 +29790,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="E25" s="22" t="inlineStr">
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $1037万
@@ -29798,7 +29798,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="F25" s="22" t="inlineStr">
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4374万
@@ -29806,7 +29806,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="G25" s="22" t="inlineStr">
+      <c r="G25" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2480万
@@ -29814,7 +29814,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="H25" s="22" t="inlineStr">
+      <c r="H25" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3122万
@@ -29829,7 +29829,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B26" s="22" t="inlineStr">
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $993万
@@ -29837,7 +29837,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="C26" s="22" t="inlineStr">
+      <c r="C26" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1000万
@@ -29845,7 +29845,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="D26" s="22" t="inlineStr">
+      <c r="D26" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1043万
@@ -29853,7 +29853,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="E26" s="22" t="inlineStr">
+      <c r="E26" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $972万
@@ -29861,7 +29861,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="F26" s="22" t="inlineStr">
+      <c r="F26" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3725万
@@ -29869,7 +29869,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="G26" s="22" t="inlineStr">
+      <c r="G26" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2406万
@@ -29877,7 +29877,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="H26" s="22" t="inlineStr">
+      <c r="H26" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2893万
@@ -29892,7 +29892,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B27" s="22" t="inlineStr">
+      <c r="B27" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $989万
@@ -29900,7 +29900,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="C27" s="22" t="inlineStr">
+      <c r="C27" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $996万
@@ -29908,7 +29908,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="D27" s="22" t="inlineStr">
+      <c r="D27" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1039万
@@ -29916,7 +29916,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="E27" s="22" t="inlineStr">
+      <c r="E27" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $968万
@@ -29924,7 +29924,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="F27" s="22" t="inlineStr">
+      <c r="F27" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3680万
@@ -29932,7 +29932,7 @@
 (25年-06月-13日)</t>
         </is>
       </c>
-      <c r="G27" s="22" t="inlineStr">
+      <c r="G27" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2526万
@@ -29940,7 +29940,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="H27" s="22" t="inlineStr">
+      <c r="H27" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2850万
@@ -29955,7 +29955,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B28" s="22" t="inlineStr">
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $985万
@@ -29963,7 +29963,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="C28" s="22" t="inlineStr">
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $992万
@@ -29971,7 +29971,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="D28" s="22" t="inlineStr">
+      <c r="D28" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1022万
@@ -29979,7 +29979,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="E28" s="22" t="inlineStr">
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $1024万
@@ -29987,7 +29987,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="F28" s="22" t="inlineStr">
+      <c r="F28" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3955万
@@ -29995,7 +29995,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="G28" s="22" t="inlineStr">
+      <c r="G28" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2349万
@@ -30003,7 +30003,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="H28" s="22" t="inlineStr">
+      <c r="H28" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2652万
@@ -30018,7 +30018,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B29" s="22" t="inlineStr">
+      <c r="B29" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $981万
@@ -30026,7 +30026,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="C29" s="22" t="inlineStr">
+      <c r="C29" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1049万
@@ -30034,7 +30034,7 @@
 (25年-07月-01日)</t>
         </is>
       </c>
-      <c r="D29" s="22" t="inlineStr">
+      <c r="D29" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1095万
@@ -30042,7 +30042,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E29" s="22" t="inlineStr">
+      <c r="E29" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $948万
@@ -30050,7 +30050,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="F29" s="22" t="inlineStr">
+      <c r="F29" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3818万
@@ -30058,7 +30058,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="G29" s="22" t="inlineStr">
+      <c r="G29" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2319万
@@ -30066,7 +30066,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="H29" s="22" t="inlineStr">
+      <c r="H29" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2784万
@@ -30081,7 +30081,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B30" s="22" t="inlineStr">
+      <c r="B30" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1038万
@@ -30089,7 +30089,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="C30" s="22" t="inlineStr">
+      <c r="C30" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1045万
@@ -30097,7 +30097,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="D30" s="22" t="inlineStr">
+      <c r="D30" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1091万
@@ -30105,7 +30105,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E30" s="22" t="inlineStr">
+      <c r="E30" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $956万
@@ -30113,7 +30113,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="F30" s="22" t="inlineStr">
+      <c r="F30" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3862万
@@ -30121,7 +30121,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="G30" s="22" t="inlineStr">
+      <c r="G30" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2396万
@@ -30129,7 +30129,7 @@
 (25年-08月-05日)</t>
         </is>
       </c>
-      <c r="H30" s="22" t="inlineStr">
+      <c r="H30" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2708万
@@ -30144,7 +30144,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B31" s="22" t="inlineStr">
+      <c r="B31" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1034万
@@ -30152,7 +30152,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="C31" s="22" t="inlineStr">
+      <c r="C31" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1041万
@@ -30160,7 +30160,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="D31" s="22" t="inlineStr">
+      <c r="D31" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1086万
@@ -30168,7 +30168,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="E31" s="22" t="inlineStr">
+      <c r="E31" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $952万
@@ -30176,7 +30176,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="F31" s="22" t="inlineStr">
+      <c r="F31" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3819万
@@ -30184,7 +30184,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="G31" s="22" t="inlineStr">
+      <c r="G31" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2361万
@@ -30192,7 +30192,7 @@
 (25年-07月-29日)</t>
         </is>
       </c>
-      <c r="H31" s="22" t="inlineStr">
+      <c r="H31" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2668万
@@ -30207,7 +30207,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B32" s="22" t="inlineStr">
+      <c r="B32" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1030万
@@ -30215,7 +30215,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="C32" s="22" t="inlineStr">
+      <c r="C32" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $976万
@@ -30223,7 +30223,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="D32" s="22" t="inlineStr">
+      <c r="D32" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1006万
@@ -30231,7 +30231,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="E32" s="22" t="inlineStr">
+      <c r="E32" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $949万
@@ -30239,7 +30239,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="F32" s="22" t="inlineStr">
+      <c r="F32" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3785万
@@ -30247,7 +30247,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="G32" s="22" t="inlineStr">
+      <c r="G32" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2338万
@@ -30255,7 +30255,7 @@
 (25年-09月-17日)</t>
         </is>
       </c>
-      <c r="H32" s="22" t="inlineStr">
+      <c r="H32" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2641万
@@ -30270,7 +30270,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B33" s="22" t="inlineStr">
+      <c r="B33" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1026万
@@ -30278,7 +30278,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="C33" s="22" t="inlineStr">
+      <c r="C33" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1033万
@@ -30286,7 +30286,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="D33" s="22" t="inlineStr">
+      <c r="D33" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1014万
@@ -30294,7 +30294,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E33" s="22" t="inlineStr">
+      <c r="E33" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $945万
@@ -30302,7 +30302,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="F33" s="22" t="inlineStr">
+      <c r="F33" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3474万
@@ -30310,7 +30310,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="G33" s="22" t="inlineStr">
+      <c r="G33" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2306万
@@ -30318,7 +30318,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="H33" s="22" t="inlineStr">
+      <c r="H33" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2578万
@@ -30333,7 +30333,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B34" s="22" t="inlineStr">
+      <c r="B34" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $962万
@@ -30341,7 +30341,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="C34" s="22" t="inlineStr">
+      <c r="C34" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $968万
@@ -30349,7 +30349,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="D34" s="22" t="inlineStr">
+      <c r="D34" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1010万
@@ -30357,7 +30357,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E34" s="22" t="inlineStr">
+      <c r="E34" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $938万
@@ -30365,7 +30365,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="F34" s="22" t="inlineStr">
+      <c r="F34" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3632万
@@ -30373,7 +30373,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="G34" s="22" t="inlineStr">
+      <c r="G34" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2392万
@@ -30381,7 +30381,7 @@
 (25年-07月-30日)</t>
         </is>
       </c>
-      <c r="H34" s="22" t="inlineStr">
+      <c r="H34" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2586万
@@ -30396,7 +30396,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B35" s="22" t="inlineStr">
+      <c r="B35" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1018万
@@ -30404,7 +30404,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="C35" s="22" t="inlineStr">
+      <c r="C35" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $964万
@@ -30412,7 +30412,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="D35" s="22" t="inlineStr">
+      <c r="D35" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1069万
@@ -30420,7 +30420,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="E35" s="22" t="inlineStr">
+      <c r="E35" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $928万
@@ -30428,7 +30428,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="F35" s="22" t="inlineStr">
+      <c r="F35" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3426万
@@ -30436,7 +30436,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="G35" s="22" t="inlineStr">
+      <c r="G35" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2399万
@@ -30444,7 +30444,7 @@
 (25年-08月-25日)</t>
         </is>
       </c>
-      <c r="H35" s="22" t="inlineStr">
+      <c r="H35" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2675万
@@ -30459,7 +30459,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B36" s="22" t="inlineStr">
+      <c r="B36" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1014万
@@ -30467,7 +30467,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="C36" s="22" t="inlineStr">
+      <c r="C36" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $960万
@@ -30475,7 +30475,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="D36" s="22" t="inlineStr">
+      <c r="D36" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1002万
@@ -30483,7 +30483,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="E36" s="22" t="inlineStr">
+      <c r="E36" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $976万
@@ -30491,7 +30491,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="F36" s="22" t="inlineStr">
+      <c r="F36" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3881万
@@ -30499,7 +30499,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="G36" s="22" t="inlineStr">
+      <c r="G36" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2314万
@@ -30507,7 +30507,7 @@
 (25年-09月-08日)</t>
         </is>
       </c>
-      <c r="H36" s="22" t="inlineStr">
+      <c r="H36" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2570万
@@ -30522,7 +30522,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B37" s="22" t="inlineStr">
+      <c r="B37" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1010万
@@ -30530,7 +30530,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="C37" s="22" t="inlineStr">
+      <c r="C37" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $957万
@@ -30538,7 +30538,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="D37" s="22" t="inlineStr">
+      <c r="D37" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $998万
@@ -30546,7 +30546,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="E37" s="22" t="inlineStr">
+      <c r="E37" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $910万
@@ -30554,7 +30554,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="F37" s="22" t="inlineStr">
+      <c r="F37" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3577万
@@ -30562,7 +30562,7 @@
 (25年-08月-05日)</t>
         </is>
       </c>
-      <c r="G37" s="22" t="inlineStr">
+      <c r="G37" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2490万
@@ -30570,7 +30570,7 @@
 (25年-12月-30日)</t>
         </is>
       </c>
-      <c r="H37" s="22" t="inlineStr">
+      <c r="H37" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2686万
@@ -30585,7 +30585,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B38" s="22" t="inlineStr">
+      <c r="B38" s="21" t="inlineStr">
         <is>
           <t>A | 440呎 (2房)
 $1088万
@@ -30593,7 +30593,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="C38" s="22" t="inlineStr">
+      <c r="C38" s="21" t="inlineStr">
         <is>
           <t>B | 448呎 (2房)
 $1120万
@@ -30601,7 +30601,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="D38" s="22" t="inlineStr">
+      <c r="D38" s="21" t="inlineStr">
         <is>
           <t>C | 467呎 (2房)
 $1238万
@@ -30609,7 +30609,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="E38" s="22" t="inlineStr">
+      <c r="E38" s="21" t="inlineStr">
         <is>
           <t>D | 430呎 (2房)
 $999万
@@ -30617,7 +30617,7 @@
 (25年-07月-20日)</t>
         </is>
       </c>
-      <c r="F38" s="22" t="inlineStr">
+      <c r="F38" s="21" t="inlineStr">
         <is>
           <t>P1 | 1162呎 (4+房)
 $3650万
@@ -30625,7 +30625,7 @@
 (25年-07月-28日)</t>
         </is>
       </c>
-      <c r="G38" s="22" t="inlineStr">
+      <c r="G38" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2436万
@@ -30633,7 +30633,7 @@
 (25年-12月-18日)</t>
         </is>
       </c>
-      <c r="H38" s="22" t="inlineStr">
+      <c r="H38" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2758万
@@ -30792,32 +30792,10 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr"/>
-      <c r="C5" s="20" t="inlineStr"/>
-      <c r="D5" s="20" t="inlineStr"/>
-      <c r="E5" s="20" t="inlineStr"/>
-      <c r="F5" s="20" t="inlineStr"/>
-      <c r="G5" s="21" t="inlineStr">
-        <is>
-          <t>P1 | 1417呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H5" s="20" t="inlineStr"/>
-      <c r="I5" s="20" t="inlineStr"/>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
           <t>41&amp;42</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>A | 1020呎 (3房)
 $3652万
@@ -30825,41 +30803,63 @@
 (26年-03月-11日)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>B | 1016呎 (3房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>C | 1029呎 (3房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>D | 1083呎 (3房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
       </c>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="21" t="inlineStr">
+      <c r="F5" s="22" t="inlineStr"/>
+      <c r="G5" s="22" t="inlineStr"/>
+      <c r="H5" s="20" t="inlineStr">
         <is>
           <t>P2 | 2871呎 (4+房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
       </c>
-      <c r="I6" s="20" t="inlineStr"/>
+      <c r="I5" s="22" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr"/>
+      <c r="C6" s="22" t="inlineStr"/>
+      <c r="D6" s="22" t="inlineStr"/>
+      <c r="E6" s="22" t="inlineStr"/>
+      <c r="F6" s="22" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>P1 | 1417呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H6" s="22" t="inlineStr"/>
+      <c r="I6" s="22" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
@@ -30867,7 +30867,7 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1245万
@@ -30875,7 +30875,7 @@
 (25年-09月-10日)</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1138万
@@ -30883,7 +30883,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1137万
@@ -30891,7 +30891,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E7" s="21" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1804万
@@ -30899,24 +30899,24 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="F7" s="20" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr">
+      <c r="F7" s="22" t="inlineStr"/>
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
       </c>
-      <c r="H7" s="21" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
       </c>
-      <c r="I7" s="20" t="inlineStr"/>
+      <c r="I7" s="22" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -30924,7 +30924,7 @@
           <t>39</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1180万
@@ -30932,7 +30932,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1556万
@@ -30940,7 +30940,7 @@
 (26年-04月-21日)</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1196万
@@ -30948,7 +30948,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr">
+      <c r="E8" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1532万
@@ -30956,24 +30956,24 @@
 (26年-06月-17日)</t>
         </is>
       </c>
-      <c r="F8" s="20" t="inlineStr"/>
-      <c r="G8" s="21" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr"/>
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
       </c>
-      <c r="H8" s="21" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
       </c>
-      <c r="I8" s="20" t="inlineStr"/>
+      <c r="I8" s="22" t="inlineStr"/>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -30981,7 +30981,7 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1543万
@@ -30989,7 +30989,7 @@
 (26年-04月-27日)</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1169万
@@ -30997,7 +30997,7 @@
 (25年-07月-30日)</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1174万
@@ -31005,7 +31005,7 @@
 (25年-07月-24日)</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1137万
@@ -31013,8 +31013,8 @@
 (25年-07月-23日)</t>
         </is>
       </c>
-      <c r="F9" s="20" t="inlineStr"/>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="F9" s="22" t="inlineStr"/>
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $6754万
@@ -31022,7 +31022,7 @@
 (25年-11月-30日)</t>
         </is>
       </c>
-      <c r="H9" s="22" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $8574万
@@ -31030,7 +31030,7 @@
 (26年-02月-11日)</t>
         </is>
       </c>
-      <c r="I9" s="20" t="inlineStr"/>
+      <c r="I9" s="22" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
@@ -31038,7 +31038,7 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1170万
@@ -31046,7 +31046,7 @@
 (25年-07月-21日)</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1112万
@@ -31054,7 +31054,7 @@
 (25年-07月-22日)</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1116万
@@ -31062,7 +31062,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="E10" s="22" t="inlineStr">
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1081万
@@ -31070,8 +31070,8 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="F10" s="20" t="inlineStr"/>
-      <c r="G10" s="22" t="inlineStr">
+      <c r="F10" s="22" t="inlineStr"/>
+      <c r="G10" s="21" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $6086万
@@ -31079,7 +31079,7 @@
 (25年-09月-08日)</t>
         </is>
       </c>
-      <c r="H10" s="22" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $7592万
@@ -31087,7 +31087,7 @@
 (25年-08月-11日)</t>
         </is>
       </c>
-      <c r="I10" s="20" t="inlineStr"/>
+      <c r="I10" s="22" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -31095,7 +31095,7 @@
           <t>36</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1084万
@@ -31103,7 +31103,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1081万
@@ -31111,7 +31111,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="D11" s="22" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1276万
@@ -31119,7 +31119,7 @@
 (26年-02月-26日)</t>
         </is>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1064万
@@ -31127,8 +31127,8 @@
 (25年-08月-03日)</t>
         </is>
       </c>
-      <c r="F11" s="20" t="inlineStr"/>
-      <c r="G11" s="22" t="inlineStr">
+      <c r="F11" s="22" t="inlineStr"/>
+      <c r="G11" s="21" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $5644万
@@ -31136,7 +31136,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="H11" s="22" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $6715万
@@ -31144,7 +31144,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="I11" s="20" t="inlineStr"/>
+      <c r="I11" s="22" t="inlineStr"/>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
@@ -31152,7 +31152,7 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1081万
@@ -31160,7 +31160,7 @@
 (25年-07月-22日)</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1078万
@@ -31168,7 +31168,7 @@
 (25年-07月-22日)</t>
         </is>
       </c>
-      <c r="D12" s="22" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1082万
@@ -31176,7 +31176,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1048万
@@ -31184,8 +31184,8 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="F12" s="20" t="inlineStr"/>
-      <c r="G12" s="22" t="inlineStr">
+      <c r="F12" s="22" t="inlineStr"/>
+      <c r="G12" s="21" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $5431万
@@ -31193,7 +31193,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="H12" s="22" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $6324万
@@ -31201,7 +31201,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="I12" s="20" t="inlineStr"/>
+      <c r="I12" s="22" t="inlineStr"/>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -31209,7 +31209,7 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1065万
@@ -31217,7 +31217,7 @@
 (25年-07月-22日)</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1128万
@@ -31225,7 +31225,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="D13" s="22" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1132万
@@ -31233,7 +31233,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="E13" s="22" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $998万
@@ -31241,8 +31241,8 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="F13" s="20" t="inlineStr"/>
-      <c r="G13" s="22" t="inlineStr">
+      <c r="F13" s="22" t="inlineStr"/>
+      <c r="G13" s="21" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $5404万
@@ -31250,7 +31250,7 @@
 (25年-07月-24日)</t>
         </is>
       </c>
-      <c r="H13" s="22" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $6018万
@@ -31258,7 +31258,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="I13" s="20" t="inlineStr"/>
+      <c r="I13" s="22" t="inlineStr"/>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -31266,7 +31266,7 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1046万
@@ -31274,7 +31274,7 @@
 (25年-06月-19日)</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1108万
@@ -31282,7 +31282,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1046万
@@ -31290,7 +31290,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="E14" s="22" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $993万
@@ -31298,8 +31298,8 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="F14" s="20" t="inlineStr"/>
-      <c r="G14" s="22" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr"/>
+      <c r="G14" s="21" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $5494万
@@ -31307,7 +31307,7 @@
 (25年-07月-22日)</t>
         </is>
       </c>
-      <c r="H14" s="22" t="inlineStr">
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $6220万
@@ -31315,7 +31315,7 @@
 (25年-06月-23日)</t>
         </is>
       </c>
-      <c r="I14" s="20" t="inlineStr"/>
+      <c r="I14" s="22" t="inlineStr"/>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
@@ -31323,7 +31323,7 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1040万
@@ -31331,7 +31331,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1102万
@@ -31339,7 +31339,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="D15" s="22" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1040万
@@ -31347,7 +31347,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="E15" s="22" t="inlineStr">
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $988万
@@ -31355,8 +31355,8 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="F15" s="20" t="inlineStr"/>
-      <c r="G15" s="22" t="inlineStr">
+      <c r="F15" s="22" t="inlineStr"/>
+      <c r="G15" s="21" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $5052万
@@ -31364,7 +31364,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="H15" s="22" t="inlineStr">
+      <c r="H15" s="21" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $5850万
@@ -31372,7 +31372,7 @@
 (25年-06月-22日)</t>
         </is>
       </c>
-      <c r="I15" s="20" t="inlineStr"/>
+      <c r="I15" s="22" t="inlineStr"/>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
@@ -31380,7 +31380,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1034万
@@ -31388,7 +31388,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="C16" s="22" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1030万
@@ -31396,7 +31396,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1099万
@@ -31404,7 +31404,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="E16" s="22" t="inlineStr">
+      <c r="E16" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $983万
@@ -31412,8 +31412,8 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="F16" s="20" t="inlineStr"/>
-      <c r="G16" s="22" t="inlineStr">
+      <c r="F16" s="22" t="inlineStr"/>
+      <c r="G16" s="21" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $4996万
@@ -31421,7 +31421,7 @@
 (25年-06月-08日)</t>
         </is>
       </c>
-      <c r="H16" s="22" t="inlineStr">
+      <c r="H16" s="21" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $5791万
@@ -31429,7 +31429,7 @@
 (25年-06月-24日)</t>
         </is>
       </c>
-      <c r="I16" s="20" t="inlineStr"/>
+      <c r="I16" s="22" t="inlineStr"/>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
@@ -31437,7 +31437,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1027万
@@ -31445,7 +31445,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1024万
@@ -31453,7 +31453,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="D17" s="22" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1028万
@@ -31461,7 +31461,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="E17" s="22" t="inlineStr">
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $978万
@@ -31469,8 +31469,8 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="F17" s="20" t="inlineStr"/>
-      <c r="G17" s="22" t="inlineStr">
+      <c r="F17" s="22" t="inlineStr"/>
+      <c r="G17" s="21" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $4839万
@@ -31478,7 +31478,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="H17" s="22" t="inlineStr">
+      <c r="H17" s="21" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $5609万
@@ -31486,7 +31486,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="I17" s="20" t="inlineStr"/>
+      <c r="I17" s="22" t="inlineStr"/>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
@@ -31494,7 +31494,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1083万
@@ -31502,7 +31502,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1063万
@@ -31510,7 +31510,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="D18" s="22" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1005万
@@ -31518,7 +31518,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E18" s="22" t="inlineStr">
+      <c r="E18" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $964万
@@ -31526,7 +31526,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="F18" s="22" t="inlineStr">
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $917万
@@ -31534,7 +31534,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="G18" s="22" t="inlineStr">
+      <c r="G18" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $3273万
@@ -31542,7 +31542,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="H18" s="22" t="inlineStr">
+      <c r="H18" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2726万
@@ -31550,7 +31550,7 @@
 (25年-07月-30日)</t>
         </is>
       </c>
-      <c r="I18" s="22" t="inlineStr">
+      <c r="I18" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2494万
@@ -31565,7 +31565,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B19" s="22" t="inlineStr">
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1015万
@@ -31573,7 +31573,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1059万
@@ -31581,7 +31581,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="D19" s="22" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1063万
@@ -31589,7 +31589,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="E19" s="22" t="inlineStr">
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $961万
@@ -31597,7 +31597,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="F19" s="22" t="inlineStr">
+      <c r="F19" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $971万
@@ -31605,7 +31605,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="G19" s="22" t="inlineStr">
+      <c r="G19" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $3084万
@@ -31613,7 +31613,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="H19" s="22" t="inlineStr">
+      <c r="H19" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2582万
@@ -31621,7 +31621,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="I19" s="22" t="inlineStr">
+      <c r="I19" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2591万
@@ -31636,7 +31636,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B20" s="22" t="inlineStr">
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1011万
@@ -31644,7 +31644,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="C20" s="22" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1054万
@@ -31652,7 +31652,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="D20" s="22" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1059万
@@ -31660,7 +31660,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="E20" s="22" t="inlineStr">
+      <c r="E20" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $957万
@@ -31668,7 +31668,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="F20" s="22" t="inlineStr">
+      <c r="F20" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $910万
@@ -31676,7 +31676,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="G20" s="22" t="inlineStr">
+      <c r="G20" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $3337万
@@ -31684,7 +31684,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="H20" s="22" t="inlineStr">
+      <c r="H20" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2541万
@@ -31692,7 +31692,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="I20" s="22" t="inlineStr">
+      <c r="I20" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2548万
@@ -31707,7 +31707,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B21" s="22" t="inlineStr">
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1070万
@@ -31715,7 +31715,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="C21" s="22" t="inlineStr">
+      <c r="C21" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1050万
@@ -31723,7 +31723,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="D21" s="22" t="inlineStr">
+      <c r="D21" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $993万
@@ -31731,7 +31731,7 @@
 (25年-06月-13日)</t>
         </is>
       </c>
-      <c r="E21" s="22" t="inlineStr">
+      <c r="E21" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1012万
@@ -31739,7 +31739,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="F21" s="22" t="inlineStr">
+      <c r="F21" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $906万
@@ -31747,7 +31747,7 @@
 (25年-06月-13日)</t>
         </is>
       </c>
-      <c r="G21" s="22" t="inlineStr">
+      <c r="G21" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $3300万
@@ -31755,7 +31755,7 @@
 (25年-06月-26日)</t>
         </is>
       </c>
-      <c r="H21" s="22" t="inlineStr">
+      <c r="H21" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2500万
@@ -31763,7 +31763,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="I21" s="22" t="inlineStr">
+      <c r="I21" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2519万
@@ -31778,7 +31778,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1003万
@@ -31786,7 +31786,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="C22" s="22" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $984万
@@ -31794,7 +31794,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="D22" s="22" t="inlineStr">
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $989万
@@ -31802,7 +31802,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="E22" s="22" t="inlineStr">
+      <c r="E22" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $949万
@@ -31810,7 +31810,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="F22" s="22" t="inlineStr">
+      <c r="F22" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $903万
@@ -31818,7 +31818,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="G22" s="22" t="inlineStr">
+      <c r="G22" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2824万
@@ -31826,7 +31826,7 @@
 (25年-06月-18日)</t>
         </is>
       </c>
-      <c r="H22" s="22" t="inlineStr">
+      <c r="H22" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2623万
@@ -31834,7 +31834,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="I22" s="22" t="inlineStr">
+      <c r="I22" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2490万
@@ -31849,7 +31849,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1062万
@@ -31857,7 +31857,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="C23" s="22" t="inlineStr">
+      <c r="C23" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $981万
@@ -31865,7 +31865,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="D23" s="22" t="inlineStr">
+      <c r="D23" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $985万
@@ -31873,7 +31873,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="E23" s="22" t="inlineStr">
+      <c r="E23" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $945万
@@ -31881,7 +31881,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="F23" s="22" t="inlineStr">
+      <c r="F23" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $955万
@@ -31889,7 +31889,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="G23" s="22" t="inlineStr">
+      <c r="G23" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2784万
@@ -31897,7 +31897,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="H23" s="22" t="inlineStr">
+      <c r="H23" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2487万
@@ -31905,7 +31905,7 @@
 (25年-07月-22日)</t>
         </is>
       </c>
-      <c r="I23" s="22" t="inlineStr">
+      <c r="I23" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2437万
@@ -31920,7 +31920,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $983万
@@ -31928,7 +31928,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="C24" s="22" t="inlineStr">
+      <c r="C24" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $977万
@@ -31936,7 +31936,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="D24" s="22" t="inlineStr">
+      <c r="D24" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1042万
@@ -31944,7 +31944,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="E24" s="22" t="inlineStr">
+      <c r="E24" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $942万
@@ -31952,7 +31952,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="F24" s="22" t="inlineStr">
+      <c r="F24" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $896万
@@ -31960,7 +31960,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="G24" s="22" t="inlineStr">
+      <c r="G24" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $3217万
@@ -31968,7 +31968,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="H24" s="22" t="inlineStr">
+      <c r="H24" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2482万
@@ -31976,7 +31976,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="I24" s="22" t="inlineStr">
+      <c r="I24" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2342万
@@ -31991,7 +31991,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1053万
@@ -31999,7 +31999,7 @@
 (25年-07月-01日)</t>
         </is>
       </c>
-      <c r="C25" s="22" t="inlineStr">
+      <c r="C25" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $973万
@@ -32007,7 +32007,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="D25" s="22" t="inlineStr">
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $977万
@@ -32015,7 +32015,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="E25" s="22" t="inlineStr">
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $996万
@@ -32023,7 +32023,7 @@
 (25年-07月-01日)</t>
         </is>
       </c>
-      <c r="F25" s="22" t="inlineStr">
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $892万
@@ -32031,7 +32031,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="G25" s="22" t="inlineStr">
+      <c r="G25" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $3045万
@@ -32039,7 +32039,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="H25" s="22" t="inlineStr">
+      <c r="H25" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2451万
@@ -32047,7 +32047,7 @@
 (25年-07月-22日)</t>
         </is>
       </c>
-      <c r="I25" s="22" t="inlineStr">
+      <c r="I25" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2321万
@@ -32062,7 +32062,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B26" s="22" t="inlineStr">
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $987万
@@ -32070,7 +32070,7 @@
 (25年-06月-29日)</t>
         </is>
       </c>
-      <c r="C26" s="22" t="inlineStr">
+      <c r="C26" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $969万
@@ -32078,7 +32078,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="D26" s="22" t="inlineStr">
+      <c r="D26" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1034万
@@ -32086,7 +32086,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="E26" s="22" t="inlineStr">
+      <c r="E26" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $934万
@@ -32094,7 +32094,7 @@
 (25年-06月-13日)</t>
         </is>
       </c>
-      <c r="F26" s="22" t="inlineStr">
+      <c r="F26" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $888万
@@ -32102,7 +32102,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="G26" s="22" t="inlineStr">
+      <c r="G26" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2727万
@@ -32110,7 +32110,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="H26" s="22" t="inlineStr">
+      <c r="H26" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2426万
@@ -32118,7 +32118,7 @@
 (25年-07月-29日)</t>
         </is>
       </c>
-      <c r="I26" s="22" t="inlineStr">
+      <c r="I26" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2310万
@@ -32133,7 +32133,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B27" s="22" t="inlineStr">
+      <c r="B27" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $983万
@@ -32141,7 +32141,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="C27" s="22" t="inlineStr">
+      <c r="C27" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $965万
@@ -32149,7 +32149,7 @@
 (25年-07月-01日)</t>
         </is>
       </c>
-      <c r="D27" s="22" t="inlineStr">
+      <c r="D27" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $969万
@@ -32157,7 +32157,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="E27" s="22" t="inlineStr">
+      <c r="E27" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $988万
@@ -32165,7 +32165,7 @@
 (25年-07月-01日)</t>
         </is>
       </c>
-      <c r="F27" s="22" t="inlineStr">
+      <c r="F27" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $885万
@@ -32173,7 +32173,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="G27" s="22" t="inlineStr">
+      <c r="G27" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2701万
@@ -32181,7 +32181,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="H27" s="22" t="inlineStr">
+      <c r="H27" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2402万
@@ -32189,7 +32189,7 @@
 (25年-07月-22日)</t>
         </is>
       </c>
-      <c r="I27" s="22" t="inlineStr">
+      <c r="I27" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2294万
@@ -32204,7 +32204,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B28" s="22" t="inlineStr">
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $979万
@@ -32212,7 +32212,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="C28" s="22" t="inlineStr">
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $949万
@@ -32220,7 +32220,7 @@
 (25年-07月-01日)</t>
         </is>
       </c>
-      <c r="D28" s="22" t="inlineStr">
+      <c r="D28" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $965万
@@ -32228,7 +32228,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="E28" s="22" t="inlineStr">
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $927万
@@ -32236,7 +32236,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="F28" s="22" t="inlineStr">
+      <c r="F28" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $926万
@@ -32244,7 +32244,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="G28" s="22" t="inlineStr">
+      <c r="G28" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2674万
@@ -32252,7 +32252,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="H28" s="22" t="inlineStr">
+      <c r="H28" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2498万
@@ -32260,7 +32260,7 @@
 (25年-07月-24日)</t>
         </is>
       </c>
-      <c r="I28" s="22" t="inlineStr">
+      <c r="I28" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2277万
@@ -32275,7 +32275,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B29" s="22" t="inlineStr">
+      <c r="B29" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $976万
@@ -32283,7 +32283,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="C29" s="22" t="inlineStr">
+      <c r="C29" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $957万
@@ -32291,7 +32291,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="D29" s="22" t="inlineStr">
+      <c r="D29" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $962万
@@ -32299,7 +32299,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="E29" s="22" t="inlineStr">
+      <c r="E29" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $981万
@@ -32307,7 +32307,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="F29" s="22" t="inlineStr">
+      <c r="F29" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $878万
@@ -32315,7 +32315,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="G29" s="22" t="inlineStr">
+      <c r="G29" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2787万
@@ -32323,7 +32323,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="H29" s="22" t="inlineStr">
+      <c r="H29" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2555万
@@ -32331,7 +32331,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="I29" s="22" t="inlineStr">
+      <c r="I29" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2355万
@@ -32346,7 +32346,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B30" s="22" t="inlineStr">
+      <c r="B30" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1032万
@@ -32354,7 +32354,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="C30" s="22" t="inlineStr">
+      <c r="C30" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1013万
@@ -32362,7 +32362,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="D30" s="22" t="inlineStr">
+      <c r="D30" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1018万
@@ -32370,7 +32370,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="E30" s="22" t="inlineStr">
+      <c r="E30" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $919万
@@ -32378,7 +32378,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="F30" s="22" t="inlineStr">
+      <c r="F30" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $874万
@@ -32386,7 +32386,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="G30" s="22" t="inlineStr">
+      <c r="G30" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2622万
@@ -32394,7 +32394,7 @@
 (25年-07月-22日)</t>
         </is>
       </c>
-      <c r="H30" s="22" t="inlineStr">
+      <c r="H30" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2378万
@@ -32402,7 +32402,7 @@
 (25年-08月-03日)</t>
         </is>
       </c>
-      <c r="I30" s="22" t="inlineStr">
+      <c r="I30" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2244万
@@ -32417,7 +32417,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B31" s="22" t="inlineStr">
+      <c r="B31" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1028万
@@ -32425,7 +32425,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="C31" s="22" t="inlineStr">
+      <c r="C31" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1009万
@@ -32433,7 +32433,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="D31" s="22" t="inlineStr">
+      <c r="D31" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1014万
@@ -32441,7 +32441,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="E31" s="22" t="inlineStr">
+      <c r="E31" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $916万
@@ -32449,7 +32449,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="F31" s="22" t="inlineStr">
+      <c r="F31" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $871万
@@ -32457,7 +32457,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="G31" s="22" t="inlineStr">
+      <c r="G31" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2734万
@@ -32465,7 +32465,7 @@
 (25年-08月-10日)</t>
         </is>
       </c>
-      <c r="H31" s="22" t="inlineStr">
+      <c r="H31" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2382万
@@ -32473,7 +32473,7 @@
 (25年-08月-20日)</t>
         </is>
       </c>
-      <c r="I31" s="22" t="inlineStr">
+      <c r="I31" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2304万
@@ -32488,7 +32488,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B32" s="22" t="inlineStr">
+      <c r="B32" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1024万
@@ -32496,7 +32496,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="C32" s="22" t="inlineStr">
+      <c r="C32" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $934万
@@ -32504,7 +32504,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="D32" s="22" t="inlineStr">
+      <c r="D32" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $950万
@@ -32512,7 +32512,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="E32" s="22" t="inlineStr">
+      <c r="E32" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $969万
@@ -32520,7 +32520,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="F32" s="22" t="inlineStr">
+      <c r="F32" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $867万
@@ -32528,7 +32528,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="G32" s="22" t="inlineStr">
+      <c r="G32" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2715万
@@ -32536,7 +32536,7 @@
 (25年-07月-31日)</t>
         </is>
       </c>
-      <c r="H32" s="22" t="inlineStr">
+      <c r="H32" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2365万
@@ -32544,7 +32544,7 @@
 (25年-08月-18日)</t>
         </is>
       </c>
-      <c r="I32" s="22" t="inlineStr">
+      <c r="I32" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2211万
@@ -32559,7 +32559,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B33" s="22" t="inlineStr">
+      <c r="B33" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1020万
@@ -32567,7 +32567,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="C33" s="22" t="inlineStr">
+      <c r="C33" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1001万
@@ -32575,7 +32575,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="D33" s="22" t="inlineStr">
+      <c r="D33" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $946万
@@ -32583,7 +32583,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="E33" s="22" t="inlineStr">
+      <c r="E33" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $908万
@@ -32591,7 +32591,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="F33" s="22" t="inlineStr">
+      <c r="F33" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $864万
@@ -32599,7 +32599,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="G33" s="22" t="inlineStr">
+      <c r="G33" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2584万
@@ -32607,7 +32607,7 @@
 (25年-08月-10日)</t>
         </is>
       </c>
-      <c r="H33" s="22" t="inlineStr">
+      <c r="H33" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2348万
@@ -32615,7 +32615,7 @@
 (25年-08月-18日)</t>
         </is>
       </c>
-      <c r="I33" s="22" t="inlineStr">
+      <c r="I33" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2272万
@@ -32630,7 +32630,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B34" s="22" t="inlineStr">
+      <c r="B34" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1016万
@@ -32638,7 +32638,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="C34" s="22" t="inlineStr">
+      <c r="C34" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $938万
@@ -32646,7 +32646,7 @@
 (25年-07月-01日)</t>
         </is>
       </c>
-      <c r="D34" s="22" t="inlineStr">
+      <c r="D34" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $943万
@@ -32654,7 +32654,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="E34" s="22" t="inlineStr">
+      <c r="E34" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $905万
@@ -32662,7 +32662,7 @@
 (25年-07月-01日)</t>
         </is>
       </c>
-      <c r="F34" s="22" t="inlineStr">
+      <c r="F34" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $914万
@@ -32670,7 +32670,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="G34" s="22" t="inlineStr">
+      <c r="G34" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2565万
@@ -32678,7 +32678,7 @@
 (25年-09月-16日)</t>
         </is>
       </c>
-      <c r="H34" s="22" t="inlineStr">
+      <c r="H34" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2331万
@@ -32686,7 +32686,7 @@
 (25年-09月-16日)</t>
         </is>
       </c>
-      <c r="I34" s="22" t="inlineStr">
+      <c r="I34" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2296万
@@ -32701,7 +32701,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B35" s="22" t="inlineStr">
+      <c r="B35" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $952万
@@ -32709,7 +32709,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="C35" s="22" t="inlineStr">
+      <c r="C35" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $993万
@@ -32717,7 +32717,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="D35" s="22" t="inlineStr">
+      <c r="D35" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $939万
@@ -32725,7 +32725,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E35" s="22" t="inlineStr">
+      <c r="E35" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $901万
@@ -32733,7 +32733,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="F35" s="22" t="inlineStr">
+      <c r="F35" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $911万
@@ -32741,7 +32741,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="G35" s="22" t="inlineStr">
+      <c r="G35" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2680万
@@ -32749,7 +32749,7 @@
 (25年-09月-02日)</t>
         </is>
       </c>
-      <c r="H35" s="22" t="inlineStr">
+      <c r="H35" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2313万
@@ -32757,7 +32757,7 @@
 (25年-09月-25日)</t>
         </is>
       </c>
-      <c r="I35" s="22" t="inlineStr">
+      <c r="I35" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2280万
@@ -32772,7 +32772,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B36" s="22" t="inlineStr">
+      <c r="B36" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $949万
@@ -32780,7 +32780,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="C36" s="22" t="inlineStr">
+      <c r="C36" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $931万
@@ -32788,7 +32788,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="D36" s="22" t="inlineStr">
+      <c r="D36" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $935万
@@ -32796,7 +32796,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E36" s="22" t="inlineStr">
+      <c r="E36" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $954万
@@ -32804,7 +32804,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="F36" s="22" t="inlineStr">
+      <c r="F36" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $854万
@@ -32812,7 +32812,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="G36" s="22" t="inlineStr">
+      <c r="G36" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2556万
@@ -32820,7 +32820,7 @@
 (25年-09月-11日)</t>
         </is>
       </c>
-      <c r="H36" s="22" t="inlineStr">
+      <c r="H36" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2339万
@@ -32828,7 +32828,7 @@
 (25年-10月-14日)</t>
         </is>
       </c>
-      <c r="I36" s="22" t="inlineStr">
+      <c r="I36" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2263万
@@ -32843,7 +32843,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B37" s="22" t="inlineStr">
+      <c r="B37" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $945万
@@ -32851,7 +32851,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="C37" s="22" t="inlineStr">
+      <c r="C37" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $927万
@@ -32859,7 +32859,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="D37" s="22" t="inlineStr">
+      <c r="D37" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $931万
@@ -32867,7 +32867,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="E37" s="22" t="inlineStr">
+      <c r="E37" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $894万
@@ -32875,7 +32875,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="F37" s="22" t="inlineStr">
+      <c r="F37" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $850万
@@ -32883,7 +32883,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="G37" s="22" t="inlineStr">
+      <c r="G37" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2574万
@@ -32891,7 +32891,7 @@
 (25年-10月-08日)</t>
         </is>
       </c>
-      <c r="H37" s="22" t="inlineStr">
+      <c r="H37" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2365万
@@ -32899,7 +32899,7 @@
 (25年-10月-20日)</t>
         </is>
       </c>
-      <c r="I37" s="22" t="inlineStr">
+      <c r="I37" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2247万
@@ -32914,7 +32914,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B38" s="22" t="inlineStr">
+      <c r="B38" s="21" t="inlineStr">
         <is>
           <t>A | 440呎 (2房)
 $1158万
@@ -32922,7 +32922,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="C38" s="22" t="inlineStr">
+      <c r="C38" s="21" t="inlineStr">
         <is>
           <t>B | 439呎 (2房)
 $1089万
@@ -32930,7 +32930,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="D38" s="22" t="inlineStr">
+      <c r="D38" s="21" t="inlineStr">
         <is>
           <t>C | 444呎 (2房)
 $1092万
@@ -32938,7 +32938,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="E38" s="22" t="inlineStr">
+      <c r="E38" s="21" t="inlineStr">
         <is>
           <t>D | 430呎 (2房)
 $1182万
@@ -32946,7 +32946,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="F38" s="22" t="inlineStr">
+      <c r="F38" s="21" t="inlineStr">
         <is>
           <t>E | 408呎 (2房)
 $1040万
@@ -32954,7 +32954,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="G38" s="22" t="inlineStr">
+      <c r="G38" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2546万
@@ -32962,7 +32962,7 @@
 (25年-10月-09日)</t>
         </is>
       </c>
-      <c r="H38" s="22" t="inlineStr">
+      <c r="H38" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2471万
@@ -32970,7 +32970,7 @@
 (25年-10月-21日)</t>
         </is>
       </c>
-      <c r="I38" s="22" t="inlineStr">
+      <c r="I38" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2354万

--- a/files/港岛-黄竹坑-滶晨.xlsx
+++ b/files/港岛-黄竹坑-滶晨.xlsx
@@ -28744,7 +28744,7 @@
           <t>C | 1083呎 (3房)
 $3890万
 $35,921/呎
-(26年-05月-07日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr"/>
@@ -28791,7 +28791,7 @@
           <t>A | 486呎 (2房)
 $1593万
 $32,776/呎
-(26年-04月-29日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -28799,7 +28799,7 @@
           <t>B | 494呎 (2房)
 $1142万
 $23,109/呎
-(25年-07月-07日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
@@ -28807,7 +28807,7 @@
           <t>C | 517呎 (2房)
 $1235万
 $23,892/呎
-(25年-07月-10日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr"/>
@@ -28840,7 +28840,7 @@
           <t>A | 486呎 (2房)
 $1566万
 $32,222/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -28848,7 +28848,7 @@
           <t>B | 494呎 (2房)
 $1130万
 $22,881/呎
-(25年-07月-02日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -28856,7 +28856,7 @@
           <t>C | 517呎 (2房)
 $1276万
 $24,689/呎
-(25年-07月-16日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr"/>
@@ -28873,7 +28873,7 @@
           <t>P2 | 1706呎 (4+房)
 $10775万
 $63,158/呎
-(26年-01月-26日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="H8" s="22" t="inlineStr"/>
@@ -28889,7 +28889,7 @@
           <t>A | 486呎 (2房)
 $1429万
 $29,401/呎
-(26年-03月-05日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -28897,7 +28897,7 @@
           <t>B | 494呎 (2房)
 $1227万
 $24,844/呎
-(25年-08月-10日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -28905,7 +28905,7 @@
           <t>C | 517呎 (2房)
 $1245万
 $24,087/呎
-(25年-07月-16日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr"/>
@@ -28914,7 +28914,7 @@
           <t>P1 | 1536呎 (4+房)
 $7296万
 $47,500/呎
-(25年-11月-05日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="G9" s="21" t="inlineStr">
@@ -28922,7 +28922,7 @@
           <t>P2 | 1706呎 (4+房)
 $8530万
 $50,000/呎
-(25年-06月-25日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="H9" s="22" t="inlineStr"/>
@@ -28938,7 +28938,7 @@
           <t>A | 486呎 (2房)
 $1117万
 $22,990/呎
-(25年-07月-17日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -28946,7 +28946,7 @@
           <t>B | 494呎 (2房)
 $1131万
 $22,903/呎
-(25年-07月-17日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -28954,7 +28954,7 @@
           <t>C | 517呎 (2房)
 $1154万
 $22,317/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr"/>
@@ -28963,7 +28963,7 @@
           <t>P1 | 1536呎 (4+房)
 $6543万
 $42,600/呎
-(25年-06月-22日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G10" s="21" t="inlineStr">
@@ -28971,7 +28971,7 @@
           <t>P2 | 1706呎 (4+房)
 $8189万
 $48,000/呎
-(25年-06月-22日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="H10" s="22" t="inlineStr"/>
@@ -28987,7 +28987,7 @@
           <t>A | 486呎 (2房)
 $1086万
 $22,346/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -28995,7 +28995,7 @@
           <t>B | 494呎 (2房)
 $1100万
 $22,265/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -29003,7 +29003,7 @@
           <t>C | 517呎 (2房)
 $1217万
 $23,536/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr"/>
@@ -29012,7 +29012,7 @@
           <t>P1 | 1536呎 (4+房)
 $6420万
 $41,800/呎
-(25年-06月-23日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr">
@@ -29020,7 +29020,7 @@
           <t>P2 | 1706呎 (4+房)
 $7558万
 $44,300/呎
-(25年-06月-23日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="H11" s="22" t="inlineStr"/>
@@ -29036,7 +29036,7 @@
           <t>A | 486呎 (2房)
 $1083万
 $22,292/呎
-(25年-07月-22日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
@@ -29044,7 +29044,7 @@
           <t>B | 494呎 (2房)
 $1097万
 $22,211/呎
-(25年-07月-22日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -29052,7 +29052,7 @@
           <t>C | 517呎 (2房)
 $1137万
 $21,986/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr"/>
@@ -29061,7 +29061,7 @@
           <t>P1 | 1536呎 (4+房)
 $6298万
 $41,000/呎
-(25年-06月-23日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr">
@@ -29069,7 +29069,7 @@
           <t>P2 | 1706呎 (4+房)
 $7421万
 $43,500/呎
-(25年-06月-23日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr"/>
@@ -29085,7 +29085,7 @@
           <t>A | 486呎 (2房)
 $1067万
 $21,963/呎
-(25年-06月-24日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -29093,7 +29093,7 @@
           <t>B | 494呎 (2房)
 $1081万
 $21,881/呎
-(25年-07月-22日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -29101,7 +29101,7 @@
           <t>C | 517呎 (2房)
 $1128万
 $21,822/呎
-(25年-07月-13日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr"/>
@@ -29110,7 +29110,7 @@
           <t>P1 | 1536呎 (4+房)
 $6089万
 $39,641/呎
-(25年-07月-13日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G13" s="21" t="inlineStr">
@@ -29118,7 +29118,7 @@
           <t>P2 | 1706呎 (4+房)
 $7319万
 $42,900/呎
-(25年-06月-23日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr"/>
@@ -29134,7 +29134,7 @@
           <t>A | 486呎 (2房)
 $1048万
 $21,562/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -29142,7 +29142,7 @@
           <t>B | 494呎 (2房)
 $1061万
 $21,482/呎
-(25年-07月-15日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -29150,7 +29150,7 @@
           <t>C | 517呎 (2房)
 $1123万
 $21,714/呎
-(25年-07月-10日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr"/>
@@ -29159,7 +29159,7 @@
           <t>P1 | 1536呎 (4+房)
 $5990万
 $39,000/呎
-(25年-07月-10日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr">
@@ -29167,7 +29167,7 @@
           <t>P2 | 1706呎 (4+房)
 $6726万
 $39,425/呎
-(25年-06月-24日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr"/>
@@ -29183,7 +29183,7 @@
           <t>A | 486呎 (2房)
 $1107万
 $22,772/呎
-(25年-07月-15日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -29191,7 +29191,7 @@
           <t>B | 494呎 (2房)
 $1055万
 $21,354/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -29199,7 +29199,7 @@
           <t>C | 517呎 (2房)
 $1187万
 $22,956/呎
-(25年-06月-19日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr"/>
@@ -29208,7 +29208,7 @@
           <t>P1 | 1536呎 (4+房)
 $5574万
 $36,290/呎
-(25年-06月-11日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr">
@@ -29216,7 +29216,7 @@
           <t>P2 | 1706呎 (4+房)
 $6596万
 $38,665/呎
-(25年-06月-11日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="H15" s="22" t="inlineStr"/>
@@ -29232,7 +29232,7 @@
           <t>A | 486呎 (2房)
 $1100万
 $22,638/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -29240,7 +29240,7 @@
           <t>B | 494呎 (2房)
 $1114万
 $22,553/呎
-(25年-07月-14日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -29248,7 +29248,7 @@
           <t>C | 517呎 (2房)
 $1112万
 $21,499/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr"/>
@@ -29257,7 +29257,7 @@
           <t>P1 | 1536呎 (4+房)
 $5076万
 $33,047/呎
-(25年-07月-16日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
@@ -29265,7 +29265,7 @@
           <t>P2 | 1706呎 (4+房)
 $6467万
 $37,906/呎
-(25年-06月-11日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="H16" s="22" t="inlineStr"/>
@@ -29281,7 +29281,7 @@
           <t>A | 486呎 (2房)
 $1094万
 $22,502/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -29289,7 +29289,7 @@
           <t>B | 494呎 (2房)
 $1108万
 $22,419/呎
-(25年-07月-14日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -29297,7 +29297,7 @@
           <t>C | 517呎 (2房)
 $1175万
 $22,729/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr"/>
@@ -29306,7 +29306,7 @@
           <t>P1 | 1469呎 (4+房)
 $5739万
 $39,066/呎
-(25年-06月-18日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G17" s="21" t="inlineStr">
@@ -29314,7 +29314,7 @@
           <t>P2 | 1706呎 (4+房)
 $6739万
 $39,501/呎
-(25年-06月-18日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr"/>
@@ -29330,7 +29330,7 @@
           <t>A | 486呎 (2房)
 $1025万
 $21,095/呎
-(25年-07月-13日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -29338,7 +29338,7 @@
           <t>B | 494呎 (2房)
 $1036万
 $20,972/呎
-(25年-07月-15日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -29346,7 +29346,7 @@
           <t>C | 517呎 (2房)
 $1084万
 $20,973/呎
-(25年-07月-03日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
@@ -29354,7 +29354,7 @@
           <t>D | 477呎 (2房)
 $1011万
 $21,201/呎
-(25年-07月-13日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr">
@@ -29362,7 +29362,7 @@
           <t>P1 | 1258呎 (4+房)
 $4422万
 $35,149/呎
-(25年-06月-10日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
@@ -29370,7 +29370,7 @@
           <t>P2 | 870呎 (3房)
 $2694万
 $30,970/呎
-(25年-07月-01日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="H18" s="21" t="inlineStr">
@@ -29378,7 +29378,7 @@
           <t>P3 | 952呎 (3房)
 $3313万
 $34,800/呎
-(25年-06月-25日)</t>
+(25年-06月)</t>
         </is>
       </c>
     </row>
@@ -29393,7 +29393,7 @@
           <t>A | 486呎 (2房)
 $1021万
 $21,010/呎
-(25年-07月-10日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -29401,7 +29401,7 @@
           <t>B | 494呎 (2房)
 $1032万
 $20,889/呎
-(25年-07月-10日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -29409,7 +29409,7 @@
           <t>C | 517呎 (2房)
 $1066万
 $20,629/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -29417,7 +29417,7 @@
           <t>D | 477呎 (2房)
 $1005万
 $21,073/呎
-(25年-07月-13日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr">
@@ -29425,7 +29425,7 @@
           <t>P1 | 1261呎 (4+房)
 $4351万
 $34,508/呎
-(25年-06月-24日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
@@ -29433,7 +29433,7 @@
           <t>P2 | 870呎 (3房)
 $2653万
 $30,495/呎
-(25年-06月-29日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="H19" s="21" t="inlineStr">
@@ -29441,7 +29441,7 @@
           <t>P3 | 952呎 (3房)
 $3447万
 $36,211/呎
-(25年-07月-02日)</t>
+(25年-07月)</t>
         </is>
       </c>
     </row>
@@ -29456,7 +29456,7 @@
           <t>A | 486呎 (2房)
 $1017万
 $20,926/呎
-(25年-07月-13日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -29464,7 +29464,7 @@
           <t>B | 494呎 (2房)
 $1028万
 $20,806/呎
-(25年-07月-13日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -29472,7 +29472,7 @@
           <t>C | 517呎 (2房)
 $1076万
 $20,805/呎
-(25年-07月-07日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -29480,7 +29480,7 @@
           <t>D | 477呎 (2房)
 $999万
 $20,948/呎
-(25年-07月-15日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr">
@@ -29488,7 +29488,7 @@
           <t>P1 | 1261呎 (4+房)
 $4540万
 $36,000/呎
-(25年-06月-25日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
@@ -29496,7 +29496,7 @@
           <t>P2 | 870呎 (3房)
 $2612万
 $30,020/呎
-(25年-06月-22日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="H20" s="21" t="inlineStr">
@@ -29504,7 +29504,7 @@
           <t>P3 | 952呎 (3房)
 $3256万
 $34,200/呎
-(25年-06月-22日)</t>
+(25年-06月)</t>
         </is>
       </c>
     </row>
@@ -29519,7 +29519,7 @@
           <t>A | 486呎 (2房)
 $1013万
 $20,844/呎
-(25年-07月-13日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -29527,7 +29527,7 @@
           <t>B | 494呎 (2房)
 $1024万
 $20,723/呎
-(25年-07月-10日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -29535,7 +29535,7 @@
           <t>C | 517呎 (2房)
 $1138万
 $22,017/呎
-(25年-07月-02日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -29543,7 +29543,7 @@
           <t>D | 477呎 (2房)
 $993万
 $20,824/呎
-(25年-07月-15日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr">
@@ -29551,7 +29551,7 @@
           <t>P1 | 1261呎 (4+房)
 $4265万
 $33,820/呎
-(25年-06月-11日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -29559,7 +29559,7 @@
           <t>P2 | 870呎 (3房)
 $2579万
 $29,640/呎
-(25年-07月-10日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="H21" s="21" t="inlineStr">
@@ -29567,7 +29567,7 @@
           <t>P3 | 952呎 (3房)
 $3220万
 $33,820/呎
-(25年-06月-22日)</t>
+(25年-06月)</t>
         </is>
       </c>
     </row>
@@ -29582,7 +29582,7 @@
           <t>A | 486呎 (2房)
 $1009万
 $20,759/呎
-(25年-07月-07日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -29590,7 +29590,7 @@
           <t>B | 494呎 (2房)
 $1020万
 $20,640/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -29598,7 +29598,7 @@
           <t>C | 517呎 (2房)
 $1067万
 $20,640/呎
-(25年-07月-13日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -29606,7 +29606,7 @@
           <t>D | 477呎 (2房)
 $987万
 $20,700/呎
-(25年-07月-06日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
@@ -29614,7 +29614,7 @@
           <t>P1 | 1261呎 (4+房)
 $4229万
 $33,535/呎
-(25年-06月-19日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
@@ -29622,7 +29622,7 @@
           <t>P2 | 870呎 (3房)
 $2688万
 $30,900/呎
-(25年-07月-03日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="H22" s="21" t="inlineStr">
@@ -29630,7 +29630,7 @@
           <t>P3 | 952呎 (3房)
 $3056万
 $32,100/呎
-(25年-06月-15日)</t>
+(25年-06月)</t>
         </is>
       </c>
     </row>
@@ -29645,7 +29645,7 @@
           <t>A | 486呎 (2房)
 $1005万
 $20,677/呎
-(25年-07月-13日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -29653,7 +29653,7 @@
           <t>B | 494呎 (2房)
 $1079万
 $21,842/呎
-(25年-07月-13日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -29661,7 +29661,7 @@
           <t>C | 517呎 (2房)
 $1063万
 $20,557/呎
-(25年-07月-13日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -29669,7 +29669,7 @@
           <t>D | 477呎 (2房)
 $984万
 $20,618/呎
-(25年-07月-17日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr">
@@ -29677,7 +29677,7 @@
           <t>P1 | 1261呎 (4+房)
 $4193万
 $33,250/呎
-(25年-06月-23日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
@@ -29685,7 +29685,7 @@
           <t>P2 | 870呎 (3房)
 $2529万
 $29,070/呎
-(25年-06月-23日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="H23" s="21" t="inlineStr">
@@ -29693,7 +29693,7 @@
           <t>P3 | 952呎 (3房)
 $2876万
 $30,210/呎
-(25年-07月-01日)</t>
+(25年-07月)</t>
         </is>
       </c>
     </row>
@@ -29708,7 +29708,7 @@
           <t>A | 486呎 (2房)
 $1001万
 $20,595/呎
-(25年-07月-13日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -29716,7 +29716,7 @@
           <t>B | 494呎 (2房)
 $1008万
 $20,397/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -29724,7 +29724,7 @@
           <t>C | 517呎 (2房)
 $1059万
 $20,476/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -29732,7 +29732,7 @@
           <t>D | 477呎 (2房)
 $980万
 $20,537/呎
-(25年-07月-13日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr">
@@ -29740,7 +29740,7 @@
           <t>P1 | 1261呎 (4+房)
 $4184万
 $33,180/呎
-(25年-07月-06日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -29748,7 +29748,7 @@
           <t>P2 | 870呎 (3房)
 $2504万
 $28,785/呎
-(25年-07月-06日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="H24" s="21" t="inlineStr">
@@ -29756,7 +29756,7 @@
           <t>P3 | 952呎 (3房)
 $3299万
 $34,651/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
     </row>
@@ -29771,7 +29771,7 @@
           <t>A | 486呎 (2房)
 $997万
 $20,512/呎
-(25年-07月-17日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -29779,7 +29779,7 @@
           <t>B | 494呎 (2房)
 $1004万
 $20,316/呎
-(25年-07月-07日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -29787,7 +29787,7 @@
           <t>C | 517呎 (2房)
 $1113万
 $21,522/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -29795,7 +29795,7 @@
           <t>D | 477呎 (2房)
 $1037万
 $21,732/呎
-(25年-07月-13日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
@@ -29803,7 +29803,7 @@
           <t>P1 | 1261呎 (4+房)
 $4374万
 $34,688/呎
-(25年-07月-10日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G25" s="21" t="inlineStr">
@@ -29811,7 +29811,7 @@
           <t>P2 | 870呎 (3房)
 $2480万
 $28,500/呎
-(25年-07月-06日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="H25" s="21" t="inlineStr">
@@ -29819,7 +29819,7 @@
           <t>P3 | 952呎 (3房)
 $3122万
 $32,791/呎
-(25年-07月-06日)</t>
+(25年-07月)</t>
         </is>
       </c>
     </row>
@@ -29834,7 +29834,7 @@
           <t>A | 486呎 (2房)
 $993万
 $20,430/呎
-(25年-07月-14日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
@@ -29842,7 +29842,7 @@
           <t>B | 494呎 (2房)
 $1000万
 $20,235/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -29850,7 +29850,7 @@
           <t>C | 517呎 (2房)
 $1043万
 $20,176/呎
-(25年-07月-02日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -29858,7 +29858,7 @@
           <t>D | 477呎 (2房)
 $972万
 $20,371/呎
-(25年-07月-14日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr">
@@ -29866,7 +29866,7 @@
           <t>P1 | 1261呎 (4+房)
 $3725万
 $29,538/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">
@@ -29874,7 +29874,7 @@
           <t>P2 | 870呎 (3房)
 $2406万
 $27,653/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="H26" s="21" t="inlineStr">
@@ -29882,7 +29882,7 @@
           <t>P3 | 952呎 (3房)
 $2893万
 $30,386/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
     </row>
@@ -29897,7 +29897,7 @@
           <t>A | 486呎 (2房)
 $989万
 $20,350/呎
-(25年-07月-13日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
@@ -29905,7 +29905,7 @@
           <t>B | 494呎 (2房)
 $996万
 $20,154/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -29913,7 +29913,7 @@
           <t>C | 517呎 (2房)
 $1039万
 $20,095/呎
-(25年-07月-07日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -29921,7 +29921,7 @@
           <t>D | 477呎 (2房)
 $968万
 $20,291/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F27" s="21" t="inlineStr">
@@ -29929,7 +29929,7 @@
           <t>P1 | 1261呎 (4+房)
 $3680万
 $29,187/呎
-(25年-06月-13日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G27" s="21" t="inlineStr">
@@ -29937,7 +29937,7 @@
           <t>P2 | 870呎 (3房)
 $2526万
 $29,032/呎
-(25年-07月-02日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="H27" s="21" t="inlineStr">
@@ -29945,7 +29945,7 @@
           <t>P3 | 952呎 (3房)
 $2850万
 $29,936/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
     </row>
@@ -29960,7 +29960,7 @@
           <t>A | 486呎 (2房)
 $985万
 $20,270/呎
-(25年-07月-10日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
@@ -29968,7 +29968,7 @@
           <t>B | 494呎 (2房)
 $992万
 $20,073/呎
-(25年-07月-03日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -29976,7 +29976,7 @@
           <t>C | 517呎 (2房)
 $1022万
 $19,764/呎
-(25年-07月-07日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr">
@@ -29984,7 +29984,7 @@
           <t>D | 477呎 (2房)
 $1024万
 $21,474/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F28" s="21" t="inlineStr">
@@ -29992,7 +29992,7 @@
           <t>P1 | 1261呎 (4+房)
 $3955万
 $31,363/呎
-(25年-07月-07日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
@@ -30000,7 +30000,7 @@
           <t>P2 | 870呎 (3房)
 $2349万
 $27,001/呎
-(25年-07月-13日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="H28" s="21" t="inlineStr">
@@ -30008,7 +30008,7 @@
           <t>P3 | 952呎 (3房)
 $2652万
 $27,852/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
     </row>
@@ -30023,7 +30023,7 @@
           <t>A | 486呎 (2房)
 $981万
 $20,189/呎
-(25年-07月-17日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C29" s="21" t="inlineStr">
@@ -30031,7 +30031,7 @@
           <t>B | 494呎 (2房)
 $1049万
 $21,243/呎
-(25年-07月-01日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D29" s="21" t="inlineStr">
@@ -30039,7 +30039,7 @@
           <t>C | 517呎 (2房)
 $1095万
 $21,182/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E29" s="21" t="inlineStr">
@@ -30047,7 +30047,7 @@
           <t>D | 477呎 (2房)
 $948万
 $19,878/呎
-(25年-07月-07日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F29" s="21" t="inlineStr">
@@ -30055,7 +30055,7 @@
           <t>P1 | 1261呎 (4+房)
 $3818万
 $30,281/呎
-(25年-07月-02日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G29" s="21" t="inlineStr">
@@ -30063,7 +30063,7 @@
           <t>P2 | 870呎 (3房)
 $2319万
 $26,654/呎
-(25年-07月-10日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="H29" s="21" t="inlineStr">
@@ -30071,7 +30071,7 @@
           <t>P3 | 952呎 (3房)
 $2784万
 $29,242/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
     </row>
@@ -30086,7 +30086,7 @@
           <t>A | 486呎 (2房)
 $1038万
 $21,364/呎
-(25年-07月-15日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C30" s="21" t="inlineStr">
@@ -30094,7 +30094,7 @@
           <t>B | 494呎 (2房)
 $1045万
 $21,158/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D30" s="21" t="inlineStr">
@@ -30102,7 +30102,7 @@
           <t>C | 517呎 (2房)
 $1091万
 $21,097/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E30" s="21" t="inlineStr">
@@ -30110,7 +30110,7 @@
           <t>D | 477呎 (2房)
 $956万
 $20,050/呎
-(25年-07月-17日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F30" s="21" t="inlineStr">
@@ -30118,7 +30118,7 @@
           <t>P1 | 1261呎 (4+房)
 $3862万
 $30,626/呎
-(25年-07月-03日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G30" s="21" t="inlineStr">
@@ -30126,7 +30126,7 @@
           <t>P2 | 870呎 (3房)
 $2396万
 $27,545/呎
-(25年-08月-05日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="H30" s="21" t="inlineStr">
@@ -30134,7 +30134,7 @@
           <t>P3 | 952呎 (3房)
 $2708万
 $28,441/呎
-(25年-07月-17日)</t>
+(25年-07月)</t>
         </is>
       </c>
     </row>
@@ -30149,7 +30149,7 @@
           <t>A | 486呎 (2房)
 $1034万
 $21,278/呎
-(25年-07月-15日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C31" s="21" t="inlineStr">
@@ -30157,7 +30157,7 @@
           <t>B | 494呎 (2房)
 $1041万
 $21,073/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D31" s="21" t="inlineStr">
@@ -30165,7 +30165,7 @@
           <t>C | 517呎 (2房)
 $1086万
 $21,012/呎
-(25年-07月-13日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E31" s="21" t="inlineStr">
@@ -30173,7 +30173,7 @@
           <t>D | 477呎 (2房)
 $952万
 $19,969/呎
-(25年-07月-14日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F31" s="21" t="inlineStr">
@@ -30181,7 +30181,7 @@
           <t>P1 | 1261呎 (4+房)
 $3819万
 $30,289/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G31" s="21" t="inlineStr">
@@ -30189,7 +30189,7 @@
           <t>P2 | 870呎 (3房)
 $2361万
 $27,138/呎
-(25年-07月-29日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="H31" s="21" t="inlineStr">
@@ -30197,7 +30197,7 @@
           <t>P3 | 952呎 (3房)
 $2668万
 $28,021/呎
-(25年-07月-15日)</t>
+(25年-07月)</t>
         </is>
       </c>
     </row>
@@ -30212,7 +30212,7 @@
           <t>A | 486呎 (2房)
 $1030万
 $21,195/呎
-(25年-07月-15日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C32" s="21" t="inlineStr">
@@ -30220,7 +30220,7 @@
           <t>B | 494呎 (2房)
 $976万
 $19,755/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D32" s="21" t="inlineStr">
@@ -30228,7 +30228,7 @@
           <t>C | 517呎 (2房)
 $1006万
 $19,451/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E32" s="21" t="inlineStr">
@@ -30236,7 +30236,7 @@
           <t>D | 477呎 (2房)
 $949万
 $19,891/呎
-(25年-07月-17日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F32" s="21" t="inlineStr">
@@ -30244,7 +30244,7 @@
           <t>P1 | 1261呎 (4+房)
 $3785万
 $30,014/呎
-(25年-07月-16日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G32" s="21" t="inlineStr">
@@ -30252,7 +30252,7 @@
           <t>P2 | 870呎 (3房)
 $2338万
 $26,869/呎
-(25年-09月-17日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="H32" s="21" t="inlineStr">
@@ -30260,7 +30260,7 @@
           <t>P3 | 952呎 (3房)
 $2641万
 $27,744/呎
-(25年-07月-02日)</t>
+(25年-07月)</t>
         </is>
       </c>
     </row>
@@ -30275,7 +30275,7 @@
           <t>A | 486呎 (2房)
 $1026万
 $21,109/呎
-(25年-07月-13日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C33" s="21" t="inlineStr">
@@ -30283,7 +30283,7 @@
           <t>B | 494呎 (2房)
 $1033万
 $20,907/呎
-(25年-07月-07日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D33" s="21" t="inlineStr">
@@ -30291,7 +30291,7 @@
           <t>C | 517呎 (2房)
 $1014万
 $19,619/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E33" s="21" t="inlineStr">
@@ -30299,7 +30299,7 @@
           <t>D | 477呎 (2房)
 $945万
 $19,811/呎
-(25年-07月-13日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F33" s="21" t="inlineStr">
@@ -30307,7 +30307,7 @@
           <t>P1 | 1261呎 (4+房)
 $3474万
 $27,550/呎
-(25年-07月-10日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G33" s="21" t="inlineStr">
@@ -30315,7 +30315,7 @@
           <t>P2 | 870呎 (3房)
 $2306万
 $26,506/呎
-(25年-07月-17日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="H33" s="21" t="inlineStr">
@@ -30323,7 +30323,7 @@
           <t>P3 | 952呎 (3房)
 $2578万
 $27,075/呎
-(25年-07月-16日)</t>
+(25年-07月)</t>
         </is>
       </c>
     </row>
@@ -30338,7 +30338,7 @@
           <t>A | 486呎 (2房)
 $962万
 $19,788/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C34" s="21" t="inlineStr">
@@ -30346,7 +30346,7 @@
           <t>B | 494呎 (2房)
 $968万
 $19,597/呎
-(25年-07月-02日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D34" s="21" t="inlineStr">
@@ -30354,7 +30354,7 @@
           <t>C | 517呎 (2房)
 $1010万
 $19,542/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E34" s="21" t="inlineStr">
@@ -30362,7 +30362,7 @@
           <t>D | 477呎 (2房)
 $938万
 $19,654/呎
-(25年-07月-10日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F34" s="21" t="inlineStr">
@@ -30370,7 +30370,7 @@
           <t>P1 | 1261呎 (4+房)
 $3632万
 $28,800/呎
-(25年-07月-07日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G34" s="21" t="inlineStr">
@@ -30378,7 +30378,7 @@
           <t>P2 | 870呎 (3房)
 $2392万
 $27,500/呎
-(25年-07月-30日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="H34" s="21" t="inlineStr">
@@ -30386,7 +30386,7 @@
           <t>P3 | 952呎 (3房)
 $2586万
 $27,168/呎
-(25年-06月-19日)</t>
+(25年-06月)</t>
         </is>
       </c>
     </row>
@@ -30401,7 +30401,7 @@
           <t>A | 486呎 (2房)
 $1018万
 $20,940/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C35" s="21" t="inlineStr">
@@ -30409,7 +30409,7 @@
           <t>B | 494呎 (2房)
 $964万
 $19,520/呎
-(25年-07月-02日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D35" s="21" t="inlineStr">
@@ -30417,7 +30417,7 @@
           <t>C | 517呎 (2房)
 $1069万
 $20,681/呎
-(25年-07月-02日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E35" s="21" t="inlineStr">
@@ -30425,7 +30425,7 @@
           <t>D | 477呎 (2房)
 $928万
 $19,459/呎
-(25年-07月-14日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F35" s="21" t="inlineStr">
@@ -30433,7 +30433,7 @@
           <t>P1 | 1261呎 (4+房)
 $3426万
 $27,170/呎
-(25年-07月-14日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G35" s="21" t="inlineStr">
@@ -30441,7 +30441,7 @@
           <t>P2 | 870呎 (3房)
 $2399万
 $27,579/呎
-(25年-08月-25日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="H35" s="21" t="inlineStr">
@@ -30449,7 +30449,7 @@
           <t>P3 | 952呎 (3房)
 $2675万
 $28,100/呎
-(25年-07月-16日)</t>
+(25年-07月)</t>
         </is>
       </c>
     </row>
@@ -30464,7 +30464,7 @@
           <t>A | 486呎 (2房)
 $1014万
 $20,858/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C36" s="21" t="inlineStr">
@@ -30472,7 +30472,7 @@
           <t>B | 494呎 (2房)
 $960万
 $19,441/呎
-(25年-07月-10日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D36" s="21" t="inlineStr">
@@ -30480,7 +30480,7 @@
           <t>C | 517呎 (2房)
 $1002万
 $19,387/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E36" s="21" t="inlineStr">
@@ -30488,7 +30488,7 @@
           <t>D | 477呎 (2房)
 $976万
 $20,470/呎
-(25年-07月-16日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F36" s="21" t="inlineStr">
@@ -30496,7 +30496,7 @@
           <t>P1 | 1261呎 (4+房)
 $3881万
 $30,779/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G36" s="21" t="inlineStr">
@@ -30504,7 +30504,7 @@
           <t>P2 | 870呎 (3房)
 $2314万
 $26,600/呎
-(25年-09月-08日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="H36" s="21" t="inlineStr">
@@ -30512,7 +30512,7 @@
           <t>P3 | 952呎 (3房)
 $2570万
 $27,000/呎
-(25年-08月-18日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -30527,7 +30527,7 @@
           <t>A | 486呎 (2房)
 $1010万
 $20,776/呎
-(25年-07月-16日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C37" s="21" t="inlineStr">
@@ -30535,7 +30535,7 @@
           <t>B | 494呎 (2房)
 $957万
 $19,364/呎
-(25年-07月-06日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D37" s="21" t="inlineStr">
@@ -30543,7 +30543,7 @@
           <t>C | 517呎 (2房)
 $998万
 $19,309/呎
-(25年-07月-06日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E37" s="21" t="inlineStr">
@@ -30551,7 +30551,7 @@
           <t>D | 477呎 (2房)
 $910万
 $19,075/呎
-(25年-07月-10日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F37" s="21" t="inlineStr">
@@ -30559,7 +30559,7 @@
           <t>P1 | 1261呎 (4+房)
 $3577万
 $28,368/呎
-(25年-08月-05日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="G37" s="21" t="inlineStr">
@@ -30567,7 +30567,7 @@
           <t>P2 | 870呎 (3房)
 $2490万
 $28,620/呎
-(25年-12月-30日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="H37" s="21" t="inlineStr">
@@ -30575,7 +30575,7 @@
           <t>P3 | 952呎 (3房)
 $2686万
 $28,211/呎
-(25年-08月-27日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -30590,7 +30590,7 @@
           <t>A | 440呎 (2房)
 $1088万
 $24,716/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C38" s="21" t="inlineStr">
@@ -30598,7 +30598,7 @@
           <t>B | 448呎 (2房)
 $1120万
 $25,000/呎
-(25年-07月-16日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D38" s="21" t="inlineStr">
@@ -30606,7 +30606,7 @@
           <t>C | 467呎 (2房)
 $1238万
 $26,501/呎
-(25年-07月-10日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E38" s="21" t="inlineStr">
@@ -30614,7 +30614,7 @@
           <t>D | 430呎 (2房)
 $999万
 $23,233/呎
-(25年-07月-20日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F38" s="21" t="inlineStr">
@@ -30622,7 +30622,7 @@
           <t>P1 | 1162呎 (4+房)
 $3650万
 $31,411/呎
-(25年-07月-28日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G38" s="21" t="inlineStr">
@@ -30630,7 +30630,7 @@
           <t>P2 | 870呎 (3房)
 $2436万
 $28,000/呎
-(25年-12月-18日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="H38" s="21" t="inlineStr">
@@ -30638,7 +30638,7 @@
           <t>P3 | 952呎 (3房)
 $2758万
 $28,971/呎
-(25年-12月-16日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -30800,7 +30800,7 @@
           <t>A | 1020呎 (3房)
 $3652万
 $35,800/呎
-(26年-03月-11日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -30872,7 +30872,7 @@
           <t>A | 486呎 (2房)
 $1245万
 $25,619/呎
-(25年-09月-10日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -30880,7 +30880,7 @@
           <t>B | 485呎 (2房)
 $1138万
 $23,474/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
@@ -30888,7 +30888,7 @@
           <t>C | 491呎 (2房)
 $1137万
 $23,161/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -30929,7 +30929,7 @@
           <t>A | 486呎 (2房)
 $1180万
 $24,274/呎
-(25年-07月-14日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -30937,7 +30937,7 @@
           <t>B | 485呎 (2房)
 $1556万
 $32,089/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -30945,7 +30945,7 @@
           <t>C | 491呎 (2房)
 $1196万
 $24,365/呎
-(25年-07月-15日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
@@ -30953,7 +30953,7 @@
           <t>D | 476呎 (2房)
 $1532万
 $32,191/呎
-(26年-06月-17日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr"/>
@@ -30986,7 +30986,7 @@
           <t>A | 486呎 (2房)
 $1543万
 $31,745/呎
-(26年-04月-27日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -30994,7 +30994,7 @@
           <t>B | 485呎 (2房)
 $1169万
 $24,095/呎
-(25年-07月-30日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -31002,7 +31002,7 @@
           <t>C | 491呎 (2房)
 $1174万
 $23,906/呎
-(25年-07月-24日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr">
@@ -31010,7 +31010,7 @@
           <t>D | 476呎 (2房)
 $1137万
 $23,895/呎
-(25年-07月-23日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr"/>
@@ -31019,7 +31019,7 @@
           <t>P1 | 1422呎 (4+房)
 $6754万
 $47,500/呎
-(25年-11月-30日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -31027,7 +31027,7 @@
           <t>P2 | 1559呎 (4+房)
 $8574万
 $55,000/呎
-(26年-02月-11日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="I9" s="22" t="inlineStr"/>
@@ -31043,7 +31043,7 @@
           <t>A | 486呎 (2房)
 $1170万
 $24,078/呎
-(25年-07月-21日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -31051,7 +31051,7 @@
           <t>B | 485呎 (2房)
 $1112万
 $22,926/呎
-(25年-07月-22日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -31059,7 +31059,7 @@
           <t>C | 491呎 (2房)
 $1116万
 $22,723/呎
-(25年-07月-17日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
@@ -31067,7 +31067,7 @@
           <t>D | 476呎 (2房)
 $1081万
 $22,714/呎
-(25年-07月-15日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr"/>
@@ -31076,7 +31076,7 @@
           <t>P1 | 1422呎 (4+房)
 $6086万
 $42,800/呎
-(25年-09月-08日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="H10" s="21" t="inlineStr">
@@ -31084,7 +31084,7 @@
           <t>P2 | 1559呎 (4+房)
 $7592万
 $48,700/呎
-(25年-08月-11日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="I10" s="22" t="inlineStr"/>
@@ -31100,7 +31100,7 @@
           <t>A | 486呎 (2房)
 $1084万
 $22,307/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -31108,7 +31108,7 @@
           <t>B | 485呎 (2房)
 $1081万
 $22,287/呎
-(25年-07月-06日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -31116,7 +31116,7 @@
           <t>C | 491呎 (2房)
 $1276万
 $25,982/呎
-(26年-02月-26日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
@@ -31124,7 +31124,7 @@
           <t>D | 476呎 (2房)
 $1064万
 $22,357/呎
-(25年-08月-03日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr"/>
@@ -31133,7 +31133,7 @@
           <t>P1 | 1422呎 (4+房)
 $5644万
 $39,690/呎
-(25年-07月-15日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
@@ -31141,7 +31141,7 @@
           <t>P2 | 1559呎 (4+房)
 $6715万
 $43,071/呎
-(25年-07月-15日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="I11" s="22" t="inlineStr"/>
@@ -31157,7 +31157,7 @@
           <t>A | 486呎 (2房)
 $1081万
 $22,251/呎
-(25年-07月-22日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
@@ -31165,7 +31165,7 @@
           <t>B | 485呎 (2房)
 $1078万
 $22,231/呎
-(25年-07月-22日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -31173,7 +31173,7 @@
           <t>C | 491呎 (2房)
 $1082万
 $22,035/呎
-(25年-07月-17日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
@@ -31181,7 +31181,7 @@
           <t>D | 476呎 (2房)
 $1048万
 $22,027/呎
-(25年-07月-14日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr"/>
@@ -31190,7 +31190,7 @@
           <t>P1 | 1422呎 (4+房)
 $5431万
 $38,190/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
@@ -31198,7 +31198,7 @@
           <t>P2 | 1559呎 (4+房)
 $6324万
 $40,565/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="I12" s="22" t="inlineStr"/>
@@ -31214,7 +31214,7 @@
           <t>A | 486呎 (2房)
 $1065万
 $21,922/呎
-(25年-07月-22日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -31222,7 +31222,7 @@
           <t>B | 485呎 (2房)
 $1128万
 $23,256/呎
-(25年-07月-17日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -31230,7 +31230,7 @@
           <t>C | 491呎 (2房)
 $1132万
 $23,051/呎
-(25年-07月-17日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
@@ -31238,7 +31238,7 @@
           <t>D | 476呎 (2房)
 $998万
 $20,958/呎
-(25年-07月-16日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr"/>
@@ -31247,7 +31247,7 @@
           <t>P1 | 1422呎 (4+房)
 $5404万
 $38,000/呎
-(25年-07月-24日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="H13" s="21" t="inlineStr">
@@ -31255,7 +31255,7 @@
           <t>P2 | 1559呎 (4+房)
 $6018万
 $38,602/呎
-(25年-07月-03日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="I13" s="22" t="inlineStr"/>
@@ -31271,7 +31271,7 @@
           <t>A | 486呎 (2房)
 $1046万
 $21,523/呎
-(25年-06月-19日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -31279,7 +31279,7 @@
           <t>B | 485呎 (2房)
 $1108万
 $22,847/呎
-(25年-07月-06日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -31287,7 +31287,7 @@
           <t>C | 491呎 (2房)
 $1046万
 $21,314/呎
-(25年-07月-03日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
@@ -31295,7 +31295,7 @@
           <t>D | 476呎 (2房)
 $993万
 $20,855/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr"/>
@@ -31304,7 +31304,7 @@
           <t>P1 | 1422呎 (4+房)
 $5494万
 $38,634/呎
-(25年-07月-22日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="H14" s="21" t="inlineStr">
@@ -31312,7 +31312,7 @@
           <t>P2 | 1559呎 (4+房)
 $6220万
 $39,900/呎
-(25年-06月-23日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="I14" s="22" t="inlineStr"/>
@@ -31328,7 +31328,7 @@
           <t>A | 486呎 (2房)
 $1040万
 $21,395/呎
-(25年-07月-13日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -31336,7 +31336,7 @@
           <t>B | 485呎 (2房)
 $1102万
 $22,713/呎
-(25年-07月-13日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -31344,7 +31344,7 @@
           <t>C | 491呎 (2房)
 $1040万
 $21,187/呎
-(25年-07月-16日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -31352,7 +31352,7 @@
           <t>D | 476呎 (2房)
 $988万
 $20,750/呎
-(25年-07月-16日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr"/>
@@ -31361,7 +31361,7 @@
           <t>P1 | 1422呎 (4+房)
 $5052万
 $35,530/呎
-(25年-07月-07日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="H15" s="21" t="inlineStr">
@@ -31369,7 +31369,7 @@
           <t>P2 | 1559呎 (4+房)
 $5850万
 $37,525/呎
-(25年-06月-22日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="I15" s="22" t="inlineStr"/>
@@ -31385,7 +31385,7 @@
           <t>A | 486呎 (2房)
 $1034万
 $21,267/呎
-(25年-07月-13日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -31393,7 +31393,7 @@
           <t>B | 485呎 (2房)
 $1030万
 $21,247/呎
-(25年-07月-17日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -31401,7 +31401,7 @@
           <t>C | 491呎 (2房)
 $1099万
 $22,377/呎
-(25年-07月-15日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -31409,7 +31409,7 @@
           <t>D | 476呎 (2房)
 $983万
 $20,647/呎
-(25年-07月-15日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr"/>
@@ -31418,7 +31418,7 @@
           <t>P1 | 1422呎 (4+房)
 $4996万
 $35,136/呎
-(25年-06月-08日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="H16" s="21" t="inlineStr">
@@ -31426,7 +31426,7 @@
           <t>P2 | 1559呎 (4+房)
 $5791万
 $37,145/呎
-(25年-06月-24日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="I16" s="22" t="inlineStr"/>
@@ -31442,7 +31442,7 @@
           <t>A | 486呎 (2房)
 $1027万
 $21,140/呎
-(25年-07月-15日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -31450,7 +31450,7 @@
           <t>B | 485呎 (2房)
 $1024万
 $21,122/呎
-(25年-07月-10日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -31458,7 +31458,7 @@
           <t>C | 491呎 (2房)
 $1028万
 $20,937/呎
-(25年-07月-15日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -31466,7 +31466,7 @@
           <t>D | 476呎 (2房)
 $978万
 $20,546/呎
-(25年-07月-15日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr"/>
@@ -31475,7 +31475,7 @@
           <t>P1 | 1422呎 (4+房)
 $4839万
 $34,028/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="H17" s="21" t="inlineStr">
@@ -31483,7 +31483,7 @@
           <t>P2 | 1559呎 (4+房)
 $5609万
 $35,977/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="I17" s="22" t="inlineStr"/>
@@ -31499,7 +31499,7 @@
           <t>A | 486呎 (2房)
 $1083万
 $22,282/呎
-(25年-07月-17日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -31507,7 +31507,7 @@
           <t>B | 485呎 (2房)
 $1063万
 $21,915/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -31515,7 +31515,7 @@
           <t>C | 490呎 (2房)
 $1005万
 $20,506/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
@@ -31523,7 +31523,7 @@
           <t>D | 476呎 (2房)
 $964万
 $20,261/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr">
@@ -31531,7 +31531,7 @@
           <t>E | 455呎 (2房)
 $917万
 $20,160/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
@@ -31539,7 +31539,7 @@
           <t>P1 | 926呎 (3房)
 $3273万
 $35,350/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="H18" s="21" t="inlineStr">
@@ -31547,7 +31547,7 @@
           <t>P2 | 860呎 (3房)
 $2726万
 $31,700/呎
-(25年-07月-30日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="I18" s="21" t="inlineStr">
@@ -31555,7 +31555,7 @@
           <t>P3 | 826呎 (3房)
 $2494万
 $30,200/呎
-(25年-07月-30日)</t>
+(25年-07月)</t>
         </is>
       </c>
     </row>
@@ -31570,7 +31570,7 @@
           <t>A | 486呎 (2房)
 $1015万
 $20,889/呎
-(25年-07月-15日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -31578,7 +31578,7 @@
           <t>B | 485呎 (2房)
 $1059万
 $21,829/呎
-(25年-07月-02日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -31586,7 +31586,7 @@
           <t>C | 490呎 (2房)
 $1063万
 $21,700/呎
-(25年-07月-07日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -31594,7 +31594,7 @@
           <t>D | 476呎 (2房)
 $961万
 $20,181/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr">
@@ -31602,7 +31602,7 @@
           <t>E | 455呎 (2房)
 $971万
 $21,334/呎
-(25年-07月-06日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
@@ -31610,7 +31610,7 @@
           <t>P1 | 926呎 (3房)
 $3084万
 $33,300/呎
-(25年-07月-03日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="H19" s="21" t="inlineStr">
@@ -31618,7 +31618,7 @@
           <t>P2 | 860呎 (3房)
 $2582万
 $30,020/呎
-(25年-07月-02日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="I19" s="21" t="inlineStr">
@@ -31626,7 +31626,7 @@
           <t>P3 | 826呎 (3房)
 $2591万
 $31,368/呎
-(25年-09月-02日)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -31641,7 +31641,7 @@
           <t>A | 486呎 (2房)
 $1011万
 $20,807/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -31649,7 +31649,7 @@
           <t>B | 485呎 (2房)
 $1054万
 $21,742/呎
-(25年-07月-02日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -31657,7 +31657,7 @@
           <t>C | 490呎 (2房)
 $1059万
 $21,614/呎
-(25年-07月-07日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -31665,7 +31665,7 @@
           <t>D | 476呎 (2房)
 $957万
 $20,101/呎
-(25年-07月-02日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr">
@@ -31673,7 +31673,7 @@
           <t>E | 455呎 (2房)
 $910万
 $20,000/呎
-(25年-07月-02日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
@@ -31681,7 +31681,7 @@
           <t>P1 | 926呎 (3房)
 $3337万
 $36,040/呎
-(25年-07月-06日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="H20" s="21" t="inlineStr">
@@ -31689,7 +31689,7 @@
           <t>P2 | 860呎 (3房)
 $2541万
 $29,545/呎
-(25年-07月-03日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="I20" s="21" t="inlineStr">
@@ -31697,7 +31697,7 @@
           <t>P3 | 826呎 (3房)
 $2548万
 $30,850/呎
-(25年-08月-27日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -31712,7 +31712,7 @@
           <t>A | 486呎 (2房)
 $1070万
 $22,016/呎
-(25年-07月-06日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -31720,7 +31720,7 @@
           <t>B | 485呎 (2房)
 $1050万
 $21,656/呎
-(25年-07月-03日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -31728,7 +31728,7 @@
           <t>C | 490呎 (2房)
 $993万
 $20,261/呎
-(25年-06月-13日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -31736,7 +31736,7 @@
           <t>D | 476呎 (2房)
 $1012万
 $21,271/呎
-(25年-07月-02日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr">
@@ -31744,7 +31744,7 @@
           <t>E | 455呎 (2房)
 $906万
 $19,921/呎
-(25年-06月-13日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -31752,7 +31752,7 @@
           <t>P1 | 926呎 (3房)
 $3300万
 $35,639/呎
-(25年-06月-26日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="H21" s="21" t="inlineStr">
@@ -31760,7 +31760,7 @@
           <t>P2 | 860呎 (3房)
 $2500万
 $29,070/呎
-(25年-07月-07日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="I21" s="21" t="inlineStr">
@@ -31768,7 +31768,7 @@
           <t>P3 | 826呎 (3房)
 $2519万
 $30,500/呎
-(25年-08月-27日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -31783,7 +31783,7 @@
           <t>A | 486呎 (2房)
 $1003万
 $20,640/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -31791,7 +31791,7 @@
           <t>B | 485呎 (2房)
 $984万
 $20,299/呎
-(25年-07月-06日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -31799,7 +31799,7 @@
           <t>C | 490呎 (2房)
 $989万
 $20,180/呎
-(25年-07月-06日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -31807,7 +31807,7 @@
           <t>D | 476呎 (2房)
 $949万
 $19,941/呎
-(25年-07月-07日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
@@ -31815,7 +31815,7 @@
           <t>E | 455呎 (2房)
 $903万
 $19,842/呎
-(25年-07月-06日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
@@ -31823,7 +31823,7 @@
           <t>P1 | 926呎 (3房)
 $2824万
 $30,495/呎
-(25年-06月-18日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="H22" s="21" t="inlineStr">
@@ -31831,7 +31831,7 @@
           <t>P2 | 860呎 (3房)
 $2623万
 $30,500/呎
-(25年-07月-06日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="I22" s="21" t="inlineStr">
@@ -31839,7 +31839,7 @@
           <t>P3 | 826呎 (3房)
 $2490万
 $30,150/呎
-(25年-09月-01日)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -31854,7 +31854,7 @@
           <t>A | 486呎 (2房)
 $1062万
 $21,842/呎
-(25年-07月-13日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -31862,7 +31862,7 @@
           <t>B | 485呎 (2房)
 $981万
 $20,219/呎
-(25年-07月-06日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -31870,7 +31870,7 @@
           <t>C | 490呎 (2房)
 $985万
 $20,100/呎
-(25年-07月-07日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -31878,7 +31878,7 @@
           <t>D | 476呎 (2房)
 $945万
 $19,861/呎
-(25年-07月-06日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr">
@@ -31886,7 +31886,7 @@
           <t>E | 455呎 (2房)
 $955万
 $20,998/呎
-(25年-07月-06日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
@@ -31894,7 +31894,7 @@
           <t>P1 | 926呎 (3房)
 $2784万
 $30,068/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="H23" s="21" t="inlineStr">
@@ -31902,7 +31902,7 @@
           <t>P2 | 860呎 (3房)
 $2487万
 $28,916/呎
-(25年-07月-22日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="I23" s="21" t="inlineStr">
@@ -31910,7 +31910,7 @@
           <t>P3 | 826呎 (3房)
 $2437万
 $29,500/呎
-(25年-07月-06日)</t>
+(25年-07月)</t>
         </is>
       </c>
     </row>
@@ -31925,7 +31925,7 @@
           <t>A | 486呎 (2房)
 $983万
 $20,220/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -31933,7 +31933,7 @@
           <t>B | 485呎 (2房)
 $977万
 $20,140/呎
-(25年-07月-06日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -31941,7 +31941,7 @@
           <t>C | 490呎 (2房)
 $1042万
 $21,269/呎
-(25年-07月-06日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -31949,7 +31949,7 @@
           <t>D | 476呎 (2房)
 $942万
 $19,782/呎
-(25年-07月-06日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr">
@@ -31957,7 +31957,7 @@
           <t>E | 455呎 (2房)
 $896万
 $19,684/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -31965,7 +31965,7 @@
           <t>P1 | 926呎 (3房)
 $3217万
 $34,740/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="H24" s="21" t="inlineStr">
@@ -31973,7 +31973,7 @@
           <t>P2 | 860呎 (3房)
 $2482万
 $28,856/呎
-(25年-07月-17日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="I24" s="21" t="inlineStr">
@@ -31981,7 +31981,7 @@
           <t>P3 | 826呎 (3房)
 $2342万
 $28,350/呎
-(25年-08月-14日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -31996,7 +31996,7 @@
           <t>A | 486呎 (2房)
 $1053万
 $21,669/呎
-(25年-07月-01日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -32004,7 +32004,7 @@
           <t>B | 485呎 (2房)
 $973万
 $20,058/呎
-(25年-07月-02日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -32012,7 +32012,7 @@
           <t>C | 490呎 (2房)
 $977万
 $19,941/呎
-(25年-07月-03日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -32020,7 +32020,7 @@
           <t>D | 476呎 (2房)
 $996万
 $20,935/呎
-(25年-07月-01日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
@@ -32028,7 +32028,7 @@
           <t>E | 455呎 (2房)
 $892万
 $19,604/呎
-(25年-07月-07日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G25" s="21" t="inlineStr">
@@ -32036,7 +32036,7 @@
           <t>P1 | 926呎 (3房)
 $3045万
 $32,880/呎
-(25年-07月-06日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="H25" s="21" t="inlineStr">
@@ -32044,7 +32044,7 @@
           <t>P2 | 860呎 (3房)
 $2451万
 $28,500/呎
-(25年-07月-22日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="I25" s="21" t="inlineStr">
@@ -32052,7 +32052,7 @@
           <t>P3 | 826呎 (3房)
 $2321万
 $28,100/呎
-(25年-08月-28日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -32067,7 +32067,7 @@
           <t>A | 486呎 (2房)
 $987万
 $20,313/呎
-(25年-06月-29日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
@@ -32075,7 +32075,7 @@
           <t>B | 485呎 (2房)
 $969万
 $19,977/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -32083,7 +32083,7 @@
           <t>C | 490呎 (2房)
 $1034万
 $21,102/呎
-(25年-07月-02日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -32091,7 +32091,7 @@
           <t>D | 476呎 (2房)
 $934万
 $19,624/呎
-(25年-06月-13日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr">
@@ -32099,7 +32099,7 @@
           <t>E | 455呎 (2房)
 $888万
 $19,525/呎
-(25年-07月-10日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">
@@ -32107,7 +32107,7 @@
           <t>P1 | 926呎 (3房)
 $2727万
 $29,450/呎
-(25年-07月-13日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="H26" s="21" t="inlineStr">
@@ -32115,7 +32115,7 @@
           <t>P2 | 860呎 (3房)
 $2426万
 $28,215/呎
-(25年-07月-29日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="I26" s="21" t="inlineStr">
@@ -32123,7 +32123,7 @@
           <t>P3 | 826呎 (3房)
 $2310万
 $27,970/呎
-(25年-09月-22日)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -32138,7 +32138,7 @@
           <t>A | 486呎 (2房)
 $983万
 $20,233/呎
-(25年-07月-06日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
@@ -32146,7 +32146,7 @@
           <t>B | 485呎 (2房)
 $965万
 $19,899/呎
-(25年-07月-01日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -32154,7 +32154,7 @@
           <t>C | 490呎 (2房)
 $969万
 $19,780/呎
-(25年-07月-06日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -32162,7 +32162,7 @@
           <t>D | 476呎 (2房)
 $988万
 $20,767/呎
-(25年-07月-01日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F27" s="21" t="inlineStr">
@@ -32170,7 +32170,7 @@
           <t>E | 455呎 (2房)
 $885万
 $19,448/呎
-(25年-07月-06日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G27" s="21" t="inlineStr">
@@ -32178,7 +32178,7 @@
           <t>P1 | 926呎 (3房)
 $2701万
 $29,165/呎
-(25年-07月-14日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="H27" s="21" t="inlineStr">
@@ -32186,7 +32186,7 @@
           <t>P2 | 860呎 (3房)
 $2402万
 $27,930/呎
-(25年-07月-22日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="I27" s="21" t="inlineStr">
@@ -32194,7 +32194,7 @@
           <t>P3 | 826呎 (3房)
 $2294万
 $27,770/呎
-(25年-09月-29日)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -32209,7 +32209,7 @@
           <t>A | 486呎 (2房)
 $979万
 $20,152/呎
-(25年-07月-03日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
@@ -32217,7 +32217,7 @@
           <t>B | 485呎 (2房)
 $949万
 $19,571/呎
-(25年-07月-01日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -32225,7 +32225,7 @@
           <t>C | 490呎 (2房)
 $965万
 $19,702/呎
-(25年-07月-03日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr">
@@ -32233,7 +32233,7 @@
           <t>D | 476呎 (2房)
 $927万
 $19,468/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F28" s="21" t="inlineStr">
@@ -32241,7 +32241,7 @@
           <t>E | 455呎 (2房)
 $926万
 $20,341/呎
-(25年-07月-07日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
@@ -32249,7 +32249,7 @@
           <t>P1 | 926呎 (3房)
 $2674万
 $28,880/呎
-(25年-07月-15日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="H28" s="21" t="inlineStr">
@@ -32257,7 +32257,7 @@
           <t>P2 | 860呎 (3房)
 $2498万
 $29,041/呎
-(25年-07月-24日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="I28" s="21" t="inlineStr">
@@ -32265,7 +32265,7 @@
           <t>P3 | 826呎 (3房)
 $2277万
 $27,570/呎
-(25年-09月-28日)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -32280,7 +32280,7 @@
           <t>A | 486呎 (2房)
 $976万
 $20,072/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C29" s="21" t="inlineStr">
@@ -32288,7 +32288,7 @@
           <t>B | 485呎 (2房)
 $957万
 $19,740/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D29" s="21" t="inlineStr">
@@ -32296,7 +32296,7 @@
           <t>C | 490呎 (2房)
 $962万
 $19,624/呎
-(25年-07月-03日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E29" s="21" t="inlineStr">
@@ -32304,7 +32304,7 @@
           <t>D | 476呎 (2房)
 $981万
 $20,603/呎
-(25年-07月-03日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F29" s="21" t="inlineStr">
@@ -32312,7 +32312,7 @@
           <t>E | 455呎 (2房)
 $878万
 $19,295/呎
-(25年-07月-02日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G29" s="21" t="inlineStr">
@@ -32320,7 +32320,7 @@
           <t>P1 | 926呎 (3房)
 $2787万
 $30,100/呎
-(25年-07月-13日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="H29" s="21" t="inlineStr">
@@ -32328,7 +32328,7 @@
           <t>P2 | 860呎 (3房)
 $2555万
 $29,713/呎
-(25年-07月-17日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="I29" s="21" t="inlineStr">
@@ -32336,7 +32336,7 @@
           <t>P3 | 826呎 (3房)
 $2355万
 $28,511/呎
-(25年-09月-18日)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -32351,7 +32351,7 @@
           <t>A | 486呎 (2房)
 $1032万
 $21,241/呎
-(25年-07月-07日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C30" s="21" t="inlineStr">
@@ -32359,7 +32359,7 @@
           <t>B | 485呎 (2房)
 $1013万
 $20,891/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D30" s="21" t="inlineStr">
@@ -32367,7 +32367,7 @@
           <t>C | 490呎 (2房)
 $1018万
 $20,767/呎
-(25年-07月-07日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E30" s="21" t="inlineStr">
@@ -32375,7 +32375,7 @@
           <t>D | 476呎 (2房)
 $919万
 $19,313/呎
-(25年-07月-07日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F30" s="21" t="inlineStr">
@@ -32383,7 +32383,7 @@
           <t>E | 455呎 (2房)
 $874万
 $19,218/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G30" s="21" t="inlineStr">
@@ -32391,7 +32391,7 @@
           <t>P1 | 926呎 (3房)
 $2622万
 $28,310/呎
-(25年-07月-22日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="H30" s="21" t="inlineStr">
@@ -32399,7 +32399,7 @@
           <t>P2 | 860呎 (3房)
 $2378万
 $27,650/呎
-(25年-08月-03日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="I30" s="21" t="inlineStr">
@@ -32407,7 +32407,7 @@
           <t>P3 | 826呎 (3房)
 $2244万
 $27,169/呎
-(25年-09月-29日)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -32422,7 +32422,7 @@
           <t>A | 486呎 (2房)
 $1028万
 $21,156/呎
-(25年-07月-03日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C31" s="21" t="inlineStr">
@@ -32430,7 +32430,7 @@
           <t>B | 485呎 (2房)
 $1009万
 $20,808/呎
-(25年-07月-03日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D31" s="21" t="inlineStr">
@@ -32438,7 +32438,7 @@
           <t>C | 490呎 (2房)
 $1014万
 $20,686/呎
-(25年-07月-07日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E31" s="21" t="inlineStr">
@@ -32446,7 +32446,7 @@
           <t>D | 476呎 (2房)
 $916万
 $19,235/呎
-(25年-07月-03日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F31" s="21" t="inlineStr">
@@ -32454,7 +32454,7 @@
           <t>E | 455呎 (2房)
 $871万
 $19,141/呎
-(25年-07月-03日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G31" s="21" t="inlineStr">
@@ -32462,7 +32462,7 @@
           <t>P1 | 926呎 (3房)
 $2734万
 $29,526/呎
-(25年-08月-10日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="H31" s="21" t="inlineStr">
@@ -32470,7 +32470,7 @@
           <t>P2 | 860呎 (3房)
 $2382万
 $27,700/呎
-(25年-08月-20日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="I31" s="21" t="inlineStr">
@@ -32478,7 +32478,7 @@
           <t>P3 | 826呎 (3房)
 $2304万
 $27,900/呎
-(25年-10月-09日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -32493,7 +32493,7 @@
           <t>A | 486呎 (2房)
 $1024万
 $21,072/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C32" s="21" t="inlineStr">
@@ -32501,7 +32501,7 @@
           <t>B | 485呎 (2房)
 $934万
 $19,262/呎
-(25年-07月-06日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D32" s="21" t="inlineStr">
@@ -32509,7 +32509,7 @@
           <t>C | 490呎 (2房)
 $950万
 $19,390/呎
-(25年-07月-07日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E32" s="21" t="inlineStr">
@@ -32517,7 +32517,7 @@
           <t>D | 476呎 (2房)
 $969万
 $20,357/呎
-(25年-07月-06日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F32" s="21" t="inlineStr">
@@ -32525,7 +32525,7 @@
           <t>E | 455呎 (2房)
 $867万
 $19,064/呎
-(25年-07月-06日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G32" s="21" t="inlineStr">
@@ -32533,7 +32533,7 @@
           <t>P1 | 926呎 (3房)
 $2715万
 $29,316/呎
-(25年-07月-31日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="H32" s="21" t="inlineStr">
@@ -32541,7 +32541,7 @@
           <t>P2 | 860呎 (3房)
 $2365万
 $27,500/呎
-(25年-08月-18日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="I32" s="21" t="inlineStr">
@@ -32549,7 +32549,7 @@
           <t>P3 | 826呎 (3房)
 $2211万
 $26,770/呎
-(25年-09月-25日)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -32564,7 +32564,7 @@
           <t>A | 486呎 (2房)
 $1020万
 $20,988/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C33" s="21" t="inlineStr">
@@ -32572,7 +32572,7 @@
           <t>B | 485呎 (2房)
 $1001万
 $20,643/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D33" s="21" t="inlineStr">
@@ -32580,7 +32580,7 @@
           <t>C | 490呎 (2房)
 $946万
 $19,314/呎
-(25年-07月-07日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E33" s="21" t="inlineStr">
@@ -32588,7 +32588,7 @@
           <t>D | 476呎 (2房)
 $908万
 $19,084/呎
-(25年-07月-06日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F33" s="21" t="inlineStr">
@@ -32596,7 +32596,7 @@
           <t>E | 455呎 (2房)
 $864万
 $18,989/呎
-(25年-07月-02日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G33" s="21" t="inlineStr">
@@ -32604,7 +32604,7 @@
           <t>P1 | 926呎 (3房)
 $2584万
 $27,900/呎
-(25年-08月-10日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="H33" s="21" t="inlineStr">
@@ -32612,7 +32612,7 @@
           <t>P2 | 860呎 (3房)
 $2348万
 $27,300/呎
-(25年-08月-18日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="I33" s="21" t="inlineStr">
@@ -32620,7 +32620,7 @@
           <t>P3 | 826呎 (3房)
 $2272万
 $27,500/呎
-(25年-10月-09日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -32635,7 +32635,7 @@
           <t>A | 486呎 (2房)
 $1016万
 $20,905/呎
-(25年-07月-06日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C34" s="21" t="inlineStr">
@@ -32643,7 +32643,7 @@
           <t>B | 485呎 (2房)
 $938万
 $19,351/呎
-(25年-07月-01日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D34" s="21" t="inlineStr">
@@ -32651,7 +32651,7 @@
           <t>C | 490呎 (2房)
 $943万
 $19,237/呎
-(25年-07月-10日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E34" s="21" t="inlineStr">
@@ -32659,7 +32659,7 @@
           <t>D | 476呎 (2房)
 $905万
 $19,008/呎
-(25年-07月-01日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F34" s="21" t="inlineStr">
@@ -32667,7 +32667,7 @@
           <t>E | 455呎 (2房)
 $914万
 $20,095/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G34" s="21" t="inlineStr">
@@ -32675,7 +32675,7 @@
           <t>P1 | 926呎 (3房)
 $2565万
 $27,700/呎
-(25年-09月-16日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="H34" s="21" t="inlineStr">
@@ -32683,7 +32683,7 @@
           <t>P2 | 860呎 (3房)
 $2331万
 $27,100/呎
-(25年-09月-16日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="I34" s="21" t="inlineStr">
@@ -32691,7 +32691,7 @@
           <t>P3 | 826呎 (3房)
 $2296万
 $27,800/呎
-(25年-10月-15日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -32706,7 +32706,7 @@
           <t>A | 486呎 (2房)
 $952万
 $19,597/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C35" s="21" t="inlineStr">
@@ -32714,7 +32714,7 @@
           <t>B | 485呎 (2房)
 $993万
 $20,478/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D35" s="21" t="inlineStr">
@@ -32722,7 +32722,7 @@
           <t>C | 490呎 (2房)
 $939万
 $19,159/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E35" s="21" t="inlineStr">
@@ -32730,7 +32730,7 @@
           <t>D | 476呎 (2房)
 $901万
 $18,933/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F35" s="21" t="inlineStr">
@@ -32738,7 +32738,7 @@
           <t>E | 455呎 (2房)
 $911万
 $20,013/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G35" s="21" t="inlineStr">
@@ -32746,7 +32746,7 @@
           <t>P1 | 926呎 (3房)
 $2680万
 $28,947/呎
-(25年-09月-02日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="H35" s="21" t="inlineStr">
@@ -32754,7 +32754,7 @@
           <t>P2 | 860呎 (3房)
 $2313万
 $26,895/呎
-(25年-09月-25日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="I35" s="21" t="inlineStr">
@@ -32762,7 +32762,7 @@
           <t>P3 | 826呎 (3房)
 $2280万
 $27,599/呎
-(25年-11月-02日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -32777,7 +32777,7 @@
           <t>A | 486呎 (2房)
 $949万
 $19,519/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C36" s="21" t="inlineStr">
@@ -32785,7 +32785,7 @@
           <t>B | 485呎 (2房)
 $931万
 $19,196/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D36" s="21" t="inlineStr">
@@ -32793,7 +32793,7 @@
           <t>C | 490呎 (2房)
 $935万
 $19,084/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E36" s="21" t="inlineStr">
@@ -32801,7 +32801,7 @@
           <t>D | 476呎 (2房)
 $954万
 $20,036/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F36" s="21" t="inlineStr">
@@ -32809,7 +32809,7 @@
           <t>E | 455呎 (2房)
 $854万
 $18,763/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G36" s="21" t="inlineStr">
@@ -32817,7 +32817,7 @@
           <t>P1 | 926呎 (3房)
 $2556万
 $27,600/呎
-(25年-09月-11日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="H36" s="21" t="inlineStr">
@@ -32825,7 +32825,7 @@
           <t>P2 | 860呎 (3房)
 $2339万
 $27,200/呎
-(25年-10月-14日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="I36" s="21" t="inlineStr">
@@ -32833,7 +32833,7 @@
           <t>P3 | 826呎 (3房)
 $2263万
 $27,400/呎
-(25年-10月-30日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -32848,7 +32848,7 @@
           <t>A | 486呎 (2房)
 $945万
 $19,440/呎
-(25年-07月-02日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C37" s="21" t="inlineStr">
@@ -32856,7 +32856,7 @@
           <t>B | 485呎 (2房)
 $927万
 $19,120/呎
-(25年-07月-02日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D37" s="21" t="inlineStr">
@@ -32864,7 +32864,7 @@
           <t>C | 490呎 (2房)
 $931万
 $19,006/呎
-(25年-07月-07日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E37" s="21" t="inlineStr">
@@ -32872,7 +32872,7 @@
           <t>D | 476呎 (2房)
 $894万
 $18,782/呎
-(25年-07月-07日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F37" s="21" t="inlineStr">
@@ -32880,7 +32880,7 @@
           <t>E | 455呎 (2房)
 $850万
 $18,688/呎
-(25年-07月-02日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G37" s="21" t="inlineStr">
@@ -32888,7 +32888,7 @@
           <t>P1 | 926呎 (3房)
 $2574万
 $27,800/呎
-(25年-10月-08日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="H37" s="21" t="inlineStr">
@@ -32896,7 +32896,7 @@
           <t>P2 | 860呎 (3房)
 $2365万
 $27,500/呎
-(25年-10月-20日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="I37" s="21" t="inlineStr">
@@ -32904,7 +32904,7 @@
           <t>P3 | 826呎 (3房)
 $2247万
 $27,200/呎
-(25年-10月-30日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -32919,7 +32919,7 @@
           <t>A | 440呎 (2房)
 $1158万
 $26,316/呎
-(25年-07月-07日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C38" s="21" t="inlineStr">
@@ -32927,7 +32927,7 @@
           <t>B | 439呎 (2房)
 $1089万
 $24,800/呎
-(25年-07月-02日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D38" s="21" t="inlineStr">
@@ -32935,7 +32935,7 @@
           <t>C | 444呎 (2房)
 $1092万
 $24,599/呎
-(25年-07月-10日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E38" s="21" t="inlineStr">
@@ -32943,7 +32943,7 @@
           <t>D | 430呎 (2房)
 $1182万
 $27,500/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F38" s="21" t="inlineStr">
@@ -32951,7 +32951,7 @@
           <t>E | 408呎 (2房)
 $1040万
 $25,500/呎
-(25年-07月-07日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G38" s="21" t="inlineStr">
@@ -32959,7 +32959,7 @@
           <t>P1 | 926呎 (3房)
 $2546万
 $27,499/呎
-(25年-10月-09日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="H38" s="21" t="inlineStr">
@@ -32967,7 +32967,7 @@
           <t>P2 | 860呎 (3房)
 $2471万
 $28,737/呎
-(25年-10月-21日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="I38" s="21" t="inlineStr">
@@ -32975,7 +32975,7 @@
           <t>P3 | 826呎 (3房)
 $2354万
 $28,500/呎
-(26年-01月-13日)</t>
+(26年-01月)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-黄竹坑-滶晨.xlsx
+++ b/files/港岛-黄竹坑-滶晨.xlsx
@@ -28744,7 +28744,7 @@
           <t>C | 1083呎 (3房)
 $3890万
 $35,921/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr"/>
@@ -28791,7 +28791,7 @@
           <t>A | 486呎 (2房)
 $1593万
 $32,776/呎
-(26年-04月)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -28799,7 +28799,7 @@
           <t>B | 494呎 (2房)
 $1142万
 $23,109/呎
-(25年-07月)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
@@ -28807,7 +28807,7 @@
           <t>C | 517呎 (2房)
 $1235万
 $23,892/呎
-(25年-07月)</t>
+(25年-07月-10日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr"/>
@@ -28840,7 +28840,7 @@
           <t>A | 486呎 (2房)
 $1566万
 $32,222/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -28848,7 +28848,7 @@
           <t>B | 494呎 (2房)
 $1130万
 $22,881/呎
-(25年-07月)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -28856,7 +28856,7 @@
           <t>C | 517呎 (2房)
 $1276万
 $24,689/呎
-(25年-07月)</t>
+(25年-07月-16日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr"/>
@@ -28873,7 +28873,7 @@
           <t>P2 | 1706呎 (4+房)
 $10775万
 $63,158/呎
-(26年-01月)</t>
+(26年-01月-26日)</t>
         </is>
       </c>
       <c r="H8" s="22" t="inlineStr"/>
@@ -28889,7 +28889,7 @@
           <t>A | 486呎 (2房)
 $1429万
 $29,401/呎
-(26年-03月)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -28897,7 +28897,7 @@
           <t>B | 494呎 (2房)
 $1227万
 $24,844/呎
-(25年-08月)</t>
+(25年-08月-10日)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -28905,7 +28905,7 @@
           <t>C | 517呎 (2房)
 $1245万
 $24,087/呎
-(25年-07月)</t>
+(25年-07月-16日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr"/>
@@ -28914,7 +28914,7 @@
           <t>P1 | 1536呎 (4+房)
 $7296万
 $47,500/呎
-(25年-11月)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
       <c r="G9" s="21" t="inlineStr">
@@ -28922,7 +28922,7 @@
           <t>P2 | 1706呎 (4+房)
 $8530万
 $50,000/呎
-(25年-06月)</t>
+(25年-06月-25日)</t>
         </is>
       </c>
       <c r="H9" s="22" t="inlineStr"/>
@@ -28938,7 +28938,7 @@
           <t>A | 486呎 (2房)
 $1117万
 $22,990/呎
-(25年-07月)</t>
+(25年-07月-17日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -28946,7 +28946,7 @@
           <t>B | 494呎 (2房)
 $1131万
 $22,903/呎
-(25年-07月)</t>
+(25年-07月-17日)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -28954,7 +28954,7 @@
           <t>C | 517呎 (2房)
 $1154万
 $22,317/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr"/>
@@ -28963,7 +28963,7 @@
           <t>P1 | 1536呎 (4+房)
 $6543万
 $42,600/呎
-(25年-06月)</t>
+(25年-06月-22日)</t>
         </is>
       </c>
       <c r="G10" s="21" t="inlineStr">
@@ -28971,7 +28971,7 @@
           <t>P2 | 1706呎 (4+房)
 $8189万
 $48,000/呎
-(25年-06月)</t>
+(25年-06月-22日)</t>
         </is>
       </c>
       <c r="H10" s="22" t="inlineStr"/>
@@ -28987,7 +28987,7 @@
           <t>A | 486呎 (2房)
 $1086万
 $22,346/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -28995,7 +28995,7 @@
           <t>B | 494呎 (2房)
 $1100万
 $22,265/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -29003,7 +29003,7 @@
           <t>C | 517呎 (2房)
 $1217万
 $23,536/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr"/>
@@ -29012,7 +29012,7 @@
           <t>P1 | 1536呎 (4+房)
 $6420万
 $41,800/呎
-(25年-06月)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr">
@@ -29020,7 +29020,7 @@
           <t>P2 | 1706呎 (4+房)
 $7558万
 $44,300/呎
-(25年-06月)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
       <c r="H11" s="22" t="inlineStr"/>
@@ -29036,7 +29036,7 @@
           <t>A | 486呎 (2房)
 $1083万
 $22,292/呎
-(25年-07月)</t>
+(25年-07月-22日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
@@ -29044,7 +29044,7 @@
           <t>B | 494呎 (2房)
 $1097万
 $22,211/呎
-(25年-07月)</t>
+(25年-07月-22日)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -29052,7 +29052,7 @@
           <t>C | 517呎 (2房)
 $1137万
 $21,986/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr"/>
@@ -29061,7 +29061,7 @@
           <t>P1 | 1536呎 (4+房)
 $6298万
 $41,000/呎
-(25年-06月)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr">
@@ -29069,7 +29069,7 @@
           <t>P2 | 1706呎 (4+房)
 $7421万
 $43,500/呎
-(25年-06月)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr"/>
@@ -29085,7 +29085,7 @@
           <t>A | 486呎 (2房)
 $1067万
 $21,963/呎
-(25年-06月)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -29093,7 +29093,7 @@
           <t>B | 494呎 (2房)
 $1081万
 $21,881/呎
-(25年-07月)</t>
+(25年-07月-22日)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -29101,7 +29101,7 @@
           <t>C | 517呎 (2房)
 $1128万
 $21,822/呎
-(25年-07月)</t>
+(25年-07月-13日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr"/>
@@ -29110,7 +29110,7 @@
           <t>P1 | 1536呎 (4+房)
 $6089万
 $39,641/呎
-(25年-07月)</t>
+(25年-07月-13日)</t>
         </is>
       </c>
       <c r="G13" s="21" t="inlineStr">
@@ -29118,7 +29118,7 @@
           <t>P2 | 1706呎 (4+房)
 $7319万
 $42,900/呎
-(25年-06月)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr"/>
@@ -29134,7 +29134,7 @@
           <t>A | 486呎 (2房)
 $1048万
 $21,562/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -29142,7 +29142,7 @@
           <t>B | 494呎 (2房)
 $1061万
 $21,482/呎
-(25年-07月)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -29150,7 +29150,7 @@
           <t>C | 517呎 (2房)
 $1123万
 $21,714/呎
-(25年-07月)</t>
+(25年-07月-10日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr"/>
@@ -29159,7 +29159,7 @@
           <t>P1 | 1536呎 (4+房)
 $5990万
 $39,000/呎
-(25年-07月)</t>
+(25年-07月-10日)</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr">
@@ -29167,7 +29167,7 @@
           <t>P2 | 1706呎 (4+房)
 $6726万
 $39,425/呎
-(25年-06月)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr"/>
@@ -29183,7 +29183,7 @@
           <t>A | 486呎 (2房)
 $1107万
 $22,772/呎
-(25年-07月)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -29191,7 +29191,7 @@
           <t>B | 494呎 (2房)
 $1055万
 $21,354/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -29199,7 +29199,7 @@
           <t>C | 517呎 (2房)
 $1187万
 $22,956/呎
-(25年-06月)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr"/>
@@ -29208,7 +29208,7 @@
           <t>P1 | 1536呎 (4+房)
 $5574万
 $36,290/呎
-(25年-06月)</t>
+(25年-06月-11日)</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr">
@@ -29216,7 +29216,7 @@
           <t>P2 | 1706呎 (4+房)
 $6596万
 $38,665/呎
-(25年-06月)</t>
+(25年-06月-11日)</t>
         </is>
       </c>
       <c r="H15" s="22" t="inlineStr"/>
@@ -29232,7 +29232,7 @@
           <t>A | 486呎 (2房)
 $1100万
 $22,638/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -29240,7 +29240,7 @@
           <t>B | 494呎 (2房)
 $1114万
 $22,553/呎
-(25年-07月)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -29248,7 +29248,7 @@
           <t>C | 517呎 (2房)
 $1112万
 $21,499/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr"/>
@@ -29257,7 +29257,7 @@
           <t>P1 | 1536呎 (4+房)
 $5076万
 $33,047/呎
-(25年-07月)</t>
+(25年-07月-16日)</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
@@ -29265,7 +29265,7 @@
           <t>P2 | 1706呎 (4+房)
 $6467万
 $37,906/呎
-(25年-06月)</t>
+(25年-06月-11日)</t>
         </is>
       </c>
       <c r="H16" s="22" t="inlineStr"/>
@@ -29281,7 +29281,7 @@
           <t>A | 486呎 (2房)
 $1094万
 $22,502/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -29289,7 +29289,7 @@
           <t>B | 494呎 (2房)
 $1108万
 $22,419/呎
-(25年-07月)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -29297,7 +29297,7 @@
           <t>C | 517呎 (2房)
 $1175万
 $22,729/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr"/>
@@ -29306,7 +29306,7 @@
           <t>P1 | 1469呎 (4+房)
 $5739万
 $39,066/呎
-(25年-06月)</t>
+(25年-06月-18日)</t>
         </is>
       </c>
       <c r="G17" s="21" t="inlineStr">
@@ -29314,7 +29314,7 @@
           <t>P2 | 1706呎 (4+房)
 $6739万
 $39,501/呎
-(25年-06月)</t>
+(25年-06月-18日)</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr"/>
@@ -29330,7 +29330,7 @@
           <t>A | 486呎 (2房)
 $1025万
 $21,095/呎
-(25年-07月)</t>
+(25年-07月-13日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -29338,7 +29338,7 @@
           <t>B | 494呎 (2房)
 $1036万
 $20,972/呎
-(25年-07月)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -29346,7 +29346,7 @@
           <t>C | 517呎 (2房)
 $1084万
 $20,973/呎
-(25年-07月)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
@@ -29354,7 +29354,7 @@
           <t>D | 477呎 (2房)
 $1011万
 $21,201/呎
-(25年-07月)</t>
+(25年-07月-13日)</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr">
@@ -29362,7 +29362,7 @@
           <t>P1 | 1258呎 (4+房)
 $4422万
 $35,149/呎
-(25年-06月)</t>
+(25年-06月-10日)</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
@@ -29370,7 +29370,7 @@
           <t>P2 | 870呎 (3房)
 $2694万
 $30,970/呎
-(25年-07月)</t>
+(25年-07月-01日)</t>
         </is>
       </c>
       <c r="H18" s="21" t="inlineStr">
@@ -29378,7 +29378,7 @@
           <t>P3 | 952呎 (3房)
 $3313万
 $34,800/呎
-(25年-06月)</t>
+(25年-06月-25日)</t>
         </is>
       </c>
     </row>
@@ -29393,7 +29393,7 @@
           <t>A | 486呎 (2房)
 $1021万
 $21,010/呎
-(25年-07月)</t>
+(25年-07月-10日)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -29401,7 +29401,7 @@
           <t>B | 494呎 (2房)
 $1032万
 $20,889/呎
-(25年-07月)</t>
+(25年-07月-10日)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -29409,7 +29409,7 @@
           <t>C | 517呎 (2房)
 $1066万
 $20,629/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -29417,7 +29417,7 @@
           <t>D | 477呎 (2房)
 $1005万
 $21,073/呎
-(25年-07月)</t>
+(25年-07月-13日)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr">
@@ -29425,7 +29425,7 @@
           <t>P1 | 1261呎 (4+房)
 $4351万
 $34,508/呎
-(25年-06月)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
@@ -29433,7 +29433,7 @@
           <t>P2 | 870呎 (3房)
 $2653万
 $30,495/呎
-(25年-06月)</t>
+(25年-06月-29日)</t>
         </is>
       </c>
       <c r="H19" s="21" t="inlineStr">
@@ -29441,7 +29441,7 @@
           <t>P3 | 952呎 (3房)
 $3447万
 $36,211/呎
-(25年-07月)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
     </row>
@@ -29456,7 +29456,7 @@
           <t>A | 486呎 (2房)
 $1017万
 $20,926/呎
-(25年-07月)</t>
+(25年-07月-13日)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -29464,7 +29464,7 @@
           <t>B | 494呎 (2房)
 $1028万
 $20,806/呎
-(25年-07月)</t>
+(25年-07月-13日)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -29472,7 +29472,7 @@
           <t>C | 517呎 (2房)
 $1076万
 $20,805/呎
-(25年-07月)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -29480,7 +29480,7 @@
           <t>D | 477呎 (2房)
 $999万
 $20,948/呎
-(25年-07月)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr">
@@ -29488,7 +29488,7 @@
           <t>P1 | 1261呎 (4+房)
 $4540万
 $36,000/呎
-(25年-06月)</t>
+(25年-06月-25日)</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
@@ -29496,7 +29496,7 @@
           <t>P2 | 870呎 (3房)
 $2612万
 $30,020/呎
-(25年-06月)</t>
+(25年-06月-22日)</t>
         </is>
       </c>
       <c r="H20" s="21" t="inlineStr">
@@ -29504,7 +29504,7 @@
           <t>P3 | 952呎 (3房)
 $3256万
 $34,200/呎
-(25年-06月)</t>
+(25年-06月-22日)</t>
         </is>
       </c>
     </row>
@@ -29519,7 +29519,7 @@
           <t>A | 486呎 (2房)
 $1013万
 $20,844/呎
-(25年-07月)</t>
+(25年-07月-13日)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -29527,7 +29527,7 @@
           <t>B | 494呎 (2房)
 $1024万
 $20,723/呎
-(25年-07月)</t>
+(25年-07月-10日)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -29535,7 +29535,7 @@
           <t>C | 517呎 (2房)
 $1138万
 $22,017/呎
-(25年-07月)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -29543,7 +29543,7 @@
           <t>D | 477呎 (2房)
 $993万
 $20,824/呎
-(25年-07月)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr">
@@ -29551,7 +29551,7 @@
           <t>P1 | 1261呎 (4+房)
 $4265万
 $33,820/呎
-(25年-06月)</t>
+(25年-06月-11日)</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -29559,7 +29559,7 @@
           <t>P2 | 870呎 (3房)
 $2579万
 $29,640/呎
-(25年-07月)</t>
+(25年-07月-10日)</t>
         </is>
       </c>
       <c r="H21" s="21" t="inlineStr">
@@ -29567,7 +29567,7 @@
           <t>P3 | 952呎 (3房)
 $3220万
 $33,820/呎
-(25年-06月)</t>
+(25年-06月-22日)</t>
         </is>
       </c>
     </row>
@@ -29582,7 +29582,7 @@
           <t>A | 486呎 (2房)
 $1009万
 $20,759/呎
-(25年-07月)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -29590,7 +29590,7 @@
           <t>B | 494呎 (2房)
 $1020万
 $20,640/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -29598,7 +29598,7 @@
           <t>C | 517呎 (2房)
 $1067万
 $20,640/呎
-(25年-07月)</t>
+(25年-07月-13日)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -29606,7 +29606,7 @@
           <t>D | 477呎 (2房)
 $987万
 $20,700/呎
-(25年-07月)</t>
+(25年-07月-06日)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
@@ -29614,7 +29614,7 @@
           <t>P1 | 1261呎 (4+房)
 $4229万
 $33,535/呎
-(25年-06月)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
@@ -29622,7 +29622,7 @@
           <t>P2 | 870呎 (3房)
 $2688万
 $30,900/呎
-(25年-07月)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="H22" s="21" t="inlineStr">
@@ -29630,7 +29630,7 @@
           <t>P3 | 952呎 (3房)
 $3056万
 $32,100/呎
-(25年-06月)</t>
+(25年-06月-15日)</t>
         </is>
       </c>
     </row>
@@ -29645,7 +29645,7 @@
           <t>A | 486呎 (2房)
 $1005万
 $20,677/呎
-(25年-07月)</t>
+(25年-07月-13日)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -29653,7 +29653,7 @@
           <t>B | 494呎 (2房)
 $1079万
 $21,842/呎
-(25年-07月)</t>
+(25年-07月-13日)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -29661,7 +29661,7 @@
           <t>C | 517呎 (2房)
 $1063万
 $20,557/呎
-(25年-07月)</t>
+(25年-07月-13日)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -29669,7 +29669,7 @@
           <t>D | 477呎 (2房)
 $984万
 $20,618/呎
-(25年-07月)</t>
+(25年-07月-17日)</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr">
@@ -29677,7 +29677,7 @@
           <t>P1 | 1261呎 (4+房)
 $4193万
 $33,250/呎
-(25年-06月)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
@@ -29685,7 +29685,7 @@
           <t>P2 | 870呎 (3房)
 $2529万
 $29,070/呎
-(25年-06月)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
       <c r="H23" s="21" t="inlineStr">
@@ -29693,7 +29693,7 @@
           <t>P3 | 952呎 (3房)
 $2876万
 $30,210/呎
-(25年-07月)</t>
+(25年-07月-01日)</t>
         </is>
       </c>
     </row>
@@ -29708,7 +29708,7 @@
           <t>A | 486呎 (2房)
 $1001万
 $20,595/呎
-(25年-07月)</t>
+(25年-07月-13日)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -29716,7 +29716,7 @@
           <t>B | 494呎 (2房)
 $1008万
 $20,397/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -29724,7 +29724,7 @@
           <t>C | 517呎 (2房)
 $1059万
 $20,476/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -29732,7 +29732,7 @@
           <t>D | 477呎 (2房)
 $980万
 $20,537/呎
-(25年-07月)</t>
+(25年-07月-13日)</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr">
@@ -29740,7 +29740,7 @@
           <t>P1 | 1261呎 (4+房)
 $4184万
 $33,180/呎
-(25年-07月)</t>
+(25年-07月-06日)</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -29748,7 +29748,7 @@
           <t>P2 | 870呎 (3房)
 $2504万
 $28,785/呎
-(25年-07月)</t>
+(25年-07月-06日)</t>
         </is>
       </c>
       <c r="H24" s="21" t="inlineStr">
@@ -29756,7 +29756,7 @@
           <t>P3 | 952呎 (3房)
 $3299万
 $34,651/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
     </row>
@@ -29771,7 +29771,7 @@
           <t>A | 486呎 (2房)
 $997万
 $20,512/呎
-(25年-07月)</t>
+(25年-07月-17日)</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -29779,7 +29779,7 @@
           <t>B | 494呎 (2房)
 $1004万
 $20,316/呎
-(25年-07月)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -29787,7 +29787,7 @@
           <t>C | 517呎 (2房)
 $1113万
 $21,522/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -29795,7 +29795,7 @@
           <t>D | 477呎 (2房)
 $1037万
 $21,732/呎
-(25年-07月)</t>
+(25年-07月-13日)</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
@@ -29803,7 +29803,7 @@
           <t>P1 | 1261呎 (4+房)
 $4374万
 $34,688/呎
-(25年-07月)</t>
+(25年-07月-10日)</t>
         </is>
       </c>
       <c r="G25" s="21" t="inlineStr">
@@ -29811,7 +29811,7 @@
           <t>P2 | 870呎 (3房)
 $2480万
 $28,500/呎
-(25年-07月)</t>
+(25年-07月-06日)</t>
         </is>
       </c>
       <c r="H25" s="21" t="inlineStr">
@@ -29819,7 +29819,7 @@
           <t>P3 | 952呎 (3房)
 $3122万
 $32,791/呎
-(25年-07月)</t>
+(25年-07月-06日)</t>
         </is>
       </c>
     </row>
@@ -29834,7 +29834,7 @@
           <t>A | 486呎 (2房)
 $993万
 $20,430/呎
-(25年-07月)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
@@ -29842,7 +29842,7 @@
           <t>B | 494呎 (2房)
 $1000万
 $20,235/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -29850,7 +29850,7 @@
           <t>C | 517呎 (2房)
 $1043万
 $20,176/呎
-(25年-07月)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -29858,7 +29858,7 @@
           <t>D | 477呎 (2房)
 $972万
 $20,371/呎
-(25年-07月)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr">
@@ -29866,7 +29866,7 @@
           <t>P1 | 1261呎 (4+房)
 $3725万
 $29,538/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">
@@ -29874,7 +29874,7 @@
           <t>P2 | 870呎 (3房)
 $2406万
 $27,653/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="H26" s="21" t="inlineStr">
@@ -29882,7 +29882,7 @@
           <t>P3 | 952呎 (3房)
 $2893万
 $30,386/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
     </row>
@@ -29897,7 +29897,7 @@
           <t>A | 486呎 (2房)
 $989万
 $20,350/呎
-(25年-07月)</t>
+(25年-07月-13日)</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
@@ -29905,7 +29905,7 @@
           <t>B | 494呎 (2房)
 $996万
 $20,154/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -29913,7 +29913,7 @@
           <t>C | 517呎 (2房)
 $1039万
 $20,095/呎
-(25年-07月)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -29921,7 +29921,7 @@
           <t>D | 477呎 (2房)
 $968万
 $20,291/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="F27" s="21" t="inlineStr">
@@ -29929,7 +29929,7 @@
           <t>P1 | 1261呎 (4+房)
 $3680万
 $29,187/呎
-(25年-06月)</t>
+(25年-06月-13日)</t>
         </is>
       </c>
       <c r="G27" s="21" t="inlineStr">
@@ -29937,7 +29937,7 @@
           <t>P2 | 870呎 (3房)
 $2526万
 $29,032/呎
-(25年-07月)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="H27" s="21" t="inlineStr">
@@ -29945,7 +29945,7 @@
           <t>P3 | 952呎 (3房)
 $2850万
 $29,936/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
     </row>
@@ -29960,7 +29960,7 @@
           <t>A | 486呎 (2房)
 $985万
 $20,270/呎
-(25年-07月)</t>
+(25年-07月-10日)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
@@ -29968,7 +29968,7 @@
           <t>B | 494呎 (2房)
 $992万
 $20,073/呎
-(25年-07月)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -29976,7 +29976,7 @@
           <t>C | 517呎 (2房)
 $1022万
 $19,764/呎
-(25年-07月)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr">
@@ -29984,7 +29984,7 @@
           <t>D | 477呎 (2房)
 $1024万
 $21,474/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="F28" s="21" t="inlineStr">
@@ -29992,7 +29992,7 @@
           <t>P1 | 1261呎 (4+房)
 $3955万
 $31,363/呎
-(25年-07月)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
@@ -30000,7 +30000,7 @@
           <t>P2 | 870呎 (3房)
 $2349万
 $27,001/呎
-(25年-07月)</t>
+(25年-07月-13日)</t>
         </is>
       </c>
       <c r="H28" s="21" t="inlineStr">
@@ -30008,7 +30008,7 @@
           <t>P3 | 952呎 (3房)
 $2652万
 $27,852/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
     </row>
@@ -30023,7 +30023,7 @@
           <t>A | 486呎 (2房)
 $981万
 $20,189/呎
-(25年-07月)</t>
+(25年-07月-17日)</t>
         </is>
       </c>
       <c r="C29" s="21" t="inlineStr">
@@ -30031,7 +30031,7 @@
           <t>B | 494呎 (2房)
 $1049万
 $21,243/呎
-(25年-07月)</t>
+(25年-07月-01日)</t>
         </is>
       </c>
       <c r="D29" s="21" t="inlineStr">
@@ -30039,7 +30039,7 @@
           <t>C | 517呎 (2房)
 $1095万
 $21,182/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="E29" s="21" t="inlineStr">
@@ -30047,7 +30047,7 @@
           <t>D | 477呎 (2房)
 $948万
 $19,878/呎
-(25年-07月)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="F29" s="21" t="inlineStr">
@@ -30055,7 +30055,7 @@
           <t>P1 | 1261呎 (4+房)
 $3818万
 $30,281/呎
-(25年-07月)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="G29" s="21" t="inlineStr">
@@ -30063,7 +30063,7 @@
           <t>P2 | 870呎 (3房)
 $2319万
 $26,654/呎
-(25年-07月)</t>
+(25年-07月-10日)</t>
         </is>
       </c>
       <c r="H29" s="21" t="inlineStr">
@@ -30071,7 +30071,7 @@
           <t>P3 | 952呎 (3房)
 $2784万
 $29,242/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
     </row>
@@ -30086,7 +30086,7 @@
           <t>A | 486呎 (2房)
 $1038万
 $21,364/呎
-(25年-07月)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
       <c r="C30" s="21" t="inlineStr">
@@ -30094,7 +30094,7 @@
           <t>B | 494呎 (2房)
 $1045万
 $21,158/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="D30" s="21" t="inlineStr">
@@ -30102,7 +30102,7 @@
           <t>C | 517呎 (2房)
 $1091万
 $21,097/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="E30" s="21" t="inlineStr">
@@ -30110,7 +30110,7 @@
           <t>D | 477呎 (2房)
 $956万
 $20,050/呎
-(25年-07月)</t>
+(25年-07月-17日)</t>
         </is>
       </c>
       <c r="F30" s="21" t="inlineStr">
@@ -30118,7 +30118,7 @@
           <t>P1 | 1261呎 (4+房)
 $3862万
 $30,626/呎
-(25年-07月)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="G30" s="21" t="inlineStr">
@@ -30126,7 +30126,7 @@
           <t>P2 | 870呎 (3房)
 $2396万
 $27,545/呎
-(25年-08月)</t>
+(25年-08月-05日)</t>
         </is>
       </c>
       <c r="H30" s="21" t="inlineStr">
@@ -30134,7 +30134,7 @@
           <t>P3 | 952呎 (3房)
 $2708万
 $28,441/呎
-(25年-07月)</t>
+(25年-07月-17日)</t>
         </is>
       </c>
     </row>
@@ -30149,7 +30149,7 @@
           <t>A | 486呎 (2房)
 $1034万
 $21,278/呎
-(25年-07月)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
       <c r="C31" s="21" t="inlineStr">
@@ -30157,7 +30157,7 @@
           <t>B | 494呎 (2房)
 $1041万
 $21,073/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="D31" s="21" t="inlineStr">
@@ -30165,7 +30165,7 @@
           <t>C | 517呎 (2房)
 $1086万
 $21,012/呎
-(25年-07月)</t>
+(25年-07月-13日)</t>
         </is>
       </c>
       <c r="E31" s="21" t="inlineStr">
@@ -30173,7 +30173,7 @@
           <t>D | 477呎 (2房)
 $952万
 $19,969/呎
-(25年-07月)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
       <c r="F31" s="21" t="inlineStr">
@@ -30181,7 +30181,7 @@
           <t>P1 | 1261呎 (4+房)
 $3819万
 $30,289/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="G31" s="21" t="inlineStr">
@@ -30189,7 +30189,7 @@
           <t>P2 | 870呎 (3房)
 $2361万
 $27,138/呎
-(25年-07月)</t>
+(25年-07月-29日)</t>
         </is>
       </c>
       <c r="H31" s="21" t="inlineStr">
@@ -30197,7 +30197,7 @@
           <t>P3 | 952呎 (3房)
 $2668万
 $28,021/呎
-(25年-07月)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
     </row>
@@ -30212,7 +30212,7 @@
           <t>A | 486呎 (2房)
 $1030万
 $21,195/呎
-(25年-07月)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
       <c r="C32" s="21" t="inlineStr">
@@ -30220,7 +30220,7 @@
           <t>B | 494呎 (2房)
 $976万
 $19,755/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="D32" s="21" t="inlineStr">
@@ -30228,7 +30228,7 @@
           <t>C | 517呎 (2房)
 $1006万
 $19,451/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="E32" s="21" t="inlineStr">
@@ -30236,7 +30236,7 @@
           <t>D | 477呎 (2房)
 $949万
 $19,891/呎
-(25年-07月)</t>
+(25年-07月-17日)</t>
         </is>
       </c>
       <c r="F32" s="21" t="inlineStr">
@@ -30244,7 +30244,7 @@
           <t>P1 | 1261呎 (4+房)
 $3785万
 $30,014/呎
-(25年-07月)</t>
+(25年-07月-16日)</t>
         </is>
       </c>
       <c r="G32" s="21" t="inlineStr">
@@ -30252,7 +30252,7 @@
           <t>P2 | 870呎 (3房)
 $2338万
 $26,869/呎
-(25年-09月)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="H32" s="21" t="inlineStr">
@@ -30260,7 +30260,7 @@
           <t>P3 | 952呎 (3房)
 $2641万
 $27,744/呎
-(25年-07月)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
     </row>
@@ -30275,7 +30275,7 @@
           <t>A | 486呎 (2房)
 $1026万
 $21,109/呎
-(25年-07月)</t>
+(25年-07月-13日)</t>
         </is>
       </c>
       <c r="C33" s="21" t="inlineStr">
@@ -30283,7 +30283,7 @@
           <t>B | 494呎 (2房)
 $1033万
 $20,907/呎
-(25年-07月)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="D33" s="21" t="inlineStr">
@@ -30291,7 +30291,7 @@
           <t>C | 517呎 (2房)
 $1014万
 $19,619/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="E33" s="21" t="inlineStr">
@@ -30299,7 +30299,7 @@
           <t>D | 477呎 (2房)
 $945万
 $19,811/呎
-(25年-07月)</t>
+(25年-07月-13日)</t>
         </is>
       </c>
       <c r="F33" s="21" t="inlineStr">
@@ -30307,7 +30307,7 @@
           <t>P1 | 1261呎 (4+房)
 $3474万
 $27,550/呎
-(25年-07月)</t>
+(25年-07月-10日)</t>
         </is>
       </c>
       <c r="G33" s="21" t="inlineStr">
@@ -30315,7 +30315,7 @@
           <t>P2 | 870呎 (3房)
 $2306万
 $26,506/呎
-(25年-07月)</t>
+(25年-07月-17日)</t>
         </is>
       </c>
       <c r="H33" s="21" t="inlineStr">
@@ -30323,7 +30323,7 @@
           <t>P3 | 952呎 (3房)
 $2578万
 $27,075/呎
-(25年-07月)</t>
+(25年-07月-16日)</t>
         </is>
       </c>
     </row>
@@ -30338,7 +30338,7 @@
           <t>A | 486呎 (2房)
 $962万
 $19,788/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="C34" s="21" t="inlineStr">
@@ -30346,7 +30346,7 @@
           <t>B | 494呎 (2房)
 $968万
 $19,597/呎
-(25年-07月)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="D34" s="21" t="inlineStr">
@@ -30354,7 +30354,7 @@
           <t>C | 517呎 (2房)
 $1010万
 $19,542/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="E34" s="21" t="inlineStr">
@@ -30362,7 +30362,7 @@
           <t>D | 477呎 (2房)
 $938万
 $19,654/呎
-(25年-07月)</t>
+(25年-07月-10日)</t>
         </is>
       </c>
       <c r="F34" s="21" t="inlineStr">
@@ -30370,7 +30370,7 @@
           <t>P1 | 1261呎 (4+房)
 $3632万
 $28,800/呎
-(25年-07月)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="G34" s="21" t="inlineStr">
@@ -30378,7 +30378,7 @@
           <t>P2 | 870呎 (3房)
 $2392万
 $27,500/呎
-(25年-07月)</t>
+(25年-07月-30日)</t>
         </is>
       </c>
       <c r="H34" s="21" t="inlineStr">
@@ -30386,7 +30386,7 @@
           <t>P3 | 952呎 (3房)
 $2586万
 $27,168/呎
-(25年-06月)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
     </row>
@@ -30401,7 +30401,7 @@
           <t>A | 486呎 (2房)
 $1018万
 $20,940/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="C35" s="21" t="inlineStr">
@@ -30409,7 +30409,7 @@
           <t>B | 494呎 (2房)
 $964万
 $19,520/呎
-(25年-07月)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="D35" s="21" t="inlineStr">
@@ -30417,7 +30417,7 @@
           <t>C | 517呎 (2房)
 $1069万
 $20,681/呎
-(25年-07月)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="E35" s="21" t="inlineStr">
@@ -30425,7 +30425,7 @@
           <t>D | 477呎 (2房)
 $928万
 $19,459/呎
-(25年-07月)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
       <c r="F35" s="21" t="inlineStr">
@@ -30433,7 +30433,7 @@
           <t>P1 | 1261呎 (4+房)
 $3426万
 $27,170/呎
-(25年-07月)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
       <c r="G35" s="21" t="inlineStr">
@@ -30441,7 +30441,7 @@
           <t>P2 | 870呎 (3房)
 $2399万
 $27,579/呎
-(25年-08月)</t>
+(25年-08月-25日)</t>
         </is>
       </c>
       <c r="H35" s="21" t="inlineStr">
@@ -30449,7 +30449,7 @@
           <t>P3 | 952呎 (3房)
 $2675万
 $28,100/呎
-(25年-07月)</t>
+(25年-07月-16日)</t>
         </is>
       </c>
     </row>
@@ -30464,7 +30464,7 @@
           <t>A | 486呎 (2房)
 $1014万
 $20,858/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="C36" s="21" t="inlineStr">
@@ -30472,7 +30472,7 @@
           <t>B | 494呎 (2房)
 $960万
 $19,441/呎
-(25年-07月)</t>
+(25年-07月-10日)</t>
         </is>
       </c>
       <c r="D36" s="21" t="inlineStr">
@@ -30480,7 +30480,7 @@
           <t>C | 517呎 (2房)
 $1002万
 $19,387/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="E36" s="21" t="inlineStr">
@@ -30488,7 +30488,7 @@
           <t>D | 477呎 (2房)
 $976万
 $20,470/呎
-(25年-07月)</t>
+(25年-07月-16日)</t>
         </is>
       </c>
       <c r="F36" s="21" t="inlineStr">
@@ -30496,7 +30496,7 @@
           <t>P1 | 1261呎 (4+房)
 $3881万
 $30,779/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="G36" s="21" t="inlineStr">
@@ -30504,7 +30504,7 @@
           <t>P2 | 870呎 (3房)
 $2314万
 $26,600/呎
-(25年-09月)</t>
+(25年-09月-08日)</t>
         </is>
       </c>
       <c r="H36" s="21" t="inlineStr">
@@ -30512,7 +30512,7 @@
           <t>P3 | 952呎 (3房)
 $2570万
 $27,000/呎
-(25年-08月)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
     </row>
@@ -30527,7 +30527,7 @@
           <t>A | 486呎 (2房)
 $1010万
 $20,776/呎
-(25年-07月)</t>
+(25年-07月-16日)</t>
         </is>
       </c>
       <c r="C37" s="21" t="inlineStr">
@@ -30535,7 +30535,7 @@
           <t>B | 494呎 (2房)
 $957万
 $19,364/呎
-(25年-07月)</t>
+(25年-07月-06日)</t>
         </is>
       </c>
       <c r="D37" s="21" t="inlineStr">
@@ -30543,7 +30543,7 @@
           <t>C | 517呎 (2房)
 $998万
 $19,309/呎
-(25年-07月)</t>
+(25年-07月-06日)</t>
         </is>
       </c>
       <c r="E37" s="21" t="inlineStr">
@@ -30551,7 +30551,7 @@
           <t>D | 477呎 (2房)
 $910万
 $19,075/呎
-(25年-07月)</t>
+(25年-07月-10日)</t>
         </is>
       </c>
       <c r="F37" s="21" t="inlineStr">
@@ -30559,7 +30559,7 @@
           <t>P1 | 1261呎 (4+房)
 $3577万
 $28,368/呎
-(25年-08月)</t>
+(25年-08月-05日)</t>
         </is>
       </c>
       <c r="G37" s="21" t="inlineStr">
@@ -30567,7 +30567,7 @@
           <t>P2 | 870呎 (3房)
 $2490万
 $28,620/呎
-(25年-12月)</t>
+(25年-12月-30日)</t>
         </is>
       </c>
       <c r="H37" s="21" t="inlineStr">
@@ -30575,7 +30575,7 @@
           <t>P3 | 952呎 (3房)
 $2686万
 $28,211/呎
-(25年-08月)</t>
+(25年-08月-27日)</t>
         </is>
       </c>
     </row>
@@ -30590,7 +30590,7 @@
           <t>A | 440呎 (2房)
 $1088万
 $24,716/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="C38" s="21" t="inlineStr">
@@ -30598,7 +30598,7 @@
           <t>B | 448呎 (2房)
 $1120万
 $25,000/呎
-(25年-07月)</t>
+(25年-07月-16日)</t>
         </is>
       </c>
       <c r="D38" s="21" t="inlineStr">
@@ -30606,7 +30606,7 @@
           <t>C | 467呎 (2房)
 $1238万
 $26,501/呎
-(25年-07月)</t>
+(25年-07月-10日)</t>
         </is>
       </c>
       <c r="E38" s="21" t="inlineStr">
@@ -30614,7 +30614,7 @@
           <t>D | 430呎 (2房)
 $999万
 $23,233/呎
-(25年-07月)</t>
+(25年-07月-20日)</t>
         </is>
       </c>
       <c r="F38" s="21" t="inlineStr">
@@ -30622,7 +30622,7 @@
           <t>P1 | 1162呎 (4+房)
 $3650万
 $31,411/呎
-(25年-07月)</t>
+(25年-07月-28日)</t>
         </is>
       </c>
       <c r="G38" s="21" t="inlineStr">
@@ -30630,7 +30630,7 @@
           <t>P2 | 870呎 (3房)
 $2436万
 $28,000/呎
-(25年-12月)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="H38" s="21" t="inlineStr">
@@ -30638,7 +30638,7 @@
           <t>P3 | 952呎 (3房)
 $2758万
 $28,971/呎
-(25年-12月)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
     </row>
@@ -30800,7 +30800,7 @@
           <t>A | 1020呎 (3房)
 $3652万
 $35,800/呎
-(26年-03月)</t>
+(26年-03月-11日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -30872,7 +30872,7 @@
           <t>A | 486呎 (2房)
 $1245万
 $25,619/呎
-(25年-09月)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -30880,7 +30880,7 @@
           <t>B | 485呎 (2房)
 $1138万
 $23,474/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
@@ -30888,7 +30888,7 @@
           <t>C | 491呎 (2房)
 $1137万
 $23,161/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -30929,7 +30929,7 @@
           <t>A | 486呎 (2房)
 $1180万
 $24,274/呎
-(25年-07月)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -30937,7 +30937,7 @@
           <t>B | 485呎 (2房)
 $1556万
 $32,089/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -30945,7 +30945,7 @@
           <t>C | 491呎 (2房)
 $1196万
 $24,365/呎
-(25年-07月)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
@@ -30953,7 +30953,7 @@
           <t>D | 476呎 (2房)
 $1532万
 $32,191/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr"/>
@@ -30986,7 +30986,7 @@
           <t>A | 486呎 (2房)
 $1543万
 $31,745/呎
-(26年-04月)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -30994,7 +30994,7 @@
           <t>B | 485呎 (2房)
 $1169万
 $24,095/呎
-(25年-07月)</t>
+(25年-07月-30日)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -31002,7 +31002,7 @@
           <t>C | 491呎 (2房)
 $1174万
 $23,906/呎
-(25年-07月)</t>
+(25年-07月-24日)</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr">
@@ -31010,7 +31010,7 @@
           <t>D | 476呎 (2房)
 $1137万
 $23,895/呎
-(25年-07月)</t>
+(25年-07月-23日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr"/>
@@ -31019,7 +31019,7 @@
           <t>P1 | 1422呎 (4+房)
 $6754万
 $47,500/呎
-(25年-11月)</t>
+(25年-11月-30日)</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -31027,7 +31027,7 @@
           <t>P2 | 1559呎 (4+房)
 $8574万
 $55,000/呎
-(26年-02月)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="I9" s="22" t="inlineStr"/>
@@ -31043,7 +31043,7 @@
           <t>A | 486呎 (2房)
 $1170万
 $24,078/呎
-(25年-07月)</t>
+(25年-07月-21日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -31051,7 +31051,7 @@
           <t>B | 485呎 (2房)
 $1112万
 $22,926/呎
-(25年-07月)</t>
+(25年-07月-22日)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -31059,7 +31059,7 @@
           <t>C | 491呎 (2房)
 $1116万
 $22,723/呎
-(25年-07月)</t>
+(25年-07月-17日)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
@@ -31067,7 +31067,7 @@
           <t>D | 476呎 (2房)
 $1081万
 $22,714/呎
-(25年-07月)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr"/>
@@ -31076,7 +31076,7 @@
           <t>P1 | 1422呎 (4+房)
 $6086万
 $42,800/呎
-(25年-09月)</t>
+(25年-09月-08日)</t>
         </is>
       </c>
       <c r="H10" s="21" t="inlineStr">
@@ -31084,7 +31084,7 @@
           <t>P2 | 1559呎 (4+房)
 $7592万
 $48,700/呎
-(25年-08月)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="I10" s="22" t="inlineStr"/>
@@ -31100,7 +31100,7 @@
           <t>A | 486呎 (2房)
 $1084万
 $22,307/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -31108,7 +31108,7 @@
           <t>B | 485呎 (2房)
 $1081万
 $22,287/呎
-(25年-07月)</t>
+(25年-07月-06日)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -31116,7 +31116,7 @@
           <t>C | 491呎 (2房)
 $1276万
 $25,982/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
@@ -31124,7 +31124,7 @@
           <t>D | 476呎 (2房)
 $1064万
 $22,357/呎
-(25年-08月)</t>
+(25年-08月-03日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr"/>
@@ -31133,7 +31133,7 @@
           <t>P1 | 1422呎 (4+房)
 $5644万
 $39,690/呎
-(25年-07月)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
@@ -31141,7 +31141,7 @@
           <t>P2 | 1559呎 (4+房)
 $6715万
 $43,071/呎
-(25年-07月)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
       <c r="I11" s="22" t="inlineStr"/>
@@ -31157,7 +31157,7 @@
           <t>A | 486呎 (2房)
 $1081万
 $22,251/呎
-(25年-07月)</t>
+(25年-07月-22日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
@@ -31165,7 +31165,7 @@
           <t>B | 485呎 (2房)
 $1078万
 $22,231/呎
-(25年-07月)</t>
+(25年-07月-22日)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -31173,7 +31173,7 @@
           <t>C | 491呎 (2房)
 $1082万
 $22,035/呎
-(25年-07月)</t>
+(25年-07月-17日)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
@@ -31181,7 +31181,7 @@
           <t>D | 476呎 (2房)
 $1048万
 $22,027/呎
-(25年-07月)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr"/>
@@ -31190,7 +31190,7 @@
           <t>P1 | 1422呎 (4+房)
 $5431万
 $38,190/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
@@ -31198,7 +31198,7 @@
           <t>P2 | 1559呎 (4+房)
 $6324万
 $40,565/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="I12" s="22" t="inlineStr"/>
@@ -31214,7 +31214,7 @@
           <t>A | 486呎 (2房)
 $1065万
 $21,922/呎
-(25年-07月)</t>
+(25年-07月-22日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -31222,7 +31222,7 @@
           <t>B | 485呎 (2房)
 $1128万
 $23,256/呎
-(25年-07月)</t>
+(25年-07月-17日)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -31230,7 +31230,7 @@
           <t>C | 491呎 (2房)
 $1132万
 $23,051/呎
-(25年-07月)</t>
+(25年-07月-17日)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
@@ -31238,7 +31238,7 @@
           <t>D | 476呎 (2房)
 $998万
 $20,958/呎
-(25年-07月)</t>
+(25年-07月-16日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr"/>
@@ -31247,7 +31247,7 @@
           <t>P1 | 1422呎 (4+房)
 $5404万
 $38,000/呎
-(25年-07月)</t>
+(25年-07月-24日)</t>
         </is>
       </c>
       <c r="H13" s="21" t="inlineStr">
@@ -31255,7 +31255,7 @@
           <t>P2 | 1559呎 (4+房)
 $6018万
 $38,602/呎
-(25年-07月)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="I13" s="22" t="inlineStr"/>
@@ -31271,7 +31271,7 @@
           <t>A | 486呎 (2房)
 $1046万
 $21,523/呎
-(25年-06月)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -31279,7 +31279,7 @@
           <t>B | 485呎 (2房)
 $1108万
 $22,847/呎
-(25年-07月)</t>
+(25年-07月-06日)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -31287,7 +31287,7 @@
           <t>C | 491呎 (2房)
 $1046万
 $21,314/呎
-(25年-07月)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
@@ -31295,7 +31295,7 @@
           <t>D | 476呎 (2房)
 $993万
 $20,855/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr"/>
@@ -31304,7 +31304,7 @@
           <t>P1 | 1422呎 (4+房)
 $5494万
 $38,634/呎
-(25年-07月)</t>
+(25年-07月-22日)</t>
         </is>
       </c>
       <c r="H14" s="21" t="inlineStr">
@@ -31312,7 +31312,7 @@
           <t>P2 | 1559呎 (4+房)
 $6220万
 $39,900/呎
-(25年-06月)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
       <c r="I14" s="22" t="inlineStr"/>
@@ -31328,7 +31328,7 @@
           <t>A | 486呎 (2房)
 $1040万
 $21,395/呎
-(25年-07月)</t>
+(25年-07月-13日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -31336,7 +31336,7 @@
           <t>B | 485呎 (2房)
 $1102万
 $22,713/呎
-(25年-07月)</t>
+(25年-07月-13日)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -31344,7 +31344,7 @@
           <t>C | 491呎 (2房)
 $1040万
 $21,187/呎
-(25年-07月)</t>
+(25年-07月-16日)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -31352,7 +31352,7 @@
           <t>D | 476呎 (2房)
 $988万
 $20,750/呎
-(25年-07月)</t>
+(25年-07月-16日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr"/>
@@ -31361,7 +31361,7 @@
           <t>P1 | 1422呎 (4+房)
 $5052万
 $35,530/呎
-(25年-07月)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="H15" s="21" t="inlineStr">
@@ -31369,7 +31369,7 @@
           <t>P2 | 1559呎 (4+房)
 $5850万
 $37,525/呎
-(25年-06月)</t>
+(25年-06月-22日)</t>
         </is>
       </c>
       <c r="I15" s="22" t="inlineStr"/>
@@ -31385,7 +31385,7 @@
           <t>A | 486呎 (2房)
 $1034万
 $21,267/呎
-(25年-07月)</t>
+(25年-07月-13日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -31393,7 +31393,7 @@
           <t>B | 485呎 (2房)
 $1030万
 $21,247/呎
-(25年-07月)</t>
+(25年-07月-17日)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -31401,7 +31401,7 @@
           <t>C | 491呎 (2房)
 $1099万
 $22,377/呎
-(25年-07月)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -31409,7 +31409,7 @@
           <t>D | 476呎 (2房)
 $983万
 $20,647/呎
-(25年-07月)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr"/>
@@ -31418,7 +31418,7 @@
           <t>P1 | 1422呎 (4+房)
 $4996万
 $35,136/呎
-(25年-06月)</t>
+(25年-06月-08日)</t>
         </is>
       </c>
       <c r="H16" s="21" t="inlineStr">
@@ -31426,7 +31426,7 @@
           <t>P2 | 1559呎 (4+房)
 $5791万
 $37,145/呎
-(25年-06月)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
       <c r="I16" s="22" t="inlineStr"/>
@@ -31442,7 +31442,7 @@
           <t>A | 486呎 (2房)
 $1027万
 $21,140/呎
-(25年-07月)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -31450,7 +31450,7 @@
           <t>B | 485呎 (2房)
 $1024万
 $21,122/呎
-(25年-07月)</t>
+(25年-07月-10日)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -31458,7 +31458,7 @@
           <t>C | 491呎 (2房)
 $1028万
 $20,937/呎
-(25年-07月)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -31466,7 +31466,7 @@
           <t>D | 476呎 (2房)
 $978万
 $20,546/呎
-(25年-07月)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr"/>
@@ -31475,7 +31475,7 @@
           <t>P1 | 1422呎 (4+房)
 $4839万
 $34,028/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="H17" s="21" t="inlineStr">
@@ -31483,7 +31483,7 @@
           <t>P2 | 1559呎 (4+房)
 $5609万
 $35,977/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="I17" s="22" t="inlineStr"/>
@@ -31499,7 +31499,7 @@
           <t>A | 486呎 (2房)
 $1083万
 $22,282/呎
-(25年-07月)</t>
+(25年-07月-17日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -31507,7 +31507,7 @@
           <t>B | 485呎 (2房)
 $1063万
 $21,915/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -31515,7 +31515,7 @@
           <t>C | 490呎 (2房)
 $1005万
 $20,506/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
@@ -31523,7 +31523,7 @@
           <t>D | 476呎 (2房)
 $964万
 $20,261/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr">
@@ -31531,7 +31531,7 @@
           <t>E | 455呎 (2房)
 $917万
 $20,160/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
@@ -31539,7 +31539,7 @@
           <t>P1 | 926呎 (3房)
 $3273万
 $35,350/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="H18" s="21" t="inlineStr">
@@ -31547,7 +31547,7 @@
           <t>P2 | 860呎 (3房)
 $2726万
 $31,700/呎
-(25年-07月)</t>
+(25年-07月-30日)</t>
         </is>
       </c>
       <c r="I18" s="21" t="inlineStr">
@@ -31555,7 +31555,7 @@
           <t>P3 | 826呎 (3房)
 $2494万
 $30,200/呎
-(25年-07月)</t>
+(25年-07月-30日)</t>
         </is>
       </c>
     </row>
@@ -31570,7 +31570,7 @@
           <t>A | 486呎 (2房)
 $1015万
 $20,889/呎
-(25年-07月)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -31578,7 +31578,7 @@
           <t>B | 485呎 (2房)
 $1059万
 $21,829/呎
-(25年-07月)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -31586,7 +31586,7 @@
           <t>C | 490呎 (2房)
 $1063万
 $21,700/呎
-(25年-07月)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -31594,7 +31594,7 @@
           <t>D | 476呎 (2房)
 $961万
 $20,181/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr">
@@ -31602,7 +31602,7 @@
           <t>E | 455呎 (2房)
 $971万
 $21,334/呎
-(25年-07月)</t>
+(25年-07月-06日)</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
@@ -31610,7 +31610,7 @@
           <t>P1 | 926呎 (3房)
 $3084万
 $33,300/呎
-(25年-07月)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="H19" s="21" t="inlineStr">
@@ -31618,7 +31618,7 @@
           <t>P2 | 860呎 (3房)
 $2582万
 $30,020/呎
-(25年-07月)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="I19" s="21" t="inlineStr">
@@ -31626,7 +31626,7 @@
           <t>P3 | 826呎 (3房)
 $2591万
 $31,368/呎
-(25年-09月)</t>
+(25年-09月-02日)</t>
         </is>
       </c>
     </row>
@@ -31641,7 +31641,7 @@
           <t>A | 486呎 (2房)
 $1011万
 $20,807/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -31649,7 +31649,7 @@
           <t>B | 485呎 (2房)
 $1054万
 $21,742/呎
-(25年-07月)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -31657,7 +31657,7 @@
           <t>C | 490呎 (2房)
 $1059万
 $21,614/呎
-(25年-07月)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -31665,7 +31665,7 @@
           <t>D | 476呎 (2房)
 $957万
 $20,101/呎
-(25年-07月)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr">
@@ -31673,7 +31673,7 @@
           <t>E | 455呎 (2房)
 $910万
 $20,000/呎
-(25年-07月)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
@@ -31681,7 +31681,7 @@
           <t>P1 | 926呎 (3房)
 $3337万
 $36,040/呎
-(25年-07月)</t>
+(25年-07月-06日)</t>
         </is>
       </c>
       <c r="H20" s="21" t="inlineStr">
@@ -31689,7 +31689,7 @@
           <t>P2 | 860呎 (3房)
 $2541万
 $29,545/呎
-(25年-07月)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="I20" s="21" t="inlineStr">
@@ -31697,7 +31697,7 @@
           <t>P3 | 826呎 (3房)
 $2548万
 $30,850/呎
-(25年-08月)</t>
+(25年-08月-27日)</t>
         </is>
       </c>
     </row>
@@ -31712,7 +31712,7 @@
           <t>A | 486呎 (2房)
 $1070万
 $22,016/呎
-(25年-07月)</t>
+(25年-07月-06日)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -31720,7 +31720,7 @@
           <t>B | 485呎 (2房)
 $1050万
 $21,656/呎
-(25年-07月)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -31728,7 +31728,7 @@
           <t>C | 490呎 (2房)
 $993万
 $20,261/呎
-(25年-06月)</t>
+(25年-06月-13日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -31736,7 +31736,7 @@
           <t>D | 476呎 (2房)
 $1012万
 $21,271/呎
-(25年-07月)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr">
@@ -31744,7 +31744,7 @@
           <t>E | 455呎 (2房)
 $906万
 $19,921/呎
-(25年-06月)</t>
+(25年-06月-13日)</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -31752,7 +31752,7 @@
           <t>P1 | 926呎 (3房)
 $3300万
 $35,639/呎
-(25年-06月)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
       <c r="H21" s="21" t="inlineStr">
@@ -31760,7 +31760,7 @@
           <t>P2 | 860呎 (3房)
 $2500万
 $29,070/呎
-(25年-07月)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="I21" s="21" t="inlineStr">
@@ -31768,7 +31768,7 @@
           <t>P3 | 826呎 (3房)
 $2519万
 $30,500/呎
-(25年-08月)</t>
+(25年-08月-27日)</t>
         </is>
       </c>
     </row>
@@ -31783,7 +31783,7 @@
           <t>A | 486呎 (2房)
 $1003万
 $20,640/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -31791,7 +31791,7 @@
           <t>B | 485呎 (2房)
 $984万
 $20,299/呎
-(25年-07月)</t>
+(25年-07月-06日)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -31799,7 +31799,7 @@
           <t>C | 490呎 (2房)
 $989万
 $20,180/呎
-(25年-07月)</t>
+(25年-07月-06日)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -31807,7 +31807,7 @@
           <t>D | 476呎 (2房)
 $949万
 $19,941/呎
-(25年-07月)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
@@ -31815,7 +31815,7 @@
           <t>E | 455呎 (2房)
 $903万
 $19,842/呎
-(25年-07月)</t>
+(25年-07月-06日)</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
@@ -31823,7 +31823,7 @@
           <t>P1 | 926呎 (3房)
 $2824万
 $30,495/呎
-(25年-06月)</t>
+(25年-06月-18日)</t>
         </is>
       </c>
       <c r="H22" s="21" t="inlineStr">
@@ -31831,7 +31831,7 @@
           <t>P2 | 860呎 (3房)
 $2623万
 $30,500/呎
-(25年-07月)</t>
+(25年-07月-06日)</t>
         </is>
       </c>
       <c r="I22" s="21" t="inlineStr">
@@ -31839,7 +31839,7 @@
           <t>P3 | 826呎 (3房)
 $2490万
 $30,150/呎
-(25年-09月)</t>
+(25年-09月-01日)</t>
         </is>
       </c>
     </row>
@@ -31854,7 +31854,7 @@
           <t>A | 486呎 (2房)
 $1062万
 $21,842/呎
-(25年-07月)</t>
+(25年-07月-13日)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -31862,7 +31862,7 @@
           <t>B | 485呎 (2房)
 $981万
 $20,219/呎
-(25年-07月)</t>
+(25年-07月-06日)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -31870,7 +31870,7 @@
           <t>C | 490呎 (2房)
 $985万
 $20,100/呎
-(25年-07月)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -31878,7 +31878,7 @@
           <t>D | 476呎 (2房)
 $945万
 $19,861/呎
-(25年-07月)</t>
+(25年-07月-06日)</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr">
@@ -31886,7 +31886,7 @@
           <t>E | 455呎 (2房)
 $955万
 $20,998/呎
-(25年-07月)</t>
+(25年-07月-06日)</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
@@ -31894,7 +31894,7 @@
           <t>P1 | 926呎 (3房)
 $2784万
 $30,068/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="H23" s="21" t="inlineStr">
@@ -31902,7 +31902,7 @@
           <t>P2 | 860呎 (3房)
 $2487万
 $28,916/呎
-(25年-07月)</t>
+(25年-07月-22日)</t>
         </is>
       </c>
       <c r="I23" s="21" t="inlineStr">
@@ -31910,7 +31910,7 @@
           <t>P3 | 826呎 (3房)
 $2437万
 $29,500/呎
-(25年-07月)</t>
+(25年-07月-06日)</t>
         </is>
       </c>
     </row>
@@ -31925,7 +31925,7 @@
           <t>A | 486呎 (2房)
 $983万
 $20,220/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -31933,7 +31933,7 @@
           <t>B | 485呎 (2房)
 $977万
 $20,140/呎
-(25年-07月)</t>
+(25年-07月-06日)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -31941,7 +31941,7 @@
           <t>C | 490呎 (2房)
 $1042万
 $21,269/呎
-(25年-07月)</t>
+(25年-07月-06日)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -31949,7 +31949,7 @@
           <t>D | 476呎 (2房)
 $942万
 $19,782/呎
-(25年-07月)</t>
+(25年-07月-06日)</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr">
@@ -31957,7 +31957,7 @@
           <t>E | 455呎 (2房)
 $896万
 $19,684/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -31965,7 +31965,7 @@
           <t>P1 | 926呎 (3房)
 $3217万
 $34,740/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="H24" s="21" t="inlineStr">
@@ -31973,7 +31973,7 @@
           <t>P2 | 860呎 (3房)
 $2482万
 $28,856/呎
-(25年-07月)</t>
+(25年-07月-17日)</t>
         </is>
       </c>
       <c r="I24" s="21" t="inlineStr">
@@ -31981,7 +31981,7 @@
           <t>P3 | 826呎 (3房)
 $2342万
 $28,350/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
     </row>
@@ -31996,7 +31996,7 @@
           <t>A | 486呎 (2房)
 $1053万
 $21,669/呎
-(25年-07月)</t>
+(25年-07月-01日)</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -32004,7 +32004,7 @@
           <t>B | 485呎 (2房)
 $973万
 $20,058/呎
-(25年-07月)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -32012,7 +32012,7 @@
           <t>C | 490呎 (2房)
 $977万
 $19,941/呎
-(25年-07月)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -32020,7 +32020,7 @@
           <t>D | 476呎 (2房)
 $996万
 $20,935/呎
-(25年-07月)</t>
+(25年-07月-01日)</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
@@ -32028,7 +32028,7 @@
           <t>E | 455呎 (2房)
 $892万
 $19,604/呎
-(25年-07月)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="G25" s="21" t="inlineStr">
@@ -32036,7 +32036,7 @@
           <t>P1 | 926呎 (3房)
 $3045万
 $32,880/呎
-(25年-07月)</t>
+(25年-07月-06日)</t>
         </is>
       </c>
       <c r="H25" s="21" t="inlineStr">
@@ -32044,7 +32044,7 @@
           <t>P2 | 860呎 (3房)
 $2451万
 $28,500/呎
-(25年-07月)</t>
+(25年-07月-22日)</t>
         </is>
       </c>
       <c r="I25" s="21" t="inlineStr">
@@ -32052,7 +32052,7 @@
           <t>P3 | 826呎 (3房)
 $2321万
 $28,100/呎
-(25年-08月)</t>
+(25年-08月-28日)</t>
         </is>
       </c>
     </row>
@@ -32067,7 +32067,7 @@
           <t>A | 486呎 (2房)
 $987万
 $20,313/呎
-(25年-06月)</t>
+(25年-06月-29日)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
@@ -32075,7 +32075,7 @@
           <t>B | 485呎 (2房)
 $969万
 $19,977/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -32083,7 +32083,7 @@
           <t>C | 490呎 (2房)
 $1034万
 $21,102/呎
-(25年-07月)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -32091,7 +32091,7 @@
           <t>D | 476呎 (2房)
 $934万
 $19,624/呎
-(25年-06月)</t>
+(25年-06月-13日)</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr">
@@ -32099,7 +32099,7 @@
           <t>E | 455呎 (2房)
 $888万
 $19,525/呎
-(25年-07月)</t>
+(25年-07月-10日)</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">
@@ -32107,7 +32107,7 @@
           <t>P1 | 926呎 (3房)
 $2727万
 $29,450/呎
-(25年-07月)</t>
+(25年-07月-13日)</t>
         </is>
       </c>
       <c r="H26" s="21" t="inlineStr">
@@ -32115,7 +32115,7 @@
           <t>P2 | 860呎 (3房)
 $2426万
 $28,215/呎
-(25年-07月)</t>
+(25年-07月-29日)</t>
         </is>
       </c>
       <c r="I26" s="21" t="inlineStr">
@@ -32123,7 +32123,7 @@
           <t>P3 | 826呎 (3房)
 $2310万
 $27,970/呎
-(25年-09月)</t>
+(25年-09月-22日)</t>
         </is>
       </c>
     </row>
@@ -32138,7 +32138,7 @@
           <t>A | 486呎 (2房)
 $983万
 $20,233/呎
-(25年-07月)</t>
+(25年-07月-06日)</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
@@ -32146,7 +32146,7 @@
           <t>B | 485呎 (2房)
 $965万
 $19,899/呎
-(25年-07月)</t>
+(25年-07月-01日)</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -32154,7 +32154,7 @@
           <t>C | 490呎 (2房)
 $969万
 $19,780/呎
-(25年-07月)</t>
+(25年-07月-06日)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -32162,7 +32162,7 @@
           <t>D | 476呎 (2房)
 $988万
 $20,767/呎
-(25年-07月)</t>
+(25年-07月-01日)</t>
         </is>
       </c>
       <c r="F27" s="21" t="inlineStr">
@@ -32170,7 +32170,7 @@
           <t>E | 455呎 (2房)
 $885万
 $19,448/呎
-(25年-07月)</t>
+(25年-07月-06日)</t>
         </is>
       </c>
       <c r="G27" s="21" t="inlineStr">
@@ -32178,7 +32178,7 @@
           <t>P1 | 926呎 (3房)
 $2701万
 $29,165/呎
-(25年-07月)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
       <c r="H27" s="21" t="inlineStr">
@@ -32186,7 +32186,7 @@
           <t>P2 | 860呎 (3房)
 $2402万
 $27,930/呎
-(25年-07月)</t>
+(25年-07月-22日)</t>
         </is>
       </c>
       <c r="I27" s="21" t="inlineStr">
@@ -32194,7 +32194,7 @@
           <t>P3 | 826呎 (3房)
 $2294万
 $27,770/呎
-(25年-09月)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
     </row>
@@ -32209,7 +32209,7 @@
           <t>A | 486呎 (2房)
 $979万
 $20,152/呎
-(25年-07月)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
@@ -32217,7 +32217,7 @@
           <t>B | 485呎 (2房)
 $949万
 $19,571/呎
-(25年-07月)</t>
+(25年-07月-01日)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -32225,7 +32225,7 @@
           <t>C | 490呎 (2房)
 $965万
 $19,702/呎
-(25年-07月)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr">
@@ -32233,7 +32233,7 @@
           <t>D | 476呎 (2房)
 $927万
 $19,468/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="F28" s="21" t="inlineStr">
@@ -32241,7 +32241,7 @@
           <t>E | 455呎 (2房)
 $926万
 $20,341/呎
-(25年-07月)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
@@ -32249,7 +32249,7 @@
           <t>P1 | 926呎 (3房)
 $2674万
 $28,880/呎
-(25年-07月)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
       <c r="H28" s="21" t="inlineStr">
@@ -32257,7 +32257,7 @@
           <t>P2 | 860呎 (3房)
 $2498万
 $29,041/呎
-(25年-07月)</t>
+(25年-07月-24日)</t>
         </is>
       </c>
       <c r="I28" s="21" t="inlineStr">
@@ -32265,7 +32265,7 @@
           <t>P3 | 826呎 (3房)
 $2277万
 $27,570/呎
-(25年-09月)</t>
+(25年-09月-28日)</t>
         </is>
       </c>
     </row>
@@ -32280,7 +32280,7 @@
           <t>A | 486呎 (2房)
 $976万
 $20,072/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="C29" s="21" t="inlineStr">
@@ -32288,7 +32288,7 @@
           <t>B | 485呎 (2房)
 $957万
 $19,740/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="D29" s="21" t="inlineStr">
@@ -32296,7 +32296,7 @@
           <t>C | 490呎 (2房)
 $962万
 $19,624/呎
-(25年-07月)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="E29" s="21" t="inlineStr">
@@ -32304,7 +32304,7 @@
           <t>D | 476呎 (2房)
 $981万
 $20,603/呎
-(25年-07月)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="F29" s="21" t="inlineStr">
@@ -32312,7 +32312,7 @@
           <t>E | 455呎 (2房)
 $878万
 $19,295/呎
-(25年-07月)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="G29" s="21" t="inlineStr">
@@ -32320,7 +32320,7 @@
           <t>P1 | 926呎 (3房)
 $2787万
 $30,100/呎
-(25年-07月)</t>
+(25年-07月-13日)</t>
         </is>
       </c>
       <c r="H29" s="21" t="inlineStr">
@@ -32328,7 +32328,7 @@
           <t>P2 | 860呎 (3房)
 $2555万
 $29,713/呎
-(25年-07月)</t>
+(25年-07月-17日)</t>
         </is>
       </c>
       <c r="I29" s="21" t="inlineStr">
@@ -32336,7 +32336,7 @@
           <t>P3 | 826呎 (3房)
 $2355万
 $28,511/呎
-(25年-09月)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
     </row>
@@ -32351,7 +32351,7 @@
           <t>A | 486呎 (2房)
 $1032万
 $21,241/呎
-(25年-07月)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="C30" s="21" t="inlineStr">
@@ -32359,7 +32359,7 @@
           <t>B | 485呎 (2房)
 $1013万
 $20,891/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="D30" s="21" t="inlineStr">
@@ -32367,7 +32367,7 @@
           <t>C | 490呎 (2房)
 $1018万
 $20,767/呎
-(25年-07月)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="E30" s="21" t="inlineStr">
@@ -32375,7 +32375,7 @@
           <t>D | 476呎 (2房)
 $919万
 $19,313/呎
-(25年-07月)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="F30" s="21" t="inlineStr">
@@ -32383,7 +32383,7 @@
           <t>E | 455呎 (2房)
 $874万
 $19,218/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="G30" s="21" t="inlineStr">
@@ -32391,7 +32391,7 @@
           <t>P1 | 926呎 (3房)
 $2622万
 $28,310/呎
-(25年-07月)</t>
+(25年-07月-22日)</t>
         </is>
       </c>
       <c r="H30" s="21" t="inlineStr">
@@ -32399,7 +32399,7 @@
           <t>P2 | 860呎 (3房)
 $2378万
 $27,650/呎
-(25年-08月)</t>
+(25年-08月-03日)</t>
         </is>
       </c>
       <c r="I30" s="21" t="inlineStr">
@@ -32407,7 +32407,7 @@
           <t>P3 | 826呎 (3房)
 $2244万
 $27,169/呎
-(25年-09月)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
     </row>
@@ -32422,7 +32422,7 @@
           <t>A | 486呎 (2房)
 $1028万
 $21,156/呎
-(25年-07月)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="C31" s="21" t="inlineStr">
@@ -32430,7 +32430,7 @@
           <t>B | 485呎 (2房)
 $1009万
 $20,808/呎
-(25年-07月)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="D31" s="21" t="inlineStr">
@@ -32438,7 +32438,7 @@
           <t>C | 490呎 (2房)
 $1014万
 $20,686/呎
-(25年-07月)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="E31" s="21" t="inlineStr">
@@ -32446,7 +32446,7 @@
           <t>D | 476呎 (2房)
 $916万
 $19,235/呎
-(25年-07月)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="F31" s="21" t="inlineStr">
@@ -32454,7 +32454,7 @@
           <t>E | 455呎 (2房)
 $871万
 $19,141/呎
-(25年-07月)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="G31" s="21" t="inlineStr">
@@ -32462,7 +32462,7 @@
           <t>P1 | 926呎 (3房)
 $2734万
 $29,526/呎
-(25年-08月)</t>
+(25年-08月-10日)</t>
         </is>
       </c>
       <c r="H31" s="21" t="inlineStr">
@@ -32470,7 +32470,7 @@
           <t>P2 | 860呎 (3房)
 $2382万
 $27,700/呎
-(25年-08月)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="I31" s="21" t="inlineStr">
@@ -32478,7 +32478,7 @@
           <t>P3 | 826呎 (3房)
 $2304万
 $27,900/呎
-(25年-10月)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
     </row>
@@ -32493,7 +32493,7 @@
           <t>A | 486呎 (2房)
 $1024万
 $21,072/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="C32" s="21" t="inlineStr">
@@ -32501,7 +32501,7 @@
           <t>B | 485呎 (2房)
 $934万
 $19,262/呎
-(25年-07月)</t>
+(25年-07月-06日)</t>
         </is>
       </c>
       <c r="D32" s="21" t="inlineStr">
@@ -32509,7 +32509,7 @@
           <t>C | 490呎 (2房)
 $950万
 $19,390/呎
-(25年-07月)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="E32" s="21" t="inlineStr">
@@ -32517,7 +32517,7 @@
           <t>D | 476呎 (2房)
 $969万
 $20,357/呎
-(25年-07月)</t>
+(25年-07月-06日)</t>
         </is>
       </c>
       <c r="F32" s="21" t="inlineStr">
@@ -32525,7 +32525,7 @@
           <t>E | 455呎 (2房)
 $867万
 $19,064/呎
-(25年-07月)</t>
+(25年-07月-06日)</t>
         </is>
       </c>
       <c r="G32" s="21" t="inlineStr">
@@ -32533,7 +32533,7 @@
           <t>P1 | 926呎 (3房)
 $2715万
 $29,316/呎
-(25年-07月)</t>
+(25年-07月-31日)</t>
         </is>
       </c>
       <c r="H32" s="21" t="inlineStr">
@@ -32541,7 +32541,7 @@
           <t>P2 | 860呎 (3房)
 $2365万
 $27,500/呎
-(25年-08月)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
       <c r="I32" s="21" t="inlineStr">
@@ -32549,7 +32549,7 @@
           <t>P3 | 826呎 (3房)
 $2211万
 $26,770/呎
-(25年-09月)</t>
+(25年-09月-25日)</t>
         </is>
       </c>
     </row>
@@ -32564,7 +32564,7 @@
           <t>A | 486呎 (2房)
 $1020万
 $20,988/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="C33" s="21" t="inlineStr">
@@ -32572,7 +32572,7 @@
           <t>B | 485呎 (2房)
 $1001万
 $20,643/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="D33" s="21" t="inlineStr">
@@ -32580,7 +32580,7 @@
           <t>C | 490呎 (2房)
 $946万
 $19,314/呎
-(25年-07月)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="E33" s="21" t="inlineStr">
@@ -32588,7 +32588,7 @@
           <t>D | 476呎 (2房)
 $908万
 $19,084/呎
-(25年-07月)</t>
+(25年-07月-06日)</t>
         </is>
       </c>
       <c r="F33" s="21" t="inlineStr">
@@ -32596,7 +32596,7 @@
           <t>E | 455呎 (2房)
 $864万
 $18,989/呎
-(25年-07月)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="G33" s="21" t="inlineStr">
@@ -32604,7 +32604,7 @@
           <t>P1 | 926呎 (3房)
 $2584万
 $27,900/呎
-(25年-08月)</t>
+(25年-08月-10日)</t>
         </is>
       </c>
       <c r="H33" s="21" t="inlineStr">
@@ -32612,7 +32612,7 @@
           <t>P2 | 860呎 (3房)
 $2348万
 $27,300/呎
-(25年-08月)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
       <c r="I33" s="21" t="inlineStr">
@@ -32620,7 +32620,7 @@
           <t>P3 | 826呎 (3房)
 $2272万
 $27,500/呎
-(25年-10月)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
     </row>
@@ -32635,7 +32635,7 @@
           <t>A | 486呎 (2房)
 $1016万
 $20,905/呎
-(25年-07月)</t>
+(25年-07月-06日)</t>
         </is>
       </c>
       <c r="C34" s="21" t="inlineStr">
@@ -32643,7 +32643,7 @@
           <t>B | 485呎 (2房)
 $938万
 $19,351/呎
-(25年-07月)</t>
+(25年-07月-01日)</t>
         </is>
       </c>
       <c r="D34" s="21" t="inlineStr">
@@ -32651,7 +32651,7 @@
           <t>C | 490呎 (2房)
 $943万
 $19,237/呎
-(25年-07月)</t>
+(25年-07月-10日)</t>
         </is>
       </c>
       <c r="E34" s="21" t="inlineStr">
@@ -32659,7 +32659,7 @@
           <t>D | 476呎 (2房)
 $905万
 $19,008/呎
-(25年-07月)</t>
+(25年-07月-01日)</t>
         </is>
       </c>
       <c r="F34" s="21" t="inlineStr">
@@ -32667,7 +32667,7 @@
           <t>E | 455呎 (2房)
 $914万
 $20,095/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="G34" s="21" t="inlineStr">
@@ -32675,7 +32675,7 @@
           <t>P1 | 926呎 (3房)
 $2565万
 $27,700/呎
-(25年-09月)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="H34" s="21" t="inlineStr">
@@ -32683,7 +32683,7 @@
           <t>P2 | 860呎 (3房)
 $2331万
 $27,100/呎
-(25年-09月)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="I34" s="21" t="inlineStr">
@@ -32691,7 +32691,7 @@
           <t>P3 | 826呎 (3房)
 $2296万
 $27,800/呎
-(25年-10月)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
     </row>
@@ -32706,7 +32706,7 @@
           <t>A | 486呎 (2房)
 $952万
 $19,597/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="C35" s="21" t="inlineStr">
@@ -32714,7 +32714,7 @@
           <t>B | 485呎 (2房)
 $993万
 $20,478/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="D35" s="21" t="inlineStr">
@@ -32722,7 +32722,7 @@
           <t>C | 490呎 (2房)
 $939万
 $19,159/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="E35" s="21" t="inlineStr">
@@ -32730,7 +32730,7 @@
           <t>D | 476呎 (2房)
 $901万
 $18,933/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="F35" s="21" t="inlineStr">
@@ -32738,7 +32738,7 @@
           <t>E | 455呎 (2房)
 $911万
 $20,013/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="G35" s="21" t="inlineStr">
@@ -32746,7 +32746,7 @@
           <t>P1 | 926呎 (3房)
 $2680万
 $28,947/呎
-(25年-09月)</t>
+(25年-09月-02日)</t>
         </is>
       </c>
       <c r="H35" s="21" t="inlineStr">
@@ -32754,7 +32754,7 @@
           <t>P2 | 860呎 (3房)
 $2313万
 $26,895/呎
-(25年-09月)</t>
+(25年-09月-25日)</t>
         </is>
       </c>
       <c r="I35" s="21" t="inlineStr">
@@ -32762,7 +32762,7 @@
           <t>P3 | 826呎 (3房)
 $2280万
 $27,599/呎
-(25年-11月)</t>
+(25年-11月-02日)</t>
         </is>
       </c>
     </row>
@@ -32777,7 +32777,7 @@
           <t>A | 486呎 (2房)
 $949万
 $19,519/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="C36" s="21" t="inlineStr">
@@ -32785,7 +32785,7 @@
           <t>B | 485呎 (2房)
 $931万
 $19,196/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="D36" s="21" t="inlineStr">
@@ -32793,7 +32793,7 @@
           <t>C | 490呎 (2房)
 $935万
 $19,084/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="E36" s="21" t="inlineStr">
@@ -32801,7 +32801,7 @@
           <t>D | 476呎 (2房)
 $954万
 $20,036/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="F36" s="21" t="inlineStr">
@@ -32809,7 +32809,7 @@
           <t>E | 455呎 (2房)
 $854万
 $18,763/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="G36" s="21" t="inlineStr">
@@ -32817,7 +32817,7 @@
           <t>P1 | 926呎 (3房)
 $2556万
 $27,600/呎
-(25年-09月)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
       <c r="H36" s="21" t="inlineStr">
@@ -32825,7 +32825,7 @@
           <t>P2 | 860呎 (3房)
 $2339万
 $27,200/呎
-(25年-10月)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="I36" s="21" t="inlineStr">
@@ -32833,7 +32833,7 @@
           <t>P3 | 826呎 (3房)
 $2263万
 $27,400/呎
-(25年-10月)</t>
+(25年-10月-30日)</t>
         </is>
       </c>
     </row>
@@ -32848,7 +32848,7 @@
           <t>A | 486呎 (2房)
 $945万
 $19,440/呎
-(25年-07月)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="C37" s="21" t="inlineStr">
@@ -32856,7 +32856,7 @@
           <t>B | 485呎 (2房)
 $927万
 $19,120/呎
-(25年-07月)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="D37" s="21" t="inlineStr">
@@ -32864,7 +32864,7 @@
           <t>C | 490呎 (2房)
 $931万
 $19,006/呎
-(25年-07月)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="E37" s="21" t="inlineStr">
@@ -32872,7 +32872,7 @@
           <t>D | 476呎 (2房)
 $894万
 $18,782/呎
-(25年-07月)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="F37" s="21" t="inlineStr">
@@ -32880,7 +32880,7 @@
           <t>E | 455呎 (2房)
 $850万
 $18,688/呎
-(25年-07月)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="G37" s="21" t="inlineStr">
@@ -32888,7 +32888,7 @@
           <t>P1 | 926呎 (3房)
 $2574万
 $27,800/呎
-(25年-10月)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="H37" s="21" t="inlineStr">
@@ -32896,7 +32896,7 @@
           <t>P2 | 860呎 (3房)
 $2365万
 $27,500/呎
-(25年-10月)</t>
+(25年-10月-20日)</t>
         </is>
       </c>
       <c r="I37" s="21" t="inlineStr">
@@ -32904,7 +32904,7 @@
           <t>P3 | 826呎 (3房)
 $2247万
 $27,200/呎
-(25年-10月)</t>
+(25年-10月-30日)</t>
         </is>
       </c>
     </row>
@@ -32919,7 +32919,7 @@
           <t>A | 440呎 (2房)
 $1158万
 $26,316/呎
-(25年-07月)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="C38" s="21" t="inlineStr">
@@ -32927,7 +32927,7 @@
           <t>B | 439呎 (2房)
 $1089万
 $24,800/呎
-(25年-07月)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="D38" s="21" t="inlineStr">
@@ -32935,7 +32935,7 @@
           <t>C | 444呎 (2房)
 $1092万
 $24,599/呎
-(25年-07月)</t>
+(25年-07月-10日)</t>
         </is>
       </c>
       <c r="E38" s="21" t="inlineStr">
@@ -32943,7 +32943,7 @@
           <t>D | 430呎 (2房)
 $1182万
 $27,500/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="F38" s="21" t="inlineStr">
@@ -32951,7 +32951,7 @@
           <t>E | 408呎 (2房)
 $1040万
 $25,500/呎
-(25年-07月)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="G38" s="21" t="inlineStr">
@@ -32959,7 +32959,7 @@
           <t>P1 | 926呎 (3房)
 $2546万
 $27,499/呎
-(25年-10月)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="H38" s="21" t="inlineStr">
@@ -32967,7 +32967,7 @@
           <t>P2 | 860呎 (3房)
 $2471万
 $28,737/呎
-(25年-10月)</t>
+(25年-10月-21日)</t>
         </is>
       </c>
       <c r="I38" s="21" t="inlineStr">
@@ -32975,7 +32975,7 @@
           <t>P3 | 826呎 (3房)
 $2354万
 $28,500/呎
-(26年-01月)</t>
+(26年-01月-13日)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-黄竹坑-滶晨.xlsx
+++ b/files/港岛-黄竹坑-滶晨.xlsx
@@ -262,13 +262,13 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -14218,7 +14218,7 @@
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K218" s="5" t="n">
@@ -28720,10 +28720,31 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr"/>
+      <c r="E5" s="20" t="inlineStr"/>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>P1 | 1536呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr"/>
+      <c r="H5" s="20" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
           <t>41&amp;42</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>A | 1020呎 (3房)
 -
@@ -28731,7 +28752,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>B | 1034呎 (3房)
 -
@@ -28739,7 +28760,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D6" s="22" t="inlineStr">
         <is>
           <t>C | 1083呎 (3房)
 $3890万
@@ -28747,9 +28768,9 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="E5" s="22" t="inlineStr"/>
-      <c r="F5" s="22" t="inlineStr"/>
-      <c r="G5" s="20" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr">
         <is>
           <t>P2 | 3120呎 (4+房)
 -
@@ -28757,19 +28778,40 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="H5" s="22" t="inlineStr"/>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B6" s="22" t="inlineStr"/>
-      <c r="C6" s="22" t="inlineStr"/>
-      <c r="D6" s="22" t="inlineStr"/>
-      <c r="E6" s="22" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1593万
+$32,776/呎
+(26年-04月-29日)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+$1142万
+$23,109/呎
+(25年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 517呎 (2房)
+$1235万
+$23,892/呎
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 -
@@ -28777,41 +28819,48 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="G6" s="22" t="inlineStr"/>
-      <c r="H6" s="22" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>P2 | 1706呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
-$1593万
-$32,776/呎
-(26年-04月-29日)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr">
+$1566万
+$32,222/呎
+(26年-04月-23日)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
-$1142万
-$23,109/呎
-(25年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
+$1130万
+$22,881/呎
+(25年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
-$1235万
-$23,892/呎
-(25年-07月-10日)</t>
-        </is>
-      </c>
-      <c r="E7" s="22" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr">
+$1276万
+$24,689/呎
+(25年-07月-16日)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr"/>
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 -
@@ -28819,56 +28868,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr">
-        <is>
-          <t>P2 | 1706呎 (4+房)
--
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H7" s="22" t="inlineStr"/>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1566万
-$32,222/呎
-(26年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="C8" s="21" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-$1130万
-$22,881/呎
-(25年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t>C | 517呎 (2房)
-$1276万
-$24,689/呎
-(25年-07月-16日)</t>
-        </is>
-      </c>
-      <c r="E8" s="22" t="inlineStr"/>
-      <c r="F8" s="20" t="inlineStr">
-        <is>
-          <t>P1 | 1536呎 (4+房)
--
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="G8" s="21" t="inlineStr">
+      <c r="G8" s="22" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $10775万
@@ -28876,7 +28876,7 @@
 (26年-01月-26日)</t>
         </is>
       </c>
-      <c r="H8" s="22" t="inlineStr"/>
+      <c r="H8" s="20" t="inlineStr"/>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -28884,7 +28884,7 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1429万
@@ -28892,7 +28892,7 @@
 (26年-03月-05日)</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1227万
@@ -28900,7 +28900,7 @@
 (25年-08月-10日)</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1245万
@@ -28908,8 +28908,8 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr"/>
-      <c r="F9" s="21" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr"/>
+      <c r="F9" s="22" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $7296万
@@ -28917,7 +28917,7 @@
 (25年-11月-05日)</t>
         </is>
       </c>
-      <c r="G9" s="21" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $8530万
@@ -28925,7 +28925,7 @@
 (25年-06月-25日)</t>
         </is>
       </c>
-      <c r="H9" s="22" t="inlineStr"/>
+      <c r="H9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
@@ -28933,7 +28933,7 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1117万
@@ -28941,7 +28941,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1131万
@@ -28949,7 +28949,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1154万
@@ -28957,8 +28957,8 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E10" s="22" t="inlineStr"/>
-      <c r="F10" s="21" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr"/>
+      <c r="F10" s="22" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $6543万
@@ -28966,7 +28966,7 @@
 (25年-06月-22日)</t>
         </is>
       </c>
-      <c r="G10" s="21" t="inlineStr">
+      <c r="G10" s="22" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $8189万
@@ -28974,7 +28974,7 @@
 (25年-06月-22日)</t>
         </is>
       </c>
-      <c r="H10" s="22" t="inlineStr"/>
+      <c r="H10" s="20" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -28982,7 +28982,7 @@
           <t>36</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1086万
@@ -28990,7 +28990,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1100万
@@ -28998,7 +28998,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1217万
@@ -29006,8 +29006,8 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="E11" s="22" t="inlineStr"/>
-      <c r="F11" s="21" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr"/>
+      <c r="F11" s="22" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $6420万
@@ -29015,7 +29015,7 @@
 (25年-06月-23日)</t>
         </is>
       </c>
-      <c r="G11" s="21" t="inlineStr">
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $7558万
@@ -29023,7 +29023,7 @@
 (25年-06月-23日)</t>
         </is>
       </c>
-      <c r="H11" s="22" t="inlineStr"/>
+      <c r="H11" s="20" t="inlineStr"/>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
@@ -29031,7 +29031,7 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1083万
@@ -29039,7 +29039,7 @@
 (25年-07月-22日)</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1097万
@@ -29047,7 +29047,7 @@
 (25年-07月-22日)</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1137万
@@ -29055,8 +29055,8 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr"/>
-      <c r="F12" s="21" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr"/>
+      <c r="F12" s="22" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $6298万
@@ -29064,7 +29064,7 @@
 (25年-06月-23日)</t>
         </is>
       </c>
-      <c r="G12" s="21" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $7421万
@@ -29072,7 +29072,7 @@
 (25年-06月-23日)</t>
         </is>
       </c>
-      <c r="H12" s="22" t="inlineStr"/>
+      <c r="H12" s="20" t="inlineStr"/>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -29080,7 +29080,7 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1067万
@@ -29088,7 +29088,7 @@
 (25年-06月-24日)</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1081万
@@ -29096,7 +29096,7 @@
 (25年-07月-22日)</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1128万
@@ -29104,8 +29104,8 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="E13" s="22" t="inlineStr"/>
-      <c r="F13" s="21" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr"/>
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $6089万
@@ -29113,7 +29113,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="G13" s="21" t="inlineStr">
+      <c r="G13" s="22" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $7319万
@@ -29121,7 +29121,7 @@
 (25年-06月-23日)</t>
         </is>
       </c>
-      <c r="H13" s="22" t="inlineStr"/>
+      <c r="H13" s="20" t="inlineStr"/>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -29129,7 +29129,7 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1048万
@@ -29137,7 +29137,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1061万
@@ -29145,7 +29145,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1123万
@@ -29153,8 +29153,8 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="E14" s="22" t="inlineStr"/>
-      <c r="F14" s="21" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr"/>
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $5990万
@@ -29162,7 +29162,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="G14" s="21" t="inlineStr">
+      <c r="G14" s="22" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $6726万
@@ -29170,7 +29170,7 @@
 (25年-06月-24日)</t>
         </is>
       </c>
-      <c r="H14" s="22" t="inlineStr"/>
+      <c r="H14" s="20" t="inlineStr"/>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
@@ -29178,7 +29178,7 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1107万
@@ -29186,7 +29186,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1055万
@@ -29194,7 +29194,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1187万
@@ -29202,8 +29202,8 @@
 (25年-06月-19日)</t>
         </is>
       </c>
-      <c r="E15" s="22" t="inlineStr"/>
-      <c r="F15" s="21" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr"/>
+      <c r="F15" s="22" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $5574万
@@ -29211,7 +29211,7 @@
 (25年-06月-11日)</t>
         </is>
       </c>
-      <c r="G15" s="21" t="inlineStr">
+      <c r="G15" s="22" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $6596万
@@ -29219,7 +29219,7 @@
 (25年-06月-11日)</t>
         </is>
       </c>
-      <c r="H15" s="22" t="inlineStr"/>
+      <c r="H15" s="20" t="inlineStr"/>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
@@ -29227,7 +29227,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B16" s="21" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1100万
@@ -29235,7 +29235,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1114万
@@ -29243,7 +29243,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="D16" s="21" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1112万
@@ -29251,8 +29251,8 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E16" s="22" t="inlineStr"/>
-      <c r="F16" s="21" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr"/>
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $5076万
@@ -29260,7 +29260,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="G16" s="21" t="inlineStr">
+      <c r="G16" s="22" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $6467万
@@ -29268,7 +29268,7 @@
 (25年-06月-11日)</t>
         </is>
       </c>
-      <c r="H16" s="22" t="inlineStr"/>
+      <c r="H16" s="20" t="inlineStr"/>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
@@ -29276,7 +29276,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B17" s="21" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1094万
@@ -29284,7 +29284,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="C17" s="21" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1108万
@@ -29292,7 +29292,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="D17" s="21" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1175万
@@ -29300,8 +29300,8 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="E17" s="22" t="inlineStr"/>
-      <c r="F17" s="21" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr"/>
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>P1 | 1469呎 (4+房)
 $5739万
@@ -29309,7 +29309,7 @@
 (25年-06月-18日)</t>
         </is>
       </c>
-      <c r="G17" s="21" t="inlineStr">
+      <c r="G17" s="22" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $6739万
@@ -29317,7 +29317,7 @@
 (25年-06月-18日)</t>
         </is>
       </c>
-      <c r="H17" s="22" t="inlineStr"/>
+      <c r="H17" s="20" t="inlineStr"/>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
@@ -29325,7 +29325,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1025万
@@ -29333,7 +29333,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="C18" s="21" t="inlineStr">
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1036万
@@ -29341,7 +29341,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1084万
@@ -29349,7 +29349,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="E18" s="21" t="inlineStr">
+      <c r="E18" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $1011万
@@ -29357,7 +29357,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="F18" s="21" t="inlineStr">
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>P1 | 1258呎 (4+房)
 $4422万
@@ -29365,7 +29365,7 @@
 (25年-06月-10日)</t>
         </is>
       </c>
-      <c r="G18" s="21" t="inlineStr">
+      <c r="G18" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2694万
@@ -29373,7 +29373,7 @@
 (25年-07月-01日)</t>
         </is>
       </c>
-      <c r="H18" s="21" t="inlineStr">
+      <c r="H18" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3313万
@@ -29388,7 +29388,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B19" s="21" t="inlineStr">
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1021万
@@ -29396,7 +29396,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="C19" s="21" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1032万
@@ -29404,7 +29404,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr">
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1066万
@@ -29412,7 +29412,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E19" s="21" t="inlineStr">
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $1005万
@@ -29420,7 +29420,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="F19" s="21" t="inlineStr">
+      <c r="F19" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4351万
@@ -29428,7 +29428,7 @@
 (25年-06月-24日)</t>
         </is>
       </c>
-      <c r="G19" s="21" t="inlineStr">
+      <c r="G19" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2653万
@@ -29436,7 +29436,7 @@
 (25年-06月-29日)</t>
         </is>
       </c>
-      <c r="H19" s="21" t="inlineStr">
+      <c r="H19" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3447万
@@ -29451,7 +29451,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B20" s="21" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1017万
@@ -29459,7 +29459,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="C20" s="21" t="inlineStr">
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1028万
@@ -29467,7 +29467,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="D20" s="21" t="inlineStr">
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1076万
@@ -29475,7 +29475,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="E20" s="21" t="inlineStr">
+      <c r="E20" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $999万
@@ -29483,7 +29483,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="F20" s="21" t="inlineStr">
+      <c r="F20" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4540万
@@ -29491,7 +29491,7 @@
 (25年-06月-25日)</t>
         </is>
       </c>
-      <c r="G20" s="21" t="inlineStr">
+      <c r="G20" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2612万
@@ -29499,7 +29499,7 @@
 (25年-06月-22日)</t>
         </is>
       </c>
-      <c r="H20" s="21" t="inlineStr">
+      <c r="H20" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3256万
@@ -29514,7 +29514,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B21" s="21" t="inlineStr">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1013万
@@ -29522,7 +29522,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="C21" s="21" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1024万
@@ -29530,7 +29530,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1138万
@@ -29538,7 +29538,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="E21" s="21" t="inlineStr">
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $993万
@@ -29546,7 +29546,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="F21" s="21" t="inlineStr">
+      <c r="F21" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4265万
@@ -29554,7 +29554,7 @@
 (25年-06月-11日)</t>
         </is>
       </c>
-      <c r="G21" s="21" t="inlineStr">
+      <c r="G21" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2579万
@@ -29562,7 +29562,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="H21" s="21" t="inlineStr">
+      <c r="H21" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3220万
@@ -29577,7 +29577,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B22" s="21" t="inlineStr">
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1009万
@@ -29585,7 +29585,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="C22" s="21" t="inlineStr">
+      <c r="C22" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1020万
@@ -29593,7 +29593,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="D22" s="21" t="inlineStr">
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1067万
@@ -29601,7 +29601,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="E22" s="21" t="inlineStr">
+      <c r="E22" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $987万
@@ -29609,7 +29609,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="F22" s="21" t="inlineStr">
+      <c r="F22" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4229万
@@ -29617,7 +29617,7 @@
 (25年-06月-19日)</t>
         </is>
       </c>
-      <c r="G22" s="21" t="inlineStr">
+      <c r="G22" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2688万
@@ -29625,7 +29625,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="H22" s="21" t="inlineStr">
+      <c r="H22" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3056万
@@ -29640,7 +29640,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B23" s="21" t="inlineStr">
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1005万
@@ -29648,7 +29648,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="C23" s="21" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1079万
@@ -29656,7 +29656,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="D23" s="21" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1063万
@@ -29664,7 +29664,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="E23" s="21" t="inlineStr">
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $984万
@@ -29672,7 +29672,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="F23" s="21" t="inlineStr">
+      <c r="F23" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4193万
@@ -29680,7 +29680,7 @@
 (25年-06月-23日)</t>
         </is>
       </c>
-      <c r="G23" s="21" t="inlineStr">
+      <c r="G23" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2529万
@@ -29688,7 +29688,7 @@
 (25年-06月-23日)</t>
         </is>
       </c>
-      <c r="H23" s="21" t="inlineStr">
+      <c r="H23" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2876万
@@ -29703,7 +29703,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B24" s="21" t="inlineStr">
+      <c r="B24" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1001万
@@ -29711,7 +29711,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="C24" s="21" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1008万
@@ -29719,7 +29719,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="D24" s="21" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1059万
@@ -29727,7 +29727,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E24" s="21" t="inlineStr">
+      <c r="E24" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $980万
@@ -29735,7 +29735,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="F24" s="21" t="inlineStr">
+      <c r="F24" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4184万
@@ -29743,7 +29743,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="G24" s="21" t="inlineStr">
+      <c r="G24" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2504万
@@ -29751,7 +29751,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="H24" s="21" t="inlineStr">
+      <c r="H24" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3299万
@@ -29766,7 +29766,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $997万
@@ -29774,7 +29774,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="C25" s="21" t="inlineStr">
+      <c r="C25" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1004万
@@ -29782,7 +29782,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="D25" s="21" t="inlineStr">
+      <c r="D25" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1113万
@@ -29790,7 +29790,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="E25" s="21" t="inlineStr">
+      <c r="E25" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $1037万
@@ -29798,7 +29798,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="F25" s="21" t="inlineStr">
+      <c r="F25" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4374万
@@ -29806,7 +29806,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="G25" s="21" t="inlineStr">
+      <c r="G25" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2480万
@@ -29814,7 +29814,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="H25" s="21" t="inlineStr">
+      <c r="H25" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3122万
@@ -29829,7 +29829,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B26" s="21" t="inlineStr">
+      <c r="B26" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $993万
@@ -29837,7 +29837,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="C26" s="21" t="inlineStr">
+      <c r="C26" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1000万
@@ -29845,7 +29845,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="D26" s="21" t="inlineStr">
+      <c r="D26" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1043万
@@ -29853,7 +29853,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="E26" s="21" t="inlineStr">
+      <c r="E26" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $972万
@@ -29861,7 +29861,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="F26" s="21" t="inlineStr">
+      <c r="F26" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3725万
@@ -29869,7 +29869,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="G26" s="21" t="inlineStr">
+      <c r="G26" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2406万
@@ -29877,7 +29877,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="H26" s="21" t="inlineStr">
+      <c r="H26" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2893万
@@ -29892,7 +29892,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B27" s="21" t="inlineStr">
+      <c r="B27" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $989万
@@ -29900,7 +29900,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="C27" s="21" t="inlineStr">
+      <c r="C27" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $996万
@@ -29908,7 +29908,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="D27" s="21" t="inlineStr">
+      <c r="D27" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1039万
@@ -29916,7 +29916,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="E27" s="21" t="inlineStr">
+      <c r="E27" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $968万
@@ -29924,7 +29924,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="F27" s="21" t="inlineStr">
+      <c r="F27" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3680万
@@ -29932,7 +29932,7 @@
 (25年-06月-13日)</t>
         </is>
       </c>
-      <c r="G27" s="21" t="inlineStr">
+      <c r="G27" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2526万
@@ -29940,7 +29940,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="H27" s="21" t="inlineStr">
+      <c r="H27" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2850万
@@ -29955,7 +29955,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B28" s="21" t="inlineStr">
+      <c r="B28" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $985万
@@ -29963,7 +29963,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="C28" s="21" t="inlineStr">
+      <c r="C28" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $992万
@@ -29971,7 +29971,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="D28" s="21" t="inlineStr">
+      <c r="D28" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1022万
@@ -29979,7 +29979,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="E28" s="21" t="inlineStr">
+      <c r="E28" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $1024万
@@ -29987,7 +29987,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="F28" s="21" t="inlineStr">
+      <c r="F28" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3955万
@@ -29995,7 +29995,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="G28" s="21" t="inlineStr">
+      <c r="G28" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2349万
@@ -30003,7 +30003,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="H28" s="21" t="inlineStr">
+      <c r="H28" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2652万
@@ -30018,7 +30018,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B29" s="21" t="inlineStr">
+      <c r="B29" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $981万
@@ -30026,7 +30026,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="C29" s="21" t="inlineStr">
+      <c r="C29" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1049万
@@ -30034,7 +30034,7 @@
 (25年-07月-01日)</t>
         </is>
       </c>
-      <c r="D29" s="21" t="inlineStr">
+      <c r="D29" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1095万
@@ -30042,7 +30042,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E29" s="21" t="inlineStr">
+      <c r="E29" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $948万
@@ -30050,7 +30050,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="F29" s="21" t="inlineStr">
+      <c r="F29" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3818万
@@ -30058,7 +30058,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="G29" s="21" t="inlineStr">
+      <c r="G29" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2319万
@@ -30066,7 +30066,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="H29" s="21" t="inlineStr">
+      <c r="H29" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2784万
@@ -30081,7 +30081,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B30" s="21" t="inlineStr">
+      <c r="B30" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1038万
@@ -30089,7 +30089,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="C30" s="21" t="inlineStr">
+      <c r="C30" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1045万
@@ -30097,7 +30097,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="D30" s="21" t="inlineStr">
+      <c r="D30" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1091万
@@ -30105,7 +30105,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E30" s="21" t="inlineStr">
+      <c r="E30" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $956万
@@ -30113,7 +30113,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="F30" s="21" t="inlineStr">
+      <c r="F30" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3862万
@@ -30121,7 +30121,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="G30" s="21" t="inlineStr">
+      <c r="G30" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2396万
@@ -30129,7 +30129,7 @@
 (25年-08月-05日)</t>
         </is>
       </c>
-      <c r="H30" s="21" t="inlineStr">
+      <c r="H30" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2708万
@@ -30144,7 +30144,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B31" s="21" t="inlineStr">
+      <c r="B31" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1034万
@@ -30152,7 +30152,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="C31" s="21" t="inlineStr">
+      <c r="C31" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1041万
@@ -30160,7 +30160,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="D31" s="21" t="inlineStr">
+      <c r="D31" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1086万
@@ -30168,7 +30168,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="E31" s="21" t="inlineStr">
+      <c r="E31" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $952万
@@ -30176,7 +30176,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="F31" s="21" t="inlineStr">
+      <c r="F31" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3819万
@@ -30184,7 +30184,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="G31" s="21" t="inlineStr">
+      <c r="G31" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2361万
@@ -30192,7 +30192,7 @@
 (25年-07月-29日)</t>
         </is>
       </c>
-      <c r="H31" s="21" t="inlineStr">
+      <c r="H31" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2668万
@@ -30207,7 +30207,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B32" s="21" t="inlineStr">
+      <c r="B32" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1030万
@@ -30215,7 +30215,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="C32" s="21" t="inlineStr">
+      <c r="C32" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $976万
@@ -30223,7 +30223,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="D32" s="21" t="inlineStr">
+      <c r="D32" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1006万
@@ -30231,7 +30231,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="E32" s="21" t="inlineStr">
+      <c r="E32" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $949万
@@ -30239,7 +30239,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="F32" s="21" t="inlineStr">
+      <c r="F32" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3785万
@@ -30247,7 +30247,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="G32" s="21" t="inlineStr">
+      <c r="G32" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2338万
@@ -30255,7 +30255,7 @@
 (25年-09月-17日)</t>
         </is>
       </c>
-      <c r="H32" s="21" t="inlineStr">
+      <c r="H32" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2641万
@@ -30270,7 +30270,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B33" s="21" t="inlineStr">
+      <c r="B33" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1026万
@@ -30278,7 +30278,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="C33" s="21" t="inlineStr">
+      <c r="C33" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1033万
@@ -30286,7 +30286,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="D33" s="21" t="inlineStr">
+      <c r="D33" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1014万
@@ -30294,7 +30294,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E33" s="21" t="inlineStr">
+      <c r="E33" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $945万
@@ -30302,7 +30302,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="F33" s="21" t="inlineStr">
+      <c r="F33" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3474万
@@ -30310,7 +30310,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="G33" s="21" t="inlineStr">
+      <c r="G33" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2306万
@@ -30318,7 +30318,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="H33" s="21" t="inlineStr">
+      <c r="H33" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2578万
@@ -30333,7 +30333,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B34" s="21" t="inlineStr">
+      <c r="B34" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $962万
@@ -30341,7 +30341,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="C34" s="21" t="inlineStr">
+      <c r="C34" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $968万
@@ -30349,7 +30349,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="D34" s="21" t="inlineStr">
+      <c r="D34" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1010万
@@ -30357,7 +30357,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E34" s="21" t="inlineStr">
+      <c r="E34" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $938万
@@ -30365,7 +30365,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="F34" s="21" t="inlineStr">
+      <c r="F34" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3632万
@@ -30373,7 +30373,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="G34" s="21" t="inlineStr">
+      <c r="G34" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2392万
@@ -30381,7 +30381,7 @@
 (25年-07月-30日)</t>
         </is>
       </c>
-      <c r="H34" s="21" t="inlineStr">
+      <c r="H34" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2586万
@@ -30396,7 +30396,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B35" s="21" t="inlineStr">
+      <c r="B35" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1018万
@@ -30404,7 +30404,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="C35" s="21" t="inlineStr">
+      <c r="C35" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $964万
@@ -30412,7 +30412,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="D35" s="21" t="inlineStr">
+      <c r="D35" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1069万
@@ -30420,7 +30420,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="E35" s="21" t="inlineStr">
+      <c r="E35" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $928万
@@ -30428,7 +30428,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="F35" s="21" t="inlineStr">
+      <c r="F35" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3426万
@@ -30436,7 +30436,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="G35" s="21" t="inlineStr">
+      <c r="G35" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2399万
@@ -30444,7 +30444,7 @@
 (25年-08月-25日)</t>
         </is>
       </c>
-      <c r="H35" s="21" t="inlineStr">
+      <c r="H35" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2675万
@@ -30459,7 +30459,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B36" s="21" t="inlineStr">
+      <c r="B36" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1014万
@@ -30467,7 +30467,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="C36" s="21" t="inlineStr">
+      <c r="C36" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $960万
@@ -30475,7 +30475,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="D36" s="21" t="inlineStr">
+      <c r="D36" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1002万
@@ -30483,7 +30483,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="E36" s="21" t="inlineStr">
+      <c r="E36" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $976万
@@ -30491,7 +30491,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="F36" s="21" t="inlineStr">
+      <c r="F36" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3881万
@@ -30499,7 +30499,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="G36" s="21" t="inlineStr">
+      <c r="G36" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2314万
@@ -30507,7 +30507,7 @@
 (25年-09月-08日)</t>
         </is>
       </c>
-      <c r="H36" s="21" t="inlineStr">
+      <c r="H36" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2570万
@@ -30522,7 +30522,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B37" s="21" t="inlineStr">
+      <c r="B37" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1010万
@@ -30530,7 +30530,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="C37" s="21" t="inlineStr">
+      <c r="C37" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $957万
@@ -30538,7 +30538,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="D37" s="21" t="inlineStr">
+      <c r="D37" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $998万
@@ -30546,7 +30546,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="E37" s="21" t="inlineStr">
+      <c r="E37" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $910万
@@ -30554,7 +30554,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="F37" s="21" t="inlineStr">
+      <c r="F37" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3577万
@@ -30562,7 +30562,7 @@
 (25年-08月-05日)</t>
         </is>
       </c>
-      <c r="G37" s="21" t="inlineStr">
+      <c r="G37" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2490万
@@ -30570,7 +30570,7 @@
 (25年-12月-30日)</t>
         </is>
       </c>
-      <c r="H37" s="21" t="inlineStr">
+      <c r="H37" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2686万
@@ -30585,7 +30585,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B38" s="21" t="inlineStr">
+      <c r="B38" s="22" t="inlineStr">
         <is>
           <t>A | 440呎 (2房)
 $1088万
@@ -30593,7 +30593,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="C38" s="21" t="inlineStr">
+      <c r="C38" s="22" t="inlineStr">
         <is>
           <t>B | 448呎 (2房)
 $1120万
@@ -30601,7 +30601,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="D38" s="21" t="inlineStr">
+      <c r="D38" s="22" t="inlineStr">
         <is>
           <t>C | 467呎 (2房)
 $1238万
@@ -30609,7 +30609,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="E38" s="21" t="inlineStr">
+      <c r="E38" s="22" t="inlineStr">
         <is>
           <t>D | 430呎 (2房)
 $999万
@@ -30617,7 +30617,7 @@
 (25年-07月-20日)</t>
         </is>
       </c>
-      <c r="F38" s="21" t="inlineStr">
+      <c r="F38" s="22" t="inlineStr">
         <is>
           <t>P1 | 1162呎 (4+房)
 $3650万
@@ -30625,7 +30625,7 @@
 (25年-07月-28日)</t>
         </is>
       </c>
-      <c r="G38" s="21" t="inlineStr">
+      <c r="G38" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2436万
@@ -30633,7 +30633,7 @@
 (25年-12月-18日)</t>
         </is>
       </c>
-      <c r="H38" s="21" t="inlineStr">
+      <c r="H38" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2758万
@@ -30792,10 +30792,32 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr"/>
+      <c r="E5" s="20" t="inlineStr"/>
+      <c r="F5" s="20" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr">
+        <is>
+          <t>P1 | 1417呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr"/>
+      <c r="I5" s="20" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
           <t>41&amp;42</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>A | 1020呎 (3房)
 $3652万
@@ -30803,7 +30825,7 @@
 (26年-03月-11日)</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>B | 1016呎 (3房)
 -
@@ -30811,7 +30833,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t>C | 1029呎 (3房)
 -
@@ -30819,7 +30841,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="E6" s="21" t="inlineStr">
         <is>
           <t>D | 1083呎 (3房)
 -
@@ -30827,9 +30849,9 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="F5" s="22" t="inlineStr"/>
-      <c r="G5" s="22" t="inlineStr"/>
-      <c r="H5" s="20" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t>P2 | 2871呎 (4+房)
 -
@@ -30837,29 +30859,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="I5" s="22" t="inlineStr"/>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B6" s="22" t="inlineStr"/>
-      <c r="C6" s="22" t="inlineStr"/>
-      <c r="D6" s="22" t="inlineStr"/>
-      <c r="E6" s="22" t="inlineStr"/>
-      <c r="F6" s="22" t="inlineStr"/>
-      <c r="G6" s="20" t="inlineStr">
-        <is>
-          <t>P1 | 1417呎 (4+房)
--
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H6" s="22" t="inlineStr"/>
-      <c r="I6" s="22" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
@@ -30867,7 +30867,7 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1245万
@@ -30875,7 +30875,7 @@
 (25年-09月-10日)</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1138万
@@ -30883,7 +30883,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1137万
@@ -30891,7 +30891,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1804万
@@ -30899,8 +30899,8 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="F7" s="22" t="inlineStr"/>
-      <c r="G7" s="20" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 -
@@ -30908,7 +30908,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="H7" s="20" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 -
@@ -30916,7 +30916,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="I7" s="22" t="inlineStr"/>
+      <c r="I7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -30924,7 +30924,7 @@
           <t>39</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1180万
@@ -30932,7 +30932,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1556万
@@ -30940,7 +30940,7 @@
 (26年-04月-21日)</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1196万
@@ -30948,7 +30948,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1532万
@@ -30956,8 +30956,8 @@
 (26年-06月-17日)</t>
         </is>
       </c>
-      <c r="F8" s="22" t="inlineStr"/>
-      <c r="G8" s="20" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr"/>
+      <c r="G8" s="21" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 -
@@ -30965,7 +30965,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="H8" s="20" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 -
@@ -30973,7 +30973,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="I8" s="22" t="inlineStr"/>
+      <c r="I8" s="20" t="inlineStr"/>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -30981,7 +30981,7 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1543万
@@ -30989,7 +30989,7 @@
 (26年-04月-27日)</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1169万
@@ -30997,7 +30997,7 @@
 (25年-07月-30日)</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1174万
@@ -31005,7 +31005,7 @@
 (25年-07月-24日)</t>
         </is>
       </c>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1137万
@@ -31013,8 +31013,8 @@
 (25年-07月-23日)</t>
         </is>
       </c>
-      <c r="F9" s="22" t="inlineStr"/>
-      <c r="G9" s="21" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr"/>
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $6754万
@@ -31022,7 +31022,7 @@
 (25年-11月-30日)</t>
         </is>
       </c>
-      <c r="H9" s="21" t="inlineStr">
+      <c r="H9" s="22" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $8574万
@@ -31030,7 +31030,7 @@
 (26年-02月-11日)</t>
         </is>
       </c>
-      <c r="I9" s="22" t="inlineStr"/>
+      <c r="I9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
@@ -31038,7 +31038,7 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1170万
@@ -31046,7 +31046,7 @@
 (25年-07月-21日)</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1112万
@@ -31054,7 +31054,7 @@
 (25年-07月-22日)</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1116万
@@ -31062,7 +31062,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="E10" s="21" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1081万
@@ -31070,8 +31070,8 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="F10" s="22" t="inlineStr"/>
-      <c r="G10" s="21" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr"/>
+      <c r="G10" s="22" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $6086万
@@ -31079,7 +31079,7 @@
 (25年-09月-08日)</t>
         </is>
       </c>
-      <c r="H10" s="21" t="inlineStr">
+      <c r="H10" s="22" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $7592万
@@ -31087,7 +31087,7 @@
 (25年-08月-11日)</t>
         </is>
       </c>
-      <c r="I10" s="22" t="inlineStr"/>
+      <c r="I10" s="20" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -31095,7 +31095,7 @@
           <t>36</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1084万
@@ -31103,7 +31103,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1081万
@@ -31111,7 +31111,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1276万
@@ -31119,7 +31119,7 @@
 (26年-02月-26日)</t>
         </is>
       </c>
-      <c r="E11" s="21" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1064万
@@ -31127,8 +31127,8 @@
 (25年-08月-03日)</t>
         </is>
       </c>
-      <c r="F11" s="22" t="inlineStr"/>
-      <c r="G11" s="21" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr"/>
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $5644万
@@ -31136,7 +31136,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="H11" s="21" t="inlineStr">
+      <c r="H11" s="22" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $6715万
@@ -31144,7 +31144,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="I11" s="22" t="inlineStr"/>
+      <c r="I11" s="20" t="inlineStr"/>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
@@ -31152,7 +31152,7 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1081万
@@ -31160,7 +31160,7 @@
 (25年-07月-22日)</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1078万
@@ -31168,7 +31168,7 @@
 (25年-07月-22日)</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1082万
@@ -31176,7 +31176,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1048万
@@ -31184,8 +31184,8 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="F12" s="22" t="inlineStr"/>
-      <c r="G12" s="21" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr"/>
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $5431万
@@ -31193,7 +31193,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="H12" s="21" t="inlineStr">
+      <c r="H12" s="22" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $6324万
@@ -31201,7 +31201,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr"/>
+      <c r="I12" s="20" t="inlineStr"/>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -31209,7 +31209,7 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1065万
@@ -31217,7 +31217,7 @@
 (25年-07月-22日)</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1128万
@@ -31225,7 +31225,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1132万
@@ -31233,7 +31233,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="E13" s="21" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $998万
@@ -31241,8 +31241,8 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="F13" s="22" t="inlineStr"/>
-      <c r="G13" s="21" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr"/>
+      <c r="G13" s="22" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $5404万
@@ -31250,7 +31250,7 @@
 (25年-07月-24日)</t>
         </is>
       </c>
-      <c r="H13" s="21" t="inlineStr">
+      <c r="H13" s="22" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $6018万
@@ -31258,7 +31258,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="I13" s="22" t="inlineStr"/>
+      <c r="I13" s="20" t="inlineStr"/>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -31266,7 +31266,7 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1046万
@@ -31274,7 +31274,7 @@
 (25年-06月-19日)</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1108万
@@ -31282,7 +31282,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1046万
@@ -31290,7 +31290,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="E14" s="21" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $993万
@@ -31298,8 +31298,8 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="F14" s="22" t="inlineStr"/>
-      <c r="G14" s="21" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr"/>
+      <c r="G14" s="22" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $5494万
@@ -31307,7 +31307,7 @@
 (25年-07月-22日)</t>
         </is>
       </c>
-      <c r="H14" s="21" t="inlineStr">
+      <c r="H14" s="22" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $6220万
@@ -31315,7 +31315,7 @@
 (25年-06月-23日)</t>
         </is>
       </c>
-      <c r="I14" s="22" t="inlineStr"/>
+      <c r="I14" s="20" t="inlineStr"/>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
@@ -31323,7 +31323,7 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1040万
@@ -31331,7 +31331,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1102万
@@ -31339,7 +31339,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1040万
@@ -31347,7 +31347,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="E15" s="21" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $988万
@@ -31355,8 +31355,8 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="F15" s="22" t="inlineStr"/>
-      <c r="G15" s="21" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr"/>
+      <c r="G15" s="22" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $5052万
@@ -31364,7 +31364,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="H15" s="21" t="inlineStr">
+      <c r="H15" s="22" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $5850万
@@ -31372,7 +31372,7 @@
 (25年-06月-22日)</t>
         </is>
       </c>
-      <c r="I15" s="22" t="inlineStr"/>
+      <c r="I15" s="20" t="inlineStr"/>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
@@ -31380,7 +31380,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B16" s="21" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1034万
@@ -31388,7 +31388,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1030万
@@ -31396,7 +31396,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="D16" s="21" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1099万
@@ -31404,7 +31404,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="E16" s="21" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $983万
@@ -31412,8 +31412,8 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="F16" s="22" t="inlineStr"/>
-      <c r="G16" s="21" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr"/>
+      <c r="G16" s="22" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $4996万
@@ -31421,7 +31421,7 @@
 (25年-06月-08日)</t>
         </is>
       </c>
-      <c r="H16" s="21" t="inlineStr">
+      <c r="H16" s="22" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $5791万
@@ -31429,7 +31429,7 @@
 (25年-06月-24日)</t>
         </is>
       </c>
-      <c r="I16" s="22" t="inlineStr"/>
+      <c r="I16" s="20" t="inlineStr"/>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
@@ -31437,7 +31437,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B17" s="21" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1027万
@@ -31445,7 +31445,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="C17" s="21" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1024万
@@ -31453,7 +31453,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="D17" s="21" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1028万
@@ -31461,7 +31461,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="E17" s="21" t="inlineStr">
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $978万
@@ -31469,8 +31469,8 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="F17" s="22" t="inlineStr"/>
-      <c r="G17" s="21" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr"/>
+      <c r="G17" s="22" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $4839万
@@ -31478,7 +31478,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="H17" s="21" t="inlineStr">
+      <c r="H17" s="22" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $5609万
@@ -31486,7 +31486,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="I17" s="22" t="inlineStr"/>
+      <c r="I17" s="20" t="inlineStr"/>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
@@ -31494,7 +31494,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1083万
@@ -31502,7 +31502,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="C18" s="21" t="inlineStr">
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1063万
@@ -31510,7 +31510,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1005万
@@ -31518,7 +31518,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E18" s="21" t="inlineStr">
+      <c r="E18" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $964万
@@ -31526,7 +31526,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="F18" s="21" t="inlineStr">
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $917万
@@ -31534,7 +31534,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="G18" s="21" t="inlineStr">
+      <c r="G18" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $3273万
@@ -31542,7 +31542,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="H18" s="21" t="inlineStr">
+      <c r="H18" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2726万
@@ -31550,7 +31550,7 @@
 (25年-07月-30日)</t>
         </is>
       </c>
-      <c r="I18" s="21" t="inlineStr">
+      <c r="I18" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2494万
@@ -31565,7 +31565,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B19" s="21" t="inlineStr">
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1015万
@@ -31573,7 +31573,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="C19" s="21" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1059万
@@ -31581,7 +31581,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr">
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1063万
@@ -31589,7 +31589,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="E19" s="21" t="inlineStr">
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $961万
@@ -31597,7 +31597,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="F19" s="21" t="inlineStr">
+      <c r="F19" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $971万
@@ -31605,7 +31605,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="G19" s="21" t="inlineStr">
+      <c r="G19" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $3084万
@@ -31613,7 +31613,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="H19" s="21" t="inlineStr">
+      <c r="H19" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2582万
@@ -31621,7 +31621,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="I19" s="21" t="inlineStr">
+      <c r="I19" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2591万
@@ -31636,7 +31636,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B20" s="21" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1011万
@@ -31644,7 +31644,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="C20" s="21" t="inlineStr">
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1054万
@@ -31652,7 +31652,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="D20" s="21" t="inlineStr">
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1059万
@@ -31660,7 +31660,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="E20" s="21" t="inlineStr">
+      <c r="E20" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $957万
@@ -31668,7 +31668,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="F20" s="21" t="inlineStr">
+      <c r="F20" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $910万
@@ -31676,7 +31676,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="G20" s="21" t="inlineStr">
+      <c r="G20" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $3337万
@@ -31684,7 +31684,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="H20" s="21" t="inlineStr">
+      <c r="H20" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2541万
@@ -31692,7 +31692,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="I20" s="21" t="inlineStr">
+      <c r="I20" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2548万
@@ -31707,7 +31707,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B21" s="21" t="inlineStr">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1070万
@@ -31715,7 +31715,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="C21" s="21" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1050万
@@ -31723,7 +31723,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $993万
@@ -31731,7 +31731,7 @@
 (25年-06月-13日)</t>
         </is>
       </c>
-      <c r="E21" s="21" t="inlineStr">
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1012万
@@ -31739,7 +31739,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="F21" s="21" t="inlineStr">
+      <c r="F21" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $906万
@@ -31747,7 +31747,7 @@
 (25年-06月-13日)</t>
         </is>
       </c>
-      <c r="G21" s="21" t="inlineStr">
+      <c r="G21" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $3300万
@@ -31755,7 +31755,7 @@
 (25年-06月-26日)</t>
         </is>
       </c>
-      <c r="H21" s="21" t="inlineStr">
+      <c r="H21" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2500万
@@ -31763,7 +31763,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="I21" s="21" t="inlineStr">
+      <c r="I21" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2519万
@@ -31778,7 +31778,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B22" s="21" t="inlineStr">
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1003万
@@ -31786,7 +31786,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="C22" s="21" t="inlineStr">
+      <c r="C22" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $984万
@@ -31794,7 +31794,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="D22" s="21" t="inlineStr">
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $989万
@@ -31802,7 +31802,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="E22" s="21" t="inlineStr">
+      <c r="E22" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $949万
@@ -31810,7 +31810,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="F22" s="21" t="inlineStr">
+      <c r="F22" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $903万
@@ -31818,7 +31818,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="G22" s="21" t="inlineStr">
+      <c r="G22" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2824万
@@ -31826,7 +31826,7 @@
 (25年-06月-18日)</t>
         </is>
       </c>
-      <c r="H22" s="21" t="inlineStr">
+      <c r="H22" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2623万
@@ -31834,7 +31834,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="I22" s="21" t="inlineStr">
+      <c r="I22" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2490万
@@ -31849,7 +31849,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B23" s="21" t="inlineStr">
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1062万
@@ -31857,7 +31857,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="C23" s="21" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $981万
@@ -31865,7 +31865,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="D23" s="21" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $985万
@@ -31873,7 +31873,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="E23" s="21" t="inlineStr">
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $945万
@@ -31881,7 +31881,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="F23" s="21" t="inlineStr">
+      <c r="F23" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $955万
@@ -31889,7 +31889,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="G23" s="21" t="inlineStr">
+      <c r="G23" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2784万
@@ -31897,7 +31897,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="H23" s="21" t="inlineStr">
+      <c r="H23" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2487万
@@ -31905,7 +31905,7 @@
 (25年-07月-22日)</t>
         </is>
       </c>
-      <c r="I23" s="21" t="inlineStr">
+      <c r="I23" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2437万
@@ -31920,7 +31920,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B24" s="21" t="inlineStr">
+      <c r="B24" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $983万
@@ -31928,7 +31928,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="C24" s="21" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $977万
@@ -31936,7 +31936,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="D24" s="21" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1042万
@@ -31944,7 +31944,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="E24" s="21" t="inlineStr">
+      <c r="E24" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $942万
@@ -31952,7 +31952,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="F24" s="21" t="inlineStr">
+      <c r="F24" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $896万
@@ -31960,7 +31960,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="G24" s="21" t="inlineStr">
+      <c r="G24" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $3217万
@@ -31968,7 +31968,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="H24" s="21" t="inlineStr">
+      <c r="H24" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2482万
@@ -31976,7 +31976,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="I24" s="21" t="inlineStr">
+      <c r="I24" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2342万
@@ -31991,7 +31991,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1053万
@@ -31999,7 +31999,7 @@
 (25年-07月-01日)</t>
         </is>
       </c>
-      <c r="C25" s="21" t="inlineStr">
+      <c r="C25" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $973万
@@ -32007,7 +32007,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="D25" s="21" t="inlineStr">
+      <c r="D25" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $977万
@@ -32015,7 +32015,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="E25" s="21" t="inlineStr">
+      <c r="E25" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $996万
@@ -32023,7 +32023,7 @@
 (25年-07月-01日)</t>
         </is>
       </c>
-      <c r="F25" s="21" t="inlineStr">
+      <c r="F25" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $892万
@@ -32031,7 +32031,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="G25" s="21" t="inlineStr">
+      <c r="G25" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $3045万
@@ -32039,7 +32039,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="H25" s="21" t="inlineStr">
+      <c r="H25" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2451万
@@ -32047,7 +32047,7 @@
 (25年-07月-22日)</t>
         </is>
       </c>
-      <c r="I25" s="21" t="inlineStr">
+      <c r="I25" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2321万
@@ -32062,7 +32062,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B26" s="21" t="inlineStr">
+      <c r="B26" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $987万
@@ -32070,7 +32070,7 @@
 (25年-06月-29日)</t>
         </is>
       </c>
-      <c r="C26" s="21" t="inlineStr">
+      <c r="C26" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $969万
@@ -32078,7 +32078,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="D26" s="21" t="inlineStr">
+      <c r="D26" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1034万
@@ -32086,7 +32086,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="E26" s="21" t="inlineStr">
+      <c r="E26" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $934万
@@ -32094,7 +32094,7 @@
 (25年-06月-13日)</t>
         </is>
       </c>
-      <c r="F26" s="21" t="inlineStr">
+      <c r="F26" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $888万
@@ -32102,7 +32102,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="G26" s="21" t="inlineStr">
+      <c r="G26" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2727万
@@ -32110,7 +32110,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="H26" s="21" t="inlineStr">
+      <c r="H26" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2426万
@@ -32118,7 +32118,7 @@
 (25年-07月-29日)</t>
         </is>
       </c>
-      <c r="I26" s="21" t="inlineStr">
+      <c r="I26" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2310万
@@ -32133,7 +32133,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B27" s="21" t="inlineStr">
+      <c r="B27" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $983万
@@ -32141,7 +32141,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="C27" s="21" t="inlineStr">
+      <c r="C27" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $965万
@@ -32149,7 +32149,7 @@
 (25年-07月-01日)</t>
         </is>
       </c>
-      <c r="D27" s="21" t="inlineStr">
+      <c r="D27" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $969万
@@ -32157,7 +32157,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="E27" s="21" t="inlineStr">
+      <c r="E27" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $988万
@@ -32165,7 +32165,7 @@
 (25年-07月-01日)</t>
         </is>
       </c>
-      <c r="F27" s="21" t="inlineStr">
+      <c r="F27" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $885万
@@ -32173,7 +32173,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="G27" s="21" t="inlineStr">
+      <c r="G27" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2701万
@@ -32181,7 +32181,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="H27" s="21" t="inlineStr">
+      <c r="H27" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2402万
@@ -32189,7 +32189,7 @@
 (25年-07月-22日)</t>
         </is>
       </c>
-      <c r="I27" s="21" t="inlineStr">
+      <c r="I27" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2294万
@@ -32204,7 +32204,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B28" s="21" t="inlineStr">
+      <c r="B28" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $979万
@@ -32212,7 +32212,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="C28" s="21" t="inlineStr">
+      <c r="C28" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $949万
@@ -32220,7 +32220,7 @@
 (25年-07月-01日)</t>
         </is>
       </c>
-      <c r="D28" s="21" t="inlineStr">
+      <c r="D28" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $965万
@@ -32228,7 +32228,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="E28" s="21" t="inlineStr">
+      <c r="E28" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $927万
@@ -32236,7 +32236,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="F28" s="21" t="inlineStr">
+      <c r="F28" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $926万
@@ -32244,7 +32244,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="G28" s="21" t="inlineStr">
+      <c r="G28" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2674万
@@ -32252,7 +32252,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="H28" s="21" t="inlineStr">
+      <c r="H28" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2498万
@@ -32260,7 +32260,7 @@
 (25年-07月-24日)</t>
         </is>
       </c>
-      <c r="I28" s="21" t="inlineStr">
+      <c r="I28" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2277万
@@ -32275,7 +32275,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B29" s="21" t="inlineStr">
+      <c r="B29" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $976万
@@ -32283,7 +32283,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="C29" s="21" t="inlineStr">
+      <c r="C29" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $957万
@@ -32291,7 +32291,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="D29" s="21" t="inlineStr">
+      <c r="D29" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $962万
@@ -32299,7 +32299,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="E29" s="21" t="inlineStr">
+      <c r="E29" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $981万
@@ -32307,7 +32307,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="F29" s="21" t="inlineStr">
+      <c r="F29" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $878万
@@ -32315,7 +32315,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="G29" s="21" t="inlineStr">
+      <c r="G29" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2787万
@@ -32323,7 +32323,7 @@
 (25年-07月-13日)</t>
         </is>
       </c>
-      <c r="H29" s="21" t="inlineStr">
+      <c r="H29" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2555万
@@ -32331,7 +32331,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="I29" s="21" t="inlineStr">
+      <c r="I29" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2355万
@@ -32346,7 +32346,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B30" s="21" t="inlineStr">
+      <c r="B30" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1032万
@@ -32354,7 +32354,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="C30" s="21" t="inlineStr">
+      <c r="C30" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1013万
@@ -32362,7 +32362,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="D30" s="21" t="inlineStr">
+      <c r="D30" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1018万
@@ -32370,7 +32370,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="E30" s="21" t="inlineStr">
+      <c r="E30" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $919万
@@ -32378,7 +32378,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="F30" s="21" t="inlineStr">
+      <c r="F30" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $874万
@@ -32386,7 +32386,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="G30" s="21" t="inlineStr">
+      <c r="G30" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2622万
@@ -32394,7 +32394,7 @@
 (25年-07月-22日)</t>
         </is>
       </c>
-      <c r="H30" s="21" t="inlineStr">
+      <c r="H30" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2378万
@@ -32402,7 +32402,7 @@
 (25年-08月-03日)</t>
         </is>
       </c>
-      <c r="I30" s="21" t="inlineStr">
+      <c r="I30" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2244万
@@ -32417,7 +32417,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B31" s="21" t="inlineStr">
+      <c r="B31" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1028万
@@ -32425,7 +32425,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="C31" s="21" t="inlineStr">
+      <c r="C31" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1009万
@@ -32433,7 +32433,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="D31" s="21" t="inlineStr">
+      <c r="D31" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1014万
@@ -32441,7 +32441,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="E31" s="21" t="inlineStr">
+      <c r="E31" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $916万
@@ -32449,7 +32449,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="F31" s="21" t="inlineStr">
+      <c r="F31" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $871万
@@ -32457,7 +32457,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="G31" s="21" t="inlineStr">
+      <c r="G31" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2734万
@@ -32465,7 +32465,7 @@
 (25年-08月-10日)</t>
         </is>
       </c>
-      <c r="H31" s="21" t="inlineStr">
+      <c r="H31" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2382万
@@ -32473,7 +32473,7 @@
 (25年-08月-20日)</t>
         </is>
       </c>
-      <c r="I31" s="21" t="inlineStr">
+      <c r="I31" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2304万
@@ -32488,7 +32488,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B32" s="21" t="inlineStr">
+      <c r="B32" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1024万
@@ -32496,7 +32496,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="C32" s="21" t="inlineStr">
+      <c r="C32" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $934万
@@ -32504,7 +32504,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="D32" s="21" t="inlineStr">
+      <c r="D32" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $950万
@@ -32512,7 +32512,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="E32" s="21" t="inlineStr">
+      <c r="E32" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $969万
@@ -32520,7 +32520,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="F32" s="21" t="inlineStr">
+      <c r="F32" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $867万
@@ -32528,7 +32528,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="G32" s="21" t="inlineStr">
+      <c r="G32" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2715万
@@ -32536,7 +32536,7 @@
 (25年-07月-31日)</t>
         </is>
       </c>
-      <c r="H32" s="21" t="inlineStr">
+      <c r="H32" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2365万
@@ -32544,7 +32544,7 @@
 (25年-08月-18日)</t>
         </is>
       </c>
-      <c r="I32" s="21" t="inlineStr">
+      <c r="I32" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2211万
@@ -32559,7 +32559,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B33" s="21" t="inlineStr">
+      <c r="B33" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1020万
@@ -32567,7 +32567,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="C33" s="21" t="inlineStr">
+      <c r="C33" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1001万
@@ -32575,7 +32575,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="D33" s="21" t="inlineStr">
+      <c r="D33" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $946万
@@ -32583,7 +32583,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="E33" s="21" t="inlineStr">
+      <c r="E33" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $908万
@@ -32591,7 +32591,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="F33" s="21" t="inlineStr">
+      <c r="F33" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $864万
@@ -32599,7 +32599,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="G33" s="21" t="inlineStr">
+      <c r="G33" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2584万
@@ -32607,7 +32607,7 @@
 (25年-08月-10日)</t>
         </is>
       </c>
-      <c r="H33" s="21" t="inlineStr">
+      <c r="H33" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2348万
@@ -32615,7 +32615,7 @@
 (25年-08月-18日)</t>
         </is>
       </c>
-      <c r="I33" s="21" t="inlineStr">
+      <c r="I33" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2272万
@@ -32630,7 +32630,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B34" s="21" t="inlineStr">
+      <c r="B34" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1016万
@@ -32638,7 +32638,7 @@
 (25年-07月-06日)</t>
         </is>
       </c>
-      <c r="C34" s="21" t="inlineStr">
+      <c r="C34" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $938万
@@ -32646,7 +32646,7 @@
 (25年-07月-01日)</t>
         </is>
       </c>
-      <c r="D34" s="21" t="inlineStr">
+      <c r="D34" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $943万
@@ -32654,7 +32654,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="E34" s="21" t="inlineStr">
+      <c r="E34" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $905万
@@ -32662,7 +32662,7 @@
 (25年-07月-01日)</t>
         </is>
       </c>
-      <c r="F34" s="21" t="inlineStr">
+      <c r="F34" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $914万
@@ -32670,7 +32670,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="G34" s="21" t="inlineStr">
+      <c r="G34" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2565万
@@ -32678,7 +32678,7 @@
 (25年-09月-16日)</t>
         </is>
       </c>
-      <c r="H34" s="21" t="inlineStr">
+      <c r="H34" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2331万
@@ -32686,7 +32686,7 @@
 (25年-09月-16日)</t>
         </is>
       </c>
-      <c r="I34" s="21" t="inlineStr">
+      <c r="I34" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2296万
@@ -32701,7 +32701,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B35" s="21" t="inlineStr">
+      <c r="B35" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $952万
@@ -32709,7 +32709,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="C35" s="21" t="inlineStr">
+      <c r="C35" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $993万
@@ -32717,7 +32717,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="D35" s="21" t="inlineStr">
+      <c r="D35" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $939万
@@ -32725,7 +32725,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E35" s="21" t="inlineStr">
+      <c r="E35" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $901万
@@ -32733,7 +32733,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="F35" s="21" t="inlineStr">
+      <c r="F35" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $911万
@@ -32741,7 +32741,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="G35" s="21" t="inlineStr">
+      <c r="G35" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2680万
@@ -32749,7 +32749,7 @@
 (25年-09月-02日)</t>
         </is>
       </c>
-      <c r="H35" s="21" t="inlineStr">
+      <c r="H35" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2313万
@@ -32757,7 +32757,7 @@
 (25年-09月-25日)</t>
         </is>
       </c>
-      <c r="I35" s="21" t="inlineStr">
+      <c r="I35" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2280万
@@ -32772,7 +32772,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B36" s="21" t="inlineStr">
+      <c r="B36" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $949万
@@ -32780,7 +32780,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="C36" s="21" t="inlineStr">
+      <c r="C36" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $931万
@@ -32788,7 +32788,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="D36" s="21" t="inlineStr">
+      <c r="D36" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $935万
@@ -32796,7 +32796,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E36" s="21" t="inlineStr">
+      <c r="E36" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $954万
@@ -32804,7 +32804,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="F36" s="21" t="inlineStr">
+      <c r="F36" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $854万
@@ -32812,7 +32812,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="G36" s="21" t="inlineStr">
+      <c r="G36" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2556万
@@ -32820,7 +32820,7 @@
 (25年-09月-11日)</t>
         </is>
       </c>
-      <c r="H36" s="21" t="inlineStr">
+      <c r="H36" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2339万
@@ -32828,7 +32828,7 @@
 (25年-10月-14日)</t>
         </is>
       </c>
-      <c r="I36" s="21" t="inlineStr">
+      <c r="I36" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2263万
@@ -32843,7 +32843,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B37" s="21" t="inlineStr">
+      <c r="B37" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $945万
@@ -32851,7 +32851,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="C37" s="21" t="inlineStr">
+      <c r="C37" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $927万
@@ -32859,7 +32859,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="D37" s="21" t="inlineStr">
+      <c r="D37" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $931万
@@ -32867,7 +32867,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="E37" s="21" t="inlineStr">
+      <c r="E37" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $894万
@@ -32875,7 +32875,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="F37" s="21" t="inlineStr">
+      <c r="F37" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $850万
@@ -32883,7 +32883,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="G37" s="21" t="inlineStr">
+      <c r="G37" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2574万
@@ -32891,7 +32891,7 @@
 (25年-10月-08日)</t>
         </is>
       </c>
-      <c r="H37" s="21" t="inlineStr">
+      <c r="H37" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2365万
@@ -32899,7 +32899,7 @@
 (25年-10月-20日)</t>
         </is>
       </c>
-      <c r="I37" s="21" t="inlineStr">
+      <c r="I37" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2247万
@@ -32914,7 +32914,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B38" s="21" t="inlineStr">
+      <c r="B38" s="22" t="inlineStr">
         <is>
           <t>A | 440呎 (2房)
 $1158万
@@ -32922,7 +32922,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="C38" s="21" t="inlineStr">
+      <c r="C38" s="22" t="inlineStr">
         <is>
           <t>B | 439呎 (2房)
 $1089万
@@ -32930,7 +32930,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="D38" s="21" t="inlineStr">
+      <c r="D38" s="22" t="inlineStr">
         <is>
           <t>C | 444呎 (2房)
 $1092万
@@ -32938,7 +32938,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="E38" s="21" t="inlineStr">
+      <c r="E38" s="22" t="inlineStr">
         <is>
           <t>D | 430呎 (2房)
 $1182万
@@ -32946,7 +32946,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="F38" s="21" t="inlineStr">
+      <c r="F38" s="22" t="inlineStr">
         <is>
           <t>E | 408呎 (2房)
 $1040万
@@ -32954,7 +32954,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="G38" s="21" t="inlineStr">
+      <c r="G38" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2546万
@@ -32962,7 +32962,7 @@
 (25年-10月-09日)</t>
         </is>
       </c>
-      <c r="H38" s="21" t="inlineStr">
+      <c r="H38" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2471万
@@ -32970,7 +32970,7 @@
 (25年-10月-21日)</t>
         </is>
       </c>
-      <c r="I38" s="21" t="inlineStr">
+      <c r="I38" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2354万
